--- a/docs/labels-review.xlsx
+++ b/docs/labels-review.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Labels" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Labels'!$A$1:$N$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Labels'!$A$1:$N$92</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N90"/>
+  <dimension ref="A1:N92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6803,27 +6803,27 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>connections.current</t>
+          <t>connections.idle</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Open connections</t>
+          <t>Open connections doing nothing</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>4.4 and later</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Connections open to this node. Shape only — the limit is in connections.used. A step is a deployment or a pool resize; a climb that never comes down is a client leaking connections.</t>
+          <t>Open connections with no operation in progress, leaving out drivers' monitoring connections, averaged over the minute. Most of a client pool is idle on any healthy server, so the share says little; the count is what costs: every connection holds a thread and memory on the server. Thousands of them is a pool sized far past what the workload uses, or one that grew during a stall and never shrank.</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/connections/current, in conns, every second</t>
+          <t>(serverStatus/connections/current + serverStatus/connections/awaitingTopologyChanges) − serverStatus/connections/active, in conns, every second</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
@@ -6838,24 +6838,32 @@
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>none — read for its shape only</t>
-        </is>
-      </c>
-      <c r="J89" s="4" t="inlineStr"/>
+          <t>few ≤300 (fading to 800) · many 800–1500 (edges 300, 2500) · excessive ≥3000 (from 1500)</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>550 conns → 50% few, 50% many</t>
+        </is>
+      </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>shape only: a step, an episode, a schedule</t>
-        </is>
-      </c>
-      <c r="L89" s="4" t="inlineStr"/>
+          <t>excessive</t>
+        </is>
+      </c>
+      <c r="L89" s="4" t="inlineStr">
+        <is>
+          <t>2000 conns or more</t>
+        </is>
+      </c>
       <c r="M89" s="4" t="inlineStr">
         <is>
-          <t>50 conns</t>
+          <t>100 conns</t>
         </is>
       </c>
       <c r="N89" s="4" t="inlineStr">
         <is>
-          <t>connections.created, memory.heap_outside_cache</t>
+          <t>connections.current, connections.created, connections.working_share, memory.heap_outside_cache</t>
         </is>
       </c>
     </row>
@@ -6867,72 +6875,208 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
+          <t>connections.working_share</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>Open connections with an operation in progress</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>4.4 and later</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>Share of the open connections with an operation in progress, leaving out drivers' monitoring connections, at the worst second of each minute. It stays low on a healthy server, because operations finish faster than they arrive; when the server stalls, every operation in flight waits and the share jumps. A pile-up here beside empty ticket pools or queued operations is a stall seen from the client side.</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>serverStatus/connections/active − serverStatus/connections/awaitingTopologyChanges ÷ serverStatus/connections/current × 100, in %, every second; minutes where the divisor sums to under 3000 are left out</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>the highest second of each minute</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>calm ≤10 (fading to 25) · busy 25–40 (edges 10, 60) · piled_up ≥60 (from 40)</t>
+        </is>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>17.5 % → 50% calm, 50% busy</t>
+        </is>
+      </c>
+      <c r="K90" s="4" t="inlineStr">
+        <is>
+          <t>piled_up</t>
+        </is>
+      </c>
+      <c r="L90" s="4" t="inlineStr">
+        <is>
+          <t>40 % or more</t>
+        </is>
+      </c>
+      <c r="M90" s="4" t="inlineStr">
+        <is>
+          <t>10 %</t>
+        </is>
+      </c>
+      <c r="N90" s="4" t="inlineStr">
+        <is>
+          <t>tickets.read.empty, tickets.write.empty, queue.readers, queue.writers, connections.created</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>connections</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>connections.current</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>Open connections</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>Connections open to this node. Shape only — the limit is in connections.used. A step is a deployment or a pool resize; a climb that never comes down is a client leaking connections.</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>serverStatus/connections/current, in conns, every second</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>each minute's mean</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>conns</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>none — read for its shape only</t>
+        </is>
+      </c>
+      <c r="J91" s="4" t="inlineStr"/>
+      <c r="K91" s="4" t="inlineStr">
+        <is>
+          <t>shape only: a step, an episode, a schedule</t>
+        </is>
+      </c>
+      <c r="L91" s="4" t="inlineStr"/>
+      <c r="M91" s="4" t="inlineStr">
+        <is>
+          <t>50 conns</t>
+        </is>
+      </c>
+      <c r="N91" s="4" t="inlineStr">
+        <is>
+          <t>connections.idle, connections.created, memory.heap_outside_cache</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>connections</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
           <t>connections.rejected</t>
         </is>
       </c>
-      <c r="C90" s="4" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>Connections refused</t>
         </is>
       </c>
-      <c r="D90" s="4" t="inlineStr">
+      <c r="D92" s="4" t="inlineStr">
         <is>
           <t>6.3 and later</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
+      <c r="E92" s="4" t="inlineStr">
         <is>
           <t>Connections mongod refused a second because it was at its limit (6.3 and later). Each one is a client error the application saw.</t>
         </is>
       </c>
-      <c r="F90" s="4" t="inlineStr">
+      <c r="F92" s="4" t="inlineStr">
         <is>
           <t>ΔserverStatus/connections/rejected per second, in /s, every second</t>
         </is>
       </c>
-      <c r="G90" s="4" t="inlineStr">
+      <c r="G92" s="4" t="inlineStr">
         <is>
           <t>each minute's mean</t>
         </is>
       </c>
-      <c r="H90" s="4" t="inlineStr">
+      <c r="H92" s="4" t="inlineStr">
         <is>
           <t>/s</t>
         </is>
       </c>
-      <c r="I90" s="4" t="inlineStr">
+      <c r="I92" s="4" t="inlineStr">
         <is>
           <t>none ≤0.001 (fading to 0.01) · some 0.01–1 (edges 0.001, 5) · many ≥5 (from 1)</t>
         </is>
       </c>
-      <c r="J90" s="4" t="inlineStr">
+      <c r="J92" s="4" t="inlineStr">
         <is>
           <t>0.005 /s → 56% none, 44% some</t>
         </is>
       </c>
-      <c r="K90" s="4" t="inlineStr">
+      <c r="K92" s="4" t="inlineStr">
         <is>
           <t>many</t>
         </is>
       </c>
-      <c r="L90" s="4" t="inlineStr">
+      <c r="L92" s="4" t="inlineStr">
         <is>
           <t>0.01 /s or more</t>
         </is>
       </c>
-      <c r="M90" s="4" t="inlineStr">
+      <c r="M92" s="4" t="inlineStr">
         <is>
           <t>0.01 /s</t>
         </is>
       </c>
-      <c r="N90" s="4" t="inlineStr">
+      <c r="N92" s="4" t="inlineStr">
         <is>
           <t>connections.scarce, connections.used</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N90"/>
+  <autoFilter ref="A1:N92"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/labels-review.xlsx
+++ b/docs/labels-review.xlsx
@@ -489,19 +489,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Labels are where an investigation starts. The report lays every label of every node out as worth opening, worth noticing, or ordinary; `mongo-log-parser label &lt;bundle&gt; &lt;label&gt; --source &lt;node&gt;` opens one: the exact seconds it was past its mark, the labels it pairs with over those seconds, and the node's log in the same window.</t>
+          <t>Labels summarize observations and guide navigation, not causes or fixes. The report uses fixed review references to group findings. Opening a label shows observed samples and timestamps, paired measurements and available matched-node logs. Legacy label IDs are stable identifiers, not proof of their implied condition.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>One second</t>
+          <t>One sample</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>FTDC samples about once a second. "What one second is" is the formula for each sample. Δ is a counter read as its change a second.</t>
+          <t>FTDC commonly samples about once a second, but cadence and gaps must be checked. Formulas apply to available samples. Counter rates use elapsed time; sample counts are not continuous elapsed durations.</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Each minute keeps its mean, its highest and lowest second, and — for a rule with a threshold — how many seconds were past it. "Read on" is the summary the bands and the shape use. A burst that a minute mean would hide (a ticket pool empty for ten seconds) is counted in seconds (s/min) instead.</t>
+          <t>Minute summaries keep the mean and extreme valid samples. Time views normalize the share of valid samples past a fixed reference to 60 s/min; this is not continuous elapsed time. A binned chart extremum does not show how long it persisted.</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Fuzzy: a value near an edge belongs to two bands by degree. "Example" shows one such value.</t>
+          <t>Fixed descriptive references, not incident severity, discovered limits or diagnostic confidence. Fuzzy membership means a value can belong to two bands by degree. "Example" shows one such value.</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>The band from which the label is listed as worth opening. The default is the top two bands of four or more, the top band otherwise; a rule can lower it (a single second with no ticket left is worth opening).</t>
+          <t>Fixed navigation rule: the top two of four or more bands, or the top band otherwise. Definitions may choose another review band, including one isolated sample. This ranking does not establish impact or cause.</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Minutes at or past this value count towards the duty cycle: how much of the window the label spent somewhere it should not stay. More than a rare minute past it also makes a label worth opening.</t>
+          <t>The fraction of retained minute summaries at or past this reference. It is a descriptive threshold crossing, not continuous elapsed duration, incident impact or proof of failure.</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>The labels read beside this one, over the same seconds, when it is opened.</t>
+          <t>Other labels read over the selected observed sample window; navigation links, not causal claims.</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>What one second is</t>
+          <t>Sample formula</t>
         </is>
       </c>
       <c r="G1" s="3" t="inlineStr">
@@ -702,12 +702,12 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Share of the whole machine's CPU doing work: user, system, interrupts and steal, not idle and not waiting on I/O. Read on the minute's mean, which is how loaded the machine was; the seconds it spent pinned at the top are cpu.saturated. Past about 90% runnable threads queue for a core and every operation's latency grows with the queue.</t>
+          <t>Share of host CPU counters recorded as user, nice, system, IRQ, soft IRQ or steal, excluding idle and iowait; steal is not process execution time. Host-wide memory or CPU counters do not establish a container's resource limit. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Δ(systemMetrics/cpu/user_ms + systemMetrics/cpu/nice_ms + systemMetrics/cpu/system_ms + systemMetrics/cpu/irq_ms + systemMetrics/cpu/softirq_ms + systemMetrics/cpu/steal_ms) ÷ Δ(systemMetrics/cpu/user_ms + systemMetrics/cpu/nice_ms + systemMetrics/cpu/system_ms + systemMetrics/cpu/idle_ms + systemMetrics/cpu/iowait_ms + systemMetrics/cpu/irq_ms + systemMetrics/cpu/softirq_ms + systemMetrics/cpu/steal_ms) × 100, in %, every second</t>
+          <t>Δ(systemMetrics/cpu/user_ms + systemMetrics/cpu/nice_ms + systemMetrics/cpu/system_ms + systemMetrics/cpu/irq_ms + systemMetrics/cpu/softirq_ms + systemMetrics/cpu/steal_ms) ÷ Δ(systemMetrics/cpu/user_ms + systemMetrics/cpu/nice_ms + systemMetrics/cpu/system_ms + systemMetrics/cpu/idle_ms + systemMetrics/cpu/iowait_ms + systemMetrics/cpu/irq_ms + systemMetrics/cpu/softirq_ms + systemMetrics/cpu/steal_ms) × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>idle ≤5 (fading to 15) · low 15–35 (edges 5, 50) · moderate 50–65 (edges 35, 80) · high 80–88 (edges 65, 95) · saturated ≥95 (from 88)</t>
+          <t>idle ≤5 (fading to 15) · low 15–35 (edges 5, 50) · moderate 50–65 (edges 35, 80) · high 80–88 (edges 65, 95) · very_high ≥95 (from 88)</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>high or saturated</t>
+          <t>high or very_high</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Seconds the CPU was saturated</t>
+          <t>CPU-busy samples above 95%</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -774,17 +774,17 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Seconds of each minute the whole machine's CPU was 95% busy or more. A minute mean of 50% can be thirty seconds pinned and thirty idle; this is the thirty. Operations that arrive in those seconds wait for a core.</t>
+          <t>Share of valid samples with the signal strictly above 95 %, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Δ(systemMetrics/cpu/user_ms + systemMetrics/cpu/nice_ms + systemMetrics/cpu/system_ms + systemMetrics/cpu/irq_ms + systemMetrics/cpu/softirq_ms + systemMetrics/cpu/steal_ms) ÷ Δ(systemMetrics/cpu/user_ms + systemMetrics/cpu/nice_ms + systemMetrics/cpu/system_ms + systemMetrics/cpu/idle_ms + systemMetrics/cpu/iowait_ms + systemMetrics/cpu/irq_ms + systemMetrics/cpu/softirq_ms + systemMetrics/cpu/steal_ms) × 100, in %, every second</t>
+          <t>Δ(systemMetrics/cpu/user_ms + systemMetrics/cpu/nice_ms + systemMetrics/cpu/system_ms + systemMetrics/cpu/irq_ms + systemMetrics/cpu/softirq_ms + systemMetrics/cpu/steal_ms) ÷ Δ(systemMetrics/cpu/user_ms + systemMetrics/cpu/nice_ms + systemMetrics/cpu/system_ms + systemMetrics/cpu/idle_ms + systemMetrics/cpu/iowait_ms + systemMetrics/cpu/irq_ms + systemMetrics/cpu/softirq_ms + systemMetrics/cpu/steal_ms) × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>seconds of each minute above 95 %</t>
+          <t>valid-sample share strictly above 95 %, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>CPU waiting on I/O</t>
+          <t>Host CPU iowait share</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Share of the machine's CPU idle with I/O outstanding. It says the processors had nothing to do but wait for storage; read it beside disk busy and disk await, which say which device.</t>
+          <t>Share of the machine's CPU idle with I/O outstanding. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>ΔsystemMetrics/cpu/iowait_ms ÷ Δ(systemMetrics/cpu/user_ms + systemMetrics/cpu/nice_ms + systemMetrics/cpu/system_ms + systemMetrics/cpu/idle_ms + systemMetrics/cpu/iowait_ms + systemMetrics/cpu/irq_ms + systemMetrics/cpu/softirq_ms + systemMetrics/cpu/steal_ms) × 100, in %, every second</t>
+          <t>ΔsystemMetrics/cpu/iowait_ms ÷ Δ(systemMetrics/cpu/user_ms + systemMetrics/cpu/nice_ms + systemMetrics/cpu/system_ms + systemMetrics/cpu/idle_ms + systemMetrics/cpu/iowait_ms + systemMetrics/cpu/irq_ms + systemMetrics/cpu/softirq_ms + systemMetrics/cpu/steal_ms) × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>CPU stolen by the hypervisor</t>
+          <t>Host CPU steal-time share</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Share of the machine's CPU a virtual machine was ready to use and the hypervisor gave to someone else. Any sustained steal is a noisy neighbour or an oversubscribed host, and mongod cannot see it.</t>
+          <t>Share of the host CPU counters recorded as steal time. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>ΔsystemMetrics/cpu/steal_ms ÷ Δ(systemMetrics/cpu/user_ms + systemMetrics/cpu/nice_ms + systemMetrics/cpu/system_ms + systemMetrics/cpu/idle_ms + systemMetrics/cpu/iowait_ms + systemMetrics/cpu/irq_ms + systemMetrics/cpu/softirq_ms + systemMetrics/cpu/steal_ms) × 100, in %, every second</t>
+          <t>ΔsystemMetrics/cpu/steal_ms ÷ Δ(systemMetrics/cpu/user_ms + systemMetrics/cpu/nice_ms + systemMetrics/cpu/system_ms + systemMetrics/cpu/idle_ms + systemMetrics/cpu/iowait_ms + systemMetrics/cpu/irq_ms + systemMetrics/cpu/softirq_ms + systemMetrics/cpu/steal_ms) × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>System CPU as a share of user plus system. mongod spends most of its CPU in user space; when the kernel takes as much or more, something below the database is working hard — TLS in the crypto library, transparent huge page compaction, reclaim under memory pressure, or a flood of small I/O. Read it beside cpu.busy: a high share of an idle machine means little.</t>
+          <t>System CPU as a share of user plus system. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>ΔsystemMetrics/cpu/system_ms ÷ Δ(systemMetrics/cpu/user_ms + systemMetrics/cpu/system_ms) × 100, in %, every second; minutes where the divisor sums to under 6000 are left out</t>
+          <t>ΔsystemMetrics/cpu/system_ms ÷ Δ(systemMetrics/cpu/user_ms + systemMetrics/cpu/system_ms) × 100, in %, at each available sample; minutes where the divisor sums to under 6000 are left out</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Threads ready to run, per logical core, averaged over the minute. Above one, threads wait for a CPU and every operation queues behind them even when cpu.busy looks moderate on a many-core host.</t>
+          <t>Threads ready to run, per logical core, averaged over the minute. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>systemMetrics/cpu/procs_running ÷ systemMetrics/cpu/num_logical_cores, in per core, every second</t>
+          <t>systemMetrics/cpu/procs_running ÷ systemMetrics/cpu/num_logical_cores, in per core, at each available sample</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>light ≤0.5 (fading to 0.8) · busy 0.8–1.2 (edges 0.5, 2) · overloaded ≥2 (from 1.2)</t>
+          <t>light ≤0.5 (fading to 0.8) · busy 0.8–1.2 (edges 0.5, 2) · very_high ≥2 (from 1.2)</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>overloaded</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Threads ready to run, per logical core, averaged over the minute. Above one, threads wait for a CPU and every operation queues behind them even when cpu.busy looks moderate on a many-core host.</t>
+          <t>Threads ready to run, per logical core, averaged over the minute. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>systemMetrics/cpu/procs_running ÷ systemMetrics/cpu/num_cpus, in per core, every second</t>
+          <t>systemMetrics/cpu/procs_running ÷ systemMetrics/cpu/num_cpus, in per core, at each available sample</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>light ≤0.5 (fading to 0.8) · busy 0.8–1.2 (edges 0.5, 2) · overloaded ≥2 (from 1.2)</t>
+          <t>light ≤0.5 (fading to 0.8) · busy 0.8–1.2 (edges 0.5, 2) · very_high ≥2 (from 1.2)</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>overloaded</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Threads blocked on I/O</t>
+          <t>Processes in uninterruptible sleep</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Processes in uninterruptible sleep, averaged over the minute — almost always waiting on storage. A sustained handful means the disk is behind; it is also how a hung network mount shows, and FTDC itself can stop when its own statfs call blocks on one.</t>
+          <t>Host process count recorded in procs_blocked (uninterruptible sleep). Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>systemMetrics/cpu/procs_blocked, in threads, every second</t>
+          <t>systemMetrics/cpu/procs_blocked, in threads, at each available sample</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1278,12 +1278,12 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Context switches a second, host-wide. There is no level that is high for every machine; a step or a burst is threads contending — lock or spinlock contention, a connection storm.</t>
+          <t>Context switches a second, host-wide. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>ΔsystemMetrics/cpu/ctxt per second, in /s, every second</t>
+          <t>ΔsystemMetrics/cpu/ctxt per second, in /s, at each available sample</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Share of the machine's memory not available to new allocations (MemTotal less MemAvailable, so the page cache the kernel can drop counts as free). Near the top the kernel reclaims hard, then the OOM killer chooses a process, and mongod is usually the largest. MongoDB collects MemAvailable from 4.2.14 and 4.4.5 (ftdc_system_stats_linux.cpp kMemKeys); earlier nodes do not get this label.</t>
+          <t>Share of the machine's memory not available to new allocations (MemTotal less MemAvailable, so the page cache the kernel can drop counts as free). Host-wide memory or CPU counters do not establish a container's resource limit. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>100 − (systemMetrics/memory/MemAvailable_kb ÷ systemMetrics/memory/MemTotal_kb × 100), in %, every second</t>
+          <t>100 − (systemMetrics/memory/MemAvailable_kb ÷ systemMetrics/memory/MemTotal_kb × 100), in %, at each available sample</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>low ≤40 (fading to 60) · moderate 60–75 (edges 40, 85) · high 85–92 (edges 75, 96) · exhausted ≥96 (from 92)</t>
+          <t>low ≤40 (fading to 60) · moderate 60–75 (edges 40, 85) · high 85–92 (edges 75, 96) · very_high ≥96 (from 92)</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>high or exhausted</t>
+          <t>high or very_high</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Share of swap holding pages. A database whose pages are swapped out pays a disk read for memory it believes it has; any sustained swap on a mongod host is worth explaining, and swappiness or a cache sized past the container is the usual reason.</t>
+          <t>Share of swap holding pages. Host-wide memory or CPU counters do not establish a container's resource limit. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>100 − (systemMetrics/memory/SwapFree_kb ÷ systemMetrics/memory/SwapTotal_kb × 100), in %, every second</t>
+          <t>100 − (systemMetrics/memory/SwapFree_kb ÷ systemMetrics/memory/SwapTotal_kb × 100), in %, at each available sample</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Major page faults mongod took a second: memory it had to read back from disk. A burst is memory pressure — swap, or a page cache too small for what is read from it.</t>
+          <t>Rate of the process's logged major-page-fault counter. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/extra_info/page_faults per second, in /s, every second</t>
+          <t>ΔserverStatus/extra_info/page_faults per second, in /s, at each available sample</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>mongod's resident memory as a share of the machine's. In a container, compare it with the cgroup limit the log reports at startup, not with the host: a cache sized from host memory in a smaller container is a common cause of OOM kills.</t>
+          <t>mongod's resident memory as a share of the machine's. Host-wide memory or CPU counters do not establish a container's resource limit. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/mem/resident ÷ systemMetrics/memory/MemTotal_kb × 102400, in %, every second</t>
+          <t>serverStatus/mem/resident ÷ systemMetrics/memory/MemTotal_kb × 102400, in %, at each available sample</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Heap outside the WiredTiger cache</t>
+          <t>Allocated bytes minus WiredTiger cache bytes</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1630,12 +1630,12 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Bytes tcmalloc has allocated beyond what the WiredTiger cache holds: connections, sorts, aggregations, plan caches and fragmentation. Rising while the cache stays flat is the shape a reported memory leak usually has — and it is usually workload or allocator retention, not a leak.</t>
+          <t>Difference between tcmalloc allocated bytes and bytes currently held in the WiredTiger cache; this is a derived estimate, not a complete inventory of non-cache allocations. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/tcmalloc/generic/current_allocated_bytes − serverStatus/wiredTiger/cache/bytes currently in the cache × 9.313225746154785e-10, in GiB, every second</t>
+          <t>serverStatus/tcmalloc/generic/current_allocated_bytes − serverStatus/wiredTiger/cache/bytes currently in the cache × 9.313225746154785e-10, in GiB, at each available sample</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Memory freed but kept by tcmalloc</t>
+          <t>tcmalloc pageheap-free share</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Share of tcmalloc's heap that is free but not returned to the operating system (pageheap_free_bytes over heap_size). A large share is memory the machine counts against mongod that no operation is using; tcmallocReleaseRate decides how fast it goes back. Before 8.0 only: 8.0 Linux builds use Google tcmalloc, which keeps most free memory in per-CPU caches that pageheap_free_bytes does not count.</t>
+          <t>Ratio of tcmalloc pageheap_free_bytes to heap_size; these counters do not describe every allocator cache. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/tcmalloc/tcmalloc/pageheap_free_bytes ÷ serverStatus/tcmalloc/generic/heap_size × 100, in %, every second</t>
+          <t>serverStatus/tcmalloc/tcmalloc/pageheap_free_bytes ÷ serverStatus/tcmalloc/generic/heap_size × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>The configured cache as a share of the machine's memory. The default is half of RAM less a gigabyte; much more than that leaves too little for connections, sorts and the page cache. In a container the machine's memory may not be the limit the process lives under.</t>
+          <t>The configured cache as a share of the machine's memory. Host-wide memory or CPU counters do not establish a container's resource limit. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/cache/maximum bytes configured ÷ systemMetrics/memory/MemTotal_kb × 0.09765625, in %, every second</t>
+          <t>serverStatus/wiredTiger/cache/maximum bytes configured ÷ systemMetrics/memory/MemTotal_kb × 0.09765625, in %, at each available sample</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -1786,17 +1786,17 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>conservative ≤30 (fading to 40) · default 40–55 (edges 30, 62) · oversized ≥70 (from 58)</t>
+          <t>low ≤30 (fading to 40) · middle 40–55 (edges 30, 62) · high ≥70 (from 58)</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>35 % → 50% conservative, 50% default</t>
+          <t>35 % → 50% low, 50% middle</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>oversized</t>
+          <t>high</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Share of each minute a block device had a request in flight (io_time). On a single spindle 100% is the limit; an SSD or a cloud volume serves many requests at once and can be 100% busy with room to spare, so read it beside disk await, which says whether requests actually waited. FTDC lists only devices with a /sys/block/&lt;dev&gt;/device entry, fixed at startup: dm-* (LVM) and md arrays are not there, only their member disks.</t>
+          <t>Device io_time counter advance divided by elapsed time; a high value does not establish device capacity exhaustion. Device coverage depends on the block-device counters present in FTDC; logical devices may be absent. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>ΔsystemMetrics/disks/{i}/io_time_ms per second × 0.1, in %, every second; real block devices only</t>
+          <t>ΔsystemMetrics/disks/{i}/io_time_ms per second × 0.1, in %, at each available sample; real block devices only</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>idle ≤5 (fading to 15) · low 15–40 (edges 5, 60) · moderate 60–75 (edges 40, 85) · high 85–92 (edges 75, 97) · saturated ≥97 (from 92)</t>
+          <t>idle ≤5 (fading to 15) · low 15–40 (edges 5, 60) · moderate 60–75 (edges 40, 85) · high 85–92 (edges 75, 97) · very_high ≥97 (from 92)</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>high or saturated</t>
+          <t>high or very_high</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Seconds the disk was saturated</t>
+          <t>Device-busy samples above 95%</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1910,17 +1910,17 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Seconds of each minute a device was busy 95% of the second or more. A checkpoint that pins a volume for twenty seconds a minute averages to a third busy; this counts the twenty. Read it beside disk await: an SSD can be pinned and still answer fast.</t>
+          <t>Share of valid samples with the signal strictly above 95 %, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>ΔsystemMetrics/disks/{i}/io_time_ms per second × 0.1, in %, every second; real block devices only</t>
+          <t>ΔsystemMetrics/disks/{i}/io_time_ms per second × 0.1, in %, at each available sample; real block devices only</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>seconds of each minute above 95 %</t>
+          <t>valid-sample share strictly above 95 %, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1982,12 +1982,12 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Average milliseconds a read or write took on each device, queueing included — what iostat calls await. A local SSD answers in under a millisecond and a cloud volume in one to a few; tens of milliseconds means requests are waiting on the device or its throughput limit. Minutes with fewer than sixty requests are left out.</t>
+          <t>Average milliseconds a read or write took on each device, queueing included — what iostat calls await. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Δ(systemMetrics/disks/{i}/read_time_ms + systemMetrics/disks/{i}/write_time_ms) ÷ Δ(systemMetrics/disks/{i}/reads + systemMetrics/disks/{i}/writes), in ms, every second; minutes where the divisor sums to under 60 are left out; real block devices only</t>
+          <t>Δ(systemMetrics/disks/{i}/read_time_ms + systemMetrics/disks/{i}/write_time_ms) ÷ Δ(systemMetrics/disks/{i}/reads + systemMetrics/disks/{i}/writes), in ms, at each available sample; minutes where the divisor sums to under 60 are left out; real block devices only</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Average milliseconds a read took on each device. Slow reads with a quiet write side point at a cache too small for the working set; slow reads only during a snapshot or backup window point at whatever else was reading the volume.</t>
+          <t>Average milliseconds a read took on each device. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>ΔsystemMetrics/disks/{i}/read_time_ms ÷ ΔsystemMetrics/disks/{i}/reads, in ms, every second; minutes where the divisor sums to under 60 are left out; real block devices only</t>
+          <t>ΔsystemMetrics/disks/{i}/read_time_ms ÷ ΔsystemMetrics/disks/{i}/reads, in ms, at each available sample; minutes where the divisor sums to under 60 are left out; real block devices only</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Average milliseconds a write took on each device. Journal and checkpoint writes wait on it; slow writes are what turn a checkpoint into a stall and drain the write tickets.</t>
+          <t>Average milliseconds a write took on each device. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>ΔsystemMetrics/disks/{i}/write_time_ms ÷ ΔsystemMetrics/disks/{i}/writes, in ms, every second; minutes where the divisor sums to under 60 are left out; real block devices only</t>
+          <t>ΔsystemMetrics/disks/{i}/write_time_ms ÷ ΔsystemMetrics/disks/{i}/writes, in ms, at each available sample; minutes where the divisor sums to under 60 are left out; real block devices only</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Average number of requests outstanding on each device over the minute (io_queued time over wall time). A deep queue on a device that is also slow per request is a device at its limit; a deep queue answered fast is a device built for it.</t>
+          <t>Average number of requests outstanding on each device over the minute (io_queued time over wall time). Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>ΔsystemMetrics/disks/{i}/io_queued_ms per second × 0.001, in requests, every second; real block devices only</t>
+          <t>ΔsystemMetrics/disks/{i}/io_queued_ms per second × 0.001, in requests, at each available sample; real block devices only</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -2270,12 +2270,12 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Reads plus writes a second on each device. No level is high for every volume; a flat ceiling that busy and await press against is a provisioned IOPS limit or exhausted burst credits.</t>
+          <t>Reads plus writes a second on each device. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Δ(systemMetrics/disks/{i}/reads + systemMetrics/disks/{i}/writes) per second, in /s, every second; real block devices only</t>
+          <t>Δ(systemMetrics/disks/{i}/reads + systemMetrics/disks/{i}/writes) per second, in /s, at each available sample; real block devices only</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -2334,12 +2334,12 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Megabytes a second read plus written on each device (sectors are 512 bytes). A volume that is busy at low IOPS and high throughput is at its bandwidth limit rather than its request limit.</t>
+          <t>Megabytes a second read plus written on each device (sectors are 512 bytes). Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Δ(systemMetrics/disks/{i}/read_sectors + systemMetrics/disks/{i}/write_sectors) per second × 0.000512, in MB/s, every second; real block devices only</t>
+          <t>Δ(systemMetrics/disks/{i}/read_sectors + systemMetrics/disks/{i}/write_sectors) per second × 0.000512, in MB/s, at each available sample; real block devices only</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
@@ -2398,12 +2398,12 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Share of TCP segments the host sent again because the first copy was not acknowledged in time, across every connection on the machine. Above about one percent replication, heartbeats and client replies all slow down, and mongod has no counter of its own that shows it. Minutes that sent fewer than a thousand segments are left out.</t>
+          <t>Ratio of the host TCP RetransSegs counter advance to the OutSegs counter advance, across host connections. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>ΔsystemMetrics/netstat/Tcp:RetransSegs ÷ ΔsystemMetrics/netstat/Tcp:OutSegs × 100, in %, every second; minutes where the divisor sums to under 1000 are left out</t>
+          <t>ΔsystemMetrics/netstat/Tcp:RetransSegs ÷ ΔsystemMetrics/netstat/Tcp:OutSegs × 100, in %, at each available sample; minutes where the divisor sums to under 1000 are left out</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -2418,17 +2418,17 @@
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>clean ≤0.1 (fading to 0.3) · minor 0.3–0.7 (edges 0.1, 1) · lossy 1–2 (edges 0.7, 3) · severe ≥3 (from 2)</t>
+          <t>low ≤0.1 (fading to 0.3) · moderate 0.3–0.7 (edges 0.1, 1) · high 1–2 (edges 0.7, 3) · very_high ≥3 (from 2)</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>0.2 % → 50% clean, 50% minor</t>
+          <t>0.2 % → 50% low, 50% moderate</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>lossy or severe</t>
+          <t>high or very_high</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Connections the kernel dropped a second because mongod's accept queue was full. A client refused here leaves nothing in the server log; any at all is worth explaining.</t>
+          <t>Rate of the host TCP ListenOverflows counter; the counter does not identify a MongoDB connection or client outcome. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>ΔsystemMetrics/netstat/TcpExt:ListenOverflows per second, in /s, every second</t>
+          <t>ΔsystemMetrics/netstat/TcpExt:ListenOverflows per second, in /s, at each available sample</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
@@ -2542,12 +2542,12 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Established connections reset a second, host-wide. A burst is clients or a load balancer tearing connections down — timeouts, a failover, a proxy recycling its pool.</t>
+          <t>Established connections reset a second, host-wide. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>ΔsystemMetrics/netstat/Tcp:EstabResets per second, in /s, every second</t>
+          <t>ΔsystemMetrics/netstat/Tcp:EstabResets per second, in /s, at each available sample</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Bytes a second in and out of mongod, from its own counters. Shape only: a step is a workload change, a periodic burst a job, and a ceiling the link or an instance's bandwidth limit.</t>
+          <t>Sum of the server's bytesIn and bytesOut counter rates, scaled to MB/s. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Δ(serverStatus/network/bytesIn + serverStatus/network/bytesOut) per second × 1e-06, in MB/s, every second</t>
+          <t>Δ(serverStatus/network/bytesIn + serverStatus/network/bytesOut) per second × 1e-06, in MB/s, at each available sample</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Read tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute. It is the general load on the pool: half used is worth noticing even when nothing ran out. Whether it ran out is tickets.read.scarce and tickets.read.empty; whether the pool itself changed size is tickets.read.pool.</t>
+          <t>Read tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/concurrentTransactions/read/out ÷ serverStatus/wiredTiger/concurrentTransactions/read/totalTickets × 100, in %, every second</t>
+          <t>serverStatus/wiredTiger/concurrentTransactions/read/out ÷ serverStatus/wiredTiger/concurrentTransactions/read/totalTickets × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Seconds with under 10% of read tickets left</t>
+          <t>Samples with under 10% of read tickets left</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -2742,17 +2742,17 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Seconds of each minute fewer than a tenth of the read ticket pool was available, measured against the pool as it was that second, so it means the same thing for a pool the server resized as for a fixed one. Near-empty is where reads start to wait; a minute mean of the pool hides ten seconds of it entirely.</t>
+          <t>Share of valid samples with the signal strictly below 10 % available, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/concurrentTransactions/read/available ÷ serverStatus/wiredTiger/concurrentTransactions/read/totalTickets × 100, in % available, every second</t>
+          <t>serverStatus/wiredTiger/concurrentTransactions/read/available ÷ serverStatus/wiredTiger/concurrentTransactions/read/totalTickets × 100, in % available, at each available sample</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>seconds of each minute below 10 % available</t>
+          <t>valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Seconds with no read ticket left</t>
+          <t>Samples with no read ticket left</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -2814,17 +2814,17 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Seconds of each minute the read ticket pool had none available. Every read that arrived in those seconds waited at the door of the storage engine. Reads waiting here are held behind whatever holds the tickets: long scans, slow reads from disk, eviction.</t>
+          <t>Share of valid samples with the signal strictly below 0.5 tickets left, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/concurrentTransactions/read/available, in tickets left, every second</t>
+          <t>serverStatus/wiredTiger/concurrentTransactions/read/available, in tickets left, at each available sample</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>seconds of each minute below 0.5 tickets left</t>
+          <t>valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2886,12 +2886,12 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>How many read tickets the pool held, averaged over the minute. Fixed unless someone changed it or, from 7.0, the server resized it to the load it measured; a step or an episode here is the pool growing under load or shrinking after it. Shape only: there is no size that is wrong for every server.</t>
+          <t>How many read tickets the pool held, averaged over the minute. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/concurrentTransactions/read/totalTickets, in tickets, every second</t>
+          <t>serverStatus/wiredTiger/concurrentTransactions/read/totalTickets, in tickets, at each available sample</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Milliseconds a second operations spent queued for a read ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. Not reported before 7.0. Reads waiting here are held behind whatever holds the tickets: long scans, slow reads from disk, eviction.</t>
+          <t>Milliseconds a second operations spent queued for a read ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/wiredTiger/concurrentTransactions/read/totalTimeQueuedMicros per second × 0.001, in ms/s, every second</t>
+          <t>ΔserverStatus/wiredTiger/concurrentTransactions/read/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Read tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute. It is the general load on the pool: half used is worth noticing even when nothing ran out. Whether it ran out is tickets.read.scarce and tickets.read.empty; whether the pool itself changed size is tickets.read.pool.</t>
+          <t>Read tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/queues/execution/read/out ÷ serverStatus/queues/execution/read/totalTickets × 100, in %, every second</t>
+          <t>serverStatus/queues/execution/read/out ÷ serverStatus/queues/execution/read/totalTickets × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Seconds with under 10% of read tickets left</t>
+          <t>Samples with under 10% of read tickets left</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -3094,17 +3094,17 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Seconds of each minute fewer than a tenth of the read ticket pool was available, measured against the pool as it was that second, so it means the same thing for a pool the server resized as for a fixed one. Near-empty is where reads start to wait; a minute mean of the pool hides ten seconds of it entirely.</t>
+          <t>Share of valid samples with the signal strictly below 10 % available, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/queues/execution/read/available ÷ serverStatus/queues/execution/read/totalTickets × 100, in % available, every second</t>
+          <t>serverStatus/queues/execution/read/available ÷ serverStatus/queues/execution/read/totalTickets × 100, in % available, at each available sample</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>seconds of each minute below 10 % available</t>
+          <t>valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Seconds with no read ticket left</t>
+          <t>Samples with no read ticket left</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -3166,17 +3166,17 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Seconds of each minute the read ticket pool had none available. Every read that arrived in those seconds waited at the door of the storage engine. Reads waiting here are held behind whatever holds the tickets: long scans, slow reads from disk, eviction.</t>
+          <t>Share of valid samples with the signal strictly below 0.5 tickets left, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/queues/execution/read/available, in tickets left, every second</t>
+          <t>serverStatus/queues/execution/read/available, in tickets left, at each available sample</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>seconds of each minute below 0.5 tickets left</t>
+          <t>valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>How many read tickets the pool held, averaged over the minute. Fixed unless someone changed it or, from 7.0, the server resized it to the load it measured; a step or an episode here is the pool growing under load or shrinking after it. Shape only: there is no size that is wrong for every server.</t>
+          <t>How many read tickets the pool held, averaged over the minute. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/queues/execution/read/totalTickets, in tickets, every second</t>
+          <t>serverStatus/queues/execution/read/totalTickets, in tickets, at each available sample</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Milliseconds a second operations spent queued for a read ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. Not reported before 7.0. Reads waiting here are held behind whatever holds the tickets: long scans, slow reads from disk, eviction. Normal-priority operations only: exempt operations bypass the pool and are not counted.</t>
+          <t>Milliseconds a second operations spent queued for a read ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. The counter covers normal-priority operations, not exempt operations. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/queues/execution/read/normalPriority/totalTimeQueuedMicros per second × 0.001, in ms/s, every second</t>
+          <t>ΔserverStatus/queues/execution/read/normalPriority/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Write tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute. It is the general load on the pool: half used is worth noticing even when nothing ran out. Whether it ran out is tickets.write.scarce and tickets.write.empty; whether the pool itself changed size is tickets.write.pool.</t>
+          <t>Write tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/concurrentTransactions/write/out ÷ serverStatus/wiredTiger/concurrentTransactions/write/totalTickets × 100, in %, every second</t>
+          <t>serverStatus/wiredTiger/concurrentTransactions/write/out ÷ serverStatus/wiredTiger/concurrentTransactions/write/totalTickets × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Seconds with under 10% of write tickets left</t>
+          <t>Samples with under 10% of write tickets left</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -3446,17 +3446,17 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Seconds of each minute fewer than a tenth of the write ticket pool was available, measured against the pool as it was that second, so it means the same thing for a pool the server resized as for a fixed one. Near-empty is where writes start to wait; a minute mean of the pool hides ten seconds of it entirely.</t>
+          <t>Share of valid samples with the signal strictly below 10 % available, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/concurrentTransactions/write/available ÷ serverStatus/wiredTiger/concurrentTransactions/write/totalTickets × 100, in % available, every second</t>
+          <t>serverStatus/wiredTiger/concurrentTransactions/write/available ÷ serverStatus/wiredTiger/concurrentTransactions/write/totalTickets × 100, in % available, at each available sample</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>seconds of each minute below 10 % available</t>
+          <t>valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Seconds with no write ticket left</t>
+          <t>Samples with no write ticket left</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -3518,17 +3518,17 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Seconds of each minute the write ticket pool had none available. Every write that arrived in those seconds waited at the door of the storage engine. Writes waiting here are usually behind checkpoints, dirty cache eviction or slow journal writes.</t>
+          <t>Share of valid samples with the signal strictly below 0.5 tickets left, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/concurrentTransactions/write/available, in tickets left, every second</t>
+          <t>serverStatus/wiredTiger/concurrentTransactions/write/available, in tickets left, at each available sample</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>seconds of each minute below 0.5 tickets left</t>
+          <t>valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>How many write tickets the pool held, averaged over the minute. Fixed unless someone changed it or, from 7.0, the server resized it to the load it measured; a step or an episode here is the pool growing under load or shrinking after it. Shape only: there is no size that is wrong for every server.</t>
+          <t>How many write tickets the pool held, averaged over the minute. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/concurrentTransactions/write/totalTickets, in tickets, every second</t>
+          <t>serverStatus/wiredTiger/concurrentTransactions/write/totalTickets, in tickets, at each available sample</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Milliseconds a second operations spent queued for a write ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. Not reported before 7.0. Writes waiting here are usually behind checkpoints, dirty cache eviction or slow journal writes.</t>
+          <t>Milliseconds a second operations spent queued for a write ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/wiredTiger/concurrentTransactions/write/totalTimeQueuedMicros per second × 0.001, in ms/s, every second</t>
+          <t>ΔserverStatus/wiredTiger/concurrentTransactions/write/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Write tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute. It is the general load on the pool: half used is worth noticing even when nothing ran out. Whether it ran out is tickets.write.scarce and tickets.write.empty; whether the pool itself changed size is tickets.write.pool.</t>
+          <t>Write tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/queues/execution/write/out ÷ serverStatus/queues/execution/write/totalTickets × 100, in %, every second</t>
+          <t>serverStatus/queues/execution/write/out ÷ serverStatus/queues/execution/write/totalTickets × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Seconds with under 10% of write tickets left</t>
+          <t>Samples with under 10% of write tickets left</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -3798,17 +3798,17 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Seconds of each minute fewer than a tenth of the write ticket pool was available, measured against the pool as it was that second, so it means the same thing for a pool the server resized as for a fixed one. Near-empty is where writes start to wait; a minute mean of the pool hides ten seconds of it entirely.</t>
+          <t>Share of valid samples with the signal strictly below 10 % available, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/queues/execution/write/available ÷ serverStatus/queues/execution/write/totalTickets × 100, in % available, every second</t>
+          <t>serverStatus/queues/execution/write/available ÷ serverStatus/queues/execution/write/totalTickets × 100, in % available, at each available sample</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>seconds of each minute below 10 % available</t>
+          <t>valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Seconds with no write ticket left</t>
+          <t>Samples with no write ticket left</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Seconds of each minute the write ticket pool had none available. Every write that arrived in those seconds waited at the door of the storage engine. Writes waiting here are usually behind checkpoints, dirty cache eviction or slow journal writes.</t>
+          <t>Share of valid samples with the signal strictly below 0.5 tickets left, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/queues/execution/write/available, in tickets left, every second</t>
+          <t>serverStatus/queues/execution/write/available, in tickets left, at each available sample</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>seconds of each minute below 0.5 tickets left</t>
+          <t>valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>How many write tickets the pool held, averaged over the minute. Fixed unless someone changed it or, from 7.0, the server resized it to the load it measured; a step or an episode here is the pool growing under load or shrinking after it. Shape only: there is no size that is wrong for every server.</t>
+          <t>How many write tickets the pool held, averaged over the minute. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/queues/execution/write/totalTickets, in tickets, every second</t>
+          <t>serverStatus/queues/execution/write/totalTickets, in tickets, at each available sample</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Milliseconds a second operations spent queued for a write ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. Not reported before 7.0. Writes waiting here are usually behind checkpoints, dirty cache eviction or slow journal writes. Normal-priority operations only: exempt operations bypass the pool and are not counted.</t>
+          <t>Milliseconds a second operations spent queued for a write ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. The counter covers normal-priority operations, not exempt operations. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/queues/execution/write/normalPriority/totalTimeQueuedMicros per second × 0.001, in ms/s, every second</t>
+          <t>ΔserverStatus/queues/execution/write/normalPriority/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Seconds with reads queued</t>
+          <t>Samples with reads queued</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -4078,17 +4078,17 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Seconds of each minute at least one read operation was queued for a lock or a ticket (globalLock.currentQueue.readers). How deep the queue got is the label's peak second.</t>
+          <t>Share of valid samples with the signal strictly above 0 operations, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/globalLock/currentQueue/readers, in operations, every second</t>
+          <t>serverStatus/globalLock/currentQueue/readers, in operations, at each available sample</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>seconds of each minute above 0 operations</t>
+          <t>valid-sample share strictly above 0 operations, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Seconds with writes queued</t>
+          <t>Samples with writes queued</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -4150,17 +4150,17 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Seconds of each minute at least one write operation was queued for a lock or a ticket (globalLock.currentQueue.writers). How deep the queue got is the label's peak second.</t>
+          <t>Share of valid samples with the signal strictly above 0 operations, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/globalLock/currentQueue/writers, in operations, every second</t>
+          <t>serverStatus/globalLock/currentQueue/writers, in operations, at each available sample</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>seconds of each minute above 0 operations</t>
+          <t>valid-sample share strictly above 0 operations, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -4222,12 +4222,12 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Bytes in the WiredTiger cache as a share of its configured size, averaged over the minute. Eviction keeps it near 80%; at 95% (eviction_trigger) application threads are made to evict before they may proceed, which turns cache pressure into operation latency. The seconds spent past that line are cache.over_trigger.</t>
+          <t>Bytes in the WiredTiger cache as a share of its configured size, averaged over the minute. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/cache/bytes currently in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, every second</t>
+          <t>serverStatus/wiredTiger/cache/bytes currently in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>low ≤50 (fading to 70) · normal 70–80 (edges 50, 86) · high 86–93 (edges 80, 95) · over_trigger ≥96 (from 94)</t>
+          <t>low ≤50 (fading to 70) · normal 70–80 (edges 50, 86) · high 86–93 (edges 80, 95) · above_reference ≥96 (from 94)</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>high or over_trigger</t>
+          <t>high or above_reference</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Seconds the cache was past its eviction trigger</t>
+          <t>Cache-fill samples above 95%</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -4294,17 +4294,17 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Seconds of each minute the cache was 95% full or more — past eviction_trigger, where operations are made to evict pages themselves before they may go on. Each of those seconds is latency added to whatever ran in it.</t>
+          <t>Share of valid samples with the signal strictly above 95 %, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/cache/bytes currently in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, every second</t>
+          <t>serverStatus/wiredTiger/cache/bytes currently in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>seconds of each minute above 95 %</t>
+          <t>valid-sample share strictly above 95 %, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Modified bytes not yet written, as a share of the configured cache, averaged over the minute. Eviction aims for 5%; at 20% (eviction_dirty_trigger) application threads are made to write dirty pages out themselves, and the seconds spent there are cache.dirty_over_trigger. Sustained high dirty cache is a write load the disk or the checkpoint is not keeping up with. From 7.0 the targets can be set in gigabytes at startup (wiredTigerEvictionDirtyTargetGB, wiredTigerEvictionDirtyMaxGB), which moves these lines.</t>
+          <t>Modified bytes not yet written, as a share of the configured cache, averaged over the minute. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/cache/tracked dirty bytes in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, every second</t>
+          <t>serverStatus/wiredTiger/cache/tracked dirty bytes in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>low ≤3 (fading to 6) · normal 6–8 (edges 3, 12) · high 12–18 (edges 8, 20) · over_trigger ≥21 (from 19)</t>
+          <t>low ≤3 (fading to 6) · normal 6–8 (edges 3, 12) · high 12–18 (edges 8, 20) · above_reference ≥21 (from 19)</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>high or over_trigger</t>
+          <t>high or above_reference</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Seconds the dirty cache was past its trigger</t>
+          <t>Dirty-cache samples above 20%</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -4438,17 +4438,17 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Seconds of each minute dirty data was 20% of the cache or more — past eviction_dirty_trigger, where operations are made to write dirty pages out themselves. Writes slow down in exactly these seconds, and the write tickets drain behind them.</t>
+          <t>Share of valid samples with the signal strictly above 20 %, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/cache/tracked dirty bytes in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, every second</t>
+          <t>serverStatus/wiredTiger/cache/tracked dirty bytes in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>seconds of each minute above 20 %</t>
+          <t>valid-sample share strictly above 20 %, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Pages a second that operations evicted themselves because the eviction workers could not keep the cache under its triggers. Each one is time a query or a write spent doing the storage engine's housekeeping instead of its own work.</t>
+          <t>Rate of pages evicted by application threads; where the version uses attempts and failures, the signal subtracts failure counts from attempt counts. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/wiredTiger/cache/pages evicted by application threads per second, in pages/s, every second</t>
+          <t>ΔserverStatus/wiredTiger/cache/pages evicted by application threads per second, in pages/s, at each available sample</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Pages a second that operations evicted themselves because the eviction workers could not keep the cache under its triggers — read from 8.0.16 as the attempts that did not fail. Each one is time a query or a write spent doing the storage engine's housekeeping instead of its own work.</t>
+          <t>Rate of pages evicted by application threads; where the version uses attempts and failures, the signal subtracts failure counts from attempt counts. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/wiredTiger/cache/page evict attempts by application threads − serverStatus/wiredTiger/cache/page evict failures by application threads per second, in pages/s, every second</t>
+          <t>ΔserverStatus/wiredTiger/cache/page evict attempts by application threads − serverStatus/wiredTiger/cache/page evict failures by application threads per second, in pages/s, at each available sample</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Milliseconds a second application threads spent evicting pages, added across every thread doing it (8.0 and later): 1000 is one operation spending the whole second on the storage engine's housekeeping. It is the latency cost of cache pressure, measured directly.</t>
+          <t>Application-thread eviction time counter advance per elapsed second, summed across threads, in milliseconds. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/wiredTiger/cache/application thread time evicting (usecs) per second × 0.001, in ms/s, every second</t>
+          <t>ΔserverStatus/wiredTiger/cache/application thread time evicting (usecs) per second × 0.001, in ms/s, at each available sample</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Megabytes a second WiredTiger read from disk into its cache. A step up with the same workload is a working set that stopped fitting, or a new scan reading what was never hot.</t>
+          <t>WiredTiger bytes-read-into-cache counter advance per elapsed second, scaled to MB/s. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/wiredTiger/cache/bytes read into cache per second × 1e-06, in MB/s, every second</t>
+          <t>ΔserverStatus/wiredTiger/cache/bytes read into cache per second × 1e-06, in MB/s, at each available sample</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
@@ -4790,17 +4790,17 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Seconds the most recent WiredTiger checkpoint took, read on the longest the minute reported. Checkpoints start every 60 seconds; one that takes longer runs back to back with the next, and dirty data accumulates behind it.</t>
+          <t>Duration recorded for the most recent WiredTiger checkpoint; the same completed-checkpoint value may appear in multiple samples. Minute summaries select the highest valid sample. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/transaction/transaction checkpoint most recent time (msecs) × 0.001, in s, every second</t>
+          <t>serverStatus/wiredTiger/transaction/transaction checkpoint most recent time (msecs) × 0.001, in s, at each available sample</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>the highest second of each minute</t>
+          <t>the highest valid sample of each minute</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -4862,17 +4862,17 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Seconds the most recent WiredTiger checkpoint took, read on the longest the minute reported. Checkpoints start every 60 seconds; one that takes longer runs back to back with the next, and dirty data accumulates behind it.</t>
+          <t>Duration recorded for the most recent WiredTiger checkpoint; the same completed-checkpoint value may appear in multiple samples. Minute summaries select the highest valid sample. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/checkpoint/most recent time (msecs) × 0.001, in s, every second</t>
+          <t>serverStatus/wiredTiger/checkpoint/most recent time (msecs) × 0.001, in s, at each available sample</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>the highest second of each minute</t>
+          <t>the highest valid sample of each minute</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Seconds spent checkpointing</t>
+          <t>Samples with checkpoint activity</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -4934,17 +4934,17 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Seconds of each minute a checkpoint was running. Checkpoints start every 60 seconds; near a full minute they run back to back, and dirty data piles up behind them.</t>
+          <t>Share of valid samples with the signal strictly above 0 running, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/transaction/transaction checkpoint currently running, in running, every second</t>
+          <t>serverStatus/wiredTiger/transaction/transaction checkpoint currently running, in running, at each available sample</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>seconds of each minute above 0 running</t>
+          <t>valid-sample share strictly above 0 running, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Seconds spent checkpointing</t>
+          <t>Samples with checkpoint activity</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -5006,17 +5006,17 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Seconds of each minute a checkpoint was running. Checkpoints start every 60 seconds; near a full minute they run back to back, and dirty data piles up behind them. From 7.1 WiredTiger reports a checkpoint progress state code instead (0 is inactive), read here as running whenever it is not zero.</t>
+          <t>Share of valid samples with the signal strictly above 0 state, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/checkpoint/progress state, in state, every second</t>
+          <t>serverStatus/wiredTiger/checkpoint/progress state, in state, at each available sample</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>seconds of each minute above 0 state</t>
+          <t>valid-sample share strictly above 0 state, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>WiredTiger data handles currently open: roughly one per collection and index in use. Climbing toward the open-file limit ends in "Too many open files" and a fatal WiredTiger panic; many collections and a periodic stats sweep across them is the usual way there.</t>
+          <t>Count reported by WiredTiger for currently open data handles. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/data-handle/connection data handles currently active, in handles, every second</t>
+          <t>serverStatus/wiredTiger/data-handle/connection data handles currently active, in handles, at each available sample</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Average milliseconds per read operation over each minute, from opLatencies: every microsecond spent on reads in the minute over every read that finished in it. Tailable getMores — a secondary or a change stream waiting for new oplog entries — count as reads and can hold this up on a healthy primary, so read it beside the slow query log. Minutes with fewer than sixty reads are left out.</t>
+          <t>Average milliseconds per read operation over each minute, from opLatencies: every microsecond spent on reads in the minute over every read that finished in it. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/opLatencies/reads/latency ÷ ΔserverStatus/opLatencies/reads/ops × 0.001, in ms, every second; minutes where the divisor sums to under 60 are left out</t>
+          <t>ΔserverStatus/opLatencies/reads/latency ÷ ΔserverStatus/opLatencies/reads/ops × 0.001, in ms, at each available sample; minutes where the divisor sums to under 60 are left out</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Average milliseconds per write operation over each minute, from opLatencies. Minutes with fewer than sixty writes are left out.</t>
+          <t>Average milliseconds per write operation over each minute, from opLatencies. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/opLatencies/writes/latency ÷ ΔserverStatus/opLatencies/writes/ops × 0.001, in ms, every second; minutes where the divisor sums to under 60 are left out</t>
+          <t>ΔserverStatus/opLatencies/writes/latency ÷ ΔserverStatus/opLatencies/writes/ops × 0.001, in ms, at each available sample; minutes where the divisor sums to under 60 are left out</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Average milliseconds per command over each minute, from opLatencies: everything that is not a CRUD read or write, aggregate included on most versions. Minutes with fewer than sixty commands are left out.</t>
+          <t>Ratio of command opLatencies counter advance to command operation-count advance, scaled to milliseconds per operation. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/opLatencies/commands/latency ÷ ΔserverStatus/opLatencies/commands/ops × 0.001, in ms, every second; minutes where the divisor sums to under 60 are left out</t>
+          <t>ΔserverStatus/opLatencies/commands/latency ÷ ΔserverStatus/opLatencies/commands/ops × 0.001, in ms, at each available sample; minutes where the divisor sums to under 60 are left out</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Every operation the server ran a second: queries, getMores, inserts, updates, deletes and commands. Shape only: a step is a new workload, a periodic burst a job or a batch.</t>
+          <t>Sum of query, getMore, insert, update, delete and command operation-counter rates. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Δ(serverStatus/opcounters/query + serverStatus/opcounters/getmore + serverStatus/opcounters/insert + serverStatus/opcounters/update + serverStatus/opcounters/delete + serverStatus/opcounters/command) per second, in ops/s, every second</t>
+          <t>Δ(serverStatus/opcounters/query + serverStatus/opcounters/getmore + serverStatus/opcounters/insert + serverStatus/opcounters/update + serverStatus/opcounters/delete + serverStatus/opcounters/command) per second, in ops/s, at each available sample</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
@@ -5418,12 +5418,12 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Inserts, updates and deletes a second. A burst of writes is what fills the dirty cache and stretches checkpoints a few minutes later.</t>
+          <t>Sum of insert, update and delete operation-counter rates. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Δ(serverStatus/opcounters/insert + serverStatus/opcounters/update + serverStatus/opcounters/delete) per second, in ops/s, every second</t>
+          <t>Δ(serverStatus/opcounters/insert + serverStatus/opcounters/update + serverStatus/opcounters/delete) per second, in ops/s, at each available sample</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Documents scanned for every document returned, across the server, over each minute. Near 1 queries are well indexed; in the hundreds or thousands something is scanning — a COLLSCAN or an index that does not cover the filter. The slow query log names which shape. Minutes that returned fewer than sixty documents are left out.</t>
+          <t>Ratio of documents-examined counter advance to documents-returned counter advance; it does not determine index suitability. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/metrics/queryExecutor/scannedObjects ÷ ΔserverStatus/metrics/document/returned, in ratio, every second; minutes where the divisor sums to under 60 are left out</t>
+          <t>ΔserverStatus/metrics/queryExecutor/scannedObjects ÷ ΔserverStatus/metrics/document/returned, in ratio, at each available sample; minutes where the divisor sums to under 60 are left out</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
@@ -5502,17 +5502,17 @@
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>efficient ≤2 (fading to 10) · loose 10–50 (edges 2, 100) · scanning 100–500 (edges 50, 1000) · very_poor ≥1000 (from 500)</t>
+          <t>low ≤2 (fading to 10) · moderate 10–50 (edges 2, 100) · high 100–500 (edges 50, 1000) · very_high ≥1000 (from 500)</t>
         </is>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>6 ratio → 50% efficient, 50% loose</t>
+          <t>6 ratio → 50% low, 50% moderate</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>scanning or very_poor</t>
+          <t>high or very_high</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Queries a second that read a whole collection (4.4 and later). Any steady rate on a large collection is a missing index; a burst is a report or a job.</t>
+          <t>Rate of the server's collection-scan counter. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/metrics/queryExecutor/collectionScans/total per second, in /s, every second</t>
+          <t>ΔserverStatus/metrics/queryExecutor/collectionScans/total per second, in /s, at each available sample</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>In-memory sorts</t>
+          <t>scanAndOrder counter rate</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Operations a second that sorted in memory because no index gave the order (scanAndOrder). They cost CPU and memory and fail past the sort limit.</t>
+          <t>Rate of the server's scanAndOrder counter. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/metrics/operation/scanAndOrder per second, in /s, every second</t>
+          <t>ΔserverStatus/metrics/operation/scanAndOrder per second, in /s, at each available sample</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Write conflicts a second: two operations updating the same document at once, one retrying. A burst means hot documents — a counter, a queue collection, a status field everyone updates.</t>
+          <t>Rate of the server's writeConflicts counter; retries, document identity and contention cause are not inferred from this counter. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/metrics/operation/writeConflicts per second, in /s, every second</t>
+          <t>ΔserverStatus/metrics/operation/writeConflicts per second, in /s, at each available sample</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Documents the TTL monitor deleted a second. TTL runs every minute; a large expiry deletes in bursts that load the disk and the oplog, and nightly expiry is a classic periodic cause.</t>
+          <t>Rate of documents reported deleted by the TTL monitor; collection identity, expiry backlog and latency impact are not inferred. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/metrics/ttl/deletedDocuments per second, in docs/s, every second</t>
+          <t>ΔserverStatus/metrics/ttl/deletedDocuments per second, in docs/s, at each available sample</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Cursors open on the server. A climb that never comes down is clients not closing or not exhausting cursors, and each one holds resources until it times out.</t>
+          <t>Count reported for currently open cursors. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/metrics/cursor/open/total, in cursors, every second</t>
+          <t>serverStatus/metrics/cursor/open/total, in cursors, at each available sample</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
@@ -5890,17 +5890,17 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>How many seconds each member's last applied write trailed the newest write any member had, as this node's replSetGetStatus reported them — one result per member, read on the worst second of each minute. A lagging member is usually short of disk or CPU, applying a large batch, or syncing across a slow link. Members are numbered by their place in the replica set config; an arbiter has no optime and gets no result. Before 6.0 optimeDate has one-second resolution.</t>
+          <t>Difference between each member's reported applied-write timestamp and the newest such timestamp in this node's replica-set status, scaled to seconds. Members without a timestamp have no result. optimeDate has one-second resolution. Minute summaries select the highest valid sample. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>newest of every replSetGetStatus/members/{i}/optimeDate − this one × 0.001, in s, every second</t>
+          <t>newest of every replSetGetStatus/members/{i}/optimeDate − this one × 0.001, in s, at each available sample</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>the highest second of each minute</t>
+          <t>the highest valid sample of each minute</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -5962,17 +5962,17 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>How many seconds each member's last applied write trailed the newest write any member had, as this node's replSetGetStatus reported them — one result per member, read on the worst second of each minute. A lagging member is usually short of disk or CPU, applying a large batch, or syncing across a slow link. Members are numbered by their place in the replica set config; an arbiter has no optime and gets no result.</t>
+          <t>Difference between each member's reported applied-write timestamp and the newest such timestamp in this node's replica-set status, scaled to seconds. Members without a timestamp have no result. Minute summaries select the highest valid sample. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>newest of every replSetGetStatus/members/{i}/lastAppliedWallTime − this one × 0.001, in s, every second</t>
+          <t>newest of every replSetGetStatus/members/{i}/lastAppliedWallTime − this one × 0.001, in s, at each available sample</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>the highest second of each minute</t>
+          <t>the highest valid sample of each minute</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -6034,17 +6034,17 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Seconds between the newest write this node applied and the newest write a majority had (lastAppliedWallTime less lastCommittedWallTime), read on the worst second of each minute. It is what w:majority writes wait for and what flow control throttles on; it grows when enough secondaries fall behind.</t>
+          <t>Difference between this node's lastAppliedWallTime and lastCommittedWallTime, scaled to seconds. Minute summaries select the highest valid sample. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>replSetGetStatus/optimes/lastAppliedWallTime − replSetGetStatus/optimes/lastCommittedWallTime × 0.001, in s, every second</t>
+          <t>replSetGetStatus/optimes/lastAppliedWallTime − replSetGetStatus/optimes/lastCommittedWallTime × 0.001, in s, at each available sample</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>the highest second of each minute</t>
+          <t>the highest valid sample of each minute</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Seconds flow control was engaged</t>
+          <t>Samples with flowControl.isLagged set</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -6106,17 +6106,17 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Seconds of each minute flow control reported the set lagged and limited writes on the primary. Any of it means writers were held back on purpose because the majority fell behind. Meaningful on a primary with flow control enabled; a secondary reports it unset.</t>
+          <t>Share of valid samples with the signal strictly above 0 lagged, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/flowControl/isLagged, in lagged, every second</t>
+          <t>serverStatus/flowControl/isLagged, in lagged, at each available sample</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>seconds of each minute above 0 lagged</t>
+          <t>valid-sample share strictly above 0 lagged, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -6178,12 +6178,12 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Milliseconds a second writes spent waiting for flow control tickets on this node, added across every write waiting.</t>
+          <t>Milliseconds a second writes spent waiting for flow control tickets on this node, added across every write waiting. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/flowControl/timeAcquiringMicros per second × 0.001, in ms/s, every second</t>
+          <t>ΔserverStatus/flowControl/timeAcquiringMicros per second × 0.001, in ms/s, at each available sample</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Operations a second this node applied from the oplog, as a secondary. A drop to nothing while the buffer holds entries is an applier that is stuck, not slow.</t>
+          <t>Rate of the node's oplog application operation counter. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/metrics/repl/apply/ops per second, in ops/s, every second</t>
+          <t>ΔserverStatus/metrics/repl/apply/ops per second, in ops/s, at each available sample</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Share of the replication apply buffer in use on a secondary, averaged over the minute. Full, the node fetches faster than it applies — it is behind on disk or CPU, not on the network.</t>
+          <t>Reported replication buffer bytes as a share of its reported maximum. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/metrics/repl/buffer/sizeBytes ÷ serverStatus/metrics/repl/buffer/maxSizeBytes × 100, in %, every second</t>
+          <t>serverStatus/metrics/repl/buffer/sizeBytes ÷ serverStatus/metrics/repl/buffer/maxSizeBytes × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Share of the replication apply buffer in use on a secondary, averaged over the minute. Full, the node fetches faster than it applies — it is behind on disk or CPU, not on the network.</t>
+          <t>Reported replication buffer bytes as a share of its reported maximum. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/metrics/repl/buffer/apply/sizeBytes ÷ serverStatus/metrics/repl/buffer/apply/maxSizeBytes × 100, in %, every second</t>
+          <t>serverStatus/metrics/repl/buffer/apply/sizeBytes ÷ serverStatus/metrics/repl/buffer/apply/maxSizeBytes × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Seconds the apply buffer was nearly full</t>
+          <t>Apply-buffer samples above 90%</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -6458,17 +6458,17 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Seconds of each minute the replication apply buffer was 90% full or more. While it is, the node stops fetching until the applier catches up.</t>
+          <t>Share of valid samples with the signal strictly above 90 %, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/metrics/repl/buffer/sizeBytes ÷ serverStatus/metrics/repl/buffer/maxSizeBytes × 100, in %, every second</t>
+          <t>serverStatus/metrics/repl/buffer/sizeBytes ÷ serverStatus/metrics/repl/buffer/maxSizeBytes × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>seconds of each minute above 90 %</t>
+          <t>valid-sample share strictly above 90 %, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -6520,7 +6520,7 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Seconds the apply buffer was nearly full</t>
+          <t>Apply-buffer samples above 90%</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -6530,17 +6530,17 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Seconds of each minute the replication apply buffer was 90% full or more. While it is, the node stops fetching until the applier catches up.</t>
+          <t>Share of valid samples with the signal strictly above 90 %, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/metrics/repl/buffer/apply/sizeBytes ÷ serverStatus/metrics/repl/buffer/apply/maxSizeBytes × 100, in %, every second</t>
+          <t>serverStatus/metrics/repl/buffer/apply/sizeBytes ÷ serverStatus/metrics/repl/buffer/apply/maxSizeBytes × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>seconds of each minute above 90 %</t>
+          <t>valid-sample share strictly above 90 %, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Connection limit in use</t>
+          <t>Current connections as a share of current plus available</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Open connections as a share of the most the server will accept (current over current plus available), averaged over the minute. Near the limit new clients are refused, and the log says so; the seconds spent there are connections.scarce.</t>
+          <t>Reported current connections divided by current plus available connections. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/connections/current ÷ (serverStatus/connections/current + serverStatus/connections/available) × 100, in %, every second</t>
+          <t>serverStatus/connections/current ÷ (serverStatus/connections/current + serverStatus/connections/available) × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Seconds with under 10% of connections left</t>
+          <t>Samples with under 10% of connections left</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -6674,17 +6674,17 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Seconds of each minute fewer than a tenth of the connection limit was still available. A reconnect storm can hit the limit for a few seconds and leave a minute mean looking calm.</t>
+          <t>Share of valid samples with the signal strictly below 10 % available, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/connections/available ÷ (serverStatus/connections/current + serverStatus/connections/available) × 100, in % available, every second</t>
+          <t>serverStatus/connections/available ÷ (serverStatus/connections/current + serverStatus/connections/available) × 100, in % available, at each available sample</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>seconds of each minute below 10 % available</t>
+          <t>valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -6746,12 +6746,12 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Connections opened a second. Drivers keep a pool, so a steady few is normal; tens a second is clients reconnecting, usually after timeouts, or an application opening a client per request. Each one costs the server a thread and an authentication.</t>
+          <t>Rate of the server's totalCreated connection counter. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/connections/totalCreated per second, in conn/s, every second</t>
+          <t>ΔserverStatus/connections/totalCreated per second, in conn/s, at each available sample</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
-          <t>quiet ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · storm ≥20 (from 10)</t>
+          <t>quiet ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · high ≥20 (from 10)</t>
         </is>
       </c>
       <c r="J88" s="4" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>storm</t>
+          <t>high</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Open connections doing nothing</t>
+          <t>Derived non-active connection count</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Open connections with no operation in progress, leaving out drivers' monitoring connections, averaged over the minute. Most of a client pool is idle on any healthy server, so the share says little; the count is what costs: every connection holds a thread and memory on the server. Thousands of them is a pool sized far past what the workload uses, or one that grew during a stall and never shrank.</t>
+          <t>Derived connection count: current plus awaitingTopologyChanges minus active; it is not evidence of unused client pools or a connection leak. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>(serverStatus/connections/current + serverStatus/connections/awaitingTopologyChanges) − serverStatus/connections/active, in conns, every second</t>
+          <t>(serverStatus/connections/current + serverStatus/connections/awaitingTopologyChanges) − serverStatus/connections/active, in conns, at each available sample</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>few ≤300 (fading to 800) · many 800–1500 (edges 300, 2500) · excessive ≥3000 (from 1500)</t>
+          <t>few ≤300 (fading to 800) · many 800–1500 (edges 300, 2500) · very_high ≥3000 (from 1500)</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>excessive</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Open connections with an operation in progress</t>
+          <t>Derived active-connection share</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -6890,17 +6890,17 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Share of the open connections with an operation in progress, leaving out drivers' monitoring connections, at the worst second of each minute. It stays low on a healthy server, because operations finish faster than they arrive; when the server stalls, every operation in flight waits and the share jumps. A pile-up here beside empty ticket pools or queued operations is a stall seen from the client side.</t>
+          <t>Derived active-connection share: active minus awaitingTopologyChanges divided by current connections. Minute summaries select the highest valid sample. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/connections/active − serverStatus/connections/awaitingTopologyChanges ÷ serverStatus/connections/current × 100, in %, every second; minutes where the divisor sums to under 3000 are left out</t>
+          <t>serverStatus/connections/active − serverStatus/connections/awaitingTopologyChanges ÷ serverStatus/connections/current × 100, in %, at each available sample; minutes where the divisor sums to under 3000 are left out</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>the highest second of each minute</t>
+          <t>the highest valid sample of each minute</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>calm ≤10 (fading to 25) · busy 25–40 (edges 10, 60) · piled_up ≥60 (from 40)</t>
+          <t>calm ≤10 (fading to 25) · busy 25–40 (edges 10, 60) · high ≥60 (from 40)</t>
         </is>
       </c>
       <c r="J90" s="4" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>piled_up</t>
+          <t>high</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Connections open to this node. Shape only — the limit is in connections.used. A step is a deployment or a pool resize; a climb that never comes down is a client leaking connections.</t>
+          <t>Count reported for currently open server connections. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/connections/current, in conns, every second</t>
+          <t>serverStatus/connections/current, in conns, at each available sample</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Connections mongod refused a second because it was at its limit (6.3 and later). Each one is a client error the application saw.</t>
+          <t>Rate of the server's rejected connection counter; client impact and rejection cause are not inferred. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/connections/rejected per second, in /s, every second</t>
+          <t>ΔserverStatus/connections/rejected per second, in /s, at each available sample</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">

--- a/docs/labels-review.xlsx
+++ b/docs/labels-review.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Labels" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Labels'!$A$1:$N$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Labels'!$A$1:$P$92</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -489,7 +489,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Labels summarize observations and guide navigation, not causes or fixes. The report uses fixed review references to group findings. Opening a label shows observed samples and timestamps, paired measurements and available matched-node logs. Legacy label IDs are stable identifiers, not proof of their implied condition.</t>
+          <t>Labels summarize observations and guide navigation, not causes or fixes. The report uses fixed review references to group findings. Opening a label shows observed samples and timestamps, paired measurements and available matched-node logs. A label ID names the measurement and the fixed number it is read against, not a condition of the server.</t>
         </is>
       </c>
     </row>
@@ -574,6 +574,30 @@
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Other labels read over the selected observed sample window; navigation links, not causal claims.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Where a fixed number comes from when it is a server default, such as a WiredTiger eviction trigger. The node's configured value is not read.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Applies</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>When the signal means what its title says: the role, setting or version it depends on, or how its instances are numbered.</t>
         </is>
       </c>
     </row>
@@ -588,7 +612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N92"/>
+  <dimension ref="A1:P92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -605,6 +629,8 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="50" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -678,6 +704,16 @@
           <t>Pairs with</t>
         </is>
       </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Applies</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -702,7 +738,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Share of host CPU counters recorded as user, nice, system, IRQ, soft IRQ or steal, excluding idle and iowait; steal is not process execution time. Host-wide memory or CPU counters do not establish a container's resource limit. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Share of host CPU counters recorded as user, nice, system, IRQ, soft IRQ or steal, excluding idle and iowait; steal is not process execution time. Host-wide memory or CPU counters do not establish a container's resource limit.</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -747,9 +783,11 @@
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>cpu.saturated, cpu.run_queue, cpu.iowait, cpu.kernel_share</t>
-        </is>
-      </c>
+          <t>cpu.busy_above_95, cpu.run_queue, cpu.iowait, cpu.kernel_share</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="inlineStr"/>
+      <c r="P2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -759,7 +797,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>cpu.saturated</t>
+          <t>cpu.busy_above_95</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -774,7 +812,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples with the signal strictly above 95 %, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Share of valid samples in which host CPU busy, computed as for cpu.busy, was strictly above 95 %, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -822,6 +860,8 @@
           <t>cpu.busy, cpu.run_queue</t>
         </is>
       </c>
+      <c r="O3" s="4" t="inlineStr"/>
+      <c r="P3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -846,7 +886,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Share of the machine's CPU idle with I/O outstanding. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Share of the machine's CPU idle with I/O outstanding.</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -894,6 +934,8 @@
           <t>disk.busy, disk.await, cpu.blocked</t>
         </is>
       </c>
+      <c r="O4" s="4" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -918,7 +960,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Share of the host CPU counters recorded as steal time. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Share of the host CPU counters recorded as steal time.</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -966,6 +1008,8 @@
           <t>cpu.busy</t>
         </is>
       </c>
+      <c r="O5" s="4" t="inlineStr"/>
+      <c r="P5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -990,7 +1034,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>System CPU as a share of user plus system. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>System CPU as a share of user plus system.</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -1038,6 +1082,8 @@
           <t>cpu.busy, cpu.context_switches</t>
         </is>
       </c>
+      <c r="O6" s="4" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1062,7 +1108,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Threads ready to run, per logical core, averaged over the minute. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Threads ready to run, per logical core, averaged over the minute.</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1107,9 +1153,11 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>cpu.busy, cpu.saturated</t>
-        </is>
-      </c>
+          <t>cpu.busy, cpu.busy_above_95</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr"/>
+      <c r="P7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1134,7 +1182,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Threads ready to run, per logical core, averaged over the minute. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Threads ready to run, per logical core, averaged over the minute.</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -1179,9 +1227,11 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>cpu.busy, cpu.saturated</t>
-        </is>
-      </c>
+          <t>cpu.busy, cpu.busy_above_95</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr"/>
+      <c r="P8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1206,7 +1256,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Host process count recorded in procs_blocked (uninterruptible sleep). Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Host process count recorded in procs_blocked (uninterruptible sleep).</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1254,6 +1304,8 @@
           <t>cpu.iowait, disk.await</t>
         </is>
       </c>
+      <c r="O9" s="4" t="inlineStr"/>
+      <c r="P9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1278,7 +1330,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Context switches a second, host-wide. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Context switches a second, host-wide.</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -1318,6 +1370,8 @@
           <t>connections.created, cpu.kernel_share</t>
         </is>
       </c>
+      <c r="O10" s="4" t="inlineStr"/>
+      <c r="P10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1342,7 +1396,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Share of the machine's memory not available to new allocations (MemTotal less MemAvailable, so the page cache the kernel can drop counts as free). Host-wide memory or CPU counters do not establish a container's resource limit. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Share of the machine's memory not available to new allocations (MemTotal less MemAvailable, so the page cache the kernel can drop counts as free). Host-wide memory or CPU counters do not establish a container's resource limit.</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1390,6 +1444,8 @@
           <t>memory.swap_used, memory.page_faults, memory.mongod_resident</t>
         </is>
       </c>
+      <c r="O11" s="4" t="inlineStr"/>
+      <c r="P11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1414,7 +1470,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Share of swap holding pages. Host-wide memory or CPU counters do not establish a container's resource limit. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Share of swap holding pages. Host-wide memory or CPU counters do not establish a container's resource limit.</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1462,6 +1518,8 @@
           <t>memory.used, memory.page_faults</t>
         </is>
       </c>
+      <c r="O12" s="4" t="inlineStr"/>
+      <c r="P12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1486,7 +1544,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Rate of the process's logged major-page-fault counter. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Rate of the process's logged major-page-fault counter.</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1534,6 +1592,8 @@
           <t>memory.used, memory.swap_used, disk.read_await</t>
         </is>
       </c>
+      <c r="O13" s="4" t="inlineStr"/>
+      <c r="P13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1558,7 +1618,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>mongod's resident memory as a share of the machine's. Host-wide memory or CPU counters do not establish a container's resource limit. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>mongod's resident memory as a share of the machine's. Host-wide memory or CPU counters do not establish a container's resource limit.</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -1606,6 +1666,8 @@
           <t>memory.used, memory.heap_outside_cache, memory.cache_of_ram</t>
         </is>
       </c>
+      <c r="O14" s="4" t="inlineStr"/>
+      <c r="P14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1630,7 +1692,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Difference between tcmalloc allocated bytes and bytes currently held in the WiredTiger cache; this is a derived estimate, not a complete inventory of non-cache allocations. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Difference between tcmalloc allocated bytes and bytes currently held in the WiredTiger cache; this is a derived estimate, not a complete inventory of non-cache allocations.</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1670,6 +1732,8 @@
           <t>connections.current, memory.allocator_free, cursors.open</t>
         </is>
       </c>
+      <c r="O15" s="4" t="inlineStr"/>
+      <c r="P15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1694,7 +1758,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Ratio of tcmalloc pageheap_free_bytes to heap_size; these counters do not describe every allocator cache. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Ratio of tcmalloc pageheap_free_bytes to heap_size; these counters do not describe every allocator cache.</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -1742,6 +1806,8 @@
           <t>memory.heap_outside_cache, memory.mongod_resident</t>
         </is>
       </c>
+      <c r="O16" s="4" t="inlineStr"/>
+      <c r="P16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1766,7 +1832,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>The configured cache as a share of the machine's memory. Host-wide memory or CPU counters do not establish a container's resource limit. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>The configured cache as a share of the machine's memory. Host-wide memory or CPU counters do not establish a container's resource limit.</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1814,6 +1880,8 @@
           <t>memory.used, memory.mongod_resident</t>
         </is>
       </c>
+      <c r="O17" s="4" t="inlineStr"/>
+      <c r="P17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1838,7 +1906,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Device io_time counter advance divided by elapsed time; a high value does not establish device capacity exhaustion. Device coverage depends on the block-device counters present in FTDC; logical devices may be absent. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Device io_time counter advance divided by elapsed time; a high value does not establish device capacity exhaustion. Device coverage depends on the block-device counters present in FTDC; logical devices may be absent.</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1883,7 +1951,13 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>disk.saturated, disk.await, disk.queue, disk.iops, disk.throughput</t>
+          <t>disk.busy_above_95, disk.await, disk.queue, disk.iops, disk.throughput</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr"/>
+      <c r="P18" s="4" t="inlineStr">
+        <is>
+          <t>A device that serves requests in parallel, such as an SSD, NVMe or network volume, can show io_time near 100 % with capacity to spare; disk.await shows whether requests waited. Device-mapper (dm-*) devices are not read by this tool; the disks under them are.</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1969,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>disk.saturated</t>
+          <t>disk.busy_above_95</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1910,7 +1984,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples with the signal strictly above 95 %, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Share of valid samples in which a device's io_time advanced by more than 95 % of the elapsed time, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1956,6 +2030,12 @@
       <c r="N19" s="4" t="inlineStr">
         <is>
           <t>disk.busy, disk.await, checkpoint.running</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr"/>
+      <c r="P19" s="4" t="inlineStr">
+        <is>
+          <t>A device that serves requests in parallel, such as an SSD, NVMe or network volume, can show io_time near 100 % with capacity to spare; disk.await shows whether requests waited. Device-mapper (dm-*) devices are not read by this tool; the disks under them are.</t>
         </is>
       </c>
     </row>
@@ -1982,7 +2062,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Average milliseconds a read or write took on each device, queueing included — what iostat calls await. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Average milliseconds a read or write took on each device, queueing included — what iostat calls await.</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -2030,6 +2110,8 @@
           <t>disk.busy, disk.queue, cpu.iowait</t>
         </is>
       </c>
+      <c r="O20" s="4" t="inlineStr"/>
+      <c r="P20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -2054,7 +2136,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Average milliseconds a read took on each device. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Average milliseconds a read took on each device.</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -2102,6 +2184,8 @@
           <t>cache.read_in, disk.busy</t>
         </is>
       </c>
+      <c r="O21" s="4" t="inlineStr"/>
+      <c r="P21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -2126,7 +2210,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Average milliseconds a write took on each device. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Average milliseconds a write took on each device.</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -2174,6 +2258,8 @@
           <t>checkpoint.duration, cache.dirty, tickets.write.scarce</t>
         </is>
       </c>
+      <c r="O22" s="4" t="inlineStr"/>
+      <c r="P22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -2198,7 +2284,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Average number of requests outstanding on each device over the minute (io_queued time over wall time). Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Average number of requests outstanding on each device over the minute (io_queued time over wall time).</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -2246,6 +2332,8 @@
           <t>disk.await, disk.busy</t>
         </is>
       </c>
+      <c r="O23" s="4" t="inlineStr"/>
+      <c r="P23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -2270,7 +2358,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Reads plus writes a second on each device. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Reads plus writes a second on each device.</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -2310,6 +2398,8 @@
           <t>disk.busy, disk.await</t>
         </is>
       </c>
+      <c r="O24" s="4" t="inlineStr"/>
+      <c r="P24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -2334,7 +2424,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Megabytes a second read plus written on each device (sectors are 512 bytes). Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Megabytes a second read plus written on each device (sectors are 512 bytes).</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -2374,6 +2464,8 @@
           <t>disk.busy, disk.iops</t>
         </is>
       </c>
+      <c r="O25" s="4" t="inlineStr"/>
+      <c r="P25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -2398,7 +2490,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Ratio of the host TCP RetransSegs counter advance to the OutSegs counter advance, across host connections. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Ratio of the host TCP RetransSegs counter advance to the OutSegs counter advance, across host connections.</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -2446,6 +2538,8 @@
           <t>repl.member_lag, net.resets</t>
         </is>
       </c>
+      <c r="O26" s="4" t="inlineStr"/>
+      <c r="P26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -2470,7 +2564,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Rate of the host TCP ListenOverflows counter; the counter does not identify a MongoDB connection or client outcome. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Rate of the host TCP ListenOverflows counter; the counter does not identify a MongoDB connection or client outcome.</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -2515,9 +2609,11 @@
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>connections.created, cpu.saturated</t>
-        </is>
-      </c>
+          <t>connections.created, cpu.busy_above_95</t>
+        </is>
+      </c>
+      <c r="O27" s="4" t="inlineStr"/>
+      <c r="P27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -2542,7 +2638,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Established connections reset a second, host-wide. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Established connections reset a second, host-wide.</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -2582,6 +2678,8 @@
           <t>connections.created, net.retransmit</t>
         </is>
       </c>
+      <c r="O28" s="4" t="inlineStr"/>
+      <c r="P28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -2606,7 +2704,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Sum of the server's bytesIn and bytesOut counter rates, scaled to MB/s. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Sum of the server's bytesIn and bytesOut counter rates, scaled to MB/s.</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -2646,6 +2744,8 @@
           <t>ops.total, net.retransmit</t>
         </is>
       </c>
+      <c r="O29" s="4" t="inlineStr"/>
+      <c r="P29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -2670,7 +2770,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Read tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Read tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -2716,6 +2816,12 @@
       <c r="N30" s="4" t="inlineStr">
         <is>
           <t>tickets.read.scarce, tickets.read.pool, tickets.read.wait, queue.readers</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr"/>
+      <c r="P30" s="4" t="inlineStr">
+        <is>
+          <t>From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2848,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples with the signal strictly below 10 % available, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Share of valid samples in which available read tickets were strictly below 10 % of the pool, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -2788,6 +2894,12 @@
       <c r="N31" s="4" t="inlineStr">
         <is>
           <t>tickets.read.empty, tickets.read.used, tickets.read.pool, tickets.read.wait</t>
+        </is>
+      </c>
+      <c r="O31" s="4" t="inlineStr"/>
+      <c r="P31" s="4" t="inlineStr">
+        <is>
+          <t>From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2926,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples with the signal strictly below 0.5 tickets left, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Share of valid samples in which fewer than 0.5 read tickets were available, that is none, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -2860,6 +2972,12 @@
       <c r="N32" s="4" t="inlineStr">
         <is>
           <t>tickets.read.used, tickets.read.scarce, tickets.read.pool, tickets.read.wait, queue.readers</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr"/>
+      <c r="P32" s="4" t="inlineStr">
+        <is>
+          <t>From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.</t>
         </is>
       </c>
     </row>
@@ -2886,7 +3004,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>How many read tickets the pool held, averaged over the minute. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>How many read tickets the pool held, averaged over the minute.</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -2926,6 +3044,8 @@
           <t>tickets.read.used, tickets.read.scarce</t>
         </is>
       </c>
+      <c r="O33" s="4" t="inlineStr"/>
+      <c r="P33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -2950,7 +3070,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Milliseconds a second operations spent queued for a read ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Milliseconds a second operations spent queued for a read ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it.</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -2998,6 +3118,8 @@
           <t>tickets.read.empty, tickets.read.scarce, queue.readers</t>
         </is>
       </c>
+      <c r="O34" s="4" t="inlineStr"/>
+      <c r="P34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -3022,7 +3144,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Read tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Read tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -3068,6 +3190,12 @@
       <c r="N35" s="4" t="inlineStr">
         <is>
           <t>tickets.read.scarce, tickets.read.pool, tickets.read.wait, queue.readers</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="inlineStr"/>
+      <c r="P35" s="4" t="inlineStr">
+        <is>
+          <t>From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3222,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples with the signal strictly below 10 % available, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Share of valid samples in which available read tickets were strictly below 10 % of the pool, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -3140,6 +3268,12 @@
       <c r="N36" s="4" t="inlineStr">
         <is>
           <t>tickets.read.empty, tickets.read.used, tickets.read.pool, tickets.read.wait</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="inlineStr"/>
+      <c r="P36" s="4" t="inlineStr">
+        <is>
+          <t>From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3300,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples with the signal strictly below 0.5 tickets left, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Share of valid samples in which fewer than 0.5 read tickets were available, that is none, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -3212,6 +3346,12 @@
       <c r="N37" s="4" t="inlineStr">
         <is>
           <t>tickets.read.used, tickets.read.scarce, tickets.read.pool, tickets.read.wait, queue.readers</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr"/>
+      <c r="P37" s="4" t="inlineStr">
+        <is>
+          <t>From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3378,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>How many read tickets the pool held, averaged over the minute. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>How many read tickets the pool held, averaged over the minute.</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -3278,6 +3418,8 @@
           <t>tickets.read.used, tickets.read.scarce</t>
         </is>
       </c>
+      <c r="O38" s="4" t="inlineStr"/>
+      <c r="P38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -3302,7 +3444,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Milliseconds a second operations spent queued for a read ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. The counter covers normal-priority operations, not exempt operations. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Milliseconds a second operations spent queued for a read ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. The counter covers normal-priority operations, not exempt operations.</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -3350,6 +3492,8 @@
           <t>tickets.read.empty, tickets.read.scarce, queue.readers</t>
         </is>
       </c>
+      <c r="O39" s="4" t="inlineStr"/>
+      <c r="P39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -3374,7 +3518,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Write tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Write tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -3420,6 +3564,12 @@
       <c r="N40" s="4" t="inlineStr">
         <is>
           <t>tickets.write.scarce, tickets.write.pool, tickets.write.wait, queue.writers</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr"/>
+      <c r="P40" s="4" t="inlineStr">
+        <is>
+          <t>From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.</t>
         </is>
       </c>
     </row>
@@ -3446,7 +3596,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples with the signal strictly below 10 % available, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Share of valid samples in which available write tickets were strictly below 10 % of the pool, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -3492,6 +3642,12 @@
       <c r="N41" s="4" t="inlineStr">
         <is>
           <t>tickets.write.empty, tickets.write.used, tickets.write.pool, tickets.write.wait</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr"/>
+      <c r="P41" s="4" t="inlineStr">
+        <is>
+          <t>From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3674,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples with the signal strictly below 0.5 tickets left, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Share of valid samples in which fewer than 0.5 write tickets were available, that is none, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -3564,6 +3720,12 @@
       <c r="N42" s="4" t="inlineStr">
         <is>
           <t>tickets.write.used, tickets.write.scarce, tickets.write.pool, tickets.write.wait, queue.writers</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="inlineStr"/>
+      <c r="P42" s="4" t="inlineStr">
+        <is>
+          <t>From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3752,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>How many write tickets the pool held, averaged over the minute. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>How many write tickets the pool held, averaged over the minute.</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -3630,6 +3792,8 @@
           <t>tickets.write.used, tickets.write.scarce</t>
         </is>
       </c>
+      <c r="O43" s="4" t="inlineStr"/>
+      <c r="P43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -3654,7 +3818,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Milliseconds a second operations spent queued for a write ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Milliseconds a second operations spent queued for a write ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it.</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -3702,6 +3866,8 @@
           <t>tickets.write.empty, tickets.write.scarce, queue.writers</t>
         </is>
       </c>
+      <c r="O44" s="4" t="inlineStr"/>
+      <c r="P44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -3726,7 +3892,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Write tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Write tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -3772,6 +3938,12 @@
       <c r="N45" s="4" t="inlineStr">
         <is>
           <t>tickets.write.scarce, tickets.write.pool, tickets.write.wait, queue.writers</t>
+        </is>
+      </c>
+      <c r="O45" s="4" t="inlineStr"/>
+      <c r="P45" s="4" t="inlineStr">
+        <is>
+          <t>From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.</t>
         </is>
       </c>
     </row>
@@ -3798,7 +3970,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples with the signal strictly below 10 % available, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Share of valid samples in which available write tickets were strictly below 10 % of the pool, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -3844,6 +4016,12 @@
       <c r="N46" s="4" t="inlineStr">
         <is>
           <t>tickets.write.empty, tickets.write.used, tickets.write.pool, tickets.write.wait</t>
+        </is>
+      </c>
+      <c r="O46" s="4" t="inlineStr"/>
+      <c r="P46" s="4" t="inlineStr">
+        <is>
+          <t>From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.</t>
         </is>
       </c>
     </row>
@@ -3870,7 +4048,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples with the signal strictly below 0.5 tickets left, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Share of valid samples in which fewer than 0.5 write tickets were available, that is none, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -3916,6 +4094,12 @@
       <c r="N47" s="4" t="inlineStr">
         <is>
           <t>tickets.write.used, tickets.write.scarce, tickets.write.pool, tickets.write.wait, queue.writers</t>
+        </is>
+      </c>
+      <c r="O47" s="4" t="inlineStr"/>
+      <c r="P47" s="4" t="inlineStr">
+        <is>
+          <t>From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.</t>
         </is>
       </c>
     </row>
@@ -3942,7 +4126,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>How many write tickets the pool held, averaged over the minute. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>How many write tickets the pool held, averaged over the minute.</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -3982,6 +4166,8 @@
           <t>tickets.write.used, tickets.write.scarce</t>
         </is>
       </c>
+      <c r="O48" s="4" t="inlineStr"/>
+      <c r="P48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -4006,7 +4192,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Milliseconds a second operations spent queued for a write ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. The counter covers normal-priority operations, not exempt operations. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Milliseconds a second operations spent queued for a write ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. The counter covers normal-priority operations, not exempt operations.</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -4054,6 +4240,8 @@
           <t>tickets.write.empty, tickets.write.scarce, queue.writers</t>
         </is>
       </c>
+      <c r="O49" s="4" t="inlineStr"/>
+      <c r="P49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -4078,7 +4266,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples with the signal strictly above 0 operations, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Share of valid samples in which globalLock.currentQueue.readers was above 0, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -4126,6 +4314,8 @@
           <t>tickets.read.empty, tickets.read.wait</t>
         </is>
       </c>
+      <c r="O50" s="4" t="inlineStr"/>
+      <c r="P50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -4150,7 +4340,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples with the signal strictly above 0 operations, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Share of valid samples in which globalLock.currentQueue.writers was above 0, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -4198,6 +4388,8 @@
           <t>tickets.write.empty, tickets.write.wait</t>
         </is>
       </c>
+      <c r="O51" s="4" t="inlineStr"/>
+      <c r="P51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -4222,7 +4414,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Bytes in the WiredTiger cache as a share of its configured size, averaged over the minute. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Bytes in the WiredTiger cache as a share of its configured size, averaged over the minute.</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -4267,9 +4459,15 @@
       </c>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>cache.over_trigger, cache.app_eviction, cache.read_in</t>
-        </is>
-      </c>
+          <t>cache.fill_above_95, cache.app_eviction, cache.read_in</t>
+        </is>
+      </c>
+      <c r="O52" s="4" t="inlineStr">
+        <is>
+          <t>95 %: WiredTiger default eviction_trigger; eviction_target defaults to 80 (configured value not read)</t>
+        </is>
+      </c>
+      <c r="P52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -4279,7 +4477,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>cache.over_trigger</t>
+          <t>cache.fill_above_95</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -4294,7 +4492,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples with the signal strictly above 95 %, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Share of valid samples in which WiredTiger cache bytes were strictly above 95 % of the configured cache size, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -4342,6 +4540,12 @@
           <t>cache.fill, cache.app_eviction, tickets.read.scarce</t>
         </is>
       </c>
+      <c r="O53" s="4" t="inlineStr">
+        <is>
+          <t>95 %: WiredTiger default eviction_trigger (configured value not read)</t>
+        </is>
+      </c>
+      <c r="P53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -4366,7 +4570,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Modified bytes not yet written, as a share of the configured cache, averaged over the minute. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Modified bytes not yet written, as a share of the configured cache, averaged over the minute.</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -4411,9 +4615,15 @@
       </c>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>cache.dirty_over_trigger, checkpoint.duration, disk.write_await, ops.writes</t>
-        </is>
-      </c>
+          <t>cache.dirty_above_20, checkpoint.duration, disk.write_await, ops.writes</t>
+        </is>
+      </c>
+      <c r="O54" s="4" t="inlineStr">
+        <is>
+          <t>20 %: WiredTiger default eviction_dirty_trigger; eviction_dirty_target defaults to 5 (configured value not read)</t>
+        </is>
+      </c>
+      <c r="P54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -4423,7 +4633,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>cache.dirty_over_trigger</t>
+          <t>cache.dirty_above_20</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -4438,7 +4648,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples with the signal strictly above 20 %, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Share of valid samples in which tracked dirty bytes were strictly above 20 % of the configured cache size, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -4486,6 +4696,12 @@
           <t>cache.dirty, checkpoint.running, tickets.write.scarce</t>
         </is>
       </c>
+      <c r="O55" s="4" t="inlineStr">
+        <is>
+          <t>20 %: WiredTiger default eviction_dirty_trigger (configured value not read)</t>
+        </is>
+      </c>
+      <c r="P55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -4510,7 +4726,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Rate of pages evicted by application threads; where the version uses attempts and failures, the signal subtracts failure counts from attempt counts. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Rate of pages evicted by application threads; where the version uses attempts and failures, the signal subtracts failure counts from attempt counts.</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -4555,9 +4771,11 @@
       </c>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>cache.over_trigger, cache.dirty_over_trigger</t>
-        </is>
-      </c>
+          <t>cache.fill_above_95, cache.dirty_above_20</t>
+        </is>
+      </c>
+      <c r="O56" s="4" t="inlineStr"/>
+      <c r="P56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -4582,7 +4800,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Rate of pages evicted by application threads; where the version uses attempts and failures, the signal subtracts failure counts from attempt counts. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Rate of pages evicted by application threads; where the version uses attempts and failures, the signal subtracts failure counts from attempt counts.</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -4627,9 +4845,11 @@
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>cache.over_trigger, cache.dirty_over_trigger, cache.app_eviction_time</t>
-        </is>
-      </c>
+          <t>cache.fill_above_95, cache.dirty_above_20, cache.app_eviction_time</t>
+        </is>
+      </c>
+      <c r="O57" s="4" t="inlineStr"/>
+      <c r="P57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -4654,7 +4874,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Application-thread eviction time counter advance per elapsed second, summed across threads, in milliseconds. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Application-thread eviction time counter advance per elapsed second, summed across threads, in milliseconds.</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -4699,9 +4919,11 @@
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>cache.app_eviction, cache.over_trigger, cache.dirty_over_trigger</t>
-        </is>
-      </c>
+          <t>cache.app_eviction, cache.fill_above_95, cache.dirty_above_20</t>
+        </is>
+      </c>
+      <c r="O58" s="4" t="inlineStr"/>
+      <c r="P58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -4726,7 +4948,7 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>WiredTiger bytes-read-into-cache counter advance per elapsed second, scaled to MB/s. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>WiredTiger bytes-read-into-cache counter advance per elapsed second, scaled to MB/s.</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -4766,6 +4988,8 @@
           <t>disk.read_await, query.collscans, cache.fill</t>
         </is>
       </c>
+      <c r="O59" s="4" t="inlineStr"/>
+      <c r="P59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -4790,7 +5014,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Duration recorded for the most recent WiredTiger checkpoint; the same completed-checkpoint value may appear in multiple samples. Minute summaries select the highest valid sample. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Duration recorded for the most recent WiredTiger checkpoint; the same completed-checkpoint value may appear in multiple samples. Minute summaries select the highest valid sample.</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -4838,6 +5062,12 @@
           <t>checkpoint.running, cache.dirty, disk.write_await</t>
         </is>
       </c>
+      <c r="O60" s="4" t="inlineStr">
+        <is>
+          <t>60 s: default checkpoint interval, storage.syncPeriodSecs (configured value not read)</t>
+        </is>
+      </c>
+      <c r="P60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -4862,7 +5092,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Duration recorded for the most recent WiredTiger checkpoint; the same completed-checkpoint value may appear in multiple samples. Minute summaries select the highest valid sample. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Duration recorded for the most recent WiredTiger checkpoint; the same completed-checkpoint value may appear in multiple samples. Minute summaries select the highest valid sample.</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -4910,6 +5140,12 @@
           <t>checkpoint.running, cache.dirty, disk.write_await</t>
         </is>
       </c>
+      <c r="O61" s="4" t="inlineStr">
+        <is>
+          <t>60 s: default checkpoint interval, storage.syncPeriodSecs (configured value not read)</t>
+        </is>
+      </c>
+      <c r="P61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -4934,7 +5170,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples with the signal strictly above 0 running, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Share of valid samples in which WiredTiger reported a checkpoint as currently running, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -4979,9 +5215,11 @@
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>checkpoint.duration, disk.saturated, cache.dirty</t>
-        </is>
-      </c>
+          <t>checkpoint.duration, disk.busy_above_95, cache.dirty</t>
+        </is>
+      </c>
+      <c r="O62" s="4" t="inlineStr"/>
+      <c r="P62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -5006,7 +5244,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples with the signal strictly above 0 state, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Share of valid samples in which WiredTiger's checkpoint progress state was non-zero, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -5051,7 +5289,13 @@
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>checkpoint.duration, disk.saturated, cache.dirty</t>
+          <t>checkpoint.duration, disk.busy_above_95, cache.dirty</t>
+        </is>
+      </c>
+      <c r="O63" s="4" t="inlineStr"/>
+      <c r="P63" s="4" t="inlineStr">
+        <is>
+          <t>The progress state's values are not decoded; any non-zero value is read as activity.</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5322,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Count reported by WiredTiger for currently open data handles. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Count reported by WiredTiger for currently open data handles.</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -5114,6 +5358,8 @@
         </is>
       </c>
       <c r="N64" s="4" t="inlineStr"/>
+      <c r="O64" s="4" t="inlineStr"/>
+      <c r="P64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -5138,7 +5384,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Average milliseconds per read operation over each minute, from opLatencies: every microsecond spent on reads in the minute over every read that finished in it. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Average milliseconds per read operation over each minute, from opLatencies: every microsecond spent on reads in the minute over every read that finished in it.</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -5183,9 +5429,11 @@
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.scarce, query.targeting, cache.over_trigger, disk.read_await</t>
-        </is>
-      </c>
+          <t>tickets.read.scarce, query.targeting, cache.fill_above_95, disk.read_await</t>
+        </is>
+      </c>
+      <c r="O65" s="4" t="inlineStr"/>
+      <c r="P65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -5210,7 +5458,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Average milliseconds per write operation over each minute, from opLatencies. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Average milliseconds per write operation over each minute, from opLatencies.</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -5255,9 +5503,11 @@
       </c>
       <c r="N66" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.scarce, cache.dirty_over_trigger, flow.throttled, repl.majority_lag</t>
-        </is>
-      </c>
+          <t>tickets.write.scarce, cache.dirty_above_20, flow.lagged, repl.majority_lag</t>
+        </is>
+      </c>
+      <c r="O66" s="4" t="inlineStr"/>
+      <c r="P66" s="4" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -5282,7 +5532,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Ratio of command opLatencies counter advance to command operation-count advance, scaled to milliseconds per operation. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Ratio of command opLatencies counter advance to command operation-count advance, scaled to milliseconds per operation.</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -5330,6 +5580,8 @@
           <t>tickets.read.scarce, query.targeting</t>
         </is>
       </c>
+      <c r="O67" s="4" t="inlineStr"/>
+      <c r="P67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -5354,7 +5606,7 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Sum of query, getMore, insert, update, delete and command operation-counter rates. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Sum of query, getMore, insert, update, delete and command operation-counter rates.</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -5394,6 +5646,8 @@
           <t>ops.writes, connections.current</t>
         </is>
       </c>
+      <c r="O68" s="4" t="inlineStr"/>
+      <c r="P68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -5418,7 +5672,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Sum of insert, update and delete operation-counter rates. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Sum of insert, update and delete operation-counter rates.</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -5458,6 +5712,8 @@
           <t>cache.dirty, checkpoint.duration</t>
         </is>
       </c>
+      <c r="O69" s="4" t="inlineStr"/>
+      <c r="P69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -5482,7 +5738,7 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Ratio of documents-examined counter advance to documents-returned counter advance; it does not determine index suitability. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Ratio of documents-examined counter advance to documents-returned counter advance; it does not determine index suitability.</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -5530,6 +5786,8 @@
           <t>query.collscans, cache.read_in, cpu.busy</t>
         </is>
       </c>
+      <c r="O70" s="4" t="inlineStr"/>
+      <c r="P70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -5554,7 +5812,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Rate of the server's collection-scan counter. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Rate of the server's collection-scan counter.</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -5602,6 +5860,8 @@
           <t>query.targeting, cache.read_in</t>
         </is>
       </c>
+      <c r="O71" s="4" t="inlineStr"/>
+      <c r="P71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -5611,7 +5871,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>query.in_memory_sorts</t>
+          <t>query.scan_and_order</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -5626,7 +5886,7 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Rate of the server's scanAndOrder counter. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Rate of the server's scanAndOrder counter.</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -5666,6 +5926,8 @@
           <t>query.targeting, memory.heap_outside_cache</t>
         </is>
       </c>
+      <c r="O72" s="4" t="inlineStr"/>
+      <c r="P72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -5690,7 +5952,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Rate of the server's writeConflicts counter; retries, document identity and contention cause are not inferred from this counter. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Rate of the server's writeConflicts counter; retries, document identity and contention cause are not inferred from this counter.</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -5738,6 +6000,8 @@
           <t>ops.writes, latency.writes</t>
         </is>
       </c>
+      <c r="O73" s="4" t="inlineStr"/>
+      <c r="P73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -5762,7 +6026,7 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Rate of documents reported deleted by the TTL monitor; collection identity, expiry backlog and latency impact are not inferred. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Rate of documents reported deleted by the TTL monitor; collection identity, expiry backlog and latency impact are not inferred.</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -5802,6 +6066,8 @@
           <t>cache.dirty, disk.write_await, repl.member_lag</t>
         </is>
       </c>
+      <c r="O74" s="4" t="inlineStr"/>
+      <c r="P74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -5826,7 +6092,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Count reported for currently open cursors. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Count reported for currently open cursors.</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -5866,6 +6132,8 @@
           <t>memory.heap_outside_cache, connections.current</t>
         </is>
       </c>
+      <c r="O75" s="4" t="inlineStr"/>
+      <c r="P75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -5890,7 +6158,7 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Difference between each member's reported applied-write timestamp and the newest such timestamp in this node's replica-set status, scaled to seconds. Members without a timestamp have no result. optimeDate has one-second resolution. Minute summaries select the highest valid sample. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Difference between each member's reported applied-write timestamp and the newest such timestamp in this node's replica-set status, scaled to seconds. Members without a timestamp have no result. optimeDate has one-second resolution. Minute summaries select the highest valid sample.</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -5935,7 +6203,13 @@
       </c>
       <c r="N76" s="4" t="inlineStr">
         <is>
-          <t>repl.majority_lag, flow.throttled, net.retransmit</t>
+          <t>repl.majority_lag, flow.lagged, net.retransmit</t>
+        </is>
+      </c>
+      <c r="O76" s="4" t="inlineStr"/>
+      <c r="P76" s="4" t="inlineStr">
+        <is>
+          <t>One result per entry of this node's replica-set status, numbered by position in that list; a position can name a different member after a reconfig. Lag is measured against the newest applied time among members, not against the primary, and a member that stopped reporting keeps its last time.</t>
         </is>
       </c>
     </row>
@@ -5962,7 +6236,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Difference between each member's reported applied-write timestamp and the newest such timestamp in this node's replica-set status, scaled to seconds. Members without a timestamp have no result. Minute summaries select the highest valid sample. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Difference between each member's reported applied-write timestamp and the newest such timestamp in this node's replica-set status, scaled to seconds. Members without a timestamp have no result. Minute summaries select the highest valid sample.</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -6007,7 +6281,13 @@
       </c>
       <c r="N77" s="4" t="inlineStr">
         <is>
-          <t>repl.majority_lag, flow.throttled, net.retransmit</t>
+          <t>repl.majority_lag, flow.lagged, net.retransmit</t>
+        </is>
+      </c>
+      <c r="O77" s="4" t="inlineStr"/>
+      <c r="P77" s="4" t="inlineStr">
+        <is>
+          <t>One result per entry of this node's replica-set status, numbered by position in that list; a position can name a different member after a reconfig. Lag is measured against the newest applied time among members, not against the primary, and a member that stopped reporting keeps its last time.</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6314,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Difference between this node's lastAppliedWallTime and lastCommittedWallTime, scaled to seconds. Minute summaries select the highest valid sample. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Difference between this node's lastAppliedWallTime and lastCommittedWallTime, scaled to seconds. Minute summaries select the highest valid sample.</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -6079,9 +6359,11 @@
       </c>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>repl.member_lag, flow.throttled, latency.writes</t>
-        </is>
-      </c>
+          <t>repl.member_lag, flow.lagged, latency.writes</t>
+        </is>
+      </c>
+      <c r="O78" s="4" t="inlineStr"/>
+      <c r="P78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -6091,7 +6373,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>flow.throttled</t>
+          <t>flow.lagged</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -6106,7 +6388,7 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples with the signal strictly above 0 lagged, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Share of valid samples in which flowControl.isLagged was set, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -6126,17 +6408,17 @@
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>off ≤0 (fading to 1) · intermittent 1–30 (edges 0, 48) · engaged ≥48 (from 30)</t>
+          <t>none ≤0 (fading to 1) · some 1–30 (edges 0, 48) · most ≥48 (from 30)</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>0.5 s/min → 50% off, 50% intermittent</t>
+          <t>0.5 s/min → 50% none, 50% some</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>engaged</t>
+          <t>most</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -6152,6 +6434,12 @@
       <c r="N79" s="4" t="inlineStr">
         <is>
           <t>flow.wait, repl.majority_lag, latency.writes</t>
+        </is>
+      </c>
+      <c r="O79" s="4" t="inlineStr"/>
+      <c r="P79" s="4" t="inlineStr">
+        <is>
+          <t>Set only on a primary with flow control enabled; a secondary, or a primary with flow control disabled, reports it unset. The flag records that the majority commit point lagged; time writers spent waiting for flow control is flow.wait.</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6466,7 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Milliseconds a second writes spent waiting for flow control tickets on this node, added across every write waiting. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Milliseconds a second writes spent waiting for flow control tickets on this node, added across every write waiting.</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -6223,9 +6511,11 @@
       </c>
       <c r="N80" s="4" t="inlineStr">
         <is>
-          <t>flow.throttled, latency.writes</t>
-        </is>
-      </c>
+          <t>flow.lagged, latency.writes</t>
+        </is>
+      </c>
+      <c r="O80" s="4" t="inlineStr"/>
+      <c r="P80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -6250,7 +6540,7 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Rate of the node's oplog application operation counter. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Rate of the node's oplog application operation counter.</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -6290,6 +6580,8 @@
           <t>repl.buffer_fill, repl.member_lag</t>
         </is>
       </c>
+      <c r="O81" s="4" t="inlineStr"/>
+      <c r="P81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -6314,7 +6606,7 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Reported replication buffer bytes as a share of its reported maximum. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Reported replication buffer bytes as a share of its reported maximum.</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -6362,6 +6654,8 @@
           <t>repl.buffer_full, repl.apply_rate, repl.member_lag</t>
         </is>
       </c>
+      <c r="O82" s="4" t="inlineStr"/>
+      <c r="P82" s="4" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -6386,7 +6680,7 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Reported replication buffer bytes as a share of its reported maximum. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Reported replication buffer bytes as a share of its reported maximum.</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -6434,6 +6728,8 @@
           <t>repl.buffer_full, repl.apply_rate, repl.member_lag</t>
         </is>
       </c>
+      <c r="O83" s="4" t="inlineStr"/>
+      <c r="P83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -6458,7 +6754,7 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples with the signal strictly above 90 %, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Share of valid samples in which replication buffer bytes were strictly above 90 % of the reported maximum, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -6506,6 +6802,8 @@
           <t>repl.buffer_fill, repl.apply_rate</t>
         </is>
       </c>
+      <c r="O84" s="4" t="inlineStr"/>
+      <c r="P84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -6530,7 +6828,7 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples with the signal strictly above 90 %, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Share of valid samples in which replication buffer bytes were strictly above 90 % of the reported maximum, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -6578,6 +6876,8 @@
           <t>repl.buffer_fill, repl.apply_rate</t>
         </is>
       </c>
+      <c r="O85" s="4" t="inlineStr"/>
+      <c r="P85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -6602,7 +6902,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Reported current connections divided by current plus available connections. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Reported current connections divided by current plus available connections.</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -6650,6 +6950,8 @@
           <t>connections.scarce, connections.created, connections.rejected</t>
         </is>
       </c>
+      <c r="O86" s="4" t="inlineStr"/>
+      <c r="P86" s="4" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -6674,7 +6976,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples with the signal strictly below 10 % available, normalized to a 60-second minute. This is a normalized sample share, not measured continuous elapsed duration; cadence and gaps must be checked. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Share of valid samples in which available connections were strictly below 10 % of current plus available, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -6722,6 +7024,8 @@
           <t>connections.used, connections.created, connections.rejected</t>
         </is>
       </c>
+      <c r="O87" s="4" t="inlineStr"/>
+      <c r="P87" s="4" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -6746,7 +7050,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Rate of the server's totalCreated connection counter. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Rate of the server's totalCreated connection counter.</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -6794,6 +7098,8 @@
           <t>connections.current, cpu.kernel_share, net.resets</t>
         </is>
       </c>
+      <c r="O88" s="4" t="inlineStr"/>
+      <c r="P88" s="4" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -6803,7 +7109,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>connections.idle</t>
+          <t>connections.non_active</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -6818,7 +7124,7 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Derived connection count: current plus awaitingTopologyChanges minus active; it is not evidence of unused client pools or a connection leak. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Derived connection count: current plus awaitingTopologyChanges minus active; it is not evidence of unused client pools or a connection leak.</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -6866,6 +7172,8 @@
           <t>connections.current, connections.created, connections.working_share, memory.heap_outside_cache</t>
         </is>
       </c>
+      <c r="O89" s="4" t="inlineStr"/>
+      <c r="P89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -6890,7 +7198,7 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Derived active-connection share: active minus awaitingTopologyChanges divided by current connections. Minute summaries select the highest valid sample. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Derived active-connection share: active minus awaitingTopologyChanges divided by current connections. Minute summaries select the highest valid sample.</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
@@ -6938,6 +7246,8 @@
           <t>tickets.read.empty, tickets.write.empty, queue.readers, queue.writers, connections.created</t>
         </is>
       </c>
+      <c r="O90" s="4" t="inlineStr"/>
+      <c r="P90" s="4" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -6962,7 +7272,7 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Count reported for currently open server connections. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Count reported for currently open server connections.</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -6999,9 +7309,11 @@
       </c>
       <c r="N91" s="4" t="inlineStr">
         <is>
-          <t>connections.idle, connections.created, memory.heap_outside_cache</t>
-        </is>
-      </c>
+          <t>connections.non_active, connections.created, memory.heap_outside_cache</t>
+        </is>
+      </c>
+      <c r="O91" s="4" t="inlineStr"/>
+      <c r="P91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -7026,7 +7338,7 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Rate of the server's rejected connection counter; client impact and rejection cause are not inferred. Minute summaries use a ratio of sums for ratio signals and a mean otherwise. Numeric bands and thresholds are fixed descriptive references, not a diagnosis or a discovered server limit. Paired labels are navigation links, not causal claims.</t>
+          <t>Rate of the server's rejected connection counter; client impact and rejection cause are not inferred.</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
@@ -7074,9 +7386,11 @@
           <t>connections.scarce, connections.used</t>
         </is>
       </c>
+      <c r="O92" s="4" t="inlineStr"/>
+      <c r="P92" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N92"/>
+  <autoFilter ref="A1:P92"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/labels-review.xlsx
+++ b/docs/labels-review.xlsx
@@ -9,9 +9,11 @@
   <sheets>
     <sheet name="How to read" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Labels" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Raw definitions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Labels'!$A$1:$P$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Labels'!$A$1:$U$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Raw definitions'!$A$1:$D$92</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -612,7 +614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P92"/>
+  <dimension ref="A1:U92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -628,9 +630,14 @@
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="34" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="50" customWidth="1" min="16" max="16"/>
+    <col width="36" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="34" customWidth="1" min="19" max="19"/>
+    <col width="30" customWidth="1" min="20" max="20"/>
+    <col width="50" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -701,15 +708,40 @@
       </c>
       <c r="N1" s="3" t="inlineStr">
         <is>
+          <t>Open with (requires supporting label)</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Signal threshold</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Signal unit</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
           <t>Pairs with</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Applies</t>
         </is>
@@ -781,13 +813,30 @@
           <t>10 %</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr"/>
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P2" s="4" t="n"/>
+      <c r="Q2" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="R2" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S2" s="4" t="inlineStr">
         <is>
           <t>cpu.busy_above_95, cpu.run_queue, cpu.iowait, cpu.kernel_share</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr"/>
-      <c r="P2" s="4" t="inlineStr"/>
+      <c r="T2" s="4" t="inlineStr"/>
+      <c r="U2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -855,13 +904,32 @@
           <t>3 s/min</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr"/>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>time_above</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>cpu.busy, cpu.run_queue</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr"/>
-      <c r="P3" s="4" t="inlineStr"/>
+      <c r="T3" s="4" t="inlineStr"/>
+      <c r="U3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -929,13 +997,30 @@
           <t>5 %</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="n"/>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
         <is>
           <t>disk.busy, disk.await, cpu.blocked</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr"/>
+      <c r="U4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1003,13 +1088,30 @@
           <t>3 %</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr"/>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="n"/>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
         <is>
           <t>cpu.busy</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr"/>
-      <c r="P5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr"/>
+      <c r="U5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1077,13 +1179,30 @@
           <t>10 %</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="n"/>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
         <is>
           <t>cpu.busy, cpu.context_switches</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr"/>
+      <c r="U6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1151,13 +1270,30 @@
           <t>0.3 per core</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr"/>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="n"/>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>per core</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
         <is>
           <t>cpu.busy, cpu.busy_above_95</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr"/>
-      <c r="P7" s="4" t="inlineStr"/>
+      <c r="T7" s="4" t="inlineStr"/>
+      <c r="U7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1225,13 +1361,30 @@
           <t>0.3 per core</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="n"/>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>per core</t>
+        </is>
+      </c>
+      <c r="R8" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S8" s="4" t="inlineStr">
         <is>
           <t>cpu.busy, cpu.busy_above_95</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr"/>
-      <c r="P8" s="4" t="inlineStr"/>
+      <c r="T8" s="4" t="inlineStr"/>
+      <c r="U8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1299,13 +1452,30 @@
           <t>2 threads</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr"/>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="n"/>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>threads</t>
+        </is>
+      </c>
+      <c r="R9" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S9" s="4" t="inlineStr">
         <is>
           <t>cpu.iowait, disk.await</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr"/>
-      <c r="P9" s="4" t="inlineStr"/>
+      <c r="T9" s="4" t="inlineStr"/>
+      <c r="U9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1365,13 +1535,30 @@
           <t>5000 /s</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="N10" s="4" t="inlineStr"/>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P10" s="4" t="n"/>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>/s</t>
+        </is>
+      </c>
+      <c r="R10" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S10" s="4" t="inlineStr">
         <is>
           <t>connections.created, cpu.kernel_share</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr"/>
-      <c r="P10" s="4" t="inlineStr"/>
+      <c r="T10" s="4" t="inlineStr"/>
+      <c r="U10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1439,13 +1626,30 @@
           <t>10 %</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr"/>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="n"/>
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="R11" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S11" s="4" t="inlineStr">
         <is>
           <t>memory.swap_used, memory.page_faults, memory.mongod_resident</t>
         </is>
       </c>
-      <c r="O11" s="4" t="inlineStr"/>
-      <c r="P11" s="4" t="inlineStr"/>
+      <c r="T11" s="4" t="inlineStr"/>
+      <c r="U11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1513,13 +1717,30 @@
           <t>5 %</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="N12" s="4" t="inlineStr"/>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P12" s="4" t="n"/>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="R12" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S12" s="4" t="inlineStr">
         <is>
           <t>memory.used, memory.page_faults</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr"/>
-      <c r="P12" s="4" t="inlineStr"/>
+      <c r="T12" s="4" t="inlineStr"/>
+      <c r="U12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1587,13 +1808,30 @@
           <t>10 /s</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="N13" s="4" t="inlineStr"/>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="n"/>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t>/s</t>
+        </is>
+      </c>
+      <c r="R13" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S13" s="4" t="inlineStr">
         <is>
           <t>memory.used, memory.swap_used, disk.read_await</t>
         </is>
       </c>
-      <c r="O13" s="4" t="inlineStr"/>
-      <c r="P13" s="4" t="inlineStr"/>
+      <c r="T13" s="4" t="inlineStr"/>
+      <c r="U13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1661,13 +1899,30 @@
           <t>5 %</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr"/>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P14" s="4" t="n"/>
+      <c r="Q14" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="R14" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S14" s="4" t="inlineStr">
         <is>
           <t>memory.used, memory.heap_outside_cache, memory.cache_of_ram</t>
         </is>
       </c>
-      <c r="O14" s="4" t="inlineStr"/>
-      <c r="P14" s="4" t="inlineStr"/>
+      <c r="T14" s="4" t="inlineStr"/>
+      <c r="U14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1727,13 +1982,30 @@
           <t>0.5 GiB</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="N15" s="4" t="inlineStr"/>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P15" s="4" t="n"/>
+      <c r="Q15" s="4" t="inlineStr">
+        <is>
+          <t>GiB</t>
+        </is>
+      </c>
+      <c r="R15" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S15" s="4" t="inlineStr">
         <is>
           <t>connections.current, memory.allocator_free, cursors.open</t>
         </is>
       </c>
-      <c r="O15" s="4" t="inlineStr"/>
-      <c r="P15" s="4" t="inlineStr"/>
+      <c r="T15" s="4" t="inlineStr"/>
+      <c r="U15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1801,13 +2073,30 @@
           <t>5 %</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr"/>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P16" s="4" t="n"/>
+      <c r="Q16" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="R16" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S16" s="4" t="inlineStr">
         <is>
           <t>memory.heap_outside_cache, memory.mongod_resident</t>
         </is>
       </c>
-      <c r="O16" s="4" t="inlineStr"/>
-      <c r="P16" s="4" t="inlineStr"/>
+      <c r="T16" s="4" t="inlineStr"/>
+      <c r="U16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1875,13 +2164,30 @@
           <t>5 %</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr"/>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P17" s="4" t="n"/>
+      <c r="Q17" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="R17" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S17" s="4" t="inlineStr">
         <is>
           <t>memory.used, memory.mongod_resident</t>
         </is>
       </c>
-      <c r="O17" s="4" t="inlineStr"/>
-      <c r="P17" s="4" t="inlineStr"/>
+      <c r="T17" s="4" t="inlineStr"/>
+      <c r="U17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1951,11 +2257,32 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
+          <t>disk.await</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P18" s="4" t="n"/>
+      <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="R18" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S18" s="4" t="inlineStr">
+        <is>
           <t>disk.busy_above_95, disk.await, disk.queue, disk.iops, disk.throughput</t>
         </is>
       </c>
-      <c r="O18" s="4" t="inlineStr"/>
-      <c r="P18" s="4" t="inlineStr">
+      <c r="T18" s="4" t="inlineStr"/>
+      <c r="U18" s="4" t="inlineStr">
         <is>
           <t>A device that serves requests in parallel, such as an SSD, NVMe or network volume, can show io_time near 100 % with capacity to spare; disk.await shows whether requests waited. Device-mapper (dm-*) devices are not read by this tool; the disks under them are.</t>
         </is>
@@ -2029,11 +2356,34 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
+          <t>disk.await</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>time_above</t>
+        </is>
+      </c>
+      <c r="P19" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q19" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="R19" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S19" s="4" t="inlineStr">
+        <is>
           <t>disk.busy, disk.await, checkpoint.running</t>
         </is>
       </c>
-      <c r="O19" s="4" t="inlineStr"/>
-      <c r="P19" s="4" t="inlineStr">
+      <c r="T19" s="4" t="inlineStr"/>
+      <c r="U19" s="4" t="inlineStr">
         <is>
           <t>A device that serves requests in parallel, such as an SSD, NVMe or network volume, can show io_time near 100 % with capacity to spare; disk.await shows whether requests waited. Device-mapper (dm-*) devices are not read by this tool; the disks under them are.</t>
         </is>
@@ -2105,13 +2455,30 @@
           <t>5 ms</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="N20" s="4" t="inlineStr"/>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P20" s="4" t="n"/>
+      <c r="Q20" s="4" t="inlineStr">
+        <is>
+          <t>ms</t>
+        </is>
+      </c>
+      <c r="R20" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S20" s="4" t="inlineStr">
         <is>
           <t>disk.busy, disk.queue, cpu.iowait</t>
         </is>
       </c>
-      <c r="O20" s="4" t="inlineStr"/>
-      <c r="P20" s="4" t="inlineStr"/>
+      <c r="T20" s="4" t="inlineStr"/>
+      <c r="U20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -2179,13 +2546,30 @@
           <t>5 ms</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="N21" s="4" t="inlineStr"/>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P21" s="4" t="n"/>
+      <c r="Q21" s="4" t="inlineStr">
+        <is>
+          <t>ms</t>
+        </is>
+      </c>
+      <c r="R21" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S21" s="4" t="inlineStr">
         <is>
           <t>cache.read_in, disk.busy</t>
         </is>
       </c>
-      <c r="O21" s="4" t="inlineStr"/>
-      <c r="P21" s="4" t="inlineStr"/>
+      <c r="T21" s="4" t="inlineStr"/>
+      <c r="U21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -2253,13 +2637,30 @@
           <t>5 ms</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="N22" s="4" t="inlineStr"/>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P22" s="4" t="n"/>
+      <c r="Q22" s="4" t="inlineStr">
+        <is>
+          <t>ms</t>
+        </is>
+      </c>
+      <c r="R22" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S22" s="4" t="inlineStr">
         <is>
           <t>checkpoint.duration, cache.dirty, tickets.write.scarce</t>
         </is>
       </c>
-      <c r="O22" s="4" t="inlineStr"/>
-      <c r="P22" s="4" t="inlineStr"/>
+      <c r="T22" s="4" t="inlineStr"/>
+      <c r="U22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -2329,11 +2730,32 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
+          <t>disk.await</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="n"/>
+      <c r="Q23" s="4" t="inlineStr">
+        <is>
+          <t>requests</t>
+        </is>
+      </c>
+      <c r="R23" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S23" s="4" t="inlineStr">
+        <is>
           <t>disk.await, disk.busy</t>
         </is>
       </c>
-      <c r="O23" s="4" t="inlineStr"/>
-      <c r="P23" s="4" t="inlineStr"/>
+      <c r="T23" s="4" t="inlineStr"/>
+      <c r="U23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -2393,13 +2815,30 @@
           <t>100 /s</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="N24" s="4" t="inlineStr"/>
+      <c r="O24" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P24" s="4" t="n"/>
+      <c r="Q24" s="4" t="inlineStr">
+        <is>
+          <t>/s</t>
+        </is>
+      </c>
+      <c r="R24" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S24" s="4" t="inlineStr">
         <is>
           <t>disk.busy, disk.await</t>
         </is>
       </c>
-      <c r="O24" s="4" t="inlineStr"/>
-      <c r="P24" s="4" t="inlineStr"/>
+      <c r="T24" s="4" t="inlineStr"/>
+      <c r="U24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -2459,13 +2898,30 @@
           <t>10 MB/s</t>
         </is>
       </c>
-      <c r="N25" s="4" t="inlineStr">
+      <c r="N25" s="4" t="inlineStr"/>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P25" s="4" t="n"/>
+      <c r="Q25" s="4" t="inlineStr">
+        <is>
+          <t>MB/s</t>
+        </is>
+      </c>
+      <c r="R25" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S25" s="4" t="inlineStr">
         <is>
           <t>disk.busy, disk.iops</t>
         </is>
       </c>
-      <c r="O25" s="4" t="inlineStr"/>
-      <c r="P25" s="4" t="inlineStr"/>
+      <c r="T25" s="4" t="inlineStr"/>
+      <c r="U25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -2533,13 +2989,30 @@
           <t>0.5 %</t>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="N26" s="4" t="inlineStr"/>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P26" s="4" t="n"/>
+      <c r="Q26" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="R26" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S26" s="4" t="inlineStr">
         <is>
           <t>repl.member_lag, net.resets</t>
         </is>
       </c>
-      <c r="O26" s="4" t="inlineStr"/>
-      <c r="P26" s="4" t="inlineStr"/>
+      <c r="T26" s="4" t="inlineStr"/>
+      <c r="U26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -2607,13 +3080,30 @@
           <t>0.1 /s</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr">
+      <c r="N27" s="4" t="inlineStr"/>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P27" s="4" t="n"/>
+      <c r="Q27" s="4" t="inlineStr">
+        <is>
+          <t>/s</t>
+        </is>
+      </c>
+      <c r="R27" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S27" s="4" t="inlineStr">
         <is>
           <t>connections.created, cpu.busy_above_95</t>
         </is>
       </c>
-      <c r="O27" s="4" t="inlineStr"/>
-      <c r="P27" s="4" t="inlineStr"/>
+      <c r="T27" s="4" t="inlineStr"/>
+      <c r="U27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -2673,13 +3163,30 @@
           <t>5 /s</t>
         </is>
       </c>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="N28" s="4" t="inlineStr"/>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P28" s="4" t="n"/>
+      <c r="Q28" s="4" t="inlineStr">
+        <is>
+          <t>/s</t>
+        </is>
+      </c>
+      <c r="R28" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S28" s="4" t="inlineStr">
         <is>
           <t>connections.created, net.retransmit</t>
         </is>
       </c>
-      <c r="O28" s="4" t="inlineStr"/>
-      <c r="P28" s="4" t="inlineStr"/>
+      <c r="T28" s="4" t="inlineStr"/>
+      <c r="U28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -2739,13 +3246,30 @@
           <t>5 MB/s</t>
         </is>
       </c>
-      <c r="N29" s="4" t="inlineStr">
+      <c r="N29" s="4" t="inlineStr"/>
+      <c r="O29" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P29" s="4" t="n"/>
+      <c r="Q29" s="4" t="inlineStr">
+        <is>
+          <t>MB/s</t>
+        </is>
+      </c>
+      <c r="R29" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S29" s="4" t="inlineStr">
         <is>
           <t>ops.total, net.retransmit</t>
         </is>
       </c>
-      <c r="O29" s="4" t="inlineStr"/>
-      <c r="P29" s="4" t="inlineStr"/>
+      <c r="T29" s="4" t="inlineStr"/>
+      <c r="U29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -2813,13 +3337,30 @@
           <t>10 %</t>
         </is>
       </c>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="N30" s="4" t="inlineStr"/>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P30" s="4" t="n"/>
+      <c r="Q30" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="R30" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S30" s="4" t="inlineStr">
         <is>
           <t>tickets.read.scarce, tickets.read.pool, tickets.read.wait, queue.readers</t>
         </is>
       </c>
-      <c r="O30" s="4" t="inlineStr"/>
-      <c r="P30" s="4" t="inlineStr">
+      <c r="T30" s="4" t="inlineStr"/>
+      <c r="U30" s="4" t="inlineStr">
         <is>
           <t>From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.</t>
         </is>
@@ -2891,13 +3432,32 @@
           <t>3 s/min</t>
         </is>
       </c>
-      <c r="N31" s="4" t="inlineStr">
+      <c r="N31" s="4" t="inlineStr"/>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>time_below</t>
+        </is>
+      </c>
+      <c r="P31" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q31" s="4" t="inlineStr">
+        <is>
+          <t>% available</t>
+        </is>
+      </c>
+      <c r="R31" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S31" s="4" t="inlineStr">
         <is>
           <t>tickets.read.empty, tickets.read.used, tickets.read.pool, tickets.read.wait</t>
         </is>
       </c>
-      <c r="O31" s="4" t="inlineStr"/>
-      <c r="P31" s="4" t="inlineStr">
+      <c r="T31" s="4" t="inlineStr"/>
+      <c r="U31" s="4" t="inlineStr">
         <is>
           <t>From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.</t>
         </is>
@@ -2969,13 +3529,32 @@
           <t>3 s/min</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="N32" s="4" t="inlineStr"/>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>time_below</t>
+        </is>
+      </c>
+      <c r="P32" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q32" s="4" t="inlineStr">
+        <is>
+          <t>tickets left</t>
+        </is>
+      </c>
+      <c r="R32" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S32" s="4" t="inlineStr">
         <is>
           <t>tickets.read.used, tickets.read.scarce, tickets.read.pool, tickets.read.wait, queue.readers</t>
         </is>
       </c>
-      <c r="O32" s="4" t="inlineStr"/>
-      <c r="P32" s="4" t="inlineStr">
+      <c r="T32" s="4" t="inlineStr"/>
+      <c r="U32" s="4" t="inlineStr">
         <is>
           <t>From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.</t>
         </is>
@@ -3039,13 +3618,30 @@
           <t>4 tickets</t>
         </is>
       </c>
-      <c r="N33" s="4" t="inlineStr">
+      <c r="N33" s="4" t="inlineStr"/>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P33" s="4" t="n"/>
+      <c r="Q33" s="4" t="inlineStr">
+        <is>
+          <t>tickets</t>
+        </is>
+      </c>
+      <c r="R33" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S33" s="4" t="inlineStr">
         <is>
           <t>tickets.read.used, tickets.read.scarce</t>
         </is>
       </c>
-      <c r="O33" s="4" t="inlineStr"/>
-      <c r="P33" s="4" t="inlineStr"/>
+      <c r="T33" s="4" t="inlineStr"/>
+      <c r="U33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -3113,13 +3709,30 @@
           <t>10 ms/s</t>
         </is>
       </c>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="N34" s="4" t="inlineStr"/>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P34" s="4" t="n"/>
+      <c r="Q34" s="4" t="inlineStr">
+        <is>
+          <t>ms/s</t>
+        </is>
+      </c>
+      <c r="R34" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S34" s="4" t="inlineStr">
         <is>
           <t>tickets.read.empty, tickets.read.scarce, queue.readers</t>
         </is>
       </c>
-      <c r="O34" s="4" t="inlineStr"/>
-      <c r="P34" s="4" t="inlineStr"/>
+      <c r="T34" s="4" t="inlineStr"/>
+      <c r="U34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -3187,13 +3800,30 @@
           <t>10 %</t>
         </is>
       </c>
-      <c r="N35" s="4" t="inlineStr">
+      <c r="N35" s="4" t="inlineStr"/>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P35" s="4" t="n"/>
+      <c r="Q35" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="R35" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S35" s="4" t="inlineStr">
         <is>
           <t>tickets.read.scarce, tickets.read.pool, tickets.read.wait, queue.readers</t>
         </is>
       </c>
-      <c r="O35" s="4" t="inlineStr"/>
-      <c r="P35" s="4" t="inlineStr">
+      <c r="T35" s="4" t="inlineStr"/>
+      <c r="U35" s="4" t="inlineStr">
         <is>
           <t>From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.</t>
         </is>
@@ -3265,13 +3895,32 @@
           <t>3 s/min</t>
         </is>
       </c>
-      <c r="N36" s="4" t="inlineStr">
+      <c r="N36" s="4" t="inlineStr"/>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
+          <t>time_below</t>
+        </is>
+      </c>
+      <c r="P36" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q36" s="4" t="inlineStr">
+        <is>
+          <t>% available</t>
+        </is>
+      </c>
+      <c r="R36" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S36" s="4" t="inlineStr">
         <is>
           <t>tickets.read.empty, tickets.read.used, tickets.read.pool, tickets.read.wait</t>
         </is>
       </c>
-      <c r="O36" s="4" t="inlineStr"/>
-      <c r="P36" s="4" t="inlineStr">
+      <c r="T36" s="4" t="inlineStr"/>
+      <c r="U36" s="4" t="inlineStr">
         <is>
           <t>From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.</t>
         </is>
@@ -3343,13 +3992,32 @@
           <t>3 s/min</t>
         </is>
       </c>
-      <c r="N37" s="4" t="inlineStr">
+      <c r="N37" s="4" t="inlineStr"/>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>time_below</t>
+        </is>
+      </c>
+      <c r="P37" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q37" s="4" t="inlineStr">
+        <is>
+          <t>tickets left</t>
+        </is>
+      </c>
+      <c r="R37" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S37" s="4" t="inlineStr">
         <is>
           <t>tickets.read.used, tickets.read.scarce, tickets.read.pool, tickets.read.wait, queue.readers</t>
         </is>
       </c>
-      <c r="O37" s="4" t="inlineStr"/>
-      <c r="P37" s="4" t="inlineStr">
+      <c r="T37" s="4" t="inlineStr"/>
+      <c r="U37" s="4" t="inlineStr">
         <is>
           <t>From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.</t>
         </is>
@@ -3413,13 +4081,30 @@
           <t>4 tickets</t>
         </is>
       </c>
-      <c r="N38" s="4" t="inlineStr">
+      <c r="N38" s="4" t="inlineStr"/>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P38" s="4" t="n"/>
+      <c r="Q38" s="4" t="inlineStr">
+        <is>
+          <t>tickets</t>
+        </is>
+      </c>
+      <c r="R38" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S38" s="4" t="inlineStr">
         <is>
           <t>tickets.read.used, tickets.read.scarce</t>
         </is>
       </c>
-      <c r="O38" s="4" t="inlineStr"/>
-      <c r="P38" s="4" t="inlineStr"/>
+      <c r="T38" s="4" t="inlineStr"/>
+      <c r="U38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -3487,13 +4172,30 @@
           <t>10 ms/s</t>
         </is>
       </c>
-      <c r="N39" s="4" t="inlineStr">
+      <c r="N39" s="4" t="inlineStr"/>
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P39" s="4" t="n"/>
+      <c r="Q39" s="4" t="inlineStr">
+        <is>
+          <t>ms/s</t>
+        </is>
+      </c>
+      <c r="R39" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S39" s="4" t="inlineStr">
         <is>
           <t>tickets.read.empty, tickets.read.scarce, queue.readers</t>
         </is>
       </c>
-      <c r="O39" s="4" t="inlineStr"/>
-      <c r="P39" s="4" t="inlineStr"/>
+      <c r="T39" s="4" t="inlineStr"/>
+      <c r="U39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -3561,13 +4263,30 @@
           <t>10 %</t>
         </is>
       </c>
-      <c r="N40" s="4" t="inlineStr">
+      <c r="N40" s="4" t="inlineStr"/>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P40" s="4" t="n"/>
+      <c r="Q40" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="R40" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S40" s="4" t="inlineStr">
         <is>
           <t>tickets.write.scarce, tickets.write.pool, tickets.write.wait, queue.writers</t>
         </is>
       </c>
-      <c r="O40" s="4" t="inlineStr"/>
-      <c r="P40" s="4" t="inlineStr">
+      <c r="T40" s="4" t="inlineStr"/>
+      <c r="U40" s="4" t="inlineStr">
         <is>
           <t>From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.</t>
         </is>
@@ -3639,13 +4358,32 @@
           <t>3 s/min</t>
         </is>
       </c>
-      <c r="N41" s="4" t="inlineStr">
+      <c r="N41" s="4" t="inlineStr"/>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>time_below</t>
+        </is>
+      </c>
+      <c r="P41" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q41" s="4" t="inlineStr">
+        <is>
+          <t>% available</t>
+        </is>
+      </c>
+      <c r="R41" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S41" s="4" t="inlineStr">
         <is>
           <t>tickets.write.empty, tickets.write.used, tickets.write.pool, tickets.write.wait</t>
         </is>
       </c>
-      <c r="O41" s="4" t="inlineStr"/>
-      <c r="P41" s="4" t="inlineStr">
+      <c r="T41" s="4" t="inlineStr"/>
+      <c r="U41" s="4" t="inlineStr">
         <is>
           <t>From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.</t>
         </is>
@@ -3717,13 +4455,32 @@
           <t>3 s/min</t>
         </is>
       </c>
-      <c r="N42" s="4" t="inlineStr">
+      <c r="N42" s="4" t="inlineStr"/>
+      <c r="O42" s="4" t="inlineStr">
+        <is>
+          <t>time_below</t>
+        </is>
+      </c>
+      <c r="P42" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q42" s="4" t="inlineStr">
+        <is>
+          <t>tickets left</t>
+        </is>
+      </c>
+      <c r="R42" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S42" s="4" t="inlineStr">
         <is>
           <t>tickets.write.used, tickets.write.scarce, tickets.write.pool, tickets.write.wait, queue.writers</t>
         </is>
       </c>
-      <c r="O42" s="4" t="inlineStr"/>
-      <c r="P42" s="4" t="inlineStr">
+      <c r="T42" s="4" t="inlineStr"/>
+      <c r="U42" s="4" t="inlineStr">
         <is>
           <t>From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.</t>
         </is>
@@ -3787,13 +4544,30 @@
           <t>4 tickets</t>
         </is>
       </c>
-      <c r="N43" s="4" t="inlineStr">
+      <c r="N43" s="4" t="inlineStr"/>
+      <c r="O43" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P43" s="4" t="n"/>
+      <c r="Q43" s="4" t="inlineStr">
+        <is>
+          <t>tickets</t>
+        </is>
+      </c>
+      <c r="R43" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S43" s="4" t="inlineStr">
         <is>
           <t>tickets.write.used, tickets.write.scarce</t>
         </is>
       </c>
-      <c r="O43" s="4" t="inlineStr"/>
-      <c r="P43" s="4" t="inlineStr"/>
+      <c r="T43" s="4" t="inlineStr"/>
+      <c r="U43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -3861,13 +4635,30 @@
           <t>10 ms/s</t>
         </is>
       </c>
-      <c r="N44" s="4" t="inlineStr">
+      <c r="N44" s="4" t="inlineStr"/>
+      <c r="O44" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P44" s="4" t="n"/>
+      <c r="Q44" s="4" t="inlineStr">
+        <is>
+          <t>ms/s</t>
+        </is>
+      </c>
+      <c r="R44" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S44" s="4" t="inlineStr">
         <is>
           <t>tickets.write.empty, tickets.write.scarce, queue.writers</t>
         </is>
       </c>
-      <c r="O44" s="4" t="inlineStr"/>
-      <c r="P44" s="4" t="inlineStr"/>
+      <c r="T44" s="4" t="inlineStr"/>
+      <c r="U44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -3935,13 +4726,30 @@
           <t>10 %</t>
         </is>
       </c>
-      <c r="N45" s="4" t="inlineStr">
+      <c r="N45" s="4" t="inlineStr"/>
+      <c r="O45" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P45" s="4" t="n"/>
+      <c r="Q45" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="R45" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S45" s="4" t="inlineStr">
         <is>
           <t>tickets.write.scarce, tickets.write.pool, tickets.write.wait, queue.writers</t>
         </is>
       </c>
-      <c r="O45" s="4" t="inlineStr"/>
-      <c r="P45" s="4" t="inlineStr">
+      <c r="T45" s="4" t="inlineStr"/>
+      <c r="U45" s="4" t="inlineStr">
         <is>
           <t>From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.</t>
         </is>
@@ -4013,13 +4821,32 @@
           <t>3 s/min</t>
         </is>
       </c>
-      <c r="N46" s="4" t="inlineStr">
+      <c r="N46" s="4" t="inlineStr"/>
+      <c r="O46" s="4" t="inlineStr">
+        <is>
+          <t>time_below</t>
+        </is>
+      </c>
+      <c r="P46" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q46" s="4" t="inlineStr">
+        <is>
+          <t>% available</t>
+        </is>
+      </c>
+      <c r="R46" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S46" s="4" t="inlineStr">
         <is>
           <t>tickets.write.empty, tickets.write.used, tickets.write.pool, tickets.write.wait</t>
         </is>
       </c>
-      <c r="O46" s="4" t="inlineStr"/>
-      <c r="P46" s="4" t="inlineStr">
+      <c r="T46" s="4" t="inlineStr"/>
+      <c r="U46" s="4" t="inlineStr">
         <is>
           <t>From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.</t>
         </is>
@@ -4091,13 +4918,32 @@
           <t>3 s/min</t>
         </is>
       </c>
-      <c r="N47" s="4" t="inlineStr">
+      <c r="N47" s="4" t="inlineStr"/>
+      <c r="O47" s="4" t="inlineStr">
+        <is>
+          <t>time_below</t>
+        </is>
+      </c>
+      <c r="P47" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q47" s="4" t="inlineStr">
+        <is>
+          <t>tickets left</t>
+        </is>
+      </c>
+      <c r="R47" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S47" s="4" t="inlineStr">
         <is>
           <t>tickets.write.used, tickets.write.scarce, tickets.write.pool, tickets.write.wait, queue.writers</t>
         </is>
       </c>
-      <c r="O47" s="4" t="inlineStr"/>
-      <c r="P47" s="4" t="inlineStr">
+      <c r="T47" s="4" t="inlineStr"/>
+      <c r="U47" s="4" t="inlineStr">
         <is>
           <t>From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.</t>
         </is>
@@ -4161,13 +5007,30 @@
           <t>4 tickets</t>
         </is>
       </c>
-      <c r="N48" s="4" t="inlineStr">
+      <c r="N48" s="4" t="inlineStr"/>
+      <c r="O48" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P48" s="4" t="n"/>
+      <c r="Q48" s="4" t="inlineStr">
+        <is>
+          <t>tickets</t>
+        </is>
+      </c>
+      <c r="R48" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S48" s="4" t="inlineStr">
         <is>
           <t>tickets.write.used, tickets.write.scarce</t>
         </is>
       </c>
-      <c r="O48" s="4" t="inlineStr"/>
-      <c r="P48" s="4" t="inlineStr"/>
+      <c r="T48" s="4" t="inlineStr"/>
+      <c r="U48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -4235,13 +5098,30 @@
           <t>10 ms/s</t>
         </is>
       </c>
-      <c r="N49" s="4" t="inlineStr">
+      <c r="N49" s="4" t="inlineStr"/>
+      <c r="O49" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P49" s="4" t="n"/>
+      <c r="Q49" s="4" t="inlineStr">
+        <is>
+          <t>ms/s</t>
+        </is>
+      </c>
+      <c r="R49" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S49" s="4" t="inlineStr">
         <is>
           <t>tickets.write.empty, tickets.write.scarce, queue.writers</t>
         </is>
       </c>
-      <c r="O49" s="4" t="inlineStr"/>
-      <c r="P49" s="4" t="inlineStr"/>
+      <c r="T49" s="4" t="inlineStr"/>
+      <c r="U49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -4309,13 +5189,32 @@
           <t>3 s/min</t>
         </is>
       </c>
-      <c r="N50" s="4" t="inlineStr">
+      <c r="N50" s="4" t="inlineStr"/>
+      <c r="O50" s="4" t="inlineStr">
+        <is>
+          <t>time_above</t>
+        </is>
+      </c>
+      <c r="P50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="4" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="R50" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S50" s="4" t="inlineStr">
         <is>
           <t>tickets.read.empty, tickets.read.wait</t>
         </is>
       </c>
-      <c r="O50" s="4" t="inlineStr"/>
-      <c r="P50" s="4" t="inlineStr"/>
+      <c r="T50" s="4" t="inlineStr"/>
+      <c r="U50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -4383,13 +5282,32 @@
           <t>3 s/min</t>
         </is>
       </c>
-      <c r="N51" s="4" t="inlineStr">
+      <c r="N51" s="4" t="inlineStr"/>
+      <c r="O51" s="4" t="inlineStr">
+        <is>
+          <t>time_above</t>
+        </is>
+      </c>
+      <c r="P51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="4" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="R51" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S51" s="4" t="inlineStr">
         <is>
           <t>tickets.write.empty, tickets.write.wait</t>
         </is>
       </c>
-      <c r="O51" s="4" t="inlineStr"/>
-      <c r="P51" s="4" t="inlineStr"/>
+      <c r="T51" s="4" t="inlineStr"/>
+      <c r="U51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -4457,17 +5375,34 @@
           <t>5 %</t>
         </is>
       </c>
-      <c r="N52" s="4" t="inlineStr">
+      <c r="N52" s="4" t="inlineStr"/>
+      <c r="O52" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P52" s="4" t="n"/>
+      <c r="Q52" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="R52" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S52" s="4" t="inlineStr">
         <is>
           <t>cache.fill_above_95, cache.app_eviction, cache.read_in</t>
         </is>
       </c>
-      <c r="O52" s="4" t="inlineStr">
+      <c r="T52" s="4" t="inlineStr">
         <is>
           <t>95 %: WiredTiger default eviction_trigger; eviction_target defaults to 80 (configured value not read)</t>
         </is>
       </c>
-      <c r="P52" s="4" t="inlineStr"/>
+      <c r="U52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -4535,17 +5470,36 @@
           <t>3 s/min</t>
         </is>
       </c>
-      <c r="N53" s="4" t="inlineStr">
+      <c r="N53" s="4" t="inlineStr"/>
+      <c r="O53" s="4" t="inlineStr">
+        <is>
+          <t>time_above</t>
+        </is>
+      </c>
+      <c r="P53" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q53" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="R53" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S53" s="4" t="inlineStr">
         <is>
           <t>cache.fill, cache.app_eviction, tickets.read.scarce</t>
         </is>
       </c>
-      <c r="O53" s="4" t="inlineStr">
+      <c r="T53" s="4" t="inlineStr">
         <is>
           <t>95 %: WiredTiger default eviction_trigger (configured value not read)</t>
         </is>
       </c>
-      <c r="P53" s="4" t="inlineStr"/>
+      <c r="U53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -4613,17 +5567,34 @@
           <t>3 %</t>
         </is>
       </c>
-      <c r="N54" s="4" t="inlineStr">
+      <c r="N54" s="4" t="inlineStr"/>
+      <c r="O54" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P54" s="4" t="n"/>
+      <c r="Q54" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="R54" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S54" s="4" t="inlineStr">
         <is>
           <t>cache.dirty_above_20, checkpoint.duration, disk.write_await, ops.writes</t>
         </is>
       </c>
-      <c r="O54" s="4" t="inlineStr">
+      <c r="T54" s="4" t="inlineStr">
         <is>
           <t>20 %: WiredTiger default eviction_dirty_trigger; eviction_dirty_target defaults to 5 (configured value not read)</t>
         </is>
       </c>
-      <c r="P54" s="4" t="inlineStr"/>
+      <c r="U54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -4691,17 +5662,36 @@
           <t>3 s/min</t>
         </is>
       </c>
-      <c r="N55" s="4" t="inlineStr">
+      <c r="N55" s="4" t="inlineStr"/>
+      <c r="O55" s="4" t="inlineStr">
+        <is>
+          <t>time_above</t>
+        </is>
+      </c>
+      <c r="P55" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q55" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="R55" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S55" s="4" t="inlineStr">
         <is>
           <t>cache.dirty, checkpoint.running, tickets.write.scarce</t>
         </is>
       </c>
-      <c r="O55" s="4" t="inlineStr">
+      <c r="T55" s="4" t="inlineStr">
         <is>
           <t>20 %: WiredTiger default eviction_dirty_trigger (configured value not read)</t>
         </is>
       </c>
-      <c r="P55" s="4" t="inlineStr"/>
+      <c r="U55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -4769,13 +5759,30 @@
           <t>5 pages/s</t>
         </is>
       </c>
-      <c r="N56" s="4" t="inlineStr">
+      <c r="N56" s="4" t="inlineStr"/>
+      <c r="O56" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P56" s="4" t="n"/>
+      <c r="Q56" s="4" t="inlineStr">
+        <is>
+          <t>pages/s</t>
+        </is>
+      </c>
+      <c r="R56" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S56" s="4" t="inlineStr">
         <is>
           <t>cache.fill_above_95, cache.dirty_above_20</t>
         </is>
       </c>
-      <c r="O56" s="4" t="inlineStr"/>
-      <c r="P56" s="4" t="inlineStr"/>
+      <c r="T56" s="4" t="inlineStr"/>
+      <c r="U56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -4843,13 +5850,30 @@
           <t>5 pages/s</t>
         </is>
       </c>
-      <c r="N57" s="4" t="inlineStr">
+      <c r="N57" s="4" t="inlineStr"/>
+      <c r="O57" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P57" s="4" t="n"/>
+      <c r="Q57" s="4" t="inlineStr">
+        <is>
+          <t>pages/s</t>
+        </is>
+      </c>
+      <c r="R57" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S57" s="4" t="inlineStr">
         <is>
           <t>cache.fill_above_95, cache.dirty_above_20, cache.app_eviction_time</t>
         </is>
       </c>
-      <c r="O57" s="4" t="inlineStr"/>
-      <c r="P57" s="4" t="inlineStr"/>
+      <c r="T57" s="4" t="inlineStr"/>
+      <c r="U57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -4917,13 +5941,30 @@
           <t>10 ms/s</t>
         </is>
       </c>
-      <c r="N58" s="4" t="inlineStr">
+      <c r="N58" s="4" t="inlineStr"/>
+      <c r="O58" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P58" s="4" t="n"/>
+      <c r="Q58" s="4" t="inlineStr">
+        <is>
+          <t>ms/s</t>
+        </is>
+      </c>
+      <c r="R58" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S58" s="4" t="inlineStr">
         <is>
           <t>cache.app_eviction, cache.fill_above_95, cache.dirty_above_20</t>
         </is>
       </c>
-      <c r="O58" s="4" t="inlineStr"/>
-      <c r="P58" s="4" t="inlineStr"/>
+      <c r="T58" s="4" t="inlineStr"/>
+      <c r="U58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -4983,13 +6024,30 @@
           <t>5 MB/s</t>
         </is>
       </c>
-      <c r="N59" s="4" t="inlineStr">
+      <c r="N59" s="4" t="inlineStr"/>
+      <c r="O59" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P59" s="4" t="n"/>
+      <c r="Q59" s="4" t="inlineStr">
+        <is>
+          <t>MB/s</t>
+        </is>
+      </c>
+      <c r="R59" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S59" s="4" t="inlineStr">
         <is>
           <t>disk.read_await, query.collscans, cache.fill</t>
         </is>
       </c>
-      <c r="O59" s="4" t="inlineStr"/>
-      <c r="P59" s="4" t="inlineStr"/>
+      <c r="T59" s="4" t="inlineStr"/>
+      <c r="U59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -5057,17 +6115,34 @@
           <t>10 s</t>
         </is>
       </c>
-      <c r="N60" s="4" t="inlineStr">
+      <c r="N60" s="4" t="inlineStr"/>
+      <c r="O60" s="4" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="P60" s="4" t="n"/>
+      <c r="Q60" s="4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="R60" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S60" s="4" t="inlineStr">
         <is>
           <t>checkpoint.running, cache.dirty, disk.write_await</t>
         </is>
       </c>
-      <c r="O60" s="4" t="inlineStr">
+      <c r="T60" s="4" t="inlineStr">
         <is>
           <t>60 s: default checkpoint interval, storage.syncPeriodSecs (configured value not read)</t>
         </is>
       </c>
-      <c r="P60" s="4" t="inlineStr"/>
+      <c r="U60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -5135,17 +6210,34 @@
           <t>10 s</t>
         </is>
       </c>
-      <c r="N61" s="4" t="inlineStr">
+      <c r="N61" s="4" t="inlineStr"/>
+      <c r="O61" s="4" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="P61" s="4" t="n"/>
+      <c r="Q61" s="4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="R61" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S61" s="4" t="inlineStr">
         <is>
           <t>checkpoint.running, cache.dirty, disk.write_await</t>
         </is>
       </c>
-      <c r="O61" s="4" t="inlineStr">
+      <c r="T61" s="4" t="inlineStr">
         <is>
           <t>60 s: default checkpoint interval, storage.syncPeriodSecs (configured value not read)</t>
         </is>
       </c>
-      <c r="P61" s="4" t="inlineStr"/>
+      <c r="U61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -5213,13 +6305,32 @@
           <t>9 s/min</t>
         </is>
       </c>
-      <c r="N62" s="4" t="inlineStr">
+      <c r="N62" s="4" t="inlineStr"/>
+      <c r="O62" s="4" t="inlineStr">
+        <is>
+          <t>time_above</t>
+        </is>
+      </c>
+      <c r="P62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="4" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="R62" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S62" s="4" t="inlineStr">
         <is>
           <t>checkpoint.duration, disk.busy_above_95, cache.dirty</t>
         </is>
       </c>
-      <c r="O62" s="4" t="inlineStr"/>
-      <c r="P62" s="4" t="inlineStr"/>
+      <c r="T62" s="4" t="inlineStr"/>
+      <c r="U62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -5287,13 +6398,32 @@
           <t>9 s/min</t>
         </is>
       </c>
-      <c r="N63" s="4" t="inlineStr">
+      <c r="N63" s="4" t="inlineStr"/>
+      <c r="O63" s="4" t="inlineStr">
+        <is>
+          <t>time_above</t>
+        </is>
+      </c>
+      <c r="P63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="4" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="R63" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S63" s="4" t="inlineStr">
         <is>
           <t>checkpoint.duration, disk.busy_above_95, cache.dirty</t>
         </is>
       </c>
-      <c r="O63" s="4" t="inlineStr"/>
-      <c r="P63" s="4" t="inlineStr">
+      <c r="T63" s="4" t="inlineStr"/>
+      <c r="U63" s="4" t="inlineStr">
         <is>
           <t>The progress state's values are not decoded; any non-zero value is read as activity.</t>
         </is>
@@ -5358,8 +6488,25 @@
         </is>
       </c>
       <c r="N64" s="4" t="inlineStr"/>
-      <c r="O64" s="4" t="inlineStr"/>
-      <c r="P64" s="4" t="inlineStr"/>
+      <c r="O64" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P64" s="4" t="n"/>
+      <c r="Q64" s="4" t="inlineStr">
+        <is>
+          <t>handles</t>
+        </is>
+      </c>
+      <c r="R64" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S64" s="4" t="inlineStr"/>
+      <c r="T64" s="4" t="inlineStr"/>
+      <c r="U64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -5427,13 +6574,30 @@
           <t>5 ms</t>
         </is>
       </c>
-      <c r="N65" s="4" t="inlineStr">
+      <c r="N65" s="4" t="inlineStr"/>
+      <c r="O65" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P65" s="4" t="n"/>
+      <c r="Q65" s="4" t="inlineStr">
+        <is>
+          <t>ms</t>
+        </is>
+      </c>
+      <c r="R65" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S65" s="4" t="inlineStr">
         <is>
           <t>tickets.read.scarce, query.targeting, cache.fill_above_95, disk.read_await</t>
         </is>
       </c>
-      <c r="O65" s="4" t="inlineStr"/>
-      <c r="P65" s="4" t="inlineStr"/>
+      <c r="T65" s="4" t="inlineStr"/>
+      <c r="U65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -5501,13 +6665,30 @@
           <t>5 ms</t>
         </is>
       </c>
-      <c r="N66" s="4" t="inlineStr">
+      <c r="N66" s="4" t="inlineStr"/>
+      <c r="O66" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P66" s="4" t="n"/>
+      <c r="Q66" s="4" t="inlineStr">
+        <is>
+          <t>ms</t>
+        </is>
+      </c>
+      <c r="R66" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S66" s="4" t="inlineStr">
         <is>
           <t>tickets.write.scarce, cache.dirty_above_20, flow.lagged, repl.majority_lag</t>
         </is>
       </c>
-      <c r="O66" s="4" t="inlineStr"/>
-      <c r="P66" s="4" t="inlineStr"/>
+      <c r="T66" s="4" t="inlineStr"/>
+      <c r="U66" s="4" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -5575,13 +6756,30 @@
           <t>5 ms</t>
         </is>
       </c>
-      <c r="N67" s="4" t="inlineStr">
+      <c r="N67" s="4" t="inlineStr"/>
+      <c r="O67" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P67" s="4" t="n"/>
+      <c r="Q67" s="4" t="inlineStr">
+        <is>
+          <t>ms</t>
+        </is>
+      </c>
+      <c r="R67" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S67" s="4" t="inlineStr">
         <is>
           <t>tickets.read.scarce, query.targeting</t>
         </is>
       </c>
-      <c r="O67" s="4" t="inlineStr"/>
-      <c r="P67" s="4" t="inlineStr"/>
+      <c r="T67" s="4" t="inlineStr"/>
+      <c r="U67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -5641,13 +6839,30 @@
           <t>50 ops/s</t>
         </is>
       </c>
-      <c r="N68" s="4" t="inlineStr">
+      <c r="N68" s="4" t="inlineStr"/>
+      <c r="O68" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P68" s="4" t="n"/>
+      <c r="Q68" s="4" t="inlineStr">
+        <is>
+          <t>ops/s</t>
+        </is>
+      </c>
+      <c r="R68" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S68" s="4" t="inlineStr">
         <is>
           <t>ops.writes, connections.current</t>
         </is>
       </c>
-      <c r="O68" s="4" t="inlineStr"/>
-      <c r="P68" s="4" t="inlineStr"/>
+      <c r="T68" s="4" t="inlineStr"/>
+      <c r="U68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -5707,13 +6922,30 @@
           <t>50 ops/s</t>
         </is>
       </c>
-      <c r="N69" s="4" t="inlineStr">
+      <c r="N69" s="4" t="inlineStr"/>
+      <c r="O69" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P69" s="4" t="n"/>
+      <c r="Q69" s="4" t="inlineStr">
+        <is>
+          <t>ops/s</t>
+        </is>
+      </c>
+      <c r="R69" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S69" s="4" t="inlineStr">
         <is>
           <t>cache.dirty, checkpoint.duration</t>
         </is>
       </c>
-      <c r="O69" s="4" t="inlineStr"/>
-      <c r="P69" s="4" t="inlineStr"/>
+      <c r="T69" s="4" t="inlineStr"/>
+      <c r="U69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -5781,13 +7013,30 @@
           <t>10 ratio</t>
         </is>
       </c>
-      <c r="N70" s="4" t="inlineStr">
+      <c r="N70" s="4" t="inlineStr"/>
+      <c r="O70" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P70" s="4" t="n"/>
+      <c r="Q70" s="4" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="R70" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S70" s="4" t="inlineStr">
         <is>
           <t>query.collscans, cache.read_in, cpu.busy</t>
         </is>
       </c>
-      <c r="O70" s="4" t="inlineStr"/>
-      <c r="P70" s="4" t="inlineStr"/>
+      <c r="T70" s="4" t="inlineStr"/>
+      <c r="U70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -5855,13 +7104,30 @@
           <t>0.5 /s</t>
         </is>
       </c>
-      <c r="N71" s="4" t="inlineStr">
+      <c r="N71" s="4" t="inlineStr"/>
+      <c r="O71" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P71" s="4" t="n"/>
+      <c r="Q71" s="4" t="inlineStr">
+        <is>
+          <t>/s</t>
+        </is>
+      </c>
+      <c r="R71" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S71" s="4" t="inlineStr">
         <is>
           <t>query.targeting, cache.read_in</t>
         </is>
       </c>
-      <c r="O71" s="4" t="inlineStr"/>
-      <c r="P71" s="4" t="inlineStr"/>
+      <c r="T71" s="4" t="inlineStr"/>
+      <c r="U71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -5921,13 +7187,30 @@
           <t>1 /s</t>
         </is>
       </c>
-      <c r="N72" s="4" t="inlineStr">
+      <c r="N72" s="4" t="inlineStr"/>
+      <c r="O72" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P72" s="4" t="n"/>
+      <c r="Q72" s="4" t="inlineStr">
+        <is>
+          <t>/s</t>
+        </is>
+      </c>
+      <c r="R72" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S72" s="4" t="inlineStr">
         <is>
           <t>query.targeting, memory.heap_outside_cache</t>
         </is>
       </c>
-      <c r="O72" s="4" t="inlineStr"/>
-      <c r="P72" s="4" t="inlineStr"/>
+      <c r="T72" s="4" t="inlineStr"/>
+      <c r="U72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -5995,13 +7278,30 @@
           <t>2 /s</t>
         </is>
       </c>
-      <c r="N73" s="4" t="inlineStr">
+      <c r="N73" s="4" t="inlineStr"/>
+      <c r="O73" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P73" s="4" t="n"/>
+      <c r="Q73" s="4" t="inlineStr">
+        <is>
+          <t>/s</t>
+        </is>
+      </c>
+      <c r="R73" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S73" s="4" t="inlineStr">
         <is>
           <t>ops.writes, latency.writes</t>
         </is>
       </c>
-      <c r="O73" s="4" t="inlineStr"/>
-      <c r="P73" s="4" t="inlineStr"/>
+      <c r="T73" s="4" t="inlineStr"/>
+      <c r="U73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -6061,13 +7361,30 @@
           <t>50 docs/s</t>
         </is>
       </c>
-      <c r="N74" s="4" t="inlineStr">
+      <c r="N74" s="4" t="inlineStr"/>
+      <c r="O74" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P74" s="4" t="n"/>
+      <c r="Q74" s="4" t="inlineStr">
+        <is>
+          <t>docs/s</t>
+        </is>
+      </c>
+      <c r="R74" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S74" s="4" t="inlineStr">
         <is>
           <t>cache.dirty, disk.write_await, repl.member_lag</t>
         </is>
       </c>
-      <c r="O74" s="4" t="inlineStr"/>
-      <c r="P74" s="4" t="inlineStr"/>
+      <c r="T74" s="4" t="inlineStr"/>
+      <c r="U74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -6127,13 +7444,30 @@
           <t>50 cursors</t>
         </is>
       </c>
-      <c r="N75" s="4" t="inlineStr">
+      <c r="N75" s="4" t="inlineStr"/>
+      <c r="O75" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P75" s="4" t="n"/>
+      <c r="Q75" s="4" t="inlineStr">
+        <is>
+          <t>cursors</t>
+        </is>
+      </c>
+      <c r="R75" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S75" s="4" t="inlineStr">
         <is>
           <t>memory.heap_outside_cache, connections.current</t>
         </is>
       </c>
-      <c r="O75" s="4" t="inlineStr"/>
-      <c r="P75" s="4" t="inlineStr"/>
+      <c r="T75" s="4" t="inlineStr"/>
+      <c r="U75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -6201,13 +7535,30 @@
           <t>5 s</t>
         </is>
       </c>
-      <c r="N76" s="4" t="inlineStr">
+      <c r="N76" s="4" t="inlineStr"/>
+      <c r="O76" s="4" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="P76" s="4" t="n"/>
+      <c r="Q76" s="4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="R76" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S76" s="4" t="inlineStr">
         <is>
           <t>repl.majority_lag, flow.lagged, net.retransmit</t>
         </is>
       </c>
-      <c r="O76" s="4" t="inlineStr"/>
-      <c r="P76" s="4" t="inlineStr">
+      <c r="T76" s="4" t="inlineStr"/>
+      <c r="U76" s="4" t="inlineStr">
         <is>
           <t>One result per entry of this node's replica-set status, numbered by position in that list; a position can name a different member after a reconfig. Lag is measured against the newest applied time among members, not against the primary, and a member that stopped reporting keeps its last time.</t>
         </is>
@@ -6279,13 +7630,30 @@
           <t>5 s</t>
         </is>
       </c>
-      <c r="N77" s="4" t="inlineStr">
+      <c r="N77" s="4" t="inlineStr"/>
+      <c r="O77" s="4" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="P77" s="4" t="n"/>
+      <c r="Q77" s="4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="R77" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S77" s="4" t="inlineStr">
         <is>
           <t>repl.majority_lag, flow.lagged, net.retransmit</t>
         </is>
       </c>
-      <c r="O77" s="4" t="inlineStr"/>
-      <c r="P77" s="4" t="inlineStr">
+      <c r="T77" s="4" t="inlineStr"/>
+      <c r="U77" s="4" t="inlineStr">
         <is>
           <t>One result per entry of this node's replica-set status, numbered by position in that list; a position can name a different member after a reconfig. Lag is measured against the newest applied time among members, not against the primary, and a member that stopped reporting keeps its last time.</t>
         </is>
@@ -6357,13 +7725,30 @@
           <t>2 s</t>
         </is>
       </c>
-      <c r="N78" s="4" t="inlineStr">
+      <c r="N78" s="4" t="inlineStr"/>
+      <c r="O78" s="4" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="P78" s="4" t="n"/>
+      <c r="Q78" s="4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="R78" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S78" s="4" t="inlineStr">
         <is>
           <t>repl.member_lag, flow.lagged, latency.writes</t>
         </is>
       </c>
-      <c r="O78" s="4" t="inlineStr"/>
-      <c r="P78" s="4" t="inlineStr"/>
+      <c r="T78" s="4" t="inlineStr"/>
+      <c r="U78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -6431,13 +7816,32 @@
           <t>3 s/min</t>
         </is>
       </c>
-      <c r="N79" s="4" t="inlineStr">
+      <c r="N79" s="4" t="inlineStr"/>
+      <c r="O79" s="4" t="inlineStr">
+        <is>
+          <t>time_above</t>
+        </is>
+      </c>
+      <c r="P79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="4" t="inlineStr">
+        <is>
+          <t>lagged</t>
+        </is>
+      </c>
+      <c r="R79" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S79" s="4" t="inlineStr">
         <is>
           <t>flow.wait, repl.majority_lag, latency.writes</t>
         </is>
       </c>
-      <c r="O79" s="4" t="inlineStr"/>
-      <c r="P79" s="4" t="inlineStr">
+      <c r="T79" s="4" t="inlineStr"/>
+      <c r="U79" s="4" t="inlineStr">
         <is>
           <t>Set only on a primary with flow control enabled; a secondary, or a primary with flow control disabled, reports it unset. The flag records that the majority commit point lagged; time writers spent waiting for flow control is flow.wait.</t>
         </is>
@@ -6509,13 +7913,30 @@
           <t>10 ms/s</t>
         </is>
       </c>
-      <c r="N80" s="4" t="inlineStr">
+      <c r="N80" s="4" t="inlineStr"/>
+      <c r="O80" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P80" s="4" t="n"/>
+      <c r="Q80" s="4" t="inlineStr">
+        <is>
+          <t>ms/s</t>
+        </is>
+      </c>
+      <c r="R80" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S80" s="4" t="inlineStr">
         <is>
           <t>flow.lagged, latency.writes</t>
         </is>
       </c>
-      <c r="O80" s="4" t="inlineStr"/>
-      <c r="P80" s="4" t="inlineStr"/>
+      <c r="T80" s="4" t="inlineStr"/>
+      <c r="U80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -6575,13 +7996,30 @@
           <t>50 ops/s</t>
         </is>
       </c>
-      <c r="N81" s="4" t="inlineStr">
+      <c r="N81" s="4" t="inlineStr"/>
+      <c r="O81" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P81" s="4" t="n"/>
+      <c r="Q81" s="4" t="inlineStr">
+        <is>
+          <t>ops/s</t>
+        </is>
+      </c>
+      <c r="R81" s="4" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="S81" s="4" t="inlineStr">
         <is>
           <t>repl.buffer_fill, repl.member_lag</t>
         </is>
       </c>
-      <c r="O81" s="4" t="inlineStr"/>
-      <c r="P81" s="4" t="inlineStr"/>
+      <c r="T81" s="4" t="inlineStr"/>
+      <c r="U81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -6649,13 +8087,30 @@
           <t>10 %</t>
         </is>
       </c>
-      <c r="N82" s="4" t="inlineStr">
+      <c r="N82" s="4" t="inlineStr"/>
+      <c r="O82" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P82" s="4" t="n"/>
+      <c r="Q82" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="R82" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S82" s="4" t="inlineStr">
         <is>
           <t>repl.buffer_full, repl.apply_rate, repl.member_lag</t>
         </is>
       </c>
-      <c r="O82" s="4" t="inlineStr"/>
-      <c r="P82" s="4" t="inlineStr"/>
+      <c r="T82" s="4" t="inlineStr"/>
+      <c r="U82" s="4" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -6723,13 +8178,30 @@
           <t>10 %</t>
         </is>
       </c>
-      <c r="N83" s="4" t="inlineStr">
+      <c r="N83" s="4" t="inlineStr"/>
+      <c r="O83" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P83" s="4" t="n"/>
+      <c r="Q83" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="R83" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S83" s="4" t="inlineStr">
         <is>
           <t>repl.buffer_full, repl.apply_rate, repl.member_lag</t>
         </is>
       </c>
-      <c r="O83" s="4" t="inlineStr"/>
-      <c r="P83" s="4" t="inlineStr"/>
+      <c r="T83" s="4" t="inlineStr"/>
+      <c r="U83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -6797,13 +8269,32 @@
           <t>3 s/min</t>
         </is>
       </c>
-      <c r="N84" s="4" t="inlineStr">
+      <c r="N84" s="4" t="inlineStr"/>
+      <c r="O84" s="4" t="inlineStr">
+        <is>
+          <t>time_above</t>
+        </is>
+      </c>
+      <c r="P84" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q84" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="R84" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S84" s="4" t="inlineStr">
         <is>
           <t>repl.buffer_fill, repl.apply_rate</t>
         </is>
       </c>
-      <c r="O84" s="4" t="inlineStr"/>
-      <c r="P84" s="4" t="inlineStr"/>
+      <c r="T84" s="4" t="inlineStr"/>
+      <c r="U84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -6871,13 +8362,32 @@
           <t>3 s/min</t>
         </is>
       </c>
-      <c r="N85" s="4" t="inlineStr">
+      <c r="N85" s="4" t="inlineStr"/>
+      <c r="O85" s="4" t="inlineStr">
+        <is>
+          <t>time_above</t>
+        </is>
+      </c>
+      <c r="P85" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q85" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="R85" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S85" s="4" t="inlineStr">
         <is>
           <t>repl.buffer_fill, repl.apply_rate</t>
         </is>
       </c>
-      <c r="O85" s="4" t="inlineStr"/>
-      <c r="P85" s="4" t="inlineStr"/>
+      <c r="T85" s="4" t="inlineStr"/>
+      <c r="U85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -6945,13 +8455,30 @@
           <t>10 %</t>
         </is>
       </c>
-      <c r="N86" s="4" t="inlineStr">
+      <c r="N86" s="4" t="inlineStr"/>
+      <c r="O86" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P86" s="4" t="n"/>
+      <c r="Q86" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="R86" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S86" s="4" t="inlineStr">
         <is>
           <t>connections.scarce, connections.created, connections.rejected</t>
         </is>
       </c>
-      <c r="O86" s="4" t="inlineStr"/>
-      <c r="P86" s="4" t="inlineStr"/>
+      <c r="T86" s="4" t="inlineStr"/>
+      <c r="U86" s="4" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -7019,13 +8546,32 @@
           <t>3 s/min</t>
         </is>
       </c>
-      <c r="N87" s="4" t="inlineStr">
+      <c r="N87" s="4" t="inlineStr"/>
+      <c r="O87" s="4" t="inlineStr">
+        <is>
+          <t>time_below</t>
+        </is>
+      </c>
+      <c r="P87" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q87" s="4" t="inlineStr">
+        <is>
+          <t>% available</t>
+        </is>
+      </c>
+      <c r="R87" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S87" s="4" t="inlineStr">
         <is>
           <t>connections.used, connections.created, connections.rejected</t>
         </is>
       </c>
-      <c r="O87" s="4" t="inlineStr"/>
-      <c r="P87" s="4" t="inlineStr"/>
+      <c r="T87" s="4" t="inlineStr"/>
+      <c r="U87" s="4" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -7093,13 +8639,30 @@
           <t>5 conn/s</t>
         </is>
       </c>
-      <c r="N88" s="4" t="inlineStr">
+      <c r="N88" s="4" t="inlineStr"/>
+      <c r="O88" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P88" s="4" t="n"/>
+      <c r="Q88" s="4" t="inlineStr">
+        <is>
+          <t>conn/s</t>
+        </is>
+      </c>
+      <c r="R88" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S88" s="4" t="inlineStr">
         <is>
           <t>connections.current, cpu.kernel_share, net.resets</t>
         </is>
       </c>
-      <c r="O88" s="4" t="inlineStr"/>
-      <c r="P88" s="4" t="inlineStr"/>
+      <c r="T88" s="4" t="inlineStr"/>
+      <c r="U88" s="4" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -7167,13 +8730,30 @@
           <t>100 conns</t>
         </is>
       </c>
-      <c r="N89" s="4" t="inlineStr">
+      <c r="N89" s="4" t="inlineStr"/>
+      <c r="O89" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P89" s="4" t="n"/>
+      <c r="Q89" s="4" t="inlineStr">
+        <is>
+          <t>conns</t>
+        </is>
+      </c>
+      <c r="R89" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S89" s="4" t="inlineStr">
         <is>
           <t>connections.current, connections.created, connections.working_share, memory.heap_outside_cache</t>
         </is>
       </c>
-      <c r="O89" s="4" t="inlineStr"/>
-      <c r="P89" s="4" t="inlineStr"/>
+      <c r="T89" s="4" t="inlineStr"/>
+      <c r="U89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -7241,13 +8821,30 @@
           <t>10 %</t>
         </is>
       </c>
-      <c r="N90" s="4" t="inlineStr">
+      <c r="N90" s="4" t="inlineStr"/>
+      <c r="O90" s="4" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="P90" s="4" t="n"/>
+      <c r="Q90" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="R90" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S90" s="4" t="inlineStr">
         <is>
           <t>tickets.read.empty, tickets.write.empty, queue.readers, queue.writers, connections.created</t>
         </is>
       </c>
-      <c r="O90" s="4" t="inlineStr"/>
-      <c r="P90" s="4" t="inlineStr"/>
+      <c r="T90" s="4" t="inlineStr"/>
+      <c r="U90" s="4" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -7307,13 +8904,30 @@
           <t>50 conns</t>
         </is>
       </c>
-      <c r="N91" s="4" t="inlineStr">
+      <c r="N91" s="4" t="inlineStr"/>
+      <c r="O91" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P91" s="4" t="n"/>
+      <c r="Q91" s="4" t="inlineStr">
+        <is>
+          <t>conns</t>
+        </is>
+      </c>
+      <c r="R91" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S91" s="4" t="inlineStr">
         <is>
           <t>connections.non_active, connections.created, memory.heap_outside_cache</t>
         </is>
       </c>
-      <c r="O91" s="4" t="inlineStr"/>
-      <c r="P91" s="4" t="inlineStr"/>
+      <c r="T91" s="4" t="inlineStr"/>
+      <c r="U91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -7381,16 +8995,1896 @@
           <t>0.01 /s</t>
         </is>
       </c>
-      <c r="N92" s="4" t="inlineStr">
+      <c r="N92" s="4" t="inlineStr"/>
+      <c r="O92" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P92" s="4" t="n"/>
+      <c r="Q92" s="4" t="inlineStr">
+        <is>
+          <t>/s</t>
+        </is>
+      </c>
+      <c r="R92" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S92" s="4" t="inlineStr">
         <is>
           <t>connections.scarce, connections.used</t>
         </is>
       </c>
-      <c r="O92" s="4" t="inlineStr"/>
-      <c r="P92" s="4" t="inlineStr"/>
+      <c r="T92" s="4" t="inlineStr"/>
+      <c r="U92" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P92"/>
+  <autoFilter ref="A1:U92"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D92"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="120" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Server versions</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Complete JSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>cpu.busy</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "idle ≤5 (fading to 15) · low 15–35 (edges 5, 50) · moderate 50–65 (edges 35, 80) · high 80–88 (edges 65, 95) · very_high ≥95 (from 88)", "doc": "Share of host CPU counters recorded as user, nice, system, IRQ, soft IRQ or steal, excluding idle and iowait; steal is not process execution time. Host-wide memory or CPU counters do not establish a container's resource limit.", "elevated": 80, "formula": "Δ(systemMetrics/cpu/user_ms + systemMetrics/cpu/nice_ms + systemMetrics/cpu/system_ms + systemMetrics/cpu/irq_ms + systemMetrics/cpu/softirq_ms + systemMetrics/cpu/steal_ms) ÷ Δ(systemMetrics/cpu/user_ms + systemMetrics/cpu/nice_ms + systemMetrics/cpu/system_ms + systemMetrics/cpu/idle_ms + systemMetrics/cpu/iowait_ms + systemMetrics/cpu/irq_ms + systemMetrics/cpu/softirq_ms + systemMetrics/cpu/steal_ms) × 100, in %, at each available sample", "levels": [{"down": [5, 15], "name": "idle"}, {"band": [5, 15, 35, 50], "name": "low"}, {"band": [35, 50, 65, 80], "name": "moderate"}, {"band": [65, 80, 88, 95], "name": "high"}, {"name": "very_high", "up": [88, 95]}], "min_change": 10, "name": "cpu.busy", "pack": "cpu", "pairs_with": ["cpu.busy_above_95", "cpu.run_queue", "cpu.iowait", "cpu.kernel_share"], "reading": "each minute's ratio of sums", "signal": {"den": ["systemMetrics/cpu/user_ms", "systemMetrics/cpu/nice_ms", "systemMetrics/cpu/system_ms", "systemMetrics/cpu/idle_ms", "systemMetrics/cpu/iowait_ms", "systemMetrics/cpu/irq_ms", "systemMetrics/cpu/softirq_ms", "systemMetrics/cpu/steal_ms"], "mode": "rate", "num": ["systemMetrics/cpu/user_ms", "systemMetrics/cpu/nice_ms", "systemMetrics/cpu/system_ms", "systemMetrics/cpu/irq_ms", "systemMetrics/cpu/softirq_ms", "systemMetrics/cpu/steal_ms"], "scale": 100, "unit": "%"}, "title": "CPU busy", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>cpu.busy_above_95</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which host CPU busy, computed as for cpu.busy, was strictly above 95 %, normalized to a 60-second minute.", "elevated": 1, "formula": "Δ(systemMetrics/cpu/user_ms + systemMetrics/cpu/nice_ms + systemMetrics/cpu/system_ms + systemMetrics/cpu/irq_ms + systemMetrics/cpu/softirq_ms + systemMetrics/cpu/steal_ms) ÷ Δ(systemMetrics/cpu/user_ms + systemMetrics/cpu/nice_ms + systemMetrics/cpu/system_ms + systemMetrics/cpu/idle_ms + systemMetrics/cpu/iowait_ms + systemMetrics/cpu/irq_ms + systemMetrics/cpu/softirq_ms + systemMetrics/cpu/steal_ms) × 100, in %, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "cpu.busy_above_95", "pack": "cpu", "pairs_with": ["cpu.busy", "cpu.run_queue"], "reading": "valid-sample share strictly above 95 %, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["systemMetrics/cpu/user_ms", "systemMetrics/cpu/nice_ms", "systemMetrics/cpu/system_ms", "systemMetrics/cpu/idle_ms", "systemMetrics/cpu/iowait_ms", "systemMetrics/cpu/irq_ms", "systemMetrics/cpu/softirq_ms", "systemMetrics/cpu/steal_ms"], "mode": "rate", "num": ["systemMetrics/cpu/user_ms", "systemMetrics/cpu/nice_ms", "systemMetrics/cpu/system_ms", "systemMetrics/cpu/irq_ms", "systemMetrics/cpu/softirq_ms", "systemMetrics/cpu/steal_ms"], "scale": 100, "unit": "%"}, "threshold": 95, "title": "CPU-busy samples above 95%", "unit": "s/min", "version_text": "all versions", "view": "time_above"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>cpu.iowait</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none ≤1 (fading to 3) · low 3–8 (edges 1, 12) · elevated 12–20 (edges 8, 30) · high ≥30 (from 20)", "doc": "Share of the machine's CPU idle with I/O outstanding.", "elevated": 10, "formula": "ΔsystemMetrics/cpu/iowait_ms ÷ Δ(systemMetrics/cpu/user_ms + systemMetrics/cpu/nice_ms + systemMetrics/cpu/system_ms + systemMetrics/cpu/idle_ms + systemMetrics/cpu/iowait_ms + systemMetrics/cpu/irq_ms + systemMetrics/cpu/softirq_ms + systemMetrics/cpu/steal_ms) × 100, in %, at each available sample", "levels": [{"down": [1, 3], "name": "none"}, {"band": [1, 3, 8, 12], "name": "low"}, {"band": [8, 12, 20, 30], "name": "elevated"}, {"name": "high", "up": [20, 30]}], "min_change": 5, "name": "cpu.iowait", "pack": "cpu", "pairs_with": ["disk.busy", "disk.await", "cpu.blocked"], "reading": "each minute's ratio of sums", "signal": {"den": ["systemMetrics/cpu/user_ms", "systemMetrics/cpu/nice_ms", "systemMetrics/cpu/system_ms", "systemMetrics/cpu/idle_ms", "systemMetrics/cpu/iowait_ms", "systemMetrics/cpu/irq_ms", "systemMetrics/cpu/softirq_ms", "systemMetrics/cpu/steal_ms"], "mode": "rate", "num": ["systemMetrics/cpu/iowait_ms"], "scale": 100, "unit": "%"}, "title": "Host CPU iowait share", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>cpu.steal</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none ≤1 (fading to 2) · present 2–5 (edges 1, 10) · high ≥10 (from 5)", "doc": "Share of the host CPU counters recorded as steal time.", "elevated": 5, "formula": "ΔsystemMetrics/cpu/steal_ms ÷ Δ(systemMetrics/cpu/user_ms + systemMetrics/cpu/nice_ms + systemMetrics/cpu/system_ms + systemMetrics/cpu/idle_ms + systemMetrics/cpu/iowait_ms + systemMetrics/cpu/irq_ms + systemMetrics/cpu/softirq_ms + systemMetrics/cpu/steal_ms) × 100, in %, at each available sample", "levels": [{"down": [1, 2], "name": "none"}, {"band": [1, 2, 5, 10], "name": "present"}, {"name": "high", "up": [5, 10]}], "min_change": 3, "name": "cpu.steal", "pack": "cpu", "pairs_with": ["cpu.busy"], "reading": "each minute's ratio of sums", "signal": {"den": ["systemMetrics/cpu/user_ms", "systemMetrics/cpu/nice_ms", "systemMetrics/cpu/system_ms", "systemMetrics/cpu/idle_ms", "systemMetrics/cpu/iowait_ms", "systemMetrics/cpu/irq_ms", "systemMetrics/cpu/softirq_ms", "systemMetrics/cpu/steal_ms"], "mode": "rate", "num": ["systemMetrics/cpu/steal_ms"], "scale": 100, "unit": "%"}, "title": "Host CPU steal-time share", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>cpu.kernel_share</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "normal ≤30 (fading to 45) · elevated 45–55 (edges 30, 65) · dominant ≥65 (from 55)", "doc": "System CPU as a share of user plus system.", "elevated": 50, "formula": "ΔsystemMetrics/cpu/system_ms ÷ Δ(systemMetrics/cpu/user_ms + systemMetrics/cpu/system_ms) × 100, in %, at each available sample; minutes where the divisor sums to under 6000 are left out", "levels": [{"down": [30, 45], "name": "normal"}, {"band": [30, 45, 55, 65], "name": "elevated"}, {"name": "dominant", "up": [55, 65]}], "min_change": 10, "name": "cpu.kernel_share", "pack": "cpu", "pairs_with": ["cpu.busy", "cpu.context_switches"], "reading": "each minute's ratio of sums", "signal": {"den": ["systemMetrics/cpu/user_ms", "systemMetrics/cpu/system_ms"], "min_den": 6000, "mode": "rate", "num": ["systemMetrics/cpu/system_ms"], "scale": 100, "unit": "%"}, "title": "CPU time in the kernel", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>cpu.run_queue</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>7.0.10 up to 7.0.11, 7.0.16 up to 7.1, 7.3 and later</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "light ≤0.5 (fading to 0.8) · busy 0.8–1.2 (edges 0.5, 2) · very_high ≥2 (from 1.2)", "doc": "Threads ready to run, per logical core, averaged over the minute.", "elevated": 1.5, "formula": "systemMetrics/cpu/procs_running ÷ systemMetrics/cpu/num_logical_cores, in per core, at each available sample", "levels": [{"down": [0.5, 0.8], "name": "light"}, {"band": [0.5, 0.8, 1.2, 2], "name": "busy"}, {"name": "very_high", "up": [1.2, 2]}], "min_change": 0.3, "name": "cpu.run_queue", "pack": "cpu", "pairs_with": ["cpu.busy", "cpu.busy_above_95"], "reading": "each minute's ratio of sums", "signal": {"den": ["systemMetrics/cpu/num_logical_cores"], "mode": "gauge", "num": ["systemMetrics/cpu/procs_running"], "scale": 1, "unit": "per core"}, "title": "Runnable threads per core", "unit": "per core", "version_text": "7.0.10 up to 7.0.11, 7.0.16 up to 7.1, 7.3 and later", "versions": ["7.0.10-7.0.11", "7.0.16-7.1", "7.3-"], "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>cpu.run_queue</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>before 7.0.10, 7.0.11 up to 7.0.16, 7.1 up to 7.3</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "light ≤0.5 (fading to 0.8) · busy 0.8–1.2 (edges 0.5, 2) · very_high ≥2 (from 1.2)", "doc": "Threads ready to run, per logical core, averaged over the minute.", "elevated": 1.5, "formula": "systemMetrics/cpu/procs_running ÷ systemMetrics/cpu/num_cpus, in per core, at each available sample", "levels": [{"down": [0.5, 0.8], "name": "light"}, {"band": [0.5, 0.8, 1.2, 2], "name": "busy"}, {"name": "very_high", "up": [1.2, 2]}], "min_change": 0.3, "name": "cpu.run_queue", "pack": "cpu", "pairs_with": ["cpu.busy", "cpu.busy_above_95"], "reading": "each minute's ratio of sums", "signal": {"den": ["systemMetrics/cpu/num_cpus"], "mode": "gauge", "num": ["systemMetrics/cpu/procs_running"], "scale": 1, "unit": "per core"}, "title": "Runnable threads per core", "unit": "per core", "version_text": "before 7.0.10, 7.0.11 up to 7.0.16, 7.1 up to 7.3", "versions": ["-7.0.10", "7.0.11-7.0.16", "7.1-7.3"], "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>cpu.blocked</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none ≤0.5 (fading to 1) · some 1–4 (edges 0.5, 10) · many ≥10 (from 4)", "doc": "Host process count recorded in procs_blocked (uninterruptible sleep).", "elevated": 4, "formula": "systemMetrics/cpu/procs_blocked, in threads, at each available sample", "levels": [{"down": [0.5, 1], "name": "none"}, {"band": [0.5, 1, 4, 10], "name": "some"}, {"name": "many", "up": [4, 10]}], "min_change": 2, "name": "cpu.blocked", "pack": "cpu", "pairs_with": ["cpu.iowait", "disk.await"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["systemMetrics/cpu/procs_blocked"], "scale": 1, "unit": "threads"}, "title": "Processes in uninterruptible sleep", "unit": "threads", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>cpu.context_switches</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none — read for its shape only", "doc": "Context switches a second, host-wide.", "formula": "ΔsystemMetrics/cpu/ctxt per second, in /s, at each available sample", "min_change": 5000, "name": "cpu.context_switches", "pack": "cpu", "pairs_with": ["connections.created", "cpu.kernel_share"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["systemMetrics/cpu/ctxt"], "scale": 1, "unit": "/s"}, "title": "Context switches", "unit": "/s", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>memory.used</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>4.2.14 up to 4.3, 4.4.5 and later</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "low ≤40 (fading to 60) · moderate 60–75 (edges 40, 85) · high 85–92 (edges 75, 96) · very_high ≥96 (from 92)", "doc": "Share of the machine's memory not available to new allocations (MemTotal less MemAvailable, so the page cache the kernel can drop counts as free). Host-wide memory or CPU counters do not establish a container's resource limit.", "elevated": 90, "formula": "100 − (systemMetrics/memory/MemAvailable_kb ÷ systemMetrics/memory/MemTotal_kb × 100), in %, at each available sample", "levels": [{"down": [40, 60], "name": "low"}, {"band": [40, 60, 75, 85], "name": "moderate"}, {"band": [75, 85, 92, 96], "name": "high"}, {"name": "very_high", "up": [92, 96]}], "min_change": 10, "name": "memory.used", "pack": "memory", "pairs_with": ["memory.swap_used", "memory.page_faults", "memory.mongod_resident"], "reading": "each minute's ratio of sums", "signal": {"complement": true, "den": ["systemMetrics/memory/MemTotal_kb"], "mode": "gauge", "num": ["systemMetrics/memory/MemAvailable_kb"], "scale": 100, "unit": "%"}, "title": "Memory in use", "unit": "%", "version_text": "4.2.14 up to 4.3, 4.4.5 and later", "versions": ["4.2.14-4.3", "4.4.5-"], "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>memory.swap_used</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none ≤1 (fading to 3) · some 3–20 (edges 1, 40) · heavy ≥40 (from 20)", "doc": "Share of swap holding pages. Host-wide memory or CPU counters do not establish a container's resource limit.", "elevated": 10, "formula": "100 − (systemMetrics/memory/SwapFree_kb ÷ systemMetrics/memory/SwapTotal_kb × 100), in %, at each available sample", "levels": [{"down": [1, 3], "name": "none"}, {"band": [1, 3, 20, 40], "name": "some"}, {"name": "heavy", "up": [20, 40]}], "min_change": 5, "name": "memory.swap_used", "pack": "memory", "pairs_with": ["memory.used", "memory.page_faults"], "reading": "each minute's ratio of sums", "signal": {"complement": true, "den": ["systemMetrics/memory/SwapTotal_kb"], "mode": "gauge", "num": ["systemMetrics/memory/SwapFree_kb"], "scale": 100, "unit": "%"}, "title": "Swap in use", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>memory.page_faults</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none ≤1 (fading to 5) · some 5–50 (edges 1, 200) · heavy ≥200 (from 50)", "doc": "Rate of the process's logged major-page-fault counter.", "elevated": 50, "formula": "ΔserverStatus/extra_info/page_faults per second, in /s, at each available sample", "levels": [{"down": [1, 5], "name": "none"}, {"band": [1, 5, 50, 200], "name": "some"}, {"name": "heavy", "up": [50, 200]}], "min_change": 10, "name": "memory.page_faults", "pack": "memory", "pairs_with": ["memory.used", "memory.swap_used", "disk.read_await"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/extra_info/page_faults"], "scale": 1, "unit": "/s"}, "title": "Page faults", "unit": "/s", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>memory.mongod_resident</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "modest ≤40 (fading to 60) · large 60–75 (edges 40, 85) · dominant ≥85 (from 75)", "doc": "mongod's resident memory as a share of the machine's. Host-wide memory or CPU counters do not establish a container's resource limit.", "elevated": 80, "formula": "serverStatus/mem/resident ÷ systemMetrics/memory/MemTotal_kb × 102400, in %, at each available sample", "levels": [{"down": [40, 60], "name": "modest"}, {"band": [40, 60, 75, 85], "name": "large"}, {"name": "dominant", "up": [75, 85]}], "min_change": 5, "name": "memory.mongod_resident", "pack": "memory", "pairs_with": ["memory.used", "memory.heap_outside_cache", "memory.cache_of_ram"], "reading": "each minute's ratio of sums", "signal": {"den": ["systemMetrics/memory/MemTotal_kb"], "mode": "gauge", "num": ["serverStatus/mem/resident"], "scale": 102400, "unit": "%"}, "title": "mongod resident memory", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>memory.heap_outside_cache</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none — read for its shape only", "doc": "Difference between tcmalloc allocated bytes and bytes currently held in the WiredTiger cache; this is a derived estimate, not a complete inventory of non-cache allocations.", "formula": "serverStatus/tcmalloc/generic/current_allocated_bytes − serverStatus/wiredTiger/cache/bytes currently in the cache × 9.313225746154785e-10, in GiB, at each available sample", "min_change": 0.5, "name": "memory.heap_outside_cache", "pack": "memory", "pairs_with": ["connections.current", "memory.allocator_free", "cursors.open"], "reading": "each minute's mean", "signal": {"minus": ["serverStatus/wiredTiger/cache/bytes currently in the cache"], "mode": "gauge", "num": ["serverStatus/tcmalloc/generic/current_allocated_bytes"], "scale": 9.313225746154785e-10, "unit": "GiB"}, "title": "Allocated bytes minus WiredTiger cache bytes", "unit": "GiB", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>memory.allocator_free</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>before 8.0</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "small ≤10 (fading to 20) · notable 20–30 (edges 10, 45) · large ≥45 (from 30)", "doc": "Ratio of tcmalloc pageheap_free_bytes to heap_size; these counters do not describe every allocator cache.", "elevated": 30, "formula": "serverStatus/tcmalloc/tcmalloc/pageheap_free_bytes ÷ serverStatus/tcmalloc/generic/heap_size × 100, in %, at each available sample", "levels": [{"down": [10, 20], "name": "small"}, {"band": [10, 20, 30, 45], "name": "notable"}, {"name": "large", "up": [30, 45]}], "min_change": 5, "name": "memory.allocator_free", "pack": "memory", "pairs_with": ["memory.heap_outside_cache", "memory.mongod_resident"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/tcmalloc/generic/heap_size"], "mode": "gauge", "num": ["serverStatus/tcmalloc/tcmalloc/pageheap_free_bytes"], "scale": 100, "unit": "%"}, "title": "tcmalloc pageheap-free share", "unit": "%", "until": "8.0", "version_text": "before 8.0", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>memory.cache_of_ram</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "low ≤30 (fading to 40) · middle 40–55 (edges 30, 62) · high ≥70 (from 58)", "doc": "The configured cache as a share of the machine's memory. Host-wide memory or CPU counters do not establish a container's resource limit.", "elevated": 60, "formula": "serverStatus/wiredTiger/cache/maximum bytes configured ÷ systemMetrics/memory/MemTotal_kb × 0.09765625, in %, at each available sample", "levels": [{"down": [30, 40], "name": "low"}, {"band": [30, 40, 55, 62], "name": "middle"}, {"name": "high", "up": [58, 70]}], "min_change": 5, "name": "memory.cache_of_ram", "pack": "memory", "pairs_with": ["memory.used", "memory.mongod_resident"], "reading": "each minute's ratio of sums", "signal": {"den": ["systemMetrics/memory/MemTotal_kb"], "mode": "gauge", "num": ["serverStatus/wiredTiger/cache/maximum bytes configured"], "scale": 0.09765625, "unit": "%"}, "title": "WiredTiger cache size against RAM", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>disk.busy</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>{"applies": "A device that serves requests in parallel, such as an SSD, NVMe or network volume, can show io_time near 100 % with capacity to spare; disk.await shows whether requests waited. Device-mapper (dm-*) devices are not read by this tool; the disks under them are.", "bands": "idle ≤5 (fading to 15) · low 15–40 (edges 5, 60) · moderate 60–75 (edges 40, 85) · high 85–92 (edges 75, 97) · very_high ≥97 (from 92)", "doc": "Device io_time counter advance divided by elapsed time; a high value does not establish device capacity exhaustion. Device coverage depends on the block-device counters present in FTDC; logical devices may be absent.", "elevated": 85, "formula": "ΔsystemMetrics/disks/{i}/io_time_ms per second × 0.1, in %, at each available sample; real block devices only", "levels": [{"down": [5, 15], "name": "idle"}, {"band": [5, 15, 40, 60], "name": "low"}, {"band": [40, 60, 75, 85], "name": "moderate"}, {"band": [75, 85, 92, 97], "name": "high"}, {"name": "very_high", "up": [92, 97]}], "min_change": 15, "name": "disk.busy", "open_with": ["disk.await"], "pack": "disk", "pairs_with": ["disk.busy_above_95", "disk.await", "disk.queue", "disk.iops", "disk.throughput"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["systemMetrics/disks/{i}/io_time_ms"], "real_device": true, "scale": 0.1, "unit": "%"}, "title": "Disk busy", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>disk.busy_above_95</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>{"applies": "A device that serves requests in parallel, such as an SSD, NVMe or network volume, can show io_time near 100 % with capacity to spare; disk.await shows whether requests waited. Device-mapper (dm-*) devices are not read by this tool; the disks under them are.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which a device's io_time advanced by more than 95 % of the elapsed time, normalized to a 60-second minute.", "elevated": 1, "formula": "ΔsystemMetrics/disks/{i}/io_time_ms per second × 0.1, in %, at each available sample; real block devices only", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "disk.busy_above_95", "open_with": ["disk.await"], "pack": "disk", "pairs_with": ["disk.busy", "disk.await", "checkpoint.running"], "reading": "valid-sample share strictly above 95 %, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "rate", "num": ["systemMetrics/disks/{i}/io_time_ms"], "real_device": true, "scale": 0.1, "unit": "%"}, "threshold": 95, "title": "Device-busy samples above 95%", "unit": "s/min", "version_text": "all versions", "view": "time_above"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>disk.await</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "fast ≤2 (fading to 5) · normal 5–10 (edges 2, 15) · slow 15–30 (edges 10, 50) · very_slow ≥50 (from 30)", "doc": "Average milliseconds a read or write took on each device, queueing included — what iostat calls await.", "elevated": 20, "formula": "Δ(systemMetrics/disks/{i}/read_time_ms + systemMetrics/disks/{i}/write_time_ms) ÷ Δ(systemMetrics/disks/{i}/reads + systemMetrics/disks/{i}/writes), in ms, at each available sample; minutes where the divisor sums to under 60 are left out; real block devices only", "levels": [{"down": [2, 5], "name": "fast"}, {"band": [2, 5, 10, 15], "name": "normal"}, {"band": [10, 15, 30, 50], "name": "slow"}, {"name": "very_slow", "up": [30, 50]}], "min_change": 5, "name": "disk.await", "pack": "disk", "pairs_with": ["disk.busy", "disk.queue", "cpu.iowait"], "reading": "each minute's ratio of sums", "signal": {"den": ["systemMetrics/disks/{i}/reads", "systemMetrics/disks/{i}/writes"], "min_den": 60, "mode": "rate", "num": ["systemMetrics/disks/{i}/read_time_ms", "systemMetrics/disks/{i}/write_time_ms"], "real_device": true, "scale": 1, "unit": "ms"}, "title": "Disk time per request", "unit": "ms", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>disk.read_await</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "fast ≤2 (fading to 5) · normal 5–10 (edges 2, 15) · slow 15–30 (edges 10, 50) · very_slow ≥50 (from 30)", "doc": "Average milliseconds a read took on each device.", "elevated": 20, "formula": "ΔsystemMetrics/disks/{i}/read_time_ms ÷ ΔsystemMetrics/disks/{i}/reads, in ms, at each available sample; minutes where the divisor sums to under 60 are left out; real block devices only", "levels": [{"down": [2, 5], "name": "fast"}, {"band": [2, 5, 10, 15], "name": "normal"}, {"band": [10, 15, 30, 50], "name": "slow"}, {"name": "very_slow", "up": [30, 50]}], "min_change": 5, "name": "disk.read_await", "pack": "disk", "pairs_with": ["cache.read_in", "disk.busy"], "reading": "each minute's ratio of sums", "signal": {"den": ["systemMetrics/disks/{i}/reads"], "min_den": 60, "mode": "rate", "num": ["systemMetrics/disks/{i}/read_time_ms"], "real_device": true, "scale": 1, "unit": "ms"}, "title": "Disk time per read", "unit": "ms", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>disk.write_await</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "fast ≤2 (fading to 5) · normal 5–10 (edges 2, 15) · slow 15–30 (edges 10, 50) · very_slow ≥50 (from 30)", "doc": "Average milliseconds a write took on each device.", "elevated": 20, "formula": "ΔsystemMetrics/disks/{i}/write_time_ms ÷ ΔsystemMetrics/disks/{i}/writes, in ms, at each available sample; minutes where the divisor sums to under 60 are left out; real block devices only", "levels": [{"down": [2, 5], "name": "fast"}, {"band": [2, 5, 10, 15], "name": "normal"}, {"band": [10, 15, 30, 50], "name": "slow"}, {"name": "very_slow", "up": [30, 50]}], "min_change": 5, "name": "disk.write_await", "pack": "disk", "pairs_with": ["checkpoint.duration", "cache.dirty", "tickets.write.scarce"], "reading": "each minute's ratio of sums", "signal": {"den": ["systemMetrics/disks/{i}/writes"], "min_den": 60, "mode": "rate", "num": ["systemMetrics/disks/{i}/write_time_ms"], "real_device": true, "scale": 1, "unit": "ms"}, "title": "Disk time per write", "unit": "ms", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>disk.queue</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "shallow ≤1 (fading to 2) · moderate 2–8 (edges 1, 16) · deep ≥16 (from 8)", "doc": "Average number of requests outstanding on each device over the minute (io_queued time over wall time).", "elevated": 8, "formula": "ΔsystemMetrics/disks/{i}/io_queued_ms per second × 0.001, in requests, at each available sample; real block devices only", "levels": [{"down": [1, 2], "name": "shallow"}, {"band": [1, 2, 8, 16], "name": "moderate"}, {"name": "deep", "up": [8, 16]}], "min_change": 2, "name": "disk.queue", "open_with": ["disk.await"], "pack": "disk", "pairs_with": ["disk.await", "disk.busy"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["systemMetrics/disks/{i}/io_queued_ms"], "real_device": true, "scale": 0.001, "unit": "requests"}, "title": "Disk requests in flight", "unit": "requests", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>disk.iops</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none — read for its shape only", "doc": "Reads plus writes a second on each device.", "formula": "Δ(systemMetrics/disks/{i}/reads + systemMetrics/disks/{i}/writes) per second, in /s, at each available sample; real block devices only", "min_change": 100, "name": "disk.iops", "pack": "disk", "pairs_with": ["disk.busy", "disk.await"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["systemMetrics/disks/{i}/reads", "systemMetrics/disks/{i}/writes"], "real_device": true, "scale": 1, "unit": "/s"}, "title": "Disk requests a second", "unit": "/s", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>disk.throughput</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none — read for its shape only", "doc": "Megabytes a second read plus written on each device (sectors are 512 bytes).", "formula": "Δ(systemMetrics/disks/{i}/read_sectors + systemMetrics/disks/{i}/write_sectors) per second × 0.000512, in MB/s, at each available sample; real block devices only", "min_change": 10, "name": "disk.throughput", "pack": "disk", "pairs_with": ["disk.busy", "disk.iops"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["systemMetrics/disks/{i}/read_sectors", "systemMetrics/disks/{i}/write_sectors"], "real_device": true, "scale": 0.000512, "unit": "MB/s"}, "title": "Disk throughput", "unit": "MB/s", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>net.retransmit</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "low ≤0.1 (fading to 0.3) · moderate 0.3–0.7 (edges 0.1, 1) · high 1–2 (edges 0.7, 3) · very_high ≥3 (from 2)", "doc": "Ratio of the host TCP RetransSegs counter advance to the OutSegs counter advance, across host connections.", "elevated": 1, "formula": "ΔsystemMetrics/netstat/Tcp:RetransSegs ÷ ΔsystemMetrics/netstat/Tcp:OutSegs × 100, in %, at each available sample; minutes where the divisor sums to under 1000 are left out", "levels": [{"down": [0.1, 0.3], "name": "low"}, {"band": [0.1, 0.3, 0.7, 1], "name": "moderate"}, {"band": [0.7, 1, 2, 3], "name": "high"}, {"name": "very_high", "up": [2, 3]}], "min_change": 0.5, "name": "net.retransmit", "pack": "network", "pairs_with": ["repl.member_lag", "net.resets"], "reading": "each minute's ratio of sums", "signal": {"den": ["systemMetrics/netstat/Tcp:OutSegs"], "min_den": 1000, "mode": "rate", "num": ["systemMetrics/netstat/Tcp:RetransSegs"], "scale": 100, "unit": "%"}, "title": "TCP retransmission", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>net.listen_overflows</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none ≤0.01 (fading to 0.1) · some 0.1–1 (edges 0.01, 5) · many ≥5 (from 1)", "doc": "Rate of the host TCP ListenOverflows counter; the counter does not identify a MongoDB connection or client outcome.", "elevated": 0.1, "formula": "ΔsystemMetrics/netstat/TcpExt:ListenOverflows per second, in /s, at each available sample", "levels": [{"down": [0.01, 0.1], "name": "none"}, {"band": [0.01, 0.1, 1, 5], "name": "some"}, {"name": "many", "up": [1, 5]}], "min_change": 0.1, "name": "net.listen_overflows", "pack": "network", "pairs_with": ["connections.created", "cpu.busy_above_95"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["systemMetrics/netstat/TcpExt:ListenOverflows"], "scale": 1, "unit": "/s"}, "title": "Listen queue overflows", "unit": "/s", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>net.resets</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none — read for its shape only", "doc": "Established connections reset a second, host-wide.", "formula": "ΔsystemMetrics/netstat/Tcp:EstabResets per second, in /s, at each available sample", "min_change": 5, "name": "net.resets", "pack": "network", "pairs_with": ["connections.created", "net.retransmit"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["systemMetrics/netstat/Tcp:EstabResets"], "scale": 1, "unit": "/s"}, "title": "TCP connections reset", "unit": "/s", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>net.traffic</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none — read for its shape only", "doc": "Sum of the server's bytesIn and bytesOut counter rates, scaled to MB/s.", "formula": "Δ(serverStatus/network/bytesIn + serverStatus/network/bytesOut) per second × 1e-06, in MB/s, at each available sample", "min_change": 5, "name": "net.traffic", "pack": "network", "pairs_with": ["ops.total", "net.retransmit"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/network/bytesIn", "serverStatus/network/bytesOut"], "scale": 1e-06, "unit": "MB/s"}, "title": "mongod network traffic", "unit": "MB/s", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>tickets.read.used</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>before 8.0</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>{"applies": "From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.", "bands": "low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)", "doc": "Read tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.", "elevated": 75, "formula": "serverStatus/wiredTiger/concurrentTransactions/read/out ÷ serverStatus/wiredTiger/concurrentTransactions/read/totalTickets × 100, in %, at each available sample", "levels": [{"down": [25, 50], "name": "low"}, {"band": [25, 40, 65, 80], "name": "moderate"}, {"band": [65, 75, 90, 95], "name": "high"}, {"name": "near_full", "up": [90, 95]}], "min_change": 10, "name": "tickets.read.used", "pack": "admission", "pairs_with": ["tickets.read.scarce", "tickets.read.pool", "tickets.read.wait", "queue.readers"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/wiredTiger/concurrentTransactions/read/totalTickets"], "mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/read/out"], "scale": 100, "unit": "%"}, "title": "Read tickets in use", "unit": "%", "until": "8.0", "version_text": "before 8.0", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>tickets.read.scarce</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>before 8.0</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>{"applies": "From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which available read tickets were strictly below 10 % of the pool, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/wiredTiger/concurrentTransactions/read/available ÷ serverStatus/wiredTiger/concurrentTransactions/read/totalTickets × 100, in % available, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.read.scarce", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.read.empty", "tickets.read.used", "tickets.read.pool", "tickets.read.wait"], "reading": "valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/wiredTiger/concurrentTransactions/read/totalTickets"], "mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/read/available"], "scale": 100, "unit": "% available"}, "threshold": 10, "title": "Samples with under 10% of read tickets left", "unit": "s/min", "until": "8.0", "version_text": "before 8.0", "view": "time_below"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>tickets.read.empty</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>before 8.0</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>{"applies": "From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which fewer than 0.5 read tickets were available, that is none, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/wiredTiger/concurrentTransactions/read/available, in tickets left, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.read.empty", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.read.used", "tickets.read.scarce", "tickets.read.pool", "tickets.read.wait", "queue.readers"], "reading": "valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/read/available"], "scale": 1, "unit": "tickets left"}, "threshold": 0.5, "title": "Samples with no read ticket left", "unit": "s/min", "until": "8.0", "version_text": "before 8.0", "view": "time_below"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>tickets.read.pool</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>before 8.0</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none — read for its shape only", "doc": "How many read tickets the pool held, averaged over the minute.", "formula": "serverStatus/wiredTiger/concurrentTransactions/read/totalTickets, in tickets, at each available sample", "min_change": 4, "name": "tickets.read.pool", "pack": "admission", "pairs_with": ["tickets.read.used", "tickets.read.scarce"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/read/totalTickets"], "scale": 1, "unit": "tickets"}, "title": "Read ticket pool size", "unit": "tickets", "until": "8.0", "version_text": "before 8.0", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>tickets.read.wait</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>7.0 up to 8.0</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)", "doc": "Milliseconds a second operations spent queued for a read ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it.", "elevated": 100, "formula": "ΔserverStatus/wiredTiger/concurrentTransactions/read/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample", "levels": [{"down": [1, 10], "name": "none"}, {"band": [1, 10, 100, 500], "name": "some"}, {"name": "heavy", "up": [100, 500]}], "min_change": 10, "name": "tickets.read.wait", "pack": "admission", "pairs_with": ["tickets.read.empty", "tickets.read.scarce", "queue.readers"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/wiredTiger/concurrentTransactions/read/totalTimeQueuedMicros"], "scale": 0.001, "unit": "ms/s"}, "since": "7.0", "title": "Time waiting for a read ticket", "unit": "ms/s", "until": "8.0", "version_text": "7.0 up to 8.0", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>tickets.read.used</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>8.0 and later</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>{"applies": "From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.", "bands": "low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)", "doc": "Read tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.", "elevated": 75, "formula": "serverStatus/queues/execution/read/out ÷ serverStatus/queues/execution/read/totalTickets × 100, in %, at each available sample", "levels": [{"down": [25, 50], "name": "low"}, {"band": [25, 40, 65, 80], "name": "moderate"}, {"band": [65, 75, 90, 95], "name": "high"}, {"name": "near_full", "up": [90, 95]}], "min_change": 10, "name": "tickets.read.used", "pack": "admission", "pairs_with": ["tickets.read.scarce", "tickets.read.pool", "tickets.read.wait", "queue.readers"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/queues/execution/read/totalTickets"], "mode": "gauge", "num": ["serverStatus/queues/execution/read/out"], "scale": 100, "unit": "%"}, "since": "8.0", "title": "Read tickets in use", "unit": "%", "version_text": "8.0 and later", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>tickets.read.scarce</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>8.0 and later</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>{"applies": "From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which available read tickets were strictly below 10 % of the pool, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/queues/execution/read/available ÷ serverStatus/queues/execution/read/totalTickets × 100, in % available, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.read.scarce", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.read.empty", "tickets.read.used", "tickets.read.pool", "tickets.read.wait"], "reading": "valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/queues/execution/read/totalTickets"], "mode": "gauge", "num": ["serverStatus/queues/execution/read/available"], "scale": 100, "unit": "% available"}, "since": "8.0", "threshold": 10, "title": "Samples with under 10% of read tickets left", "unit": "s/min", "version_text": "8.0 and later", "view": "time_below"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>tickets.read.empty</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>8.0 and later</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>{"applies": "From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which fewer than 0.5 read tickets were available, that is none, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/queues/execution/read/available, in tickets left, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.read.empty", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.read.used", "tickets.read.scarce", "tickets.read.pool", "tickets.read.wait", "queue.readers"], "reading": "valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/queues/execution/read/available"], "scale": 1, "unit": "tickets left"}, "since": "8.0", "threshold": 0.5, "title": "Samples with no read ticket left", "unit": "s/min", "version_text": "8.0 and later", "view": "time_below"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>tickets.read.pool</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>8.0 and later</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none — read for its shape only", "doc": "How many read tickets the pool held, averaged over the minute.", "formula": "serverStatus/queues/execution/read/totalTickets, in tickets, at each available sample", "min_change": 4, "name": "tickets.read.pool", "pack": "admission", "pairs_with": ["tickets.read.used", "tickets.read.scarce"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/queues/execution/read/totalTickets"], "scale": 1, "unit": "tickets"}, "since": "8.0", "title": "Read ticket pool size", "unit": "tickets", "version_text": "8.0 and later", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>tickets.read.wait</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>8.0 and later</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)", "doc": "Milliseconds a second operations spent queued for a read ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. The counter covers normal-priority operations, not exempt operations.", "elevated": 100, "formula": "ΔserverStatus/queues/execution/read/normalPriority/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample", "levels": [{"down": [1, 10], "name": "none"}, {"band": [1, 10, 100, 500], "name": "some"}, {"name": "heavy", "up": [100, 500]}], "min_change": 10, "name": "tickets.read.wait", "pack": "admission", "pairs_with": ["tickets.read.empty", "tickets.read.scarce", "queue.readers"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/queues/execution/read/normalPriority/totalTimeQueuedMicros"], "scale": 0.001, "unit": "ms/s"}, "since": "8.0", "title": "Time waiting for a read ticket", "unit": "ms/s", "version_text": "8.0 and later", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>tickets.write.used</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>before 8.0</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>{"applies": "From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.", "bands": "low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)", "doc": "Write tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.", "elevated": 75, "formula": "serverStatus/wiredTiger/concurrentTransactions/write/out ÷ serverStatus/wiredTiger/concurrentTransactions/write/totalTickets × 100, in %, at each available sample", "levels": [{"down": [25, 50], "name": "low"}, {"band": [25, 40, 65, 80], "name": "moderate"}, {"band": [65, 75, 90, 95], "name": "high"}, {"name": "near_full", "up": [90, 95]}], "min_change": 10, "name": "tickets.write.used", "pack": "admission", "pairs_with": ["tickets.write.scarce", "tickets.write.pool", "tickets.write.wait", "queue.writers"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/wiredTiger/concurrentTransactions/write/totalTickets"], "mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/write/out"], "scale": 100, "unit": "%"}, "title": "Write tickets in use", "unit": "%", "until": "8.0", "version_text": "before 8.0", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>tickets.write.scarce</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>before 8.0</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>{"applies": "From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which available write tickets were strictly below 10 % of the pool, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/wiredTiger/concurrentTransactions/write/available ÷ serverStatus/wiredTiger/concurrentTransactions/write/totalTickets × 100, in % available, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.write.scarce", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.write.empty", "tickets.write.used", "tickets.write.pool", "tickets.write.wait"], "reading": "valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/wiredTiger/concurrentTransactions/write/totalTickets"], "mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/write/available"], "scale": 100, "unit": "% available"}, "threshold": 10, "title": "Samples with under 10% of write tickets left", "unit": "s/min", "until": "8.0", "version_text": "before 8.0", "view": "time_below"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>tickets.write.empty</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>before 8.0</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>{"applies": "From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which fewer than 0.5 write tickets were available, that is none, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/wiredTiger/concurrentTransactions/write/available, in tickets left, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.write.empty", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.write.used", "tickets.write.scarce", "tickets.write.pool", "tickets.write.wait", "queue.writers"], "reading": "valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/write/available"], "scale": 1, "unit": "tickets left"}, "threshold": 0.5, "title": "Samples with no write ticket left", "unit": "s/min", "until": "8.0", "version_text": "before 8.0", "view": "time_below"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>tickets.write.pool</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>before 8.0</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none — read for its shape only", "doc": "How many write tickets the pool held, averaged over the minute.", "formula": "serverStatus/wiredTiger/concurrentTransactions/write/totalTickets, in tickets, at each available sample", "min_change": 4, "name": "tickets.write.pool", "pack": "admission", "pairs_with": ["tickets.write.used", "tickets.write.scarce"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/write/totalTickets"], "scale": 1, "unit": "tickets"}, "title": "Write ticket pool size", "unit": "tickets", "until": "8.0", "version_text": "before 8.0", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>tickets.write.wait</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>7.0 up to 8.0</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)", "doc": "Milliseconds a second operations spent queued for a write ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it.", "elevated": 100, "formula": "ΔserverStatus/wiredTiger/concurrentTransactions/write/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample", "levels": [{"down": [1, 10], "name": "none"}, {"band": [1, 10, 100, 500], "name": "some"}, {"name": "heavy", "up": [100, 500]}], "min_change": 10, "name": "tickets.write.wait", "pack": "admission", "pairs_with": ["tickets.write.empty", "tickets.write.scarce", "queue.writers"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/wiredTiger/concurrentTransactions/write/totalTimeQueuedMicros"], "scale": 0.001, "unit": "ms/s"}, "since": "7.0", "title": "Time waiting for a write ticket", "unit": "ms/s", "until": "8.0", "version_text": "7.0 up to 8.0", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>tickets.write.used</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>8.0 and later</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>{"applies": "From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.", "bands": "low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)", "doc": "Write tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.", "elevated": 75, "formula": "serverStatus/queues/execution/write/out ÷ serverStatus/queues/execution/write/totalTickets × 100, in %, at each available sample", "levels": [{"down": [25, 50], "name": "low"}, {"band": [25, 40, 65, 80], "name": "moderate"}, {"band": [65, 75, 90, 95], "name": "high"}, {"name": "near_full", "up": [90, 95]}], "min_change": 10, "name": "tickets.write.used", "pack": "admission", "pairs_with": ["tickets.write.scarce", "tickets.write.pool", "tickets.write.wait", "queue.writers"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/queues/execution/write/totalTickets"], "mode": "gauge", "num": ["serverStatus/queues/execution/write/out"], "scale": 100, "unit": "%"}, "since": "8.0", "title": "Write tickets in use", "unit": "%", "version_text": "8.0 and later", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>tickets.write.scarce</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>8.0 and later</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>{"applies": "From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which available write tickets were strictly below 10 % of the pool, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/queues/execution/write/available ÷ serverStatus/queues/execution/write/totalTickets × 100, in % available, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.write.scarce", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.write.empty", "tickets.write.used", "tickets.write.pool", "tickets.write.wait"], "reading": "valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/queues/execution/write/totalTickets"], "mode": "gauge", "num": ["serverStatus/queues/execution/write/available"], "scale": 100, "unit": "% available"}, "since": "8.0", "threshold": 10, "title": "Samples with under 10% of write tickets left", "unit": "s/min", "version_text": "8.0 and later", "view": "time_below"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>tickets.write.empty</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>8.0 and later</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>{"applies": "From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which fewer than 0.5 write tickets were available, that is none, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/queues/execution/write/available, in tickets left, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.write.empty", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.write.used", "tickets.write.scarce", "tickets.write.pool", "tickets.write.wait", "queue.writers"], "reading": "valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/queues/execution/write/available"], "scale": 1, "unit": "tickets left"}, "since": "8.0", "threshold": 0.5, "title": "Samples with no write ticket left", "unit": "s/min", "version_text": "8.0 and later", "view": "time_below"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>tickets.write.pool</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>8.0 and later</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none — read for its shape only", "doc": "How many write tickets the pool held, averaged over the minute.", "formula": "serverStatus/queues/execution/write/totalTickets, in tickets, at each available sample", "min_change": 4, "name": "tickets.write.pool", "pack": "admission", "pairs_with": ["tickets.write.used", "tickets.write.scarce"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/queues/execution/write/totalTickets"], "scale": 1, "unit": "tickets"}, "since": "8.0", "title": "Write ticket pool size", "unit": "tickets", "version_text": "8.0 and later", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>tickets.write.wait</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>8.0 and later</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)", "doc": "Milliseconds a second operations spent queued for a write ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. The counter covers normal-priority operations, not exempt operations.", "elevated": 100, "formula": "ΔserverStatus/queues/execution/write/normalPriority/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample", "levels": [{"down": [1, 10], "name": "none"}, {"band": [1, 10, 100, 500], "name": "some"}, {"name": "heavy", "up": [100, 500]}], "min_change": 10, "name": "tickets.write.wait", "pack": "admission", "pairs_with": ["tickets.write.empty", "tickets.write.scarce", "queue.writers"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/queues/execution/write/normalPriority/totalTimeQueuedMicros"], "scale": 0.001, "unit": "ms/s"}, "since": "8.0", "title": "Time waiting for a write ticket", "unit": "ms/s", "version_text": "8.0 and later", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>queue.readers</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which globalLock.currentQueue.readers was above 0, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/globalLock/currentQueue/readers, in operations, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "queue.readers", "pack": "admission", "pairs_with": ["tickets.read.empty", "tickets.read.wait"], "reading": "valid-sample share strictly above 0 operations, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/globalLock/currentQueue/readers"], "scale": 1, "unit": "operations"}, "threshold": 0, "title": "Samples with reads queued", "unit": "s/min", "version_text": "all versions", "view": "time_above"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>queue.writers</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which globalLock.currentQueue.writers was above 0, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/globalLock/currentQueue/writers, in operations, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "queue.writers", "pack": "admission", "pairs_with": ["tickets.write.empty", "tickets.write.wait"], "reading": "valid-sample share strictly above 0 operations, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/globalLock/currentQueue/writers"], "scale": 1, "unit": "operations"}, "threshold": 0, "title": "Samples with writes queued", "unit": "s/min", "version_text": "all versions", "view": "time_above"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>cache.fill</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "low ≤50 (fading to 70) · normal 70–80 (edges 50, 86) · high 86–93 (edges 80, 95) · above_reference ≥96 (from 94)", "doc": "Bytes in the WiredTiger cache as a share of its configured size, averaged over the minute.", "elevated": 95, "formula": "serverStatus/wiredTiger/cache/bytes currently in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample", "levels": [{"down": [50, 70], "name": "low"}, {"band": [50, 70, 80, 86], "name": "normal"}, {"band": [80, 86, 93, 95], "name": "high"}, {"name": "above_reference", "up": [94, 96]}], "min_change": 5, "name": "cache.fill", "pack": "storage-engine", "pairs_with": ["cache.fill_above_95", "cache.app_eviction", "cache.read_in"], "reading": "each minute's ratio of sums", "reference": {"configured": "not read", "source": "WiredTiger default eviction_trigger; eviction_target defaults to 80", "unit": "%", "value": 95}, "signal": {"den": ["serverStatus/wiredTiger/cache/maximum bytes configured"], "mode": "gauge", "num": ["serverStatus/wiredTiger/cache/bytes currently in the cache"], "scale": 100, "unit": "%"}, "title": "WiredTiger cache fill", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>cache.fill_above_95</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which WiredTiger cache bytes were strictly above 95 % of the configured cache size, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/wiredTiger/cache/bytes currently in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "cache.fill_above_95", "pack": "storage-engine", "pairs_with": ["cache.fill", "cache.app_eviction", "tickets.read.scarce"], "reading": "valid-sample share strictly above 95 %, normalized to 60 s/min; not continuous elapsed time", "reference": {"configured": "not read", "source": "WiredTiger default eviction_trigger", "unit": "%", "value": 95}, "signal": {"den": ["serverStatus/wiredTiger/cache/maximum bytes configured"], "mode": "gauge", "num": ["serverStatus/wiredTiger/cache/bytes currently in the cache"], "scale": 100, "unit": "%"}, "threshold": 95, "title": "Cache-fill samples above 95%", "unit": "s/min", "version_text": "all versions", "view": "time_above"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>cache.dirty</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "low ≤3 (fading to 6) · normal 6–8 (edges 3, 12) · high 12–18 (edges 8, 20) · above_reference ≥21 (from 19)", "doc": "Modified bytes not yet written, as a share of the configured cache, averaged over the minute.", "elevated": 20, "formula": "serverStatus/wiredTiger/cache/tracked dirty bytes in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample", "levels": [{"down": [3, 6], "name": "low"}, {"band": [3, 6, 8, 12], "name": "normal"}, {"band": [8, 12, 18, 20], "name": "high"}, {"name": "above_reference", "up": [19, 21]}], "min_change": 3, "name": "cache.dirty", "pack": "storage-engine", "pairs_with": ["cache.dirty_above_20", "checkpoint.duration", "disk.write_await", "ops.writes"], "reading": "each minute's ratio of sums", "reference": {"configured": "not read", "source": "WiredTiger default eviction_dirty_trigger; eviction_dirty_target defaults to 5", "unit": "%", "value": 20}, "signal": {"den": ["serverStatus/wiredTiger/cache/maximum bytes configured"], "mode": "gauge", "num": ["serverStatus/wiredTiger/cache/tracked dirty bytes in the cache"], "scale": 100, "unit": "%"}, "title": "WiredTiger dirty cache", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>cache.dirty_above_20</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which tracked dirty bytes were strictly above 20 % of the configured cache size, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/wiredTiger/cache/tracked dirty bytes in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "cache.dirty_above_20", "pack": "storage-engine", "pairs_with": ["cache.dirty", "checkpoint.running", "tickets.write.scarce"], "reading": "valid-sample share strictly above 20 %, normalized to 60 s/min; not continuous elapsed time", "reference": {"configured": "not read", "source": "WiredTiger default eviction_dirty_trigger", "unit": "%", "value": 20}, "signal": {"den": ["serverStatus/wiredTiger/cache/maximum bytes configured"], "mode": "gauge", "num": ["serverStatus/wiredTiger/cache/tracked dirty bytes in the cache"], "scale": 100, "unit": "%"}, "threshold": 20, "title": "Dirty-cache samples above 20%", "unit": "s/min", "version_text": "all versions", "view": "time_above"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>cache.app_eviction</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>before 8.0.16</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none ≤0.1 (fading to 1) · some 1–10 (edges 0.1, 50) · heavy ≥50 (from 10)", "doc": "Rate of pages evicted by application threads; where the version uses attempts and failures, the signal subtracts failure counts from attempt counts.", "elevated": 1, "formula": "ΔserverStatus/wiredTiger/cache/pages evicted by application threads per second, in pages/s, at each available sample", "levels": [{"down": [0.1, 1], "name": "none"}, {"band": [0.1, 1, 10, 50], "name": "some"}, {"name": "heavy", "up": [10, 50]}], "min_change": 5, "name": "cache.app_eviction", "pack": "storage-engine", "pairs_with": ["cache.fill_above_95", "cache.dirty_above_20"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/wiredTiger/cache/pages evicted by application threads"], "scale": 1, "unit": "pages/s"}, "title": "Eviction by application threads", "unit": "pages/s", "until": "8.0.16", "version_text": "before 8.0.16", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>cache.app_eviction</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>8.0.16 and later</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none ≤0.1 (fading to 1) · some 1–10 (edges 0.1, 50) · heavy ≥50 (from 10)", "doc": "Rate of pages evicted by application threads; where the version uses attempts and failures, the signal subtracts failure counts from attempt counts.", "elevated": 1, "formula": "ΔserverStatus/wiredTiger/cache/page evict attempts by application threads − serverStatus/wiredTiger/cache/page evict failures by application threads per second, in pages/s, at each available sample", "levels": [{"down": [0.1, 1], "name": "none"}, {"band": [0.1, 1, 10, 50], "name": "some"}, {"name": "heavy", "up": [10, 50]}], "min_change": 5, "name": "cache.app_eviction", "pack": "storage-engine", "pairs_with": ["cache.fill_above_95", "cache.dirty_above_20", "cache.app_eviction_time"], "reading": "each minute's mean", "signal": {"minus": ["serverStatus/wiredTiger/cache/page evict failures by application threads"], "mode": "rate", "num": ["serverStatus/wiredTiger/cache/page evict attempts by application threads"], "scale": 1, "unit": "pages/s"}, "since": "8.0.16", "title": "Eviction by application threads", "unit": "pages/s", "version_text": "8.0.16 and later", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>cache.app_eviction_time</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>8.0 and later</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)", "doc": "Application-thread eviction time counter advance per elapsed second, summed across threads, in milliseconds.", "elevated": 100, "formula": "ΔserverStatus/wiredTiger/cache/application thread time evicting (usecs) per second × 0.001, in ms/s, at each available sample", "levels": [{"down": [1, 10], "name": "none"}, {"band": [1, 10, 100, 500], "name": "some"}, {"name": "heavy", "up": [100, 500]}], "min_change": 10, "name": "cache.app_eviction_time", "pack": "storage-engine", "pairs_with": ["cache.app_eviction", "cache.fill_above_95", "cache.dirty_above_20"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/wiredTiger/cache/application thread time evicting (usecs)"], "scale": 0.001, "unit": "ms/s"}, "since": "8.0", "title": "Time operations spent evicting", "unit": "ms/s", "version_text": "8.0 and later", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>cache.read_in</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none — read for its shape only", "doc": "WiredTiger bytes-read-into-cache counter advance per elapsed second, scaled to MB/s.", "formula": "ΔserverStatus/wiredTiger/cache/bytes read into cache per second × 1e-06, in MB/s, at each available sample", "min_change": 5, "name": "cache.read_in", "pack": "storage-engine", "pairs_with": ["disk.read_await", "query.collscans", "cache.fill"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/wiredTiger/cache/bytes read into cache"], "scale": 1e-06, "unit": "MB/s"}, "title": "Data read into the cache", "unit": "MB/s", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>checkpoint.duration</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>before 7.1</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "quick ≤5 (fading to 15) · slow 15–40 (edges 5, 60) · back_to_back ≥60 (from 50)", "doc": "Duration recorded for the most recent WiredTiger checkpoint; the same completed-checkpoint value may appear in multiple samples. Minute summaries select the highest valid sample.", "elevated": 60, "formula": "serverStatus/wiredTiger/transaction/transaction checkpoint most recent time (msecs) × 0.001, in s, at each available sample", "levels": [{"down": [5, 15], "name": "quick"}, {"band": [5, 15, 40, 60], "name": "slow"}, {"name": "back_to_back", "up": [50, 60]}], "min_change": 10, "name": "checkpoint.duration", "pack": "storage-engine", "pairs_with": ["checkpoint.running", "cache.dirty", "disk.write_await"], "reading": "the highest valid sample of each minute", "reference": {"configured": "not read", "source": "default checkpoint interval, storage.syncPeriodSecs", "unit": "s", "value": 60}, "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/transaction/transaction checkpoint most recent time (msecs)"], "scale": 0.001, "unit": "s"}, "title": "Checkpoint duration", "unit": "s", "until": "7.1", "version_text": "before 7.1", "view": "max"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>checkpoint.duration</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>7.1 and later</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "quick ≤5 (fading to 15) · slow 15–40 (edges 5, 60) · back_to_back ≥60 (from 50)", "doc": "Duration recorded for the most recent WiredTiger checkpoint; the same completed-checkpoint value may appear in multiple samples. Minute summaries select the highest valid sample.", "elevated": 60, "formula": "serverStatus/wiredTiger/checkpoint/most recent time (msecs) × 0.001, in s, at each available sample", "levels": [{"down": [5, 15], "name": "quick"}, {"band": [5, 15, 40, 60], "name": "slow"}, {"name": "back_to_back", "up": [50, 60]}], "min_change": 10, "name": "checkpoint.duration", "pack": "storage-engine", "pairs_with": ["checkpoint.running", "cache.dirty", "disk.write_await"], "reading": "the highest valid sample of each minute", "reference": {"configured": "not read", "source": "default checkpoint interval, storage.syncPeriodSecs", "unit": "s", "value": 60}, "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/checkpoint/most recent time (msecs)"], "scale": 0.001, "unit": "s"}, "since": "7.1", "title": "Checkpoint duration", "unit": "s", "version_text": "7.1 and later", "view": "max"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>checkpoint.running</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>before 7.1</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "brief ≤12 (fading to 24) · long 24–42 (edges 12, 54) · continuous ≥57 (from 48)", "doc": "Share of valid samples in which WiredTiger reported a checkpoint as currently running, normalized to a 60-second minute.", "elevated": 48, "formula": "serverStatus/wiredTiger/transaction/transaction checkpoint currently running, in running, at each available sample", "levels": [{"down": [12, 24], "name": "brief"}, {"band": [12, 24, 42, 54], "name": "long"}, {"name": "continuous", "up": [48, 57]}], "min_change": 9, "name": "checkpoint.running", "pack": "storage-engine", "pairs_with": ["checkpoint.duration", "disk.busy_above_95", "cache.dirty"], "reading": "valid-sample share strictly above 0 running, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/transaction/transaction checkpoint currently running"], "scale": 1, "unit": "running"}, "threshold": 0, "title": "Samples with checkpoint activity", "unit": "s/min", "until": "7.1", "version_text": "before 7.1", "view": "time_above"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>checkpoint.running</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>7.1 and later</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>{"applies": "The progress state's values are not decoded; any non-zero value is read as activity.", "bands": "brief ≤12 (fading to 24) · long 24–42 (edges 12, 54) · continuous ≥57 (from 48)", "doc": "Share of valid samples in which WiredTiger's checkpoint progress state was non-zero, normalized to a 60-second minute.", "elevated": 48, "formula": "serverStatus/wiredTiger/checkpoint/progress state, in state, at each available sample", "levels": [{"down": [12, 24], "name": "brief"}, {"band": [12, 24, 42, 54], "name": "long"}, {"name": "continuous", "up": [48, 57]}], "min_change": 9, "name": "checkpoint.running", "pack": "storage-engine", "pairs_with": ["checkpoint.duration", "disk.busy_above_95", "cache.dirty"], "reading": "valid-sample share strictly above 0 state, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/checkpoint/progress state"], "scale": 1, "unit": "state"}, "since": "7.1", "threshold": 0, "title": "Samples with checkpoint activity", "unit": "s/min", "version_text": "7.1 and later", "view": "time_above"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>storage.open_handles</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none — read for its shape only", "doc": "Count reported by WiredTiger for currently open data handles.", "formula": "serverStatus/wiredTiger/data-handle/connection data handles currently active, in handles, at each available sample", "min_change": 500, "name": "storage.open_handles", "pack": "storage-engine", "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/data-handle/connection data handles currently active"], "scale": 1, "unit": "handles"}, "title": "Open data handles", "unit": "handles", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>latency.reads</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "fast ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · slow 20–50 (edges 10, 100) · very_slow ≥100 (from 50)", "doc": "Average milliseconds per read operation over each minute, from opLatencies: every microsecond spent on reads in the minute over every read that finished in it.", "elevated": 50, "formula": "ΔserverStatus/opLatencies/reads/latency ÷ ΔserverStatus/opLatencies/reads/ops × 0.001, in ms, at each available sample; minutes where the divisor sums to under 60 are left out", "levels": [{"down": [1, 3], "name": "fast"}, {"band": [1, 3, 10, 20], "name": "normal"}, {"band": [10, 20, 50, 100], "name": "slow"}, {"name": "very_slow", "up": [50, 100]}], "min_change": 5, "name": "latency.reads", "pack": "workload", "pairs_with": ["tickets.read.scarce", "query.targeting", "cache.fill_above_95", "disk.read_await"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/opLatencies/reads/ops"], "min_den": 60, "mode": "rate", "num": ["serverStatus/opLatencies/reads/latency"], "scale": 0.001, "unit": "ms"}, "title": "Read latency", "unit": "ms", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>latency.writes</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "fast ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · slow 20–50 (edges 10, 100) · very_slow ≥100 (from 50)", "doc": "Average milliseconds per write operation over each minute, from opLatencies.", "elevated": 50, "formula": "ΔserverStatus/opLatencies/writes/latency ÷ ΔserverStatus/opLatencies/writes/ops × 0.001, in ms, at each available sample; minutes where the divisor sums to under 60 are left out", "levels": [{"down": [1, 3], "name": "fast"}, {"band": [1, 3, 10, 20], "name": "normal"}, {"band": [10, 20, 50, 100], "name": "slow"}, {"name": "very_slow", "up": [50, 100]}], "min_change": 5, "name": "latency.writes", "pack": "workload", "pairs_with": ["tickets.write.scarce", "cache.dirty_above_20", "flow.lagged", "repl.majority_lag"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/opLatencies/writes/ops"], "min_den": 60, "mode": "rate", "num": ["serverStatus/opLatencies/writes/latency"], "scale": 0.001, "unit": "ms"}, "title": "Write latency", "unit": "ms", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>latency.commands</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "fast ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · slow 20–50 (edges 10, 100) · very_slow ≥100 (from 50)", "doc": "Ratio of command opLatencies counter advance to command operation-count advance, scaled to milliseconds per operation.", "elevated": 50, "formula": "ΔserverStatus/opLatencies/commands/latency ÷ ΔserverStatus/opLatencies/commands/ops × 0.001, in ms, at each available sample; minutes where the divisor sums to under 60 are left out", "levels": [{"down": [1, 3], "name": "fast"}, {"band": [1, 3, 10, 20], "name": "normal"}, {"band": [10, 20, 50, 100], "name": "slow"}, {"name": "very_slow", "up": [50, 100]}], "min_change": 5, "name": "latency.commands", "pack": "workload", "pairs_with": ["tickets.read.scarce", "query.targeting"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/opLatencies/commands/ops"], "min_den": 60, "mode": "rate", "num": ["serverStatus/opLatencies/commands/latency"], "scale": 0.001, "unit": "ms"}, "title": "Command latency", "unit": "ms", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>ops.total</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none — read for its shape only", "doc": "Sum of query, getMore, insert, update, delete and command operation-counter rates.", "formula": "Δ(serverStatus/opcounters/query + serverStatus/opcounters/getmore + serverStatus/opcounters/insert + serverStatus/opcounters/update + serverStatus/opcounters/delete + serverStatus/opcounters/command) per second, in ops/s, at each available sample", "min_change": 50, "name": "ops.total", "pack": "workload", "pairs_with": ["ops.writes", "connections.current"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/opcounters/query", "serverStatus/opcounters/getmore", "serverStatus/opcounters/insert", "serverStatus/opcounters/update", "serverStatus/opcounters/delete", "serverStatus/opcounters/command"], "scale": 1, "unit": "ops/s"}, "title": "Operations a second", "unit": "ops/s", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>ops.writes</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none — read for its shape only", "doc": "Sum of insert, update and delete operation-counter rates.", "formula": "Δ(serverStatus/opcounters/insert + serverStatus/opcounters/update + serverStatus/opcounters/delete) per second, in ops/s, at each available sample", "min_change": 50, "name": "ops.writes", "pack": "workload", "pairs_with": ["cache.dirty", "checkpoint.duration"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/opcounters/insert", "serverStatus/opcounters/update", "serverStatus/opcounters/delete"], "scale": 1, "unit": "ops/s"}, "title": "Writes a second", "unit": "ops/s", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>query.targeting</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "low ≤2 (fading to 10) · moderate 10–50 (edges 2, 100) · high 100–500 (edges 50, 1000) · very_high ≥1000 (from 500)", "doc": "Ratio of documents-examined counter advance to documents-returned counter advance; it does not determine index suitability.", "elevated": 100, "formula": "ΔserverStatus/metrics/queryExecutor/scannedObjects ÷ ΔserverStatus/metrics/document/returned, in ratio, at each available sample; minutes where the divisor sums to under 60 are left out", "levels": [{"down": [2, 10], "name": "low"}, {"band": [2, 10, 50, 100], "name": "moderate"}, {"band": [50, 100, 500, 1000], "name": "high"}, {"name": "very_high", "up": [500, 1000]}], "min_change": 10, "name": "query.targeting", "pack": "workload", "pairs_with": ["query.collscans", "cache.read_in", "cpu.busy"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/metrics/document/returned"], "min_den": 60, "mode": "rate", "num": ["serverStatus/metrics/queryExecutor/scannedObjects"], "scale": 1, "unit": "ratio"}, "title": "Documents examined per document returned", "unit": "ratio", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>query.collscans</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>4.4 and later</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none ≤0.01 (fading to 0.1) · some 0.1–1 (edges 0.01, 10) · many ≥10 (from 1)", "doc": "Rate of the server's collection-scan counter.", "elevated": 1, "formula": "ΔserverStatus/metrics/queryExecutor/collectionScans/total per second, in /s, at each available sample", "levels": [{"down": [0.01, 0.1], "name": "none"}, {"band": [0.01, 0.1, 1, 10], "name": "some"}, {"name": "many", "up": [1, 10]}], "min_change": 0.5, "name": "query.collscans", "pack": "workload", "pairs_with": ["query.targeting", "cache.read_in"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/metrics/queryExecutor/collectionScans/total"], "scale": 1, "unit": "/s"}, "since": "4.4", "title": "Collection scans", "unit": "/s", "version_text": "4.4 and later", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>query.scan_and_order</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none — read for its shape only", "doc": "Rate of the server's scanAndOrder counter.", "formula": "ΔserverStatus/metrics/operation/scanAndOrder per second, in /s, at each available sample", "min_change": 1, "name": "query.scan_and_order", "pack": "workload", "pairs_with": ["query.targeting", "memory.heap_outside_cache"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/metrics/operation/scanAndOrder"], "scale": 1, "unit": "/s"}, "title": "scanAndOrder counter rate", "unit": "/s", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>writes.conflicts</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "rare ≤0.1 (fading to 1) · some 1–10 (edges 0.1, 50) · heavy ≥50 (from 10)", "doc": "Rate of the server's writeConflicts counter; retries, document identity and contention cause are not inferred from this counter.", "elevated": 10, "formula": "ΔserverStatus/metrics/operation/writeConflicts per second, in /s, at each available sample", "levels": [{"down": [0.1, 1], "name": "rare"}, {"band": [0.1, 1, 10, 50], "name": "some"}, {"name": "heavy", "up": [10, 50]}], "min_change": 2, "name": "writes.conflicts", "pack": "workload", "pairs_with": ["ops.writes", "latency.writes"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/metrics/operation/writeConflicts"], "scale": 1, "unit": "/s"}, "title": "Write conflicts", "unit": "/s", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>ttl.deletes</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none — read for its shape only", "doc": "Rate of documents reported deleted by the TTL monitor; collection identity, expiry backlog and latency impact are not inferred.", "formula": "ΔserverStatus/metrics/ttl/deletedDocuments per second, in docs/s, at each available sample", "min_change": 50, "name": "ttl.deletes", "pack": "workload", "pairs_with": ["cache.dirty", "disk.write_await", "repl.member_lag"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/metrics/ttl/deletedDocuments"], "scale": 1, "unit": "docs/s"}, "title": "Documents deleted by TTL", "unit": "docs/s", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>cursors.open</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none — read for its shape only", "doc": "Count reported for currently open cursors.", "formula": "serverStatus/metrics/cursor/open/total, in cursors, at each available sample", "min_change": 50, "name": "cursors.open", "pack": "workload", "pairs_with": ["memory.heap_outside_cache", "connections.current"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/metrics/cursor/open/total"], "scale": 1, "unit": "cursors"}, "title": "Open cursors", "unit": "cursors", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>repl.member_lag</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>before 6.0</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>{"applies": "One result per entry of this node's replica-set status, numbered by position in that list; a position can name a different member after a reconfig. Lag is measured against the newest applied time among members, not against the primary, and a member that stopped reporting keeps its last time.", "bands": "current ≤2 (fading to 5) · behind 5–20 (edges 2, 30) · lagging 30–120 (edges 20, 300) · far_behind ≥300 (from 120)", "doc": "Difference between each member's reported applied-write timestamp and the newest such timestamp in this node's replica-set status, scaled to seconds. Members without a timestamp have no result. optimeDate has one-second resolution. Minute summaries select the highest valid sample.", "elevated": 30, "formula": "newest of every replSetGetStatus/members/{i}/optimeDate − this one × 0.001, in s, at each available sample", "levels": [{"down": [2, 5], "name": "current"}, {"band": [2, 5, 20, 30], "name": "behind"}, {"band": [20, 30, 120, 300], "name": "lagging"}, {"name": "far_behind", "up": [120, 300]}], "min_change": 5, "name": "repl.member_lag", "pack": "replication", "pairs_with": ["repl.majority_lag", "flow.lagged", "net.retransmit"], "reading": "the highest valid sample of each minute", "signal": {"behind": true, "mode": "gauge", "num": ["replSetGetStatus/members/{i}/optimeDate"], "scale": 0.001, "unit": "s"}, "title": "Member replication lag", "unit": "s", "until": "6.0", "version_text": "before 6.0", "view": "max"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>repl.member_lag</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>6.0 and later</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>{"applies": "One result per entry of this node's replica-set status, numbered by position in that list; a position can name a different member after a reconfig. Lag is measured against the newest applied time among members, not against the primary, and a member that stopped reporting keeps its last time.", "bands": "current ≤2 (fading to 5) · behind 5–20 (edges 2, 30) · lagging 30–120 (edges 20, 300) · far_behind ≥300 (from 120)", "doc": "Difference between each member's reported applied-write timestamp and the newest such timestamp in this node's replica-set status, scaled to seconds. Members without a timestamp have no result. Minute summaries select the highest valid sample.", "elevated": 30, "formula": "newest of every replSetGetStatus/members/{i}/lastAppliedWallTime − this one × 0.001, in s, at each available sample", "levels": [{"down": [2, 5], "name": "current"}, {"band": [2, 5, 20, 30], "name": "behind"}, {"band": [20, 30, 120, 300], "name": "lagging"}, {"name": "far_behind", "up": [120, 300]}], "min_change": 5, "name": "repl.member_lag", "pack": "replication", "pairs_with": ["repl.majority_lag", "flow.lagged", "net.retransmit"], "reading": "the highest valid sample of each minute", "signal": {"behind": true, "mode": "gauge", "num": ["replSetGetStatus/members/{i}/lastAppliedWallTime"], "scale": 0.001, "unit": "s"}, "since": "6.0", "title": "Member replication lag", "unit": "s", "version_text": "6.0 and later", "view": "max"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>repl.majority_lag</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>4.2 and later</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "current ≤1 (fading to 3) · behind 3–10 (edges 1, 20) · lagging ≥20 (from 10)", "doc": "Difference between this node's lastAppliedWallTime and lastCommittedWallTime, scaled to seconds. Minute summaries select the highest valid sample.", "elevated": 10, "formula": "replSetGetStatus/optimes/lastAppliedWallTime − replSetGetStatus/optimes/lastCommittedWallTime × 0.001, in s, at each available sample", "levels": [{"down": [1, 3], "name": "current"}, {"band": [1, 3, 10, 20], "name": "behind"}, {"name": "lagging", "up": [10, 20]}], "min_change": 2, "name": "repl.majority_lag", "pack": "replication", "pairs_with": ["repl.member_lag", "flow.lagged", "latency.writes"], "reading": "the highest valid sample of each minute", "signal": {"minus": ["replSetGetStatus/optimes/lastCommittedWallTime"], "mode": "gauge", "num": ["replSetGetStatus/optimes/lastAppliedWallTime"], "scale": 0.001, "unit": "s"}, "since": "4.2", "title": "Majority commit lag", "unit": "s", "version_text": "4.2 and later", "view": "max"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>flow.lagged</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>{"applies": "Set only on a primary with flow control enabled; a secondary, or a primary with flow control disabled, reports it unset. The flag records that the majority commit point lagged; time writers spent waiting for flow control is flow.wait.", "bands": "none ≤0 (fading to 1) · some 1–30 (edges 0, 48) · most ≥48 (from 30)", "doc": "Share of valid samples in which flowControl.isLagged was set, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/flowControl/isLagged, in lagged, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 30, 48], "name": "some"}, {"name": "most", "up": [30, 48]}], "min_change": 3, "name": "flow.lagged", "pack": "replication", "pairs_with": ["flow.wait", "repl.majority_lag", "latency.writes"], "reading": "valid-sample share strictly above 0 lagged, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/flowControl/isLagged"], "scale": 1, "unit": "lagged"}, "threshold": 0, "title": "Samples with flowControl.isLagged set", "unit": "s/min", "version_text": "all versions", "view": "time_above"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>flow.wait</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)", "doc": "Milliseconds a second writes spent waiting for flow control tickets on this node, added across every write waiting.", "elevated": 100, "formula": "ΔserverStatus/flowControl/timeAcquiringMicros per second × 0.001, in ms/s, at each available sample", "levels": [{"down": [1, 10], "name": "none"}, {"band": [1, 10, 100, 500], "name": "some"}, {"name": "heavy", "up": [100, 500]}], "min_change": 10, "name": "flow.wait", "pack": "replication", "pairs_with": ["flow.lagged", "latency.writes"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/flowControl/timeAcquiringMicros"], "scale": 0.001, "unit": "ms/s"}, "title": "Time writers waited on flow control", "unit": "ms/s", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>repl.apply_rate</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none — read for its shape only", "direction": "down", "doc": "Rate of the node's oplog application operation counter.", "formula": "ΔserverStatus/metrics/repl/apply/ops per second, in ops/s, at each available sample", "min_change": 50, "name": "repl.apply_rate", "pack": "replication", "pairs_with": ["repl.buffer_fill", "repl.member_lag"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/metrics/repl/apply/ops"], "scale": 1, "unit": "ops/s"}, "title": "Oplog entries applied", "unit": "ops/s", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>repl.buffer_fill</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>before 8.0</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "empty ≤5 (fading to 20) · filling 20–60 (edges 5, 85) · full ≥90 (from 70)", "doc": "Reported replication buffer bytes as a share of its reported maximum.", "elevated": 70, "formula": "serverStatus/metrics/repl/buffer/sizeBytes ÷ serverStatus/metrics/repl/buffer/maxSizeBytes × 100, in %, at each available sample", "levels": [{"down": [5, 20], "name": "empty"}, {"band": [5, 20, 60, 85], "name": "filling"}, {"name": "full", "up": [70, 90]}], "min_change": 10, "name": "repl.buffer_fill", "pack": "replication", "pairs_with": ["repl.buffer_full", "repl.apply_rate", "repl.member_lag"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/metrics/repl/buffer/maxSizeBytes"], "mode": "gauge", "num": ["serverStatus/metrics/repl/buffer/sizeBytes"], "scale": 100, "unit": "%"}, "title": "Apply buffer fill", "unit": "%", "until": "8.0", "version_text": "before 8.0", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>repl.buffer_fill</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>8.0 and later</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "empty ≤5 (fading to 20) · filling 20–60 (edges 5, 85) · full ≥90 (from 70)", "doc": "Reported replication buffer bytes as a share of its reported maximum.", "elevated": 70, "formula": "serverStatus/metrics/repl/buffer/apply/sizeBytes ÷ serverStatus/metrics/repl/buffer/apply/maxSizeBytes × 100, in %, at each available sample", "levels": [{"down": [5, 20], "name": "empty"}, {"band": [5, 20, 60, 85], "name": "filling"}, {"name": "full", "up": [70, 90]}], "min_change": 10, "name": "repl.buffer_fill", "pack": "replication", "pairs_with": ["repl.buffer_full", "repl.apply_rate", "repl.member_lag"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/metrics/repl/buffer/apply/maxSizeBytes"], "mode": "gauge", "num": ["serverStatus/metrics/repl/buffer/apply/sizeBytes"], "scale": 100, "unit": "%"}, "since": "8.0", "title": "Apply buffer fill", "unit": "%", "version_text": "8.0 and later", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>repl.buffer_full</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>before 8.0</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which replication buffer bytes were strictly above 90 % of the reported maximum, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/metrics/repl/buffer/sizeBytes ÷ serverStatus/metrics/repl/buffer/maxSizeBytes × 100, in %, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "repl.buffer_full", "pack": "replication", "pairs_with": ["repl.buffer_fill", "repl.apply_rate"], "reading": "valid-sample share strictly above 90 %, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/metrics/repl/buffer/maxSizeBytes"], "mode": "gauge", "num": ["serverStatus/metrics/repl/buffer/sizeBytes"], "scale": 100, "unit": "%"}, "threshold": 90, "title": "Apply-buffer samples above 90%", "unit": "s/min", "until": "8.0", "version_text": "before 8.0", "view": "time_above"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>repl.buffer_full</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>8.0 and later</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which replication buffer bytes were strictly above 90 % of the reported maximum, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/metrics/repl/buffer/apply/sizeBytes ÷ serverStatus/metrics/repl/buffer/apply/maxSizeBytes × 100, in %, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "repl.buffer_full", "pack": "replication", "pairs_with": ["repl.buffer_fill", "repl.apply_rate"], "reading": "valid-sample share strictly above 90 %, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/metrics/repl/buffer/apply/maxSizeBytes"], "mode": "gauge", "num": ["serverStatus/metrics/repl/buffer/apply/sizeBytes"], "scale": 100, "unit": "%"}, "since": "8.0", "threshold": 90, "title": "Apply-buffer samples above 90%", "unit": "s/min", "version_text": "8.0 and later", "view": "time_above"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>connections.used</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "low ≤25 (fading to 50) · moderate 50–70 (edges 25, 85) · high 85–90 (edges 70, 95) · near_limit ≥95 (from 90)", "doc": "Reported current connections divided by current plus available connections.", "elevated": 85, "formula": "serverStatus/connections/current ÷ (serverStatus/connections/current + serverStatus/connections/available) × 100, in %, at each available sample", "levels": [{"down": [25, 50], "name": "low"}, {"band": [25, 50, 70, 85], "name": "moderate"}, {"band": [70, 85, 90, 95], "name": "high"}, {"name": "near_limit", "up": [90, 95]}], "min_change": 10, "name": "connections.used", "pack": "connections", "pairs_with": ["connections.scarce", "connections.created", "connections.rejected"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/connections/current", "serverStatus/connections/available"], "mode": "gauge", "num": ["serverStatus/connections/current"], "scale": 100, "unit": "%"}, "title": "Current connections as a share of current plus available", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>connections.scarce</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which available connections were strictly below 10 % of current plus available, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/connections/available ÷ (serverStatus/connections/current + serverStatus/connections/available) × 100, in % available, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "connections.scarce", "open_at": "brief", "pack": "connections", "pairs_with": ["connections.used", "connections.created", "connections.rejected"], "reading": "valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/connections/current", "serverStatus/connections/available"], "mode": "gauge", "num": ["serverStatus/connections/available"], "scale": 100, "unit": "% available"}, "threshold": 10, "title": "Samples with under 10% of connections left", "unit": "s/min", "version_text": "all versions", "view": "time_below"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>connections.created</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "quiet ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · high ≥20 (from 10)", "doc": "Rate of the server's totalCreated connection counter.", "elevated": 20, "formula": "ΔserverStatus/connections/totalCreated per second, in conn/s, at each available sample", "levels": [{"down": [1, 3], "name": "quiet"}, {"band": [1, 3, 10, 20], "name": "normal"}, {"name": "high", "up": [10, 20]}], "min_change": 5, "name": "connections.created", "pack": "connections", "pairs_with": ["connections.current", "cpu.kernel_share", "net.resets"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/connections/totalCreated"], "scale": 1, "unit": "conn/s"}, "title": "New connections", "unit": "conn/s", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>connections.non_active</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>4.4 and later</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "few ≤300 (fading to 800) · many 800–1500 (edges 300, 2500) · very_high ≥3000 (from 1500)", "doc": "Derived connection count: current plus awaitingTopologyChanges minus active; it is not evidence of unused client pools or a connection leak.", "elevated": 2000, "formula": "(serverStatus/connections/current + serverStatus/connections/awaitingTopologyChanges) − serverStatus/connections/active, in conns, at each available sample", "levels": [{"down": [300, 800], "name": "few"}, {"band": [300, 800, 1500, 2500], "name": "many"}, {"name": "very_high", "up": [1500, 3000]}], "min_change": 100, "name": "connections.non_active", "pack": "connections", "pairs_with": ["connections.current", "connections.created", "connections.working_share", "memory.heap_outside_cache"], "reading": "each minute's mean", "signal": {"minus": ["serverStatus/connections/active"], "mode": "gauge", "num": ["serverStatus/connections/current", "serverStatus/connections/awaitingTopologyChanges"], "scale": 1, "unit": "conns"}, "since": "4.4", "title": "Derived non-active connection count", "unit": "conns", "version_text": "4.4 and later", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>connections.working_share</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>4.4 and later</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "calm ≤10 (fading to 25) · busy 25–40 (edges 10, 60) · high ≥60 (from 40)", "doc": "Derived active-connection share: active minus awaitingTopologyChanges divided by current connections. Minute summaries select the highest valid sample.", "elevated": 40, "formula": "serverStatus/connections/active − serverStatus/connections/awaitingTopologyChanges ÷ serverStatus/connections/current × 100, in %, at each available sample; minutes where the divisor sums to under 3000 are left out", "levels": [{"down": [10, 25], "name": "calm"}, {"band": [10, 25, 40, 60], "name": "busy"}, {"name": "high", "up": [40, 60]}], "min_change": 10, "name": "connections.working_share", "pack": "connections", "pairs_with": ["tickets.read.empty", "tickets.write.empty", "queue.readers", "queue.writers", "connections.created"], "reading": "the highest valid sample of each minute", "signal": {"den": ["serverStatus/connections/current"], "min_den": 3000, "minus": ["serverStatus/connections/awaitingTopologyChanges"], "mode": "gauge", "num": ["serverStatus/connections/active"], "scale": 100, "unit": "%"}, "since": "4.4", "title": "Derived active-connection share", "unit": "%", "version_text": "4.4 and later", "view": "max"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>connections.current</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none — read for its shape only", "doc": "Count reported for currently open server connections.", "formula": "serverStatus/connections/current, in conns, at each available sample", "min_change": 50, "name": "connections.current", "pack": "connections", "pairs_with": ["connections.non_active", "connections.created", "memory.heap_outside_cache"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/connections/current"], "scale": 1, "unit": "conns"}, "title": "Open connections", "unit": "conns", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>connections.rejected</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>6.3 and later</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none ≤0.001 (fading to 0.01) · some 0.01–1 (edges 0.001, 5) · many ≥5 (from 1)", "doc": "Rate of the server's rejected connection counter; client impact and rejection cause are not inferred.", "elevated": 0.01, "formula": "ΔserverStatus/connections/rejected per second, in /s, at each available sample", "levels": [{"down": [0.001, 0.01], "name": "none"}, {"band": [0.001, 0.01, 1, 5], "name": "some"}, {"name": "many", "up": [1, 5]}], "min_change": 0.01, "name": "connections.rejected", "pack": "connections", "pairs_with": ["connections.scarce", "connections.used"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/connections/rejected"], "scale": 1, "unit": "/s"}, "since": "6.3", "title": "Connections refused", "unit": "/s", "version_text": "6.3 and later", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D92"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/labels-review.xlsx
+++ b/docs/labels-review.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Raw definitions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Labels'!$A$1:$U$92</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Raw definitions'!$A$1:$D$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Labels'!$A$1:$U$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Raw definitions'!$A$1:$D$93</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -614,7 +614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U92"/>
+  <dimension ref="A1:U93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3274,67 +3274,67 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>admission</t>
+          <t>files</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.used</t>
+          <t>files.handles</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Read tickets in use</t>
+          <t>File handles in use</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>before 8.0</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Read tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.</t>
+          <t>File handles allocated on the whole machine, every process together. FTDC does not record the kernel's limit (fs.file-max), so the bands are fixed reference counts, not a share of this host's limit; when the limit is reached the kernel refuses new files and sockets to every process. A climb that never comes back down is worth reading beside connections.</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/concurrentTransactions/read/out ÷ serverStatus/wiredTiger/concurrentTransactions/read/totalTickets × 100, in %, at each available sample</t>
+          <t>systemMetrics/files/sys_file_handles_in_use, in handles, at each available sample</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>each minute's ratio of sums</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>handles</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)</t>
+          <t>normal ≤15000 (fading to 30000) · many 30000–60000 (edges 15000, 90000) · very_high ≥90000 (from 60000)</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>37.5 % → 50% low, 83% moderate</t>
+          <t>22500 handles → 50% normal, 50% many</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>high or near_full</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>75 % or more</t>
+          <t>60000 handles or more</t>
         </is>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>10 %</t>
+          <t>2000 handles</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr"/>
@@ -3346,7 +3346,7 @@
       <c r="P30" s="4" t="n"/>
       <c r="Q30" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>handles</t>
         </is>
       </c>
       <c r="R30" s="4" t="inlineStr">
@@ -3356,15 +3356,11 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.scarce, tickets.read.pool, tickets.read.wait, queue.readers</t>
+          <t>connections.current</t>
         </is>
       </c>
       <c r="T30" s="4" t="inlineStr"/>
-      <c r="U30" s="4" t="inlineStr">
-        <is>
-          <t>From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.</t>
-        </is>
-      </c>
+      <c r="U30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -3374,12 +3370,12 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.scarce</t>
+          <t>tickets.read.used</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Samples with under 10% of read tickets left</t>
+          <t>Read tickets in use</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -3389,61 +3385,59 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which available read tickets were strictly below 10 % of the pool, normalized to a 60-second minute.</t>
+          <t>Read tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/concurrentTransactions/read/available ÷ serverStatus/wiredTiger/concurrentTransactions/read/totalTickets × 100, in % available, at each available sample</t>
+          <t>serverStatus/wiredTiger/concurrentTransactions/read/out ÷ serverStatus/wiredTiger/concurrentTransactions/read/totalTickets × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>each minute's ratio of sums</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>s/min</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
+          <t>low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>0.5 s/min → 50% none, 50% brief</t>
+          <t>37.5 % → 50% low, 83% moderate</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>brief and above (set by the rule)</t>
+          <t>high or near_full</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>1 s/min or more</t>
+          <t>75 % or more</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>3 s/min</t>
+          <t>10 %</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr"/>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>time_below</t>
-        </is>
-      </c>
-      <c r="P31" s="4" t="n">
-        <v>10</v>
-      </c>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P31" s="4" t="n"/>
       <c r="Q31" s="4" t="inlineStr">
         <is>
-          <t>% available</t>
+          <t>%</t>
         </is>
       </c>
       <c r="R31" s="4" t="inlineStr">
@@ -3453,7 +3447,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.empty, tickets.read.used, tickets.read.pool, tickets.read.wait</t>
+          <t>tickets.read.scarce, tickets.read.pool, tickets.read.wait, queue.readers</t>
         </is>
       </c>
       <c r="T31" s="4" t="inlineStr"/>
@@ -3471,12 +3465,12 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.empty</t>
+          <t>tickets.read.scarce</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Samples with no read ticket left</t>
+          <t>Samples with under 10% of read tickets left</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -3486,17 +3480,17 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which fewer than 0.5 read tickets were available, that is none, normalized to a 60-second minute.</t>
+          <t>Share of valid samples in which available read tickets were strictly below 10 % of the pool, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/concurrentTransactions/read/available, in tickets left, at each available sample</t>
+          <t>serverStatus/wiredTiger/concurrentTransactions/read/available ÷ serverStatus/wiredTiger/concurrentTransactions/read/totalTickets × 100, in % available, at each available sample</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -3536,11 +3530,11 @@
         </is>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="Q32" s="4" t="inlineStr">
         <is>
-          <t>tickets left</t>
+          <t>% available</t>
         </is>
       </c>
       <c r="R32" s="4" t="inlineStr">
@@ -3550,7 +3544,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.used, tickets.read.scarce, tickets.read.pool, tickets.read.wait, queue.readers</t>
+          <t>tickets.read.empty, tickets.read.used, tickets.read.pool, tickets.read.wait</t>
         </is>
       </c>
       <c r="T32" s="4" t="inlineStr"/>
@@ -3568,12 +3562,12 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.pool</t>
+          <t>tickets.read.empty</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Read ticket pool size</t>
+          <t>Samples with no read ticket left</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -3583,51 +3577,61 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>How many read tickets the pool held, averaged over the minute.</t>
+          <t>Share of valid samples in which fewer than 0.5 read tickets were available, that is none, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/concurrentTransactions/read/totalTickets, in tickets, at each available sample</t>
+          <t>serverStatus/wiredTiger/concurrentTransactions/read/available, in tickets left, at each available sample</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>tickets</t>
+          <t>s/min</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>none — read for its shape only</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr"/>
+          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>0.5 s/min → 50% none, 50% brief</t>
+        </is>
+      </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>shape only: a step, an episode, a schedule</t>
-        </is>
-      </c>
-      <c r="L33" s="4" t="inlineStr"/>
+          <t>brief and above (set by the rule)</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>1 s/min or more</t>
+        </is>
+      </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>4 tickets</t>
+          <t>3 s/min</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr"/>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="P33" s="4" t="n"/>
+          <t>time_below</t>
+        </is>
+      </c>
+      <c r="P33" s="4" t="n">
+        <v>0.5</v>
+      </c>
       <c r="Q33" s="4" t="inlineStr">
         <is>
-          <t>tickets</t>
+          <t>tickets left</t>
         </is>
       </c>
       <c r="R33" s="4" t="inlineStr">
@@ -3637,11 +3641,15 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.used, tickets.read.scarce</t>
+          <t>tickets.read.used, tickets.read.scarce, tickets.read.pool, tickets.read.wait, queue.readers</t>
         </is>
       </c>
       <c r="T33" s="4" t="inlineStr"/>
-      <c r="U33" s="4" t="inlineStr"/>
+      <c r="U33" s="4" t="inlineStr">
+        <is>
+          <t>From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -3651,27 +3659,27 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.wait</t>
+          <t>tickets.read.pool</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Time waiting for a read ticket</t>
+          <t>Read ticket pool size</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>7.0 up to 8.0</t>
+          <t>before 8.0</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Milliseconds a second operations spent queued for a read ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it.</t>
+          <t>How many read tickets the pool held, averaged over the minute.</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/wiredTiger/concurrentTransactions/read/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample</t>
+          <t>serverStatus/wiredTiger/concurrentTransactions/read/totalTickets, in tickets, at each available sample</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -3681,32 +3689,24 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>ms/s</t>
+          <t>tickets</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>5.5 ms/s → 50% none, 50% some</t>
-        </is>
-      </c>
+          <t>none — read for its shape only</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr"/>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>heavy</t>
-        </is>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>100 ms/s or more</t>
-        </is>
-      </c>
+          <t>shape only: a step, an episode, a schedule</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr"/>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>10 ms/s</t>
+          <t>4 tickets</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr"/>
@@ -3718,7 +3718,7 @@
       <c r="P34" s="4" t="n"/>
       <c r="Q34" s="4" t="inlineStr">
         <is>
-          <t>ms/s</t>
+          <t>tickets</t>
         </is>
       </c>
       <c r="R34" s="4" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.empty, tickets.read.scarce, queue.readers</t>
+          <t>tickets.read.used, tickets.read.scarce</t>
         </is>
       </c>
       <c r="T34" s="4" t="inlineStr"/>
@@ -3742,62 +3742,62 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.used</t>
+          <t>tickets.read.wait</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Read tickets in use</t>
+          <t>Time waiting for a read ticket</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>8.0 and later</t>
+          <t>7.0 up to 8.0</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Read tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.</t>
+          <t>Milliseconds a second operations spent queued for a read ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it.</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/queues/execution/read/out ÷ serverStatus/queues/execution/read/totalTickets × 100, in %, at each available sample</t>
+          <t>ΔserverStatus/wiredTiger/concurrentTransactions/read/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>each minute's ratio of sums</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>ms/s</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)</t>
+          <t>none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>37.5 % → 50% low, 83% moderate</t>
+          <t>5.5 ms/s → 50% none, 50% some</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>high or near_full</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>75 % or more</t>
+          <t>100 ms/s or more</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>10 %</t>
+          <t>10 ms/s</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr"/>
@@ -3809,7 +3809,7 @@
       <c r="P35" s="4" t="n"/>
       <c r="Q35" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>ms/s</t>
         </is>
       </c>
       <c r="R35" s="4" t="inlineStr">
@@ -3819,15 +3819,11 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.scarce, tickets.read.pool, tickets.read.wait, queue.readers</t>
+          <t>tickets.read.empty, tickets.read.scarce, queue.readers</t>
         </is>
       </c>
       <c r="T35" s="4" t="inlineStr"/>
-      <c r="U35" s="4" t="inlineStr">
-        <is>
-          <t>From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.</t>
-        </is>
-      </c>
+      <c r="U35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -3837,12 +3833,12 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.scarce</t>
+          <t>tickets.read.used</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Samples with under 10% of read tickets left</t>
+          <t>Read tickets in use</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -3852,61 +3848,59 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which available read tickets were strictly below 10 % of the pool, normalized to a 60-second minute.</t>
+          <t>Read tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/queues/execution/read/available ÷ serverStatus/queues/execution/read/totalTickets × 100, in % available, at each available sample</t>
+          <t>serverStatus/queues/execution/read/out ÷ serverStatus/queues/execution/read/totalTickets × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>each minute's ratio of sums</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>s/min</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
+          <t>low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>0.5 s/min → 50% none, 50% brief</t>
+          <t>37.5 % → 50% low, 83% moderate</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>brief and above (set by the rule)</t>
+          <t>high or near_full</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>1 s/min or more</t>
+          <t>75 % or more</t>
         </is>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>3 s/min</t>
+          <t>10 %</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr"/>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>time_below</t>
-        </is>
-      </c>
-      <c r="P36" s="4" t="n">
-        <v>10</v>
-      </c>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P36" s="4" t="n"/>
       <c r="Q36" s="4" t="inlineStr">
         <is>
-          <t>% available</t>
+          <t>%</t>
         </is>
       </c>
       <c r="R36" s="4" t="inlineStr">
@@ -3916,7 +3910,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.empty, tickets.read.used, tickets.read.pool, tickets.read.wait</t>
+          <t>tickets.read.scarce, tickets.read.pool, tickets.read.wait, queue.readers</t>
         </is>
       </c>
       <c r="T36" s="4" t="inlineStr"/>
@@ -3934,12 +3928,12 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.empty</t>
+          <t>tickets.read.scarce</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Samples with no read ticket left</t>
+          <t>Samples with under 10% of read tickets left</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -3949,17 +3943,17 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which fewer than 0.5 read tickets were available, that is none, normalized to a 60-second minute.</t>
+          <t>Share of valid samples in which available read tickets were strictly below 10 % of the pool, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/queues/execution/read/available, in tickets left, at each available sample</t>
+          <t>serverStatus/queues/execution/read/available ÷ serverStatus/queues/execution/read/totalTickets × 100, in % available, at each available sample</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -3999,11 +3993,11 @@
         </is>
       </c>
       <c r="P37" s="4" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="Q37" s="4" t="inlineStr">
         <is>
-          <t>tickets left</t>
+          <t>% available</t>
         </is>
       </c>
       <c r="R37" s="4" t="inlineStr">
@@ -4013,7 +4007,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.used, tickets.read.scarce, tickets.read.pool, tickets.read.wait, queue.readers</t>
+          <t>tickets.read.empty, tickets.read.used, tickets.read.pool, tickets.read.wait</t>
         </is>
       </c>
       <c r="T37" s="4" t="inlineStr"/>
@@ -4031,12 +4025,12 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.pool</t>
+          <t>tickets.read.empty</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Read ticket pool size</t>
+          <t>Samples with no read ticket left</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -4046,51 +4040,61 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>How many read tickets the pool held, averaged over the minute.</t>
+          <t>Share of valid samples in which fewer than 0.5 read tickets were available, that is none, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/queues/execution/read/totalTickets, in tickets, at each available sample</t>
+          <t>serverStatus/queues/execution/read/available, in tickets left, at each available sample</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>tickets</t>
+          <t>s/min</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>none — read for its shape only</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="inlineStr"/>
+          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>0.5 s/min → 50% none, 50% brief</t>
+        </is>
+      </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>shape only: a step, an episode, a schedule</t>
-        </is>
-      </c>
-      <c r="L38" s="4" t="inlineStr"/>
+          <t>brief and above (set by the rule)</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>1 s/min or more</t>
+        </is>
+      </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>4 tickets</t>
+          <t>3 s/min</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr"/>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="P38" s="4" t="n"/>
+          <t>time_below</t>
+        </is>
+      </c>
+      <c r="P38" s="4" t="n">
+        <v>0.5</v>
+      </c>
       <c r="Q38" s="4" t="inlineStr">
         <is>
-          <t>tickets</t>
+          <t>tickets left</t>
         </is>
       </c>
       <c r="R38" s="4" t="inlineStr">
@@ -4100,11 +4104,15 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.used, tickets.read.scarce</t>
+          <t>tickets.read.used, tickets.read.scarce, tickets.read.pool, tickets.read.wait, queue.readers</t>
         </is>
       </c>
       <c r="T38" s="4" t="inlineStr"/>
-      <c r="U38" s="4" t="inlineStr"/>
+      <c r="U38" s="4" t="inlineStr">
+        <is>
+          <t>From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -4114,12 +4122,12 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.wait</t>
+          <t>tickets.read.pool</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Time waiting for a read ticket</t>
+          <t>Read ticket pool size</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -4129,12 +4137,12 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Milliseconds a second operations spent queued for a read ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. The counter covers normal-priority operations, not exempt operations.</t>
+          <t>How many read tickets the pool held, averaged over the minute.</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/queues/execution/read/normalPriority/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample</t>
+          <t>serverStatus/queues/execution/read/totalTickets, in tickets, at each available sample</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
@@ -4144,32 +4152,24 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>ms/s</t>
+          <t>tickets</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)</t>
-        </is>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>5.5 ms/s → 50% none, 50% some</t>
-        </is>
-      </c>
+          <t>none — read for its shape only</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr"/>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>heavy</t>
-        </is>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>100 ms/s or more</t>
-        </is>
-      </c>
+          <t>shape only: a step, an episode, a schedule</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr"/>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>10 ms/s</t>
+          <t>4 tickets</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr"/>
@@ -4181,7 +4181,7 @@
       <c r="P39" s="4" t="n"/>
       <c r="Q39" s="4" t="inlineStr">
         <is>
-          <t>ms/s</t>
+          <t>tickets</t>
         </is>
       </c>
       <c r="R39" s="4" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.empty, tickets.read.scarce, queue.readers</t>
+          <t>tickets.read.used, tickets.read.scarce</t>
         </is>
       </c>
       <c r="T39" s="4" t="inlineStr"/>
@@ -4205,62 +4205,62 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.used</t>
+          <t>tickets.read.wait</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Write tickets in use</t>
+          <t>Time waiting for a read ticket</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>before 8.0</t>
+          <t>8.0 and later</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Write tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.</t>
+          <t>Milliseconds a second operations spent queued for a read ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. The counter covers normal-priority operations, not exempt operations.</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/concurrentTransactions/write/out ÷ serverStatus/wiredTiger/concurrentTransactions/write/totalTickets × 100, in %, at each available sample</t>
+          <t>ΔserverStatus/queues/execution/read/normalPriority/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>each minute's ratio of sums</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>ms/s</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)</t>
+          <t>none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>37.5 % → 50% low, 83% moderate</t>
+          <t>5.5 ms/s → 50% none, 50% some</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>high or near_full</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>75 % or more</t>
+          <t>100 ms/s or more</t>
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>10 %</t>
+          <t>10 ms/s</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr"/>
@@ -4272,7 +4272,7 @@
       <c r="P40" s="4" t="n"/>
       <c r="Q40" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>ms/s</t>
         </is>
       </c>
       <c r="R40" s="4" t="inlineStr">
@@ -4282,15 +4282,11 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.scarce, tickets.write.pool, tickets.write.wait, queue.writers</t>
+          <t>tickets.read.empty, tickets.read.scarce, queue.readers</t>
         </is>
       </c>
       <c r="T40" s="4" t="inlineStr"/>
-      <c r="U40" s="4" t="inlineStr">
-        <is>
-          <t>From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.</t>
-        </is>
-      </c>
+      <c r="U40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -4300,12 +4296,12 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.scarce</t>
+          <t>tickets.write.used</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Samples with under 10% of write tickets left</t>
+          <t>Write tickets in use</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -4315,61 +4311,59 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which available write tickets were strictly below 10 % of the pool, normalized to a 60-second minute.</t>
+          <t>Write tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/concurrentTransactions/write/available ÷ serverStatus/wiredTiger/concurrentTransactions/write/totalTickets × 100, in % available, at each available sample</t>
+          <t>serverStatus/wiredTiger/concurrentTransactions/write/out ÷ serverStatus/wiredTiger/concurrentTransactions/write/totalTickets × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>each minute's ratio of sums</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>s/min</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
+          <t>low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>0.5 s/min → 50% none, 50% brief</t>
+          <t>37.5 % → 50% low, 83% moderate</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>brief and above (set by the rule)</t>
+          <t>high or near_full</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>1 s/min or more</t>
+          <t>75 % or more</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>3 s/min</t>
+          <t>10 %</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr"/>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>time_below</t>
-        </is>
-      </c>
-      <c r="P41" s="4" t="n">
-        <v>10</v>
-      </c>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P41" s="4" t="n"/>
       <c r="Q41" s="4" t="inlineStr">
         <is>
-          <t>% available</t>
+          <t>%</t>
         </is>
       </c>
       <c r="R41" s="4" t="inlineStr">
@@ -4379,7 +4373,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.empty, tickets.write.used, tickets.write.pool, tickets.write.wait</t>
+          <t>tickets.write.scarce, tickets.write.pool, tickets.write.wait, queue.writers</t>
         </is>
       </c>
       <c r="T41" s="4" t="inlineStr"/>
@@ -4397,12 +4391,12 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.empty</t>
+          <t>tickets.write.scarce</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Samples with no write ticket left</t>
+          <t>Samples with under 10% of write tickets left</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -4412,17 +4406,17 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which fewer than 0.5 write tickets were available, that is none, normalized to a 60-second minute.</t>
+          <t>Share of valid samples in which available write tickets were strictly below 10 % of the pool, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/concurrentTransactions/write/available, in tickets left, at each available sample</t>
+          <t>serverStatus/wiredTiger/concurrentTransactions/write/available ÷ serverStatus/wiredTiger/concurrentTransactions/write/totalTickets × 100, in % available, at each available sample</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -4462,11 +4456,11 @@
         </is>
       </c>
       <c r="P42" s="4" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="Q42" s="4" t="inlineStr">
         <is>
-          <t>tickets left</t>
+          <t>% available</t>
         </is>
       </c>
       <c r="R42" s="4" t="inlineStr">
@@ -4476,7 +4470,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.used, tickets.write.scarce, tickets.write.pool, tickets.write.wait, queue.writers</t>
+          <t>tickets.write.empty, tickets.write.used, tickets.write.pool, tickets.write.wait</t>
         </is>
       </c>
       <c r="T42" s="4" t="inlineStr"/>
@@ -4494,12 +4488,12 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.pool</t>
+          <t>tickets.write.empty</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Write ticket pool size</t>
+          <t>Samples with no write ticket left</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -4509,51 +4503,61 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>How many write tickets the pool held, averaged over the minute.</t>
+          <t>Share of valid samples in which fewer than 0.5 write tickets were available, that is none, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/concurrentTransactions/write/totalTickets, in tickets, at each available sample</t>
+          <t>serverStatus/wiredTiger/concurrentTransactions/write/available, in tickets left, at each available sample</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>tickets</t>
+          <t>s/min</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>none — read for its shape only</t>
-        </is>
-      </c>
-      <c r="J43" s="4" t="inlineStr"/>
+          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>0.5 s/min → 50% none, 50% brief</t>
+        </is>
+      </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>shape only: a step, an episode, a schedule</t>
-        </is>
-      </c>
-      <c r="L43" s="4" t="inlineStr"/>
+          <t>brief and above (set by the rule)</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>1 s/min or more</t>
+        </is>
+      </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>4 tickets</t>
+          <t>3 s/min</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr"/>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="P43" s="4" t="n"/>
+          <t>time_below</t>
+        </is>
+      </c>
+      <c r="P43" s="4" t="n">
+        <v>0.5</v>
+      </c>
       <c r="Q43" s="4" t="inlineStr">
         <is>
-          <t>tickets</t>
+          <t>tickets left</t>
         </is>
       </c>
       <c r="R43" s="4" t="inlineStr">
@@ -4563,11 +4567,15 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.used, tickets.write.scarce</t>
+          <t>tickets.write.used, tickets.write.scarce, tickets.write.pool, tickets.write.wait, queue.writers</t>
         </is>
       </c>
       <c r="T43" s="4" t="inlineStr"/>
-      <c r="U43" s="4" t="inlineStr"/>
+      <c r="U43" s="4" t="inlineStr">
+        <is>
+          <t>From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -4577,27 +4585,27 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.wait</t>
+          <t>tickets.write.pool</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Time waiting for a write ticket</t>
+          <t>Write ticket pool size</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>7.0 up to 8.0</t>
+          <t>before 8.0</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Milliseconds a second operations spent queued for a write ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it.</t>
+          <t>How many write tickets the pool held, averaged over the minute.</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/wiredTiger/concurrentTransactions/write/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample</t>
+          <t>serverStatus/wiredTiger/concurrentTransactions/write/totalTickets, in tickets, at each available sample</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
@@ -4607,32 +4615,24 @@
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>ms/s</t>
+          <t>tickets</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)</t>
-        </is>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>5.5 ms/s → 50% none, 50% some</t>
-        </is>
-      </c>
+          <t>none — read for its shape only</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr"/>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>heavy</t>
-        </is>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
-        <is>
-          <t>100 ms/s or more</t>
-        </is>
-      </c>
+          <t>shape only: a step, an episode, a schedule</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="inlineStr"/>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>10 ms/s</t>
+          <t>4 tickets</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr"/>
@@ -4644,7 +4644,7 @@
       <c r="P44" s="4" t="n"/>
       <c r="Q44" s="4" t="inlineStr">
         <is>
-          <t>ms/s</t>
+          <t>tickets</t>
         </is>
       </c>
       <c r="R44" s="4" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.empty, tickets.write.scarce, queue.writers</t>
+          <t>tickets.write.used, tickets.write.scarce</t>
         </is>
       </c>
       <c r="T44" s="4" t="inlineStr"/>
@@ -4668,62 +4668,62 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.used</t>
+          <t>tickets.write.wait</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Write tickets in use</t>
+          <t>Time waiting for a write ticket</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>8.0 and later</t>
+          <t>7.0 up to 8.0</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Write tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.</t>
+          <t>Milliseconds a second operations spent queued for a write ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it.</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/queues/execution/write/out ÷ serverStatus/queues/execution/write/totalTickets × 100, in %, at each available sample</t>
+          <t>ΔserverStatus/wiredTiger/concurrentTransactions/write/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>each minute's ratio of sums</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>ms/s</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)</t>
+          <t>none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>37.5 % → 50% low, 83% moderate</t>
+          <t>5.5 ms/s → 50% none, 50% some</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>high or near_full</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>75 % or more</t>
+          <t>100 ms/s or more</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>10 %</t>
+          <t>10 ms/s</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr"/>
@@ -4735,7 +4735,7 @@
       <c r="P45" s="4" t="n"/>
       <c r="Q45" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>ms/s</t>
         </is>
       </c>
       <c r="R45" s="4" t="inlineStr">
@@ -4745,15 +4745,11 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.scarce, tickets.write.pool, tickets.write.wait, queue.writers</t>
+          <t>tickets.write.empty, tickets.write.scarce, queue.writers</t>
         </is>
       </c>
       <c r="T45" s="4" t="inlineStr"/>
-      <c r="U45" s="4" t="inlineStr">
-        <is>
-          <t>From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.</t>
-        </is>
-      </c>
+      <c r="U45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -4763,12 +4759,12 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.scarce</t>
+          <t>tickets.write.used</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Samples with under 10% of write tickets left</t>
+          <t>Write tickets in use</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -4778,61 +4774,59 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which available write tickets were strictly below 10 % of the pool, normalized to a 60-second minute.</t>
+          <t>Write tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/queues/execution/write/available ÷ serverStatus/queues/execution/write/totalTickets × 100, in % available, at each available sample</t>
+          <t>serverStatus/queues/execution/write/out ÷ serverStatus/queues/execution/write/totalTickets × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>each minute's ratio of sums</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>s/min</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
+          <t>low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>0.5 s/min → 50% none, 50% brief</t>
+          <t>37.5 % → 50% low, 83% moderate</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>brief and above (set by the rule)</t>
+          <t>high or near_full</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>1 s/min or more</t>
+          <t>75 % or more</t>
         </is>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>3 s/min</t>
+          <t>10 %</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr"/>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t>time_below</t>
-        </is>
-      </c>
-      <c r="P46" s="4" t="n">
-        <v>10</v>
-      </c>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P46" s="4" t="n"/>
       <c r="Q46" s="4" t="inlineStr">
         <is>
-          <t>% available</t>
+          <t>%</t>
         </is>
       </c>
       <c r="R46" s="4" t="inlineStr">
@@ -4842,7 +4836,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.empty, tickets.write.used, tickets.write.pool, tickets.write.wait</t>
+          <t>tickets.write.scarce, tickets.write.pool, tickets.write.wait, queue.writers</t>
         </is>
       </c>
       <c r="T46" s="4" t="inlineStr"/>
@@ -4860,12 +4854,12 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.empty</t>
+          <t>tickets.write.scarce</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Samples with no write ticket left</t>
+          <t>Samples with under 10% of write tickets left</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -4875,17 +4869,17 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which fewer than 0.5 write tickets were available, that is none, normalized to a 60-second minute.</t>
+          <t>Share of valid samples in which available write tickets were strictly below 10 % of the pool, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/queues/execution/write/available, in tickets left, at each available sample</t>
+          <t>serverStatus/queues/execution/write/available ÷ serverStatus/queues/execution/write/totalTickets × 100, in % available, at each available sample</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -4925,11 +4919,11 @@
         </is>
       </c>
       <c r="P47" s="4" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="Q47" s="4" t="inlineStr">
         <is>
-          <t>tickets left</t>
+          <t>% available</t>
         </is>
       </c>
       <c r="R47" s="4" t="inlineStr">
@@ -4939,7 +4933,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.used, tickets.write.scarce, tickets.write.pool, tickets.write.wait, queue.writers</t>
+          <t>tickets.write.empty, tickets.write.used, tickets.write.pool, tickets.write.wait</t>
         </is>
       </c>
       <c r="T47" s="4" t="inlineStr"/>
@@ -4957,12 +4951,12 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.pool</t>
+          <t>tickets.write.empty</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Write ticket pool size</t>
+          <t>Samples with no write ticket left</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -4972,51 +4966,61 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>How many write tickets the pool held, averaged over the minute.</t>
+          <t>Share of valid samples in which fewer than 0.5 write tickets were available, that is none, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/queues/execution/write/totalTickets, in tickets, at each available sample</t>
+          <t>serverStatus/queues/execution/write/available, in tickets left, at each available sample</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>tickets</t>
+          <t>s/min</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>none — read for its shape only</t>
-        </is>
-      </c>
-      <c r="J48" s="4" t="inlineStr"/>
+          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>0.5 s/min → 50% none, 50% brief</t>
+        </is>
+      </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>shape only: a step, an episode, a schedule</t>
-        </is>
-      </c>
-      <c r="L48" s="4" t="inlineStr"/>
+          <t>brief and above (set by the rule)</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>1 s/min or more</t>
+        </is>
+      </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>4 tickets</t>
+          <t>3 s/min</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr"/>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="P48" s="4" t="n"/>
+          <t>time_below</t>
+        </is>
+      </c>
+      <c r="P48" s="4" t="n">
+        <v>0.5</v>
+      </c>
       <c r="Q48" s="4" t="inlineStr">
         <is>
-          <t>tickets</t>
+          <t>tickets left</t>
         </is>
       </c>
       <c r="R48" s="4" t="inlineStr">
@@ -5026,11 +5030,15 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.used, tickets.write.scarce</t>
+          <t>tickets.write.used, tickets.write.scarce, tickets.write.pool, tickets.write.wait, queue.writers</t>
         </is>
       </c>
       <c r="T48" s="4" t="inlineStr"/>
-      <c r="U48" s="4" t="inlineStr"/>
+      <c r="U48" s="4" t="inlineStr">
+        <is>
+          <t>From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -5040,12 +5048,12 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.wait</t>
+          <t>tickets.write.pool</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Time waiting for a write ticket</t>
+          <t>Write ticket pool size</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -5055,12 +5063,12 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Milliseconds a second operations spent queued for a write ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. The counter covers normal-priority operations, not exempt operations.</t>
+          <t>How many write tickets the pool held, averaged over the minute.</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/queues/execution/write/normalPriority/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample</t>
+          <t>serverStatus/queues/execution/write/totalTickets, in tickets, at each available sample</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
@@ -5070,32 +5078,24 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>ms/s</t>
+          <t>tickets</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)</t>
-        </is>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>5.5 ms/s → 50% none, 50% some</t>
-        </is>
-      </c>
+          <t>none — read for its shape only</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr"/>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>heavy</t>
-        </is>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>100 ms/s or more</t>
-        </is>
-      </c>
+          <t>shape only: a step, an episode, a schedule</t>
+        </is>
+      </c>
+      <c r="L49" s="4" t="inlineStr"/>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>10 ms/s</t>
+          <t>4 tickets</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr"/>
@@ -5107,7 +5107,7 @@
       <c r="P49" s="4" t="n"/>
       <c r="Q49" s="4" t="inlineStr">
         <is>
-          <t>ms/s</t>
+          <t>tickets</t>
         </is>
       </c>
       <c r="R49" s="4" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.empty, tickets.write.scarce, queue.writers</t>
+          <t>tickets.write.used, tickets.write.scarce</t>
         </is>
       </c>
       <c r="T49" s="4" t="inlineStr"/>
@@ -5131,76 +5131,74 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>queue.readers</t>
+          <t>tickets.write.wait</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Samples with reads queued</t>
+          <t>Time waiting for a write ticket</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>8.0 and later</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which globalLock.currentQueue.readers was above 0, normalized to a 60-second minute.</t>
+          <t>Milliseconds a second operations spent queued for a write ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. The counter covers normal-priority operations, not exempt operations.</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/globalLock/currentQueue/readers, in operations, at each available sample</t>
+          <t>ΔserverStatus/queues/execution/write/normalPriority/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly above 0 operations, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>s/min</t>
+          <t>ms/s</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
+          <t>none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>0.5 s/min → 50% none, 50% brief</t>
+          <t>5.5 ms/s → 50% none, 50% some</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>frequent or constant</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>1 s/min or more</t>
+          <t>100 ms/s or more</t>
         </is>
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>3 s/min</t>
+          <t>10 ms/s</t>
         </is>
       </c>
       <c r="N50" s="4" t="inlineStr"/>
       <c r="O50" s="4" t="inlineStr">
         <is>
-          <t>time_above</t>
-        </is>
-      </c>
-      <c r="P50" s="4" t="n">
-        <v>0</v>
-      </c>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P50" s="4" t="n"/>
       <c r="Q50" s="4" t="inlineStr">
         <is>
-          <t>operations</t>
+          <t>ms/s</t>
         </is>
       </c>
       <c r="R50" s="4" t="inlineStr">
@@ -5210,7 +5208,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.empty, tickets.read.wait</t>
+          <t>tickets.write.empty, tickets.write.scarce, queue.writers</t>
         </is>
       </c>
       <c r="T50" s="4" t="inlineStr"/>
@@ -5224,12 +5222,12 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>queue.writers</t>
+          <t>queue.readers</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Samples with writes queued</t>
+          <t>Samples with reads queued</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -5239,12 +5237,12 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which globalLock.currentQueue.writers was above 0, normalized to a 60-second minute.</t>
+          <t>Share of valid samples in which globalLock.currentQueue.readers was above 0, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/globalLock/currentQueue/writers, in operations, at each available sample</t>
+          <t>serverStatus/globalLock/currentQueue/readers, in operations, at each available sample</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
@@ -5303,7 +5301,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.empty, tickets.write.wait</t>
+          <t>tickets.read.empty, tickets.read.wait</t>
         </is>
       </c>
       <c r="T51" s="4" t="inlineStr"/>
@@ -5312,17 +5310,17 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>storage-engine</t>
+          <t>admission</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>cache.fill</t>
+          <t>queue.writers</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>WiredTiger cache fill</t>
+          <t>Samples with writes queued</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -5332,59 +5330,61 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Bytes in the WiredTiger cache as a share of its configured size, averaged over the minute.</t>
+          <t>Share of valid samples in which globalLock.currentQueue.writers was above 0, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/cache/bytes currently in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample</t>
+          <t>serverStatus/globalLock/currentQueue/writers, in operations, at each available sample</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>each minute's ratio of sums</t>
+          <t>valid-sample share strictly above 0 operations, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>s/min</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>low ≤50 (fading to 70) · normal 70–80 (edges 50, 86) · high 86–93 (edges 80, 95) · above_reference ≥96 (from 94)</t>
+          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>60 % → 50% low, 50% normal</t>
+          <t>0.5 s/min → 50% none, 50% brief</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>high or above_reference</t>
+          <t>frequent or constant</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>95 % or more</t>
+          <t>1 s/min or more</t>
         </is>
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>5 %</t>
+          <t>3 s/min</t>
         </is>
       </c>
       <c r="N52" s="4" t="inlineStr"/>
       <c r="O52" s="4" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="P52" s="4" t="n"/>
+          <t>time_above</t>
+        </is>
+      </c>
+      <c r="P52" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Q52" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="R52" s="4" t="inlineStr">
@@ -5394,14 +5394,10 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>cache.fill_above_95, cache.app_eviction, cache.read_in</t>
-        </is>
-      </c>
-      <c r="T52" s="4" t="inlineStr">
-        <is>
-          <t>95 %: WiredTiger default eviction_trigger; eviction_target defaults to 80 (configured value not read)</t>
-        </is>
-      </c>
+          <t>tickets.write.empty, tickets.write.wait</t>
+        </is>
+      </c>
+      <c r="T52" s="4" t="inlineStr"/>
       <c r="U52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
@@ -5412,12 +5408,12 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>cache.fill_above_95</t>
+          <t>cache.fill</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Cache-fill samples above 95%</t>
+          <t>WiredTiger cache fill</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -5427,7 +5423,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which WiredTiger cache bytes were strictly above 95 % of the configured cache size, normalized to a 60-second minute.</t>
+          <t>Bytes in the WiredTiger cache as a share of its configured size, averaged over the minute.</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -5437,48 +5433,46 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly above 95 %, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>each minute's ratio of sums</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>s/min</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
+          <t>low ≤50 (fading to 70) · normal 70–80 (edges 50, 86) · high 86–93 (edges 80, 95) · above_reference ≥96 (from 94)</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>0.5 s/min → 50% none, 50% brief</t>
+          <t>60 % → 50% low, 50% normal</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>frequent or constant</t>
+          <t>high or above_reference</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>1 s/min or more</t>
+          <t>95 % or more</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>3 s/min</t>
+          <t>5 %</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr"/>
       <c r="O53" s="4" t="inlineStr">
         <is>
-          <t>time_above</t>
-        </is>
-      </c>
-      <c r="P53" s="4" t="n">
-        <v>95</v>
-      </c>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P53" s="4" t="n"/>
       <c r="Q53" s="4" t="inlineStr">
         <is>
           <t>%</t>
@@ -5491,12 +5485,12 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>cache.fill, cache.app_eviction, tickets.read.scarce</t>
+          <t>cache.fill_above_95, cache.app_eviction, cache.read_in</t>
         </is>
       </c>
       <c r="T53" s="4" t="inlineStr">
         <is>
-          <t>95 %: WiredTiger default eviction_trigger (configured value not read)</t>
+          <t>95 %: WiredTiger default eviction_trigger; eviction_target defaults to 80 (configured value not read)</t>
         </is>
       </c>
       <c r="U53" s="4" t="inlineStr"/>
@@ -5509,12 +5503,12 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>cache.dirty</t>
+          <t>cache.fill_above_95</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>WiredTiger dirty cache</t>
+          <t>Cache-fill samples above 95%</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -5524,56 +5518,58 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Modified bytes not yet written, as a share of the configured cache, averaged over the minute.</t>
+          <t>Share of valid samples in which WiredTiger cache bytes were strictly above 95 % of the configured cache size, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/cache/tracked dirty bytes in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample</t>
+          <t>serverStatus/wiredTiger/cache/bytes currently in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>each minute's ratio of sums</t>
+          <t>valid-sample share strictly above 95 %, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>s/min</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>low ≤3 (fading to 6) · normal 6–8 (edges 3, 12) · high 12–18 (edges 8, 20) · above_reference ≥21 (from 19)</t>
+          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>4.5 % → 50% low, 50% normal</t>
+          <t>0.5 s/min → 50% none, 50% brief</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>high or above_reference</t>
+          <t>frequent or constant</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>20 % or more</t>
+          <t>1 s/min or more</t>
         </is>
       </c>
       <c r="M54" s="4" t="inlineStr">
         <is>
-          <t>3 %</t>
+          <t>3 s/min</t>
         </is>
       </c>
       <c r="N54" s="4" t="inlineStr"/>
       <c r="O54" s="4" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="P54" s="4" t="n"/>
+          <t>time_above</t>
+        </is>
+      </c>
+      <c r="P54" s="4" t="n">
+        <v>95</v>
+      </c>
       <c r="Q54" s="4" t="inlineStr">
         <is>
           <t>%</t>
@@ -5586,12 +5582,12 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>cache.dirty_above_20, checkpoint.duration, disk.write_await, ops.writes</t>
+          <t>cache.fill, cache.app_eviction, tickets.read.scarce</t>
         </is>
       </c>
       <c r="T54" s="4" t="inlineStr">
         <is>
-          <t>20 %: WiredTiger default eviction_dirty_trigger; eviction_dirty_target defaults to 5 (configured value not read)</t>
+          <t>95 %: WiredTiger default eviction_trigger (configured value not read)</t>
         </is>
       </c>
       <c r="U54" s="4" t="inlineStr"/>
@@ -5604,12 +5600,12 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>cache.dirty_above_20</t>
+          <t>cache.dirty</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Dirty-cache samples above 20%</t>
+          <t>WiredTiger dirty cache</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -5619,7 +5615,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which tracked dirty bytes were strictly above 20 % of the configured cache size, normalized to a 60-second minute.</t>
+          <t>Modified bytes not yet written, as a share of the configured cache, averaged over the minute.</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -5629,48 +5625,46 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly above 20 %, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>each minute's ratio of sums</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>s/min</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
+          <t>low ≤3 (fading to 6) · normal 6–8 (edges 3, 12) · high 12–18 (edges 8, 20) · above_reference ≥21 (from 19)</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>0.5 s/min → 50% none, 50% brief</t>
+          <t>4.5 % → 50% low, 50% normal</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>frequent or constant</t>
+          <t>high or above_reference</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>1 s/min or more</t>
+          <t>20 % or more</t>
         </is>
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>3 s/min</t>
+          <t>3 %</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr"/>
       <c r="O55" s="4" t="inlineStr">
         <is>
-          <t>time_above</t>
-        </is>
-      </c>
-      <c r="P55" s="4" t="n">
-        <v>20</v>
-      </c>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P55" s="4" t="n"/>
       <c r="Q55" s="4" t="inlineStr">
         <is>
           <t>%</t>
@@ -5683,12 +5677,12 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>cache.dirty, checkpoint.running, tickets.write.scarce</t>
+          <t>cache.dirty_above_20, checkpoint.duration, disk.write_await, ops.writes</t>
         </is>
       </c>
       <c r="T55" s="4" t="inlineStr">
         <is>
-          <t>20 %: WiredTiger default eviction_dirty_trigger (configured value not read)</t>
+          <t>20 %: WiredTiger default eviction_dirty_trigger; eviction_dirty_target defaults to 5 (configured value not read)</t>
         </is>
       </c>
       <c r="U55" s="4" t="inlineStr"/>
@@ -5701,74 +5695,76 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>cache.app_eviction</t>
+          <t>cache.dirty_above_20</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Eviction by application threads</t>
+          <t>Dirty-cache samples above 20%</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>before 8.0.16</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Rate of pages evicted by application threads; where the version uses attempts and failures, the signal subtracts failure counts from attempt counts.</t>
+          <t>Share of valid samples in which tracked dirty bytes were strictly above 20 % of the configured cache size, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/wiredTiger/cache/pages evicted by application threads per second, in pages/s, at each available sample</t>
+          <t>serverStatus/wiredTiger/cache/tracked dirty bytes in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>valid-sample share strictly above 20 %, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>pages/s</t>
+          <t>s/min</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>none ≤0.1 (fading to 1) · some 1–10 (edges 0.1, 50) · heavy ≥50 (from 10)</t>
+          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>0.55 pages/s → 50% none, 50% some</t>
+          <t>0.5 s/min → 50% none, 50% brief</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>frequent or constant</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>1 pages/s or more</t>
+          <t>1 s/min or more</t>
         </is>
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>5 pages/s</t>
+          <t>3 s/min</t>
         </is>
       </c>
       <c r="N56" s="4" t="inlineStr"/>
       <c r="O56" s="4" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="P56" s="4" t="n"/>
+          <t>time_above</t>
+        </is>
+      </c>
+      <c r="P56" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="Q56" s="4" t="inlineStr">
         <is>
-          <t>pages/s</t>
+          <t>%</t>
         </is>
       </c>
       <c r="R56" s="4" t="inlineStr">
@@ -5778,10 +5774,14 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>cache.fill_above_95, cache.dirty_above_20</t>
-        </is>
-      </c>
-      <c r="T56" s="4" t="inlineStr"/>
+          <t>cache.dirty, checkpoint.running, tickets.write.scarce</t>
+        </is>
+      </c>
+      <c r="T56" s="4" t="inlineStr">
+        <is>
+          <t>20 %: WiredTiger default eviction_dirty_trigger (configured value not read)</t>
+        </is>
+      </c>
       <c r="U56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>8.0.16 and later</t>
+          <t>before 8.0.16</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/wiredTiger/cache/page evict attempts by application threads − serverStatus/wiredTiger/cache/page evict failures by application threads per second, in pages/s, at each available sample</t>
+          <t>ΔserverStatus/wiredTiger/cache/pages evicted by application threads per second, in pages/s, at each available sample</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>cache.fill_above_95, cache.dirty_above_20, cache.app_eviction_time</t>
+          <t>cache.fill_above_95, cache.dirty_above_20</t>
         </is>
       </c>
       <c r="T57" s="4" t="inlineStr"/>
@@ -5883,27 +5883,27 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>cache.app_eviction_time</t>
+          <t>cache.app_eviction</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Time operations spent evicting</t>
+          <t>Eviction by application threads</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>8.0 and later</t>
+          <t>8.0.16 and later</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Application-thread eviction time counter advance per elapsed second, summed across threads, in milliseconds.</t>
+          <t>Rate of pages evicted by application threads; where the version uses attempts and failures, the signal subtracts failure counts from attempt counts.</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/wiredTiger/cache/application thread time evicting (usecs) per second × 0.001, in ms/s, at each available sample</t>
+          <t>ΔserverStatus/wiredTiger/cache/page evict attempts by application threads − serverStatus/wiredTiger/cache/page evict failures by application threads per second, in pages/s, at each available sample</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
@@ -5913,17 +5913,17 @@
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>ms/s</t>
+          <t>pages/s</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)</t>
+          <t>none ≤0.1 (fading to 1) · some 1–10 (edges 0.1, 50) · heavy ≥50 (from 10)</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>5.5 ms/s → 50% none, 50% some</t>
+          <t>0.55 pages/s → 50% none, 50% some</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>100 ms/s or more</t>
+          <t>1 pages/s or more</t>
         </is>
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>10 ms/s</t>
+          <t>5 pages/s</t>
         </is>
       </c>
       <c r="N58" s="4" t="inlineStr"/>
@@ -5950,7 +5950,7 @@
       <c r="P58" s="4" t="n"/>
       <c r="Q58" s="4" t="inlineStr">
         <is>
-          <t>ms/s</t>
+          <t>pages/s</t>
         </is>
       </c>
       <c r="R58" s="4" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>cache.app_eviction, cache.fill_above_95, cache.dirty_above_20</t>
+          <t>cache.fill_above_95, cache.dirty_above_20, cache.app_eviction_time</t>
         </is>
       </c>
       <c r="T58" s="4" t="inlineStr"/>
@@ -5974,27 +5974,27 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>cache.read_in</t>
+          <t>cache.app_eviction_time</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Data read into the cache</t>
+          <t>Time operations spent evicting</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>8.0 and later</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>WiredTiger bytes-read-into-cache counter advance per elapsed second, scaled to MB/s.</t>
+          <t>Application-thread eviction time counter advance per elapsed second, summed across threads, in milliseconds.</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/wiredTiger/cache/bytes read into cache per second × 1e-06, in MB/s, at each available sample</t>
+          <t>ΔserverStatus/wiredTiger/cache/application thread time evicting (usecs) per second × 0.001, in ms/s, at each available sample</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
@@ -6004,24 +6004,32 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>MB/s</t>
+          <t>ms/s</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>none — read for its shape only</t>
-        </is>
-      </c>
-      <c r="J59" s="4" t="inlineStr"/>
+          <t>none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>5.5 ms/s → 50% none, 50% some</t>
+        </is>
+      </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>shape only: a step, an episode, a schedule</t>
-        </is>
-      </c>
-      <c r="L59" s="4" t="inlineStr"/>
+          <t>heavy</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>100 ms/s or more</t>
+        </is>
+      </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>5 MB/s</t>
+          <t>10 ms/s</t>
         </is>
       </c>
       <c r="N59" s="4" t="inlineStr"/>
@@ -6033,7 +6041,7 @@
       <c r="P59" s="4" t="n"/>
       <c r="Q59" s="4" t="inlineStr">
         <is>
-          <t>MB/s</t>
+          <t>ms/s</t>
         </is>
       </c>
       <c r="R59" s="4" t="inlineStr">
@@ -6043,7 +6051,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>disk.read_await, query.collscans, cache.fill</t>
+          <t>cache.app_eviction, cache.fill_above_95, cache.dirty_above_20</t>
         </is>
       </c>
       <c r="T59" s="4" t="inlineStr"/>
@@ -6057,74 +6065,66 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>checkpoint.duration</t>
+          <t>cache.read_in</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Checkpoint duration</t>
+          <t>Data read into the cache</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>before 7.1</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Duration recorded for the most recent WiredTiger checkpoint; the same completed-checkpoint value may appear in multiple samples. Minute summaries select the highest valid sample.</t>
+          <t>WiredTiger bytes-read-into-cache counter advance per elapsed second, scaled to MB/s.</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/transaction/transaction checkpoint most recent time (msecs) × 0.001, in s, at each available sample</t>
+          <t>ΔserverStatus/wiredTiger/cache/bytes read into cache per second × 1e-06, in MB/s, at each available sample</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>the highest valid sample of each minute</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>MB/s</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>quick ≤5 (fading to 15) · slow 15–40 (edges 5, 60) · back_to_back ≥60 (from 50)</t>
-        </is>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>10 s → 50% quick, 50% slow</t>
-        </is>
-      </c>
+          <t>none — read for its shape only</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr"/>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>back_to_back</t>
-        </is>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>60 s or more</t>
-        </is>
-      </c>
+          <t>shape only: a step, an episode, a schedule</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="inlineStr"/>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>10 s</t>
+          <t>5 MB/s</t>
         </is>
       </c>
       <c r="N60" s="4" t="inlineStr"/>
       <c r="O60" s="4" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="P60" s="4" t="n"/>
       <c r="Q60" s="4" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>MB/s</t>
         </is>
       </c>
       <c r="R60" s="4" t="inlineStr">
@@ -6134,14 +6134,10 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>checkpoint.running, cache.dirty, disk.write_await</t>
-        </is>
-      </c>
-      <c r="T60" s="4" t="inlineStr">
-        <is>
-          <t>60 s: default checkpoint interval, storage.syncPeriodSecs (configured value not read)</t>
-        </is>
-      </c>
+          <t>disk.read_await, query.collscans, cache.fill</t>
+        </is>
+      </c>
+      <c r="T60" s="4" t="inlineStr"/>
       <c r="U60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
@@ -6162,7 +6158,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>7.1 and later</t>
+          <t>before 7.1</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -6172,7 +6168,7 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/checkpoint/most recent time (msecs) × 0.001, in s, at each available sample</t>
+          <t>serverStatus/wiredTiger/transaction/transaction checkpoint most recent time (msecs) × 0.001, in s, at each available sample</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
@@ -6247,76 +6243,74 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>checkpoint.running</t>
+          <t>checkpoint.duration</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Samples with checkpoint activity</t>
+          <t>Checkpoint duration</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>before 7.1</t>
+          <t>7.1 and later</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which WiredTiger reported a checkpoint as currently running, normalized to a 60-second minute.</t>
+          <t>Duration recorded for the most recent WiredTiger checkpoint; the same completed-checkpoint value may appear in multiple samples. Minute summaries select the highest valid sample.</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/transaction/transaction checkpoint currently running, in running, at each available sample</t>
+          <t>serverStatus/wiredTiger/checkpoint/most recent time (msecs) × 0.001, in s, at each available sample</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly above 0 running, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>the highest valid sample of each minute</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>s/min</t>
+          <t>s</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>brief ≤12 (fading to 24) · long 24–42 (edges 12, 54) · continuous ≥57 (from 48)</t>
+          <t>quick ≤5 (fading to 15) · slow 15–40 (edges 5, 60) · back_to_back ≥60 (from 50)</t>
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>18 s/min → 50% brief, 50% long</t>
+          <t>10 s → 50% quick, 50% slow</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>continuous</t>
+          <t>back_to_back</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>48 s/min or more</t>
+          <t>60 s or more</t>
         </is>
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>9 s/min</t>
+          <t>10 s</t>
         </is>
       </c>
       <c r="N62" s="4" t="inlineStr"/>
       <c r="O62" s="4" t="inlineStr">
         <is>
-          <t>time_above</t>
-        </is>
-      </c>
-      <c r="P62" s="4" t="n">
-        <v>0</v>
-      </c>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="P62" s="4" t="n"/>
       <c r="Q62" s="4" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>s</t>
         </is>
       </c>
       <c r="R62" s="4" t="inlineStr">
@@ -6326,10 +6320,14 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>checkpoint.duration, disk.busy_above_95, cache.dirty</t>
-        </is>
-      </c>
-      <c r="T62" s="4" t="inlineStr"/>
+          <t>checkpoint.running, cache.dirty, disk.write_await</t>
+        </is>
+      </c>
+      <c r="T62" s="4" t="inlineStr">
+        <is>
+          <t>60 s: default checkpoint interval, storage.syncPeriodSecs (configured value not read)</t>
+        </is>
+      </c>
       <c r="U62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
@@ -6350,22 +6348,22 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>7.1 and later</t>
+          <t>before 7.1</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which WiredTiger's checkpoint progress state was non-zero, normalized to a 60-second minute.</t>
+          <t>Share of valid samples in which WiredTiger reported a checkpoint as currently running, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/checkpoint/progress state, in state, at each available sample</t>
+          <t>serverStatus/wiredTiger/transaction/transaction checkpoint currently running, in running, at each available sample</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly above 0 state, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>valid-sample share strictly above 0 running, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -6409,7 +6407,7 @@
       </c>
       <c r="Q63" s="4" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>running</t>
         </is>
       </c>
       <c r="R63" s="4" t="inlineStr">
@@ -6423,11 +6421,7 @@
         </is>
       </c>
       <c r="T63" s="4" t="inlineStr"/>
-      <c r="U63" s="4" t="inlineStr">
-        <is>
-          <t>The progress state's values are not decoded; any non-zero value is read as activity.</t>
-        </is>
-      </c>
+      <c r="U63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -6437,66 +6431,76 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>storage.open_handles</t>
+          <t>checkpoint.running</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Open data handles</t>
+          <t>Samples with checkpoint activity</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>7.1 and later</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Count reported by WiredTiger for currently open data handles.</t>
+          <t>Share of valid samples in which WiredTiger's checkpoint progress state was non-zero, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/data-handle/connection data handles currently active, in handles, at each available sample</t>
+          <t>serverStatus/wiredTiger/checkpoint/progress state, in state, at each available sample</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>valid-sample share strictly above 0 state, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>handles</t>
+          <t>s/min</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>none — read for its shape only</t>
-        </is>
-      </c>
-      <c r="J64" s="4" t="inlineStr"/>
+          <t>brief ≤12 (fading to 24) · long 24–42 (edges 12, 54) · continuous ≥57 (from 48)</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>18 s/min → 50% brief, 50% long</t>
+        </is>
+      </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>shape only: a step, an episode, a schedule</t>
-        </is>
-      </c>
-      <c r="L64" s="4" t="inlineStr"/>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>48 s/min or more</t>
+        </is>
+      </c>
       <c r="M64" s="4" t="inlineStr">
         <is>
-          <t>500 handles</t>
+          <t>9 s/min</t>
         </is>
       </c>
       <c r="N64" s="4" t="inlineStr"/>
       <c r="O64" s="4" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="P64" s="4" t="n"/>
+          <t>time_above</t>
+        </is>
+      </c>
+      <c r="P64" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Q64" s="4" t="inlineStr">
         <is>
-          <t>handles</t>
+          <t>state</t>
         </is>
       </c>
       <c r="R64" s="4" t="inlineStr">
@@ -6504,24 +6508,32 @@
           <t>up</t>
         </is>
       </c>
-      <c r="S64" s="4" t="inlineStr"/>
+      <c r="S64" s="4" t="inlineStr">
+        <is>
+          <t>checkpoint.duration, disk.busy_above_95, cache.dirty</t>
+        </is>
+      </c>
       <c r="T64" s="4" t="inlineStr"/>
-      <c r="U64" s="4" t="inlineStr"/>
+      <c r="U64" s="4" t="inlineStr">
+        <is>
+          <t>The progress state's values are not decoded; any non-zero value is read as activity.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>workload</t>
+          <t>storage-engine</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>latency.reads</t>
+          <t>storage.open_handles</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Read latency</t>
+          <t>Open data handles</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -6531,47 +6543,39 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Average milliseconds per read operation over each minute, from opLatencies: every microsecond spent on reads in the minute over every read that finished in it.</t>
+          <t>Count reported by WiredTiger for currently open data handles.</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/opLatencies/reads/latency ÷ ΔserverStatus/opLatencies/reads/ops × 0.001, in ms, at each available sample; minutes where the divisor sums to under 60 are left out</t>
+          <t>serverStatus/wiredTiger/data-handle/connection data handles currently active, in handles, at each available sample</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>each minute's ratio of sums</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>ms</t>
+          <t>handles</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>fast ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · slow 20–50 (edges 10, 100) · very_slow ≥100 (from 50)</t>
-        </is>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>2 ms → 50% fast, 50% normal</t>
-        </is>
-      </c>
+          <t>none — read for its shape only</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr"/>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>slow or very_slow</t>
-        </is>
-      </c>
-      <c r="L65" s="4" t="inlineStr">
-        <is>
-          <t>50 ms or more</t>
-        </is>
-      </c>
+          <t>shape only: a step, an episode, a schedule</t>
+        </is>
+      </c>
+      <c r="L65" s="4" t="inlineStr"/>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>5 ms</t>
+          <t>500 handles</t>
         </is>
       </c>
       <c r="N65" s="4" t="inlineStr"/>
@@ -6583,7 +6587,7 @@
       <c r="P65" s="4" t="n"/>
       <c r="Q65" s="4" t="inlineStr">
         <is>
-          <t>ms</t>
+          <t>handles</t>
         </is>
       </c>
       <c r="R65" s="4" t="inlineStr">
@@ -6591,11 +6595,7 @@
           <t>up</t>
         </is>
       </c>
-      <c r="S65" s="4" t="inlineStr">
-        <is>
-          <t>tickets.read.scarce, query.targeting, cache.fill_above_95, disk.read_await</t>
-        </is>
-      </c>
+      <c r="S65" s="4" t="inlineStr"/>
       <c r="T65" s="4" t="inlineStr"/>
       <c r="U65" s="4" t="inlineStr"/>
     </row>
@@ -6607,12 +6607,12 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>latency.writes</t>
+          <t>latency.reads</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Write latency</t>
+          <t>Read latency</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Average milliseconds per write operation over each minute, from opLatencies.</t>
+          <t>Average milliseconds per read operation over each minute, from opLatencies: every microsecond spent on reads in the minute over every read that finished in it.</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/opLatencies/writes/latency ÷ ΔserverStatus/opLatencies/writes/ops × 0.001, in ms, at each available sample; minutes where the divisor sums to under 60 are left out</t>
+          <t>ΔserverStatus/opLatencies/reads/latency ÷ ΔserverStatus/opLatencies/reads/ops × 0.001, in ms, at each available sample; minutes where the divisor sums to under 60 are left out</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.scarce, cache.dirty_above_20, flow.lagged, repl.majority_lag</t>
+          <t>tickets.read.scarce, query.targeting, cache.fill_above_95, disk.read_await</t>
         </is>
       </c>
       <c r="T66" s="4" t="inlineStr"/>
@@ -6698,12 +6698,12 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>latency.commands</t>
+          <t>latency.writes</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Command latency</t>
+          <t>Write latency</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -6713,12 +6713,12 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Ratio of command opLatencies counter advance to command operation-count advance, scaled to milliseconds per operation.</t>
+          <t>Average milliseconds per write operation over each minute, from opLatencies.</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/opLatencies/commands/latency ÷ ΔserverStatus/opLatencies/commands/ops × 0.001, in ms, at each available sample; minutes where the divisor sums to under 60 are left out</t>
+          <t>ΔserverStatus/opLatencies/writes/latency ÷ ΔserverStatus/opLatencies/writes/ops × 0.001, in ms, at each available sample; minutes where the divisor sums to under 60 are left out</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.scarce, query.targeting</t>
+          <t>tickets.write.scarce, cache.dirty_above_20, flow.lagged, repl.majority_lag</t>
         </is>
       </c>
       <c r="T67" s="4" t="inlineStr"/>
@@ -6789,12 +6789,12 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>ops.total</t>
+          <t>latency.commands</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Operations a second</t>
+          <t>Command latency</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -6804,39 +6804,47 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Sum of query, getMore, insert, update, delete and command operation-counter rates.</t>
+          <t>Ratio of command opLatencies counter advance to command operation-count advance, scaled to milliseconds per operation.</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Δ(serverStatus/opcounters/query + serverStatus/opcounters/getmore + serverStatus/opcounters/insert + serverStatus/opcounters/update + serverStatus/opcounters/delete + serverStatus/opcounters/command) per second, in ops/s, at each available sample</t>
+          <t>ΔserverStatus/opLatencies/commands/latency ÷ ΔserverStatus/opLatencies/commands/ops × 0.001, in ms, at each available sample; minutes where the divisor sums to under 60 are left out</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>each minute's ratio of sums</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>ops/s</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>none — read for its shape only</t>
-        </is>
-      </c>
-      <c r="J68" s="4" t="inlineStr"/>
+          <t>fast ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · slow 20–50 (edges 10, 100) · very_slow ≥100 (from 50)</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>2 ms → 50% fast, 50% normal</t>
+        </is>
+      </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>shape only: a step, an episode, a schedule</t>
-        </is>
-      </c>
-      <c r="L68" s="4" t="inlineStr"/>
+          <t>slow or very_slow</t>
+        </is>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>50 ms or more</t>
+        </is>
+      </c>
       <c r="M68" s="4" t="inlineStr">
         <is>
-          <t>50 ops/s</t>
+          <t>5 ms</t>
         </is>
       </c>
       <c r="N68" s="4" t="inlineStr"/>
@@ -6848,7 +6856,7 @@
       <c r="P68" s="4" t="n"/>
       <c r="Q68" s="4" t="inlineStr">
         <is>
-          <t>ops/s</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="R68" s="4" t="inlineStr">
@@ -6858,7 +6866,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>ops.writes, connections.current</t>
+          <t>tickets.read.scarce, query.targeting</t>
         </is>
       </c>
       <c r="T68" s="4" t="inlineStr"/>
@@ -6872,12 +6880,12 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>ops.writes</t>
+          <t>ops.total</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Writes a second</t>
+          <t>Operations a second</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -6887,12 +6895,12 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Sum of insert, update and delete operation-counter rates.</t>
+          <t>Sum of query, getMore, insert, update, delete and command operation-counter rates.</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Δ(serverStatus/opcounters/insert + serverStatus/opcounters/update + serverStatus/opcounters/delete) per second, in ops/s, at each available sample</t>
+          <t>Δ(serverStatus/opcounters/query + serverStatus/opcounters/getmore + serverStatus/opcounters/insert + serverStatus/opcounters/update + serverStatus/opcounters/delete + serverStatus/opcounters/command) per second, in ops/s, at each available sample</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -6941,7 +6949,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>cache.dirty, checkpoint.duration</t>
+          <t>ops.writes, connections.current</t>
         </is>
       </c>
       <c r="T69" s="4" t="inlineStr"/>
@@ -6955,12 +6963,12 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>query.targeting</t>
+          <t>ops.writes</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Documents examined per document returned</t>
+          <t>Writes a second</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -6970,47 +6978,39 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Ratio of documents-examined counter advance to documents-returned counter advance; it does not determine index suitability.</t>
+          <t>Sum of insert, update and delete operation-counter rates.</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/metrics/queryExecutor/scannedObjects ÷ ΔserverStatus/metrics/document/returned, in ratio, at each available sample; minutes where the divisor sums to under 60 are left out</t>
+          <t>Δ(serverStatus/opcounters/insert + serverStatus/opcounters/update + serverStatus/opcounters/delete) per second, in ops/s, at each available sample</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>each minute's ratio of sums</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>ops/s</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>low ≤2 (fading to 10) · moderate 10–50 (edges 2, 100) · high 100–500 (edges 50, 1000) · very_high ≥1000 (from 500)</t>
-        </is>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>6 ratio → 50% low, 50% moderate</t>
-        </is>
-      </c>
+          <t>none — read for its shape only</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr"/>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>high or very_high</t>
-        </is>
-      </c>
-      <c r="L70" s="4" t="inlineStr">
-        <is>
-          <t>100 ratio or more</t>
-        </is>
-      </c>
+          <t>shape only: a step, an episode, a schedule</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="inlineStr"/>
       <c r="M70" s="4" t="inlineStr">
         <is>
-          <t>10 ratio</t>
+          <t>50 ops/s</t>
         </is>
       </c>
       <c r="N70" s="4" t="inlineStr"/>
@@ -7022,7 +7022,7 @@
       <c r="P70" s="4" t="n"/>
       <c r="Q70" s="4" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>ops/s</t>
         </is>
       </c>
       <c r="R70" s="4" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>query.collscans, cache.read_in, cpu.busy</t>
+          <t>cache.dirty, checkpoint.duration</t>
         </is>
       </c>
       <c r="T70" s="4" t="inlineStr"/>
@@ -7046,62 +7046,62 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>query.collscans</t>
+          <t>query.targeting</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Collection scans</t>
+          <t>Documents examined per document returned</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>4.4 and later</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Rate of the server's collection-scan counter.</t>
+          <t>Ratio of documents-examined counter advance to documents-returned counter advance; it does not determine index suitability.</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/metrics/queryExecutor/collectionScans/total per second, in /s, at each available sample</t>
+          <t>ΔserverStatus/metrics/queryExecutor/scannedObjects ÷ ΔserverStatus/metrics/document/returned, in ratio, at each available sample; minutes where the divisor sums to under 60 are left out</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>each minute's ratio of sums</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>/s</t>
+          <t>ratio</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>none ≤0.01 (fading to 0.1) · some 0.1–1 (edges 0.01, 10) · many ≥10 (from 1)</t>
+          <t>low ≤2 (fading to 10) · moderate 10–50 (edges 2, 100) · high 100–500 (edges 50, 1000) · very_high ≥1000 (from 500)</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>0.055 /s → 50% none, 50% some</t>
+          <t>6 ratio → 50% low, 50% moderate</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>many</t>
+          <t>high or very_high</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>1 /s or more</t>
+          <t>100 ratio or more</t>
         </is>
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>0.5 /s</t>
+          <t>10 ratio</t>
         </is>
       </c>
       <c r="N71" s="4" t="inlineStr"/>
@@ -7113,7 +7113,7 @@
       <c r="P71" s="4" t="n"/>
       <c r="Q71" s="4" t="inlineStr">
         <is>
-          <t>/s</t>
+          <t>ratio</t>
         </is>
       </c>
       <c r="R71" s="4" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>query.targeting, cache.read_in</t>
+          <t>query.collscans, cache.read_in, cpu.busy</t>
         </is>
       </c>
       <c r="T71" s="4" t="inlineStr"/>
@@ -7137,27 +7137,27 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>query.scan_and_order</t>
+          <t>query.collscans</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>scanAndOrder counter rate</t>
+          <t>Collection scans</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>4.4 and later</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Rate of the server's scanAndOrder counter.</t>
+          <t>Rate of the server's collection-scan counter.</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/metrics/operation/scanAndOrder per second, in /s, at each available sample</t>
+          <t>ΔserverStatus/metrics/queryExecutor/collectionScans/total per second, in /s, at each available sample</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
@@ -7172,19 +7172,27 @@
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>none — read for its shape only</t>
-        </is>
-      </c>
-      <c r="J72" s="4" t="inlineStr"/>
+          <t>none ≤0.01 (fading to 0.1) · some 0.1–1 (edges 0.01, 10) · many ≥10 (from 1)</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>0.055 /s → 50% none, 50% some</t>
+        </is>
+      </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>shape only: a step, an episode, a schedule</t>
-        </is>
-      </c>
-      <c r="L72" s="4" t="inlineStr"/>
+          <t>many</t>
+        </is>
+      </c>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>1 /s or more</t>
+        </is>
+      </c>
       <c r="M72" s="4" t="inlineStr">
         <is>
-          <t>1 /s</t>
+          <t>0.5 /s</t>
         </is>
       </c>
       <c r="N72" s="4" t="inlineStr"/>
@@ -7206,7 +7214,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>query.targeting, memory.heap_outside_cache</t>
+          <t>query.targeting, cache.read_in</t>
         </is>
       </c>
       <c r="T72" s="4" t="inlineStr"/>
@@ -7220,12 +7228,12 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>writes.conflicts</t>
+          <t>query.scan_and_order</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Write conflicts</t>
+          <t>scanAndOrder counter rate</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -7235,12 +7243,12 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Rate of the server's writeConflicts counter; retries, document identity and contention cause are not inferred from this counter.</t>
+          <t>Rate of the server's scanAndOrder counter.</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/metrics/operation/writeConflicts per second, in /s, at each available sample</t>
+          <t>ΔserverStatus/metrics/operation/scanAndOrder per second, in /s, at each available sample</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -7255,27 +7263,19 @@
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>rare ≤0.1 (fading to 1) · some 1–10 (edges 0.1, 50) · heavy ≥50 (from 10)</t>
-        </is>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>0.55 /s → 50% rare, 50% some</t>
-        </is>
-      </c>
+          <t>none — read for its shape only</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr"/>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>heavy</t>
-        </is>
-      </c>
-      <c r="L73" s="4" t="inlineStr">
-        <is>
-          <t>10 /s or more</t>
-        </is>
-      </c>
+          <t>shape only: a step, an episode, a schedule</t>
+        </is>
+      </c>
+      <c r="L73" s="4" t="inlineStr"/>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>2 /s</t>
+          <t>1 /s</t>
         </is>
       </c>
       <c r="N73" s="4" t="inlineStr"/>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>ops.writes, latency.writes</t>
+          <t>query.targeting, memory.heap_outside_cache</t>
         </is>
       </c>
       <c r="T73" s="4" t="inlineStr"/>
@@ -7311,12 +7311,12 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>ttl.deletes</t>
+          <t>writes.conflicts</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Documents deleted by TTL</t>
+          <t>Write conflicts</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -7326,12 +7326,12 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Rate of documents reported deleted by the TTL monitor; collection identity, expiry backlog and latency impact are not inferred.</t>
+          <t>Rate of the server's writeConflicts counter; retries, document identity and contention cause are not inferred from this counter.</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/metrics/ttl/deletedDocuments per second, in docs/s, at each available sample</t>
+          <t>ΔserverStatus/metrics/operation/writeConflicts per second, in /s, at each available sample</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -7341,24 +7341,32 @@
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>docs/s</t>
+          <t>/s</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>none — read for its shape only</t>
-        </is>
-      </c>
-      <c r="J74" s="4" t="inlineStr"/>
+          <t>rare ≤0.1 (fading to 1) · some 1–10 (edges 0.1, 50) · heavy ≥50 (from 10)</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>0.55 /s → 50% rare, 50% some</t>
+        </is>
+      </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>shape only: a step, an episode, a schedule</t>
-        </is>
-      </c>
-      <c r="L74" s="4" t="inlineStr"/>
+          <t>heavy</t>
+        </is>
+      </c>
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>10 /s or more</t>
+        </is>
+      </c>
       <c r="M74" s="4" t="inlineStr">
         <is>
-          <t>50 docs/s</t>
+          <t>2 /s</t>
         </is>
       </c>
       <c r="N74" s="4" t="inlineStr"/>
@@ -7370,7 +7378,7 @@
       <c r="P74" s="4" t="n"/>
       <c r="Q74" s="4" t="inlineStr">
         <is>
-          <t>docs/s</t>
+          <t>/s</t>
         </is>
       </c>
       <c r="R74" s="4" t="inlineStr">
@@ -7380,7 +7388,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>cache.dirty, disk.write_await, repl.member_lag</t>
+          <t>ops.writes, latency.writes</t>
         </is>
       </c>
       <c r="T74" s="4" t="inlineStr"/>
@@ -7394,12 +7402,12 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>cursors.open</t>
+          <t>ttl.deletes</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Open cursors</t>
+          <t>Documents deleted by TTL</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -7409,12 +7417,12 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Count reported for currently open cursors.</t>
+          <t>Rate of documents reported deleted by the TTL monitor; collection identity, expiry backlog and latency impact are not inferred.</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/metrics/cursor/open/total, in cursors, at each available sample</t>
+          <t>ΔserverStatus/metrics/ttl/deletedDocuments per second, in docs/s, at each available sample</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
@@ -7424,7 +7432,7 @@
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>cursors</t>
+          <t>docs/s</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -7441,7 +7449,7 @@
       <c r="L75" s="4" t="inlineStr"/>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>50 cursors</t>
+          <t>50 docs/s</t>
         </is>
       </c>
       <c r="N75" s="4" t="inlineStr"/>
@@ -7453,7 +7461,7 @@
       <c r="P75" s="4" t="n"/>
       <c r="Q75" s="4" t="inlineStr">
         <is>
-          <t>cursors</t>
+          <t>docs/s</t>
         </is>
       </c>
       <c r="R75" s="4" t="inlineStr">
@@ -7463,7 +7471,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>memory.heap_outside_cache, connections.current</t>
+          <t>cache.dirty, disk.write_await, repl.member_lag</t>
         </is>
       </c>
       <c r="T75" s="4" t="inlineStr"/>
@@ -7472,79 +7480,71 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>replication</t>
+          <t>workload</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>repl.member_lag</t>
+          <t>cursors.open</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Member replication lag</t>
+          <t>Open cursors</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>before 6.0</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Difference between each member's reported applied-write timestamp and the newest such timestamp in this node's replica-set status, scaled to seconds. Members without a timestamp have no result. optimeDate has one-second resolution. Minute summaries select the highest valid sample.</t>
+          <t>Count reported for currently open cursors.</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>newest of every replSetGetStatus/members/{i}/optimeDate − this one × 0.001, in s, at each available sample</t>
+          <t>serverStatus/metrics/cursor/open/total, in cursors, at each available sample</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>the highest valid sample of each minute</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>cursors</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>current ≤2 (fading to 5) · behind 5–20 (edges 2, 30) · lagging 30–120 (edges 20, 300) · far_behind ≥300 (from 120)</t>
-        </is>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>3.5 s → 50% current, 50% behind</t>
-        </is>
-      </c>
+          <t>none — read for its shape only</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr"/>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>lagging or far_behind</t>
-        </is>
-      </c>
-      <c r="L76" s="4" t="inlineStr">
-        <is>
-          <t>30 s or more</t>
-        </is>
-      </c>
+          <t>shape only: a step, an episode, a schedule</t>
+        </is>
+      </c>
+      <c r="L76" s="4" t="inlineStr"/>
       <c r="M76" s="4" t="inlineStr">
         <is>
-          <t>5 s</t>
+          <t>50 cursors</t>
         </is>
       </c>
       <c r="N76" s="4" t="inlineStr"/>
       <c r="O76" s="4" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="P76" s="4" t="n"/>
       <c r="Q76" s="4" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>cursors</t>
         </is>
       </c>
       <c r="R76" s="4" t="inlineStr">
@@ -7554,15 +7554,11 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>repl.majority_lag, flow.lagged, net.retransmit</t>
+          <t>memory.heap_outside_cache, connections.current</t>
         </is>
       </c>
       <c r="T76" s="4" t="inlineStr"/>
-      <c r="U76" s="4" t="inlineStr">
-        <is>
-          <t>One result per entry of this node's replica-set status, numbered by position in that list; a position can name a different member after a reconfig. Lag is measured against the newest applied time among members, not against the primary, and a member that stopped reporting keeps its last time.</t>
-        </is>
-      </c>
+      <c r="U76" s="4" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -7582,17 +7578,17 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>6.0 and later</t>
+          <t>before 6.0</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Difference between each member's reported applied-write timestamp and the newest such timestamp in this node's replica-set status, scaled to seconds. Members without a timestamp have no result. Minute summaries select the highest valid sample.</t>
+          <t>Difference between each member's reported applied-write timestamp and the newest such timestamp in this node's replica-set status, scaled to seconds. Members without a timestamp have no result. optimeDate has one-second resolution. Minute summaries select the highest valid sample.</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>newest of every replSetGetStatus/members/{i}/lastAppliedWallTime − this one × 0.001, in s, at each available sample</t>
+          <t>newest of every replSetGetStatus/members/{i}/optimeDate − this one × 0.001, in s, at each available sample</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
@@ -7667,27 +7663,27 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>repl.majority_lag</t>
+          <t>repl.member_lag</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Majority commit lag</t>
+          <t>Member replication lag</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>4.2 and later</t>
+          <t>6.0 and later</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Difference between this node's lastAppliedWallTime and lastCommittedWallTime, scaled to seconds. Minute summaries select the highest valid sample.</t>
+          <t>Difference between each member's reported applied-write timestamp and the newest such timestamp in this node's replica-set status, scaled to seconds. Members without a timestamp have no result. Minute summaries select the highest valid sample.</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>replSetGetStatus/optimes/lastAppliedWallTime − replSetGetStatus/optimes/lastCommittedWallTime × 0.001, in s, at each available sample</t>
+          <t>newest of every replSetGetStatus/members/{i}/lastAppliedWallTime − this one × 0.001, in s, at each available sample</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
@@ -7702,27 +7698,27 @@
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>current ≤1 (fading to 3) · behind 3–10 (edges 1, 20) · lagging ≥20 (from 10)</t>
+          <t>current ≤2 (fading to 5) · behind 5–20 (edges 2, 30) · lagging 30–120 (edges 20, 300) · far_behind ≥300 (from 120)</t>
         </is>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>2 s → 50% current, 50% behind</t>
+          <t>3.5 s → 50% current, 50% behind</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>lagging</t>
+          <t>lagging or far_behind</t>
         </is>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>10 s or more</t>
+          <t>30 s or more</t>
         </is>
       </c>
       <c r="M78" s="4" t="inlineStr">
         <is>
-          <t>2 s</t>
+          <t>5 s</t>
         </is>
       </c>
       <c r="N78" s="4" t="inlineStr"/>
@@ -7744,11 +7740,15 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>repl.member_lag, flow.lagged, latency.writes</t>
+          <t>repl.majority_lag, flow.lagged, net.retransmit</t>
         </is>
       </c>
       <c r="T78" s="4" t="inlineStr"/>
-      <c r="U78" s="4" t="inlineStr"/>
+      <c r="U78" s="4" t="inlineStr">
+        <is>
+          <t>One result per entry of this node's replica-set status, numbered by position in that list; a position can name a different member after a reconfig. Lag is measured against the newest applied time among members, not against the primary, and a member that stopped reporting keeps its last time.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -7758,76 +7758,74 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>flow.lagged</t>
+          <t>repl.majority_lag</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Samples with flowControl.isLagged set</t>
+          <t>Majority commit lag</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>4.2 and later</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which flowControl.isLagged was set, normalized to a 60-second minute.</t>
+          <t>Difference between this node's lastAppliedWallTime and lastCommittedWallTime, scaled to seconds. Minute summaries select the highest valid sample. A sample with either time unset (zero) is left out.</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/flowControl/isLagged, in lagged, at each available sample</t>
+          <t>replSetGetStatus/optimes/lastAppliedWallTime − replSetGetStatus/optimes/lastCommittedWallTime × 0.001, in s, at each available sample</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly above 0 lagged, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>the highest valid sample of each minute</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>s/min</t>
+          <t>s</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>none ≤0 (fading to 1) · some 1–30 (edges 0, 48) · most ≥48 (from 30)</t>
+          <t>current ≤1 (fading to 3) · behind 3–10 (edges 1, 20) · lagging ≥20 (from 10)</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>0.5 s/min → 50% none, 50% some</t>
+          <t>2 s → 50% current, 50% behind</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>most</t>
+          <t>lagging</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>1 s/min or more</t>
+          <t>10 s or more</t>
         </is>
       </c>
       <c r="M79" s="4" t="inlineStr">
         <is>
-          <t>3 s/min</t>
+          <t>2 s</t>
         </is>
       </c>
       <c r="N79" s="4" t="inlineStr"/>
       <c r="O79" s="4" t="inlineStr">
         <is>
-          <t>time_above</t>
-        </is>
-      </c>
-      <c r="P79" s="4" t="n">
-        <v>0</v>
-      </c>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="P79" s="4" t="n"/>
       <c r="Q79" s="4" t="inlineStr">
         <is>
-          <t>lagged</t>
+          <t>s</t>
         </is>
       </c>
       <c r="R79" s="4" t="inlineStr">
@@ -7837,15 +7835,11 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>flow.wait, repl.majority_lag, latency.writes</t>
+          <t>repl.member_lag, flow.lagged, latency.writes</t>
         </is>
       </c>
       <c r="T79" s="4" t="inlineStr"/>
-      <c r="U79" s="4" t="inlineStr">
-        <is>
-          <t>Set only on a primary with flow control enabled; a secondary, or a primary with flow control disabled, reports it unset. The flag records that the majority commit point lagged; time writers spent waiting for flow control is flow.wait.</t>
-        </is>
-      </c>
+      <c r="U79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -7855,12 +7849,12 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>flow.wait</t>
+          <t>flow.lagged</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Time writers waited on flow control</t>
+          <t>Samples with flowControl.isLagged set</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -7870,59 +7864,61 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Milliseconds a second writes spent waiting for flow control tickets on this node, added across every write waiting.</t>
+          <t>Share of valid samples in which flowControl.isLagged was set, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/flowControl/timeAcquiringMicros per second × 0.001, in ms/s, at each available sample</t>
+          <t>serverStatus/flowControl/isLagged, in lagged, at each available sample</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>valid-sample share strictly above 0 lagged, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>ms/s</t>
+          <t>s/min</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)</t>
+          <t>none ≤0 (fading to 1) · some 1–30 (edges 0, 48) · most ≥48 (from 30)</t>
         </is>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>5.5 ms/s → 50% none, 50% some</t>
+          <t>0.5 s/min → 50% none, 50% some</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>most</t>
         </is>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
-          <t>100 ms/s or more</t>
+          <t>1 s/min or more</t>
         </is>
       </c>
       <c r="M80" s="4" t="inlineStr">
         <is>
-          <t>10 ms/s</t>
+          <t>3 s/min</t>
         </is>
       </c>
       <c r="N80" s="4" t="inlineStr"/>
       <c r="O80" s="4" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="P80" s="4" t="n"/>
+          <t>time_above</t>
+        </is>
+      </c>
+      <c r="P80" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Q80" s="4" t="inlineStr">
         <is>
-          <t>ms/s</t>
+          <t>lagged</t>
         </is>
       </c>
       <c r="R80" s="4" t="inlineStr">
@@ -7932,11 +7928,15 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>flow.lagged, latency.writes</t>
+          <t>flow.wait, repl.majority_lag, latency.writes</t>
         </is>
       </c>
       <c r="T80" s="4" t="inlineStr"/>
-      <c r="U80" s="4" t="inlineStr"/>
+      <c r="U80" s="4" t="inlineStr">
+        <is>
+          <t>Set only on a primary with flow control enabled; a secondary, or a primary with flow control disabled, reports it unset. The flag records that the majority commit point lagged; time writers spent waiting for flow control is flow.wait.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -7946,12 +7946,12 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>repl.apply_rate</t>
+          <t>flow.wait</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Oplog entries applied</t>
+          <t>Time writers waited on flow control</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Rate of the node's oplog application operation counter.</t>
+          <t>Milliseconds a second writes spent waiting for flow control tickets on this node, added across every write waiting.</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/metrics/repl/apply/ops per second, in ops/s, at each available sample</t>
+          <t>ΔserverStatus/flowControl/timeAcquiringMicros per second × 0.001, in ms/s, at each available sample</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
@@ -7976,24 +7976,32 @@
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>ops/s</t>
+          <t>ms/s</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>none — read for its shape only</t>
-        </is>
-      </c>
-      <c r="J81" s="4" t="inlineStr"/>
+          <t>none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>5.5 ms/s → 50% none, 50% some</t>
+        </is>
+      </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>shape only: a step, an episode, a schedule</t>
-        </is>
-      </c>
-      <c r="L81" s="4" t="inlineStr"/>
+          <t>heavy</t>
+        </is>
+      </c>
+      <c r="L81" s="4" t="inlineStr">
+        <is>
+          <t>100 ms/s or more</t>
+        </is>
+      </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>50 ops/s</t>
+          <t>10 ms/s</t>
         </is>
       </c>
       <c r="N81" s="4" t="inlineStr"/>
@@ -8005,17 +8013,17 @@
       <c r="P81" s="4" t="n"/>
       <c r="Q81" s="4" t="inlineStr">
         <is>
-          <t>ops/s</t>
+          <t>ms/s</t>
         </is>
       </c>
       <c r="R81" s="4" t="inlineStr">
         <is>
-          <t>down</t>
+          <t>up</t>
         </is>
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>repl.buffer_fill, repl.member_lag</t>
+          <t>flow.lagged, latency.writes</t>
         </is>
       </c>
       <c r="T81" s="4" t="inlineStr"/>
@@ -8029,62 +8037,54 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>repl.buffer_fill</t>
+          <t>repl.apply_rate</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Apply buffer fill</t>
+          <t>Oplog entries applied</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>before 8.0</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Reported replication buffer bytes as a share of its reported maximum.</t>
+          <t>Rate of the node's oplog application operation counter.</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/metrics/repl/buffer/sizeBytes ÷ serverStatus/metrics/repl/buffer/maxSizeBytes × 100, in %, at each available sample</t>
+          <t>ΔserverStatus/metrics/repl/apply/ops per second, in ops/s, at each available sample</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>each minute's ratio of sums</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>ops/s</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>empty ≤5 (fading to 20) · filling 20–60 (edges 5, 85) · full ≥90 (from 70)</t>
-        </is>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>12.5 % → 50% empty, 50% filling</t>
-        </is>
-      </c>
+          <t>none — read for its shape only</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr"/>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="L82" s="4" t="inlineStr">
-        <is>
-          <t>70 % or more</t>
-        </is>
-      </c>
+          <t>shape only: a step, an episode, a schedule</t>
+        </is>
+      </c>
+      <c r="L82" s="4" t="inlineStr"/>
       <c r="M82" s="4" t="inlineStr">
         <is>
-          <t>10 %</t>
+          <t>50 ops/s</t>
         </is>
       </c>
       <c r="N82" s="4" t="inlineStr"/>
@@ -8096,17 +8096,17 @@
       <c r="P82" s="4" t="n"/>
       <c r="Q82" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>ops/s</t>
         </is>
       </c>
       <c r="R82" s="4" t="inlineStr">
         <is>
-          <t>up</t>
+          <t>down</t>
         </is>
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>repl.buffer_full, repl.apply_rate, repl.member_lag</t>
+          <t>repl.buffer_fill, repl.member_lag</t>
         </is>
       </c>
       <c r="T82" s="4" t="inlineStr"/>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>8.0 and later</t>
+          <t>before 8.0</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/metrics/repl/buffer/apply/sizeBytes ÷ serverStatus/metrics/repl/buffer/apply/maxSizeBytes × 100, in %, at each available sample</t>
+          <t>serverStatus/metrics/repl/buffer/sizeBytes ÷ serverStatus/metrics/repl/buffer/maxSizeBytes × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
@@ -8211,73 +8211,71 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>repl.buffer_full</t>
+          <t>repl.buffer_fill</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Apply-buffer samples above 90%</t>
+          <t>Apply buffer fill</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>before 8.0</t>
+          <t>8.0 and later</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which replication buffer bytes were strictly above 90 % of the reported maximum, normalized to a 60-second minute.</t>
+          <t>Reported replication buffer bytes as a share of its reported maximum.</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/metrics/repl/buffer/sizeBytes ÷ serverStatus/metrics/repl/buffer/maxSizeBytes × 100, in %, at each available sample</t>
+          <t>serverStatus/metrics/repl/buffer/apply/sizeBytes ÷ serverStatus/metrics/repl/buffer/apply/maxSizeBytes × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly above 90 %, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>each minute's ratio of sums</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>s/min</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
         <is>
-          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
+          <t>empty ≤5 (fading to 20) · filling 20–60 (edges 5, 85) · full ≥90 (from 70)</t>
         </is>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>0.5 s/min → 50% none, 50% brief</t>
+          <t>12.5 % → 50% empty, 50% filling</t>
         </is>
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>frequent or constant</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
-          <t>1 s/min or more</t>
+          <t>70 % or more</t>
         </is>
       </c>
       <c r="M84" s="4" t="inlineStr">
         <is>
-          <t>3 s/min</t>
+          <t>10 %</t>
         </is>
       </c>
       <c r="N84" s="4" t="inlineStr"/>
       <c r="O84" s="4" t="inlineStr">
         <is>
-          <t>time_above</t>
-        </is>
-      </c>
-      <c r="P84" s="4" t="n">
-        <v>90</v>
-      </c>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P84" s="4" t="n"/>
       <c r="Q84" s="4" t="inlineStr">
         <is>
           <t>%</t>
@@ -8290,7 +8288,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>repl.buffer_fill, repl.apply_rate</t>
+          <t>repl.buffer_full, repl.apply_rate, repl.member_lag</t>
         </is>
       </c>
       <c r="T84" s="4" t="inlineStr"/>
@@ -8314,7 +8312,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>8.0 and later</t>
+          <t>before 8.0</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -8324,7 +8322,7 @@
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/metrics/repl/buffer/apply/sizeBytes ÷ serverStatus/metrics/repl/buffer/apply/maxSizeBytes × 100, in %, at each available sample</t>
+          <t>serverStatus/metrics/repl/buffer/sizeBytes ÷ serverStatus/metrics/repl/buffer/maxSizeBytes × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
@@ -8392,76 +8390,78 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>connections</t>
+          <t>replication</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>connections.used</t>
+          <t>repl.buffer_full</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Current connections as a share of current plus available</t>
+          <t>Apply-buffer samples above 90%</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>8.0 and later</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Reported current connections divided by current plus available connections.</t>
+          <t>Share of valid samples in which replication buffer bytes were strictly above 90 % of the reported maximum, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/connections/current ÷ (serverStatus/connections/current + serverStatus/connections/available) × 100, in %, at each available sample</t>
+          <t>serverStatus/metrics/repl/buffer/apply/sizeBytes ÷ serverStatus/metrics/repl/buffer/apply/maxSizeBytes × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>each minute's ratio of sums</t>
+          <t>valid-sample share strictly above 90 %, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>s/min</t>
         </is>
       </c>
       <c r="I86" s="4" t="inlineStr">
         <is>
-          <t>low ≤25 (fading to 50) · moderate 50–70 (edges 25, 85) · high 85–90 (edges 70, 95) · near_limit ≥95 (from 90)</t>
+          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
         </is>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>37.5 % → 50% low, 50% moderate</t>
+          <t>0.5 s/min → 50% none, 50% brief</t>
         </is>
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>high or near_limit</t>
+          <t>frequent or constant</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>85 % or more</t>
+          <t>1 s/min or more</t>
         </is>
       </c>
       <c r="M86" s="4" t="inlineStr">
         <is>
-          <t>10 %</t>
+          <t>3 s/min</t>
         </is>
       </c>
       <c r="N86" s="4" t="inlineStr"/>
       <c r="O86" s="4" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="P86" s="4" t="n"/>
+          <t>time_above</t>
+        </is>
+      </c>
+      <c r="P86" s="4" t="n">
+        <v>90</v>
+      </c>
       <c r="Q86" s="4" t="inlineStr">
         <is>
           <t>%</t>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>connections.scarce, connections.created, connections.rejected</t>
+          <t>repl.buffer_fill, repl.apply_rate</t>
         </is>
       </c>
       <c r="T86" s="4" t="inlineStr"/>
@@ -8488,12 +8488,12 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>connections.scarce</t>
+          <t>connections.used</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Samples with under 10% of connections left</t>
+          <t>Current connections as a share of current plus available</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -8503,61 +8503,59 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which available connections were strictly below 10 % of current plus available, normalized to a 60-second minute.</t>
+          <t>Reported current connections divided by current plus available connections.</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/connections/available ÷ (serverStatus/connections/current + serverStatus/connections/available) × 100, in % available, at each available sample</t>
+          <t>serverStatus/connections/current ÷ (serverStatus/connections/current + serverStatus/connections/available) × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>each minute's ratio of sums</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>s/min</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
+          <t>low ≤25 (fading to 50) · moderate 50–70 (edges 25, 85) · high 85–90 (edges 70, 95) · near_limit ≥95 (from 90)</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>0.5 s/min → 50% none, 50% brief</t>
+          <t>37.5 % → 50% low, 50% moderate</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>brief and above (set by the rule)</t>
+          <t>high or near_limit</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>1 s/min or more</t>
+          <t>85 % or more</t>
         </is>
       </c>
       <c r="M87" s="4" t="inlineStr">
         <is>
-          <t>3 s/min</t>
+          <t>10 %</t>
         </is>
       </c>
       <c r="N87" s="4" t="inlineStr"/>
       <c r="O87" s="4" t="inlineStr">
         <is>
-          <t>time_below</t>
-        </is>
-      </c>
-      <c r="P87" s="4" t="n">
-        <v>10</v>
-      </c>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P87" s="4" t="n"/>
       <c r="Q87" s="4" t="inlineStr">
         <is>
-          <t>% available</t>
+          <t>%</t>
         </is>
       </c>
       <c r="R87" s="4" t="inlineStr">
@@ -8567,7 +8565,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>connections.used, connections.created, connections.rejected</t>
+          <t>connections.scarce, connections.created, connections.rejected</t>
         </is>
       </c>
       <c r="T87" s="4" t="inlineStr"/>
@@ -8581,12 +8579,12 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>connections.created</t>
+          <t>connections.scarce</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>New connections</t>
+          <t>Samples with under 10% of connections left</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -8596,59 +8594,61 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Rate of the server's totalCreated connection counter.</t>
+          <t>Share of valid samples in which available connections were strictly below 10 % of current plus available, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/connections/totalCreated per second, in conn/s, at each available sample</t>
+          <t>serverStatus/connections/available ÷ (serverStatus/connections/current + serverStatus/connections/available) × 100, in % available, at each available sample</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>conn/s</t>
+          <t>s/min</t>
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
-          <t>quiet ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · high ≥20 (from 10)</t>
+          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
         </is>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>2 conn/s → 50% quiet, 50% normal</t>
+          <t>0.5 s/min → 50% none, 50% brief</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>brief and above (set by the rule)</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>20 conn/s or more</t>
+          <t>1 s/min or more</t>
         </is>
       </c>
       <c r="M88" s="4" t="inlineStr">
         <is>
-          <t>5 conn/s</t>
+          <t>3 s/min</t>
         </is>
       </c>
       <c r="N88" s="4" t="inlineStr"/>
       <c r="O88" s="4" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="P88" s="4" t="n"/>
+          <t>time_below</t>
+        </is>
+      </c>
+      <c r="P88" s="4" t="n">
+        <v>10</v>
+      </c>
       <c r="Q88" s="4" t="inlineStr">
         <is>
-          <t>conn/s</t>
+          <t>% available</t>
         </is>
       </c>
       <c r="R88" s="4" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>connections.current, cpu.kernel_share, net.resets</t>
+          <t>connections.used, connections.created, connections.rejected</t>
         </is>
       </c>
       <c r="T88" s="4" t="inlineStr"/>
@@ -8672,27 +8672,27 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>connections.non_active</t>
+          <t>connections.created</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Derived non-active connection count</t>
+          <t>New connections</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>4.4 and later</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Derived connection count: current plus awaitingTopologyChanges minus active; it is not evidence of unused client pools or a connection leak.</t>
+          <t>Rate of the server's totalCreated connection counter.</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>(serverStatus/connections/current + serverStatus/connections/awaitingTopologyChanges) − serverStatus/connections/active, in conns, at each available sample</t>
+          <t>ΔserverStatus/connections/totalCreated per second, in conn/s, at each available sample</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
@@ -8702,32 +8702,32 @@
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>conns</t>
+          <t>conn/s</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>few ≤300 (fading to 800) · many 800–1500 (edges 300, 2500) · very_high ≥3000 (from 1500)</t>
+          <t>quiet ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · high ≥20 (from 10)</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>550 conns → 50% few, 50% many</t>
+          <t>2 conn/s → 50% quiet, 50% normal</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>high</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>2000 conns or more</t>
+          <t>20 conn/s or more</t>
         </is>
       </c>
       <c r="M89" s="4" t="inlineStr">
         <is>
-          <t>100 conns</t>
+          <t>5 conn/s</t>
         </is>
       </c>
       <c r="N89" s="4" t="inlineStr"/>
@@ -8739,7 +8739,7 @@
       <c r="P89" s="4" t="n"/>
       <c r="Q89" s="4" t="inlineStr">
         <is>
-          <t>conns</t>
+          <t>conn/s</t>
         </is>
       </c>
       <c r="R89" s="4" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>connections.current, connections.created, connections.working_share, memory.heap_outside_cache</t>
+          <t>connections.current, cpu.kernel_share, net.resets</t>
         </is>
       </c>
       <c r="T89" s="4" t="inlineStr"/>
@@ -8763,12 +8763,12 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>connections.working_share</t>
+          <t>connections.non_active</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Derived active-connection share</t>
+          <t>Derived non-active connection count</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -8778,59 +8778,59 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Derived active-connection share: active minus awaitingTopologyChanges divided by current connections. Minute summaries select the highest valid sample.</t>
+          <t>Derived connection count: current plus awaitingTopologyChanges minus active; it is not evidence of unused client pools or a connection leak.</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/connections/active − serverStatus/connections/awaitingTopologyChanges ÷ serverStatus/connections/current × 100, in %, at each available sample; minutes where the divisor sums to under 3000 are left out</t>
+          <t>(serverStatus/connections/current + serverStatus/connections/awaitingTopologyChanges) − serverStatus/connections/active, in conns, at each available sample</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>the highest valid sample of each minute</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>conns</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>calm ≤10 (fading to 25) · busy 25–40 (edges 10, 60) · high ≥60 (from 40)</t>
+          <t>few ≤300 (fading to 800) · many 800–1500 (edges 300, 2500) · very_high ≥3000 (from 1500)</t>
         </is>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>17.5 % → 50% calm, 50% busy</t>
+          <t>550 conns → 50% few, 50% many</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>40 % or more</t>
+          <t>2000 conns or more</t>
         </is>
       </c>
       <c r="M90" s="4" t="inlineStr">
         <is>
-          <t>10 %</t>
+          <t>100 conns</t>
         </is>
       </c>
       <c r="N90" s="4" t="inlineStr"/>
       <c r="O90" s="4" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="P90" s="4" t="n"/>
       <c r="Q90" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>conns</t>
         </is>
       </c>
       <c r="R90" s="4" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.empty, tickets.write.empty, queue.readers, queue.writers, connections.created</t>
+          <t>connections.current, connections.created, connections.working_share, memory.heap_outside_cache</t>
         </is>
       </c>
       <c r="T90" s="4" t="inlineStr"/>
@@ -8854,66 +8854,74 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>connections.current</t>
+          <t>connections.working_share</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Open connections</t>
+          <t>Derived active-connection share</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>4.4 and later</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Count reported for currently open server connections.</t>
+          <t>Derived active-connection share: active minus awaitingTopologyChanges divided by current connections. Minute summaries select the highest valid sample.</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/connections/current, in conns, at each available sample</t>
+          <t>serverStatus/connections/active − serverStatus/connections/awaitingTopologyChanges ÷ serverStatus/connections/current × 100, in %, at each available sample; minutes where the divisor sums to under 3000 are left out</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>the highest valid sample of each minute</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>conns</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>none — read for its shape only</t>
-        </is>
-      </c>
-      <c r="J91" s="4" t="inlineStr"/>
+          <t>calm ≤10 (fading to 25) · busy 25–40 (edges 10, 60) · high ≥60 (from 40)</t>
+        </is>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>17.5 % → 50% calm, 50% busy</t>
+        </is>
+      </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>shape only: a step, an episode, a schedule</t>
-        </is>
-      </c>
-      <c r="L91" s="4" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="L91" s="4" t="inlineStr">
+        <is>
+          <t>40 % or more</t>
+        </is>
+      </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>50 conns</t>
+          <t>10 %</t>
         </is>
       </c>
       <c r="N91" s="4" t="inlineStr"/>
       <c r="O91" s="4" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>max</t>
         </is>
       </c>
       <c r="P91" s="4" t="n"/>
       <c r="Q91" s="4" t="inlineStr">
         <is>
-          <t>conns</t>
+          <t>%</t>
         </is>
       </c>
       <c r="R91" s="4" t="inlineStr">
@@ -8923,7 +8931,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>connections.non_active, connections.created, memory.heap_outside_cache</t>
+          <t>tickets.read.empty, tickets.write.empty, queue.readers, queue.writers, connections.created</t>
         </is>
       </c>
       <c r="T91" s="4" t="inlineStr"/>
@@ -8937,27 +8945,27 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>connections.rejected</t>
+          <t>connections.current</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Connections refused</t>
+          <t>Open connections</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>6.3 and later</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Rate of the server's rejected connection counter; client impact and rejection cause are not inferred.</t>
+          <t>Count reported for currently open server connections.</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/connections/rejected per second, in /s, at each available sample</t>
+          <t>serverStatus/connections/current, in conns, at each available sample</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
@@ -8967,32 +8975,24 @@
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>/s</t>
+          <t>conns</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>none ≤0.001 (fading to 0.01) · some 0.01–1 (edges 0.001, 5) · many ≥5 (from 1)</t>
-        </is>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>0.005 /s → 56% none, 44% some</t>
-        </is>
-      </c>
+          <t>none — read for its shape only</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr"/>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>many</t>
-        </is>
-      </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>0.01 /s or more</t>
-        </is>
-      </c>
+          <t>shape only: a step, an episode, a schedule</t>
+        </is>
+      </c>
+      <c r="L92" s="4" t="inlineStr"/>
       <c r="M92" s="4" t="inlineStr">
         <is>
-          <t>0.01 /s</t>
+          <t>50 conns</t>
         </is>
       </c>
       <c r="N92" s="4" t="inlineStr"/>
@@ -9004,7 +9004,7 @@
       <c r="P92" s="4" t="n"/>
       <c r="Q92" s="4" t="inlineStr">
         <is>
-          <t>/s</t>
+          <t>conns</t>
         </is>
       </c>
       <c r="R92" s="4" t="inlineStr">
@@ -9014,14 +9014,105 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>connections.scarce, connections.used</t>
+          <t>connections.non_active, connections.created, memory.heap_outside_cache</t>
         </is>
       </c>
       <c r="T92" s="4" t="inlineStr"/>
       <c r="U92" s="4" t="inlineStr"/>
     </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>connections</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>connections.rejected</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>Connections refused</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>6.3 and later</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>Rate of the server's rejected connection counter; client impact and rejection cause are not inferred.</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>ΔserverStatus/connections/rejected per second, in /s, at each available sample</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>each minute's mean</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>/s</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>none ≤0.001 (fading to 0.01) · some 0.01–1 (edges 0.001, 5) · many ≥5 (from 1)</t>
+        </is>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>0.005 /s → 56% none, 44% some</t>
+        </is>
+      </c>
+      <c r="K93" s="4" t="inlineStr">
+        <is>
+          <t>many</t>
+        </is>
+      </c>
+      <c r="L93" s="4" t="inlineStr">
+        <is>
+          <t>0.01 /s or more</t>
+        </is>
+      </c>
+      <c r="M93" s="4" t="inlineStr">
+        <is>
+          <t>0.01 /s</t>
+        </is>
+      </c>
+      <c r="N93" s="4" t="inlineStr"/>
+      <c r="O93" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P93" s="4" t="n"/>
+      <c r="Q93" s="4" t="inlineStr">
+        <is>
+          <t>/s</t>
+        </is>
+      </c>
+      <c r="R93" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S93" s="4" t="inlineStr">
+        <is>
+          <t>connections.scarce, connections.used</t>
+        </is>
+      </c>
+      <c r="T93" s="4" t="inlineStr"/>
+      <c r="U93" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U92"/>
+  <autoFilter ref="A1:U93"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9032,7 +9123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9629,17 +9720,17 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.used</t>
+          <t>files.handles</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>before 8.0</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.", "bands": "low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)", "doc": "Read tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.", "elevated": 75, "formula": "serverStatus/wiredTiger/concurrentTransactions/read/out ÷ serverStatus/wiredTiger/concurrentTransactions/read/totalTickets × 100, in %, at each available sample", "levels": [{"down": [25, 50], "name": "low"}, {"band": [25, 40, 65, 80], "name": "moderate"}, {"band": [65, 75, 90, 95], "name": "high"}, {"name": "near_full", "up": [90, 95]}], "min_change": 10, "name": "tickets.read.used", "pack": "admission", "pairs_with": ["tickets.read.scarce", "tickets.read.pool", "tickets.read.wait", "queue.readers"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/wiredTiger/concurrentTransactions/read/totalTickets"], "mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/read/out"], "scale": 100, "unit": "%"}, "title": "Read tickets in use", "unit": "%", "until": "8.0", "version_text": "before 8.0", "view": "mean"}</t>
+          <t>{"bands": "normal ≤15000 (fading to 30000) · many 30000–60000 (edges 15000, 90000) · very_high ≥90000 (from 60000)", "doc": "File handles allocated on the whole machine, every process together. FTDC does not record the kernel's limit (fs.file-max), so the bands are fixed reference counts, not a share of this host's limit; when the limit is reached the kernel refuses new files and sockets to every process. A climb that never comes back down is worth reading beside connections.", "elevated": 60000, "formula": "systemMetrics/files/sys_file_handles_in_use, in handles, at each available sample", "levels": [{"down": [15000, 30000], "name": "normal"}, {"band": [15000, 30000, 60000, 90000], "name": "many"}, {"name": "very_high", "up": [60000, 90000]}], "min_change": 2000, "name": "files.handles", "pack": "files", "pairs_with": ["connections.current"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["systemMetrics/files/sys_file_handles_in_use"], "scale": 1, "unit": "handles"}, "title": "File handles in use", "unit": "handles", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9649,7 +9740,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.scarce</t>
+          <t>tickets.read.used</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -9659,7 +9750,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which available read tickets were strictly below 10 % of the pool, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/wiredTiger/concurrentTransactions/read/available ÷ serverStatus/wiredTiger/concurrentTransactions/read/totalTickets × 100, in % available, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.read.scarce", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.read.empty", "tickets.read.used", "tickets.read.pool", "tickets.read.wait"], "reading": "valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/wiredTiger/concurrentTransactions/read/totalTickets"], "mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/read/available"], "scale": 100, "unit": "% available"}, "threshold": 10, "title": "Samples with under 10% of read tickets left", "unit": "s/min", "until": "8.0", "version_text": "before 8.0", "view": "time_below"}</t>
+          <t>{"applies": "From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.", "bands": "low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)", "doc": "Read tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.", "elevated": 75, "formula": "serverStatus/wiredTiger/concurrentTransactions/read/out ÷ serverStatus/wiredTiger/concurrentTransactions/read/totalTickets × 100, in %, at each available sample", "levels": [{"down": [25, 50], "name": "low"}, {"band": [25, 40, 65, 80], "name": "moderate"}, {"band": [65, 75, 90, 95], "name": "high"}, {"name": "near_full", "up": [90, 95]}], "min_change": 10, "name": "tickets.read.used", "pack": "admission", "pairs_with": ["tickets.read.scarce", "tickets.read.pool", "tickets.read.wait", "queue.readers"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/wiredTiger/concurrentTransactions/read/totalTickets"], "mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/read/out"], "scale": 100, "unit": "%"}, "title": "Read tickets in use", "unit": "%", "until": "8.0", "version_text": "before 8.0", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9669,7 +9760,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.empty</t>
+          <t>tickets.read.scarce</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -9679,7 +9770,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which fewer than 0.5 read tickets were available, that is none, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/wiredTiger/concurrentTransactions/read/available, in tickets left, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.read.empty", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.read.used", "tickets.read.scarce", "tickets.read.pool", "tickets.read.wait", "queue.readers"], "reading": "valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/read/available"], "scale": 1, "unit": "tickets left"}, "threshold": 0.5, "title": "Samples with no read ticket left", "unit": "s/min", "until": "8.0", "version_text": "before 8.0", "view": "time_below"}</t>
+          <t>{"applies": "From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which available read tickets were strictly below 10 % of the pool, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/wiredTiger/concurrentTransactions/read/available ÷ serverStatus/wiredTiger/concurrentTransactions/read/totalTickets × 100, in % available, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.read.scarce", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.read.empty", "tickets.read.used", "tickets.read.pool", "tickets.read.wait"], "reading": "valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/wiredTiger/concurrentTransactions/read/totalTickets"], "mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/read/available"], "scale": 100, "unit": "% available"}, "threshold": 10, "title": "Samples with under 10% of read tickets left", "unit": "s/min", "until": "8.0", "version_text": "before 8.0", "view": "time_below"}</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9780,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.pool</t>
+          <t>tickets.read.empty</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -9699,7 +9790,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "doc": "How many read tickets the pool held, averaged over the minute.", "formula": "serverStatus/wiredTiger/concurrentTransactions/read/totalTickets, in tickets, at each available sample", "min_change": 4, "name": "tickets.read.pool", "pack": "admission", "pairs_with": ["tickets.read.used", "tickets.read.scarce"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/read/totalTickets"], "scale": 1, "unit": "tickets"}, "title": "Read ticket pool size", "unit": "tickets", "until": "8.0", "version_text": "before 8.0", "view": "mean"}</t>
+          <t>{"applies": "From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which fewer than 0.5 read tickets were available, that is none, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/wiredTiger/concurrentTransactions/read/available, in tickets left, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.read.empty", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.read.used", "tickets.read.scarce", "tickets.read.pool", "tickets.read.wait", "queue.readers"], "reading": "valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/read/available"], "scale": 1, "unit": "tickets left"}, "threshold": 0.5, "title": "Samples with no read ticket left", "unit": "s/min", "until": "8.0", "version_text": "before 8.0", "view": "time_below"}</t>
         </is>
       </c>
     </row>
@@ -9709,17 +9800,17 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.wait</t>
+          <t>tickets.read.pool</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>7.0 up to 8.0</t>
+          <t>before 8.0</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)", "doc": "Milliseconds a second operations spent queued for a read ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it.", "elevated": 100, "formula": "ΔserverStatus/wiredTiger/concurrentTransactions/read/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample", "levels": [{"down": [1, 10], "name": "none"}, {"band": [1, 10, 100, 500], "name": "some"}, {"name": "heavy", "up": [100, 500]}], "min_change": 10, "name": "tickets.read.wait", "pack": "admission", "pairs_with": ["tickets.read.empty", "tickets.read.scarce", "queue.readers"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/wiredTiger/concurrentTransactions/read/totalTimeQueuedMicros"], "scale": 0.001, "unit": "ms/s"}, "since": "7.0", "title": "Time waiting for a read ticket", "unit": "ms/s", "until": "8.0", "version_text": "7.0 up to 8.0", "view": "mean"}</t>
+          <t>{"bands": "none — read for its shape only", "doc": "How many read tickets the pool held, averaged over the minute.", "formula": "serverStatus/wiredTiger/concurrentTransactions/read/totalTickets, in tickets, at each available sample", "min_change": 4, "name": "tickets.read.pool", "pack": "admission", "pairs_with": ["tickets.read.used", "tickets.read.scarce"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/read/totalTickets"], "scale": 1, "unit": "tickets"}, "title": "Read ticket pool size", "unit": "tickets", "until": "8.0", "version_text": "before 8.0", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9729,17 +9820,17 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.used</t>
+          <t>tickets.read.wait</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>8.0 and later</t>
+          <t>7.0 up to 8.0</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.", "bands": "low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)", "doc": "Read tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.", "elevated": 75, "formula": "serverStatus/queues/execution/read/out ÷ serverStatus/queues/execution/read/totalTickets × 100, in %, at each available sample", "levels": [{"down": [25, 50], "name": "low"}, {"band": [25, 40, 65, 80], "name": "moderate"}, {"band": [65, 75, 90, 95], "name": "high"}, {"name": "near_full", "up": [90, 95]}], "min_change": 10, "name": "tickets.read.used", "pack": "admission", "pairs_with": ["tickets.read.scarce", "tickets.read.pool", "tickets.read.wait", "queue.readers"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/queues/execution/read/totalTickets"], "mode": "gauge", "num": ["serverStatus/queues/execution/read/out"], "scale": 100, "unit": "%"}, "since": "8.0", "title": "Read tickets in use", "unit": "%", "version_text": "8.0 and later", "view": "mean"}</t>
+          <t>{"bands": "none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)", "doc": "Milliseconds a second operations spent queued for a read ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it.", "elevated": 100, "formula": "ΔserverStatus/wiredTiger/concurrentTransactions/read/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample", "levels": [{"down": [1, 10], "name": "none"}, {"band": [1, 10, 100, 500], "name": "some"}, {"name": "heavy", "up": [100, 500]}], "min_change": 10, "name": "tickets.read.wait", "pack": "admission", "pairs_with": ["tickets.read.empty", "tickets.read.scarce", "queue.readers"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/wiredTiger/concurrentTransactions/read/totalTimeQueuedMicros"], "scale": 0.001, "unit": "ms/s"}, "since": "7.0", "title": "Time waiting for a read ticket", "unit": "ms/s", "until": "8.0", "version_text": "7.0 up to 8.0", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9749,7 +9840,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.scarce</t>
+          <t>tickets.read.used</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -9759,7 +9850,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which available read tickets were strictly below 10 % of the pool, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/queues/execution/read/available ÷ serverStatus/queues/execution/read/totalTickets × 100, in % available, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.read.scarce", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.read.empty", "tickets.read.used", "tickets.read.pool", "tickets.read.wait"], "reading": "valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/queues/execution/read/totalTickets"], "mode": "gauge", "num": ["serverStatus/queues/execution/read/available"], "scale": 100, "unit": "% available"}, "since": "8.0", "threshold": 10, "title": "Samples with under 10% of read tickets left", "unit": "s/min", "version_text": "8.0 and later", "view": "time_below"}</t>
+          <t>{"applies": "From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.", "bands": "low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)", "doc": "Read tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.", "elevated": 75, "formula": "serverStatus/queues/execution/read/out ÷ serverStatus/queues/execution/read/totalTickets × 100, in %, at each available sample", "levels": [{"down": [25, 50], "name": "low"}, {"band": [25, 40, 65, 80], "name": "moderate"}, {"band": [65, 75, 90, 95], "name": "high"}, {"name": "near_full", "up": [90, 95]}], "min_change": 10, "name": "tickets.read.used", "pack": "admission", "pairs_with": ["tickets.read.scarce", "tickets.read.pool", "tickets.read.wait", "queue.readers"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/queues/execution/read/totalTickets"], "mode": "gauge", "num": ["serverStatus/queues/execution/read/out"], "scale": 100, "unit": "%"}, "since": "8.0", "title": "Read tickets in use", "unit": "%", "version_text": "8.0 and later", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9860,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.empty</t>
+          <t>tickets.read.scarce</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -9779,7 +9870,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which fewer than 0.5 read tickets were available, that is none, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/queues/execution/read/available, in tickets left, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.read.empty", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.read.used", "tickets.read.scarce", "tickets.read.pool", "tickets.read.wait", "queue.readers"], "reading": "valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/queues/execution/read/available"], "scale": 1, "unit": "tickets left"}, "since": "8.0", "threshold": 0.5, "title": "Samples with no read ticket left", "unit": "s/min", "version_text": "8.0 and later", "view": "time_below"}</t>
+          <t>{"applies": "From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which available read tickets were strictly below 10 % of the pool, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/queues/execution/read/available ÷ serverStatus/queues/execution/read/totalTickets × 100, in % available, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.read.scarce", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.read.empty", "tickets.read.used", "tickets.read.pool", "tickets.read.wait"], "reading": "valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/queues/execution/read/totalTickets"], "mode": "gauge", "num": ["serverStatus/queues/execution/read/available"], "scale": 100, "unit": "% available"}, "since": "8.0", "threshold": 10, "title": "Samples with under 10% of read tickets left", "unit": "s/min", "version_text": "8.0 and later", "view": "time_below"}</t>
         </is>
       </c>
     </row>
@@ -9789,7 +9880,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.pool</t>
+          <t>tickets.read.empty</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -9799,7 +9890,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "doc": "How many read tickets the pool held, averaged over the minute.", "formula": "serverStatus/queues/execution/read/totalTickets, in tickets, at each available sample", "min_change": 4, "name": "tickets.read.pool", "pack": "admission", "pairs_with": ["tickets.read.used", "tickets.read.scarce"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/queues/execution/read/totalTickets"], "scale": 1, "unit": "tickets"}, "since": "8.0", "title": "Read ticket pool size", "unit": "tickets", "version_text": "8.0 and later", "view": "mean"}</t>
+          <t>{"applies": "From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which fewer than 0.5 read tickets were available, that is none, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/queues/execution/read/available, in tickets left, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.read.empty", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.read.used", "tickets.read.scarce", "tickets.read.pool", "tickets.read.wait", "queue.readers"], "reading": "valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/queues/execution/read/available"], "scale": 1, "unit": "tickets left"}, "since": "8.0", "threshold": 0.5, "title": "Samples with no read ticket left", "unit": "s/min", "version_text": "8.0 and later", "view": "time_below"}</t>
         </is>
       </c>
     </row>
@@ -9809,7 +9900,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.wait</t>
+          <t>tickets.read.pool</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -9819,7 +9910,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)", "doc": "Milliseconds a second operations spent queued for a read ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. The counter covers normal-priority operations, not exempt operations.", "elevated": 100, "formula": "ΔserverStatus/queues/execution/read/normalPriority/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample", "levels": [{"down": [1, 10], "name": "none"}, {"band": [1, 10, 100, 500], "name": "some"}, {"name": "heavy", "up": [100, 500]}], "min_change": 10, "name": "tickets.read.wait", "pack": "admission", "pairs_with": ["tickets.read.empty", "tickets.read.scarce", "queue.readers"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/queues/execution/read/normalPriority/totalTimeQueuedMicros"], "scale": 0.001, "unit": "ms/s"}, "since": "8.0", "title": "Time waiting for a read ticket", "unit": "ms/s", "version_text": "8.0 and later", "view": "mean"}</t>
+          <t>{"bands": "none — read for its shape only", "doc": "How many read tickets the pool held, averaged over the minute.", "formula": "serverStatus/queues/execution/read/totalTickets, in tickets, at each available sample", "min_change": 4, "name": "tickets.read.pool", "pack": "admission", "pairs_with": ["tickets.read.used", "tickets.read.scarce"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/queues/execution/read/totalTickets"], "scale": 1, "unit": "tickets"}, "since": "8.0", "title": "Read ticket pool size", "unit": "tickets", "version_text": "8.0 and later", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9829,17 +9920,17 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.used</t>
+          <t>tickets.read.wait</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>before 8.0</t>
+          <t>8.0 and later</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.", "bands": "low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)", "doc": "Write tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.", "elevated": 75, "formula": "serverStatus/wiredTiger/concurrentTransactions/write/out ÷ serverStatus/wiredTiger/concurrentTransactions/write/totalTickets × 100, in %, at each available sample", "levels": [{"down": [25, 50], "name": "low"}, {"band": [25, 40, 65, 80], "name": "moderate"}, {"band": [65, 75, 90, 95], "name": "high"}, {"name": "near_full", "up": [90, 95]}], "min_change": 10, "name": "tickets.write.used", "pack": "admission", "pairs_with": ["tickets.write.scarce", "tickets.write.pool", "tickets.write.wait", "queue.writers"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/wiredTiger/concurrentTransactions/write/totalTickets"], "mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/write/out"], "scale": 100, "unit": "%"}, "title": "Write tickets in use", "unit": "%", "until": "8.0", "version_text": "before 8.0", "view": "mean"}</t>
+          <t>{"bands": "none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)", "doc": "Milliseconds a second operations spent queued for a read ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. The counter covers normal-priority operations, not exempt operations.", "elevated": 100, "formula": "ΔserverStatus/queues/execution/read/normalPriority/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample", "levels": [{"down": [1, 10], "name": "none"}, {"band": [1, 10, 100, 500], "name": "some"}, {"name": "heavy", "up": [100, 500]}], "min_change": 10, "name": "tickets.read.wait", "pack": "admission", "pairs_with": ["tickets.read.empty", "tickets.read.scarce", "queue.readers"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/queues/execution/read/normalPriority/totalTimeQueuedMicros"], "scale": 0.001, "unit": "ms/s"}, "since": "8.0", "title": "Time waiting for a read ticket", "unit": "ms/s", "version_text": "8.0 and later", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9940,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.scarce</t>
+          <t>tickets.write.used</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -9859,7 +9950,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which available write tickets were strictly below 10 % of the pool, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/wiredTiger/concurrentTransactions/write/available ÷ serverStatus/wiredTiger/concurrentTransactions/write/totalTickets × 100, in % available, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.write.scarce", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.write.empty", "tickets.write.used", "tickets.write.pool", "tickets.write.wait"], "reading": "valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/wiredTiger/concurrentTransactions/write/totalTickets"], "mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/write/available"], "scale": 100, "unit": "% available"}, "threshold": 10, "title": "Samples with under 10% of write tickets left", "unit": "s/min", "until": "8.0", "version_text": "before 8.0", "view": "time_below"}</t>
+          <t>{"applies": "From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.", "bands": "low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)", "doc": "Write tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.", "elevated": 75, "formula": "serverStatus/wiredTiger/concurrentTransactions/write/out ÷ serverStatus/wiredTiger/concurrentTransactions/write/totalTickets × 100, in %, at each available sample", "levels": [{"down": [25, 50], "name": "low"}, {"band": [25, 40, 65, 80], "name": "moderate"}, {"band": [65, 75, 90, 95], "name": "high"}, {"name": "near_full", "up": [90, 95]}], "min_change": 10, "name": "tickets.write.used", "pack": "admission", "pairs_with": ["tickets.write.scarce", "tickets.write.pool", "tickets.write.wait", "queue.writers"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/wiredTiger/concurrentTransactions/write/totalTickets"], "mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/write/out"], "scale": 100, "unit": "%"}, "title": "Write tickets in use", "unit": "%", "until": "8.0", "version_text": "before 8.0", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9960,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.empty</t>
+          <t>tickets.write.scarce</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -9879,7 +9970,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which fewer than 0.5 write tickets were available, that is none, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/wiredTiger/concurrentTransactions/write/available, in tickets left, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.write.empty", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.write.used", "tickets.write.scarce", "tickets.write.pool", "tickets.write.wait", "queue.writers"], "reading": "valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/write/available"], "scale": 1, "unit": "tickets left"}, "threshold": 0.5, "title": "Samples with no write ticket left", "unit": "s/min", "until": "8.0", "version_text": "before 8.0", "view": "time_below"}</t>
+          <t>{"applies": "From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which available write tickets were strictly below 10 % of the pool, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/wiredTiger/concurrentTransactions/write/available ÷ serverStatus/wiredTiger/concurrentTransactions/write/totalTickets × 100, in % available, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.write.scarce", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.write.empty", "tickets.write.used", "tickets.write.pool", "tickets.write.wait"], "reading": "valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/wiredTiger/concurrentTransactions/write/totalTickets"], "mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/write/available"], "scale": 100, "unit": "% available"}, "threshold": 10, "title": "Samples with under 10% of write tickets left", "unit": "s/min", "until": "8.0", "version_text": "before 8.0", "view": "time_below"}</t>
         </is>
       </c>
     </row>
@@ -9889,7 +9980,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.pool</t>
+          <t>tickets.write.empty</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -9899,7 +9990,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "doc": "How many write tickets the pool held, averaged over the minute.", "formula": "serverStatus/wiredTiger/concurrentTransactions/write/totalTickets, in tickets, at each available sample", "min_change": 4, "name": "tickets.write.pool", "pack": "admission", "pairs_with": ["tickets.write.used", "tickets.write.scarce"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/write/totalTickets"], "scale": 1, "unit": "tickets"}, "title": "Write ticket pool size", "unit": "tickets", "until": "8.0", "version_text": "before 8.0", "view": "mean"}</t>
+          <t>{"applies": "From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which fewer than 0.5 write tickets were available, that is none, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/wiredTiger/concurrentTransactions/write/available, in tickets left, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.write.empty", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.write.used", "tickets.write.scarce", "tickets.write.pool", "tickets.write.wait", "queue.writers"], "reading": "valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/write/available"], "scale": 1, "unit": "tickets left"}, "threshold": 0.5, "title": "Samples with no write ticket left", "unit": "s/min", "until": "8.0", "version_text": "before 8.0", "view": "time_below"}</t>
         </is>
       </c>
     </row>
@@ -9909,17 +10000,17 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.wait</t>
+          <t>tickets.write.pool</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>7.0 up to 8.0</t>
+          <t>before 8.0</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)", "doc": "Milliseconds a second operations spent queued for a write ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it.", "elevated": 100, "formula": "ΔserverStatus/wiredTiger/concurrentTransactions/write/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample", "levels": [{"down": [1, 10], "name": "none"}, {"band": [1, 10, 100, 500], "name": "some"}, {"name": "heavy", "up": [100, 500]}], "min_change": 10, "name": "tickets.write.wait", "pack": "admission", "pairs_with": ["tickets.write.empty", "tickets.write.scarce", "queue.writers"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/wiredTiger/concurrentTransactions/write/totalTimeQueuedMicros"], "scale": 0.001, "unit": "ms/s"}, "since": "7.0", "title": "Time waiting for a write ticket", "unit": "ms/s", "until": "8.0", "version_text": "7.0 up to 8.0", "view": "mean"}</t>
+          <t>{"bands": "none — read for its shape only", "doc": "How many write tickets the pool held, averaged over the minute.", "formula": "serverStatus/wiredTiger/concurrentTransactions/write/totalTickets, in tickets, at each available sample", "min_change": 4, "name": "tickets.write.pool", "pack": "admission", "pairs_with": ["tickets.write.used", "tickets.write.scarce"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/write/totalTickets"], "scale": 1, "unit": "tickets"}, "title": "Write ticket pool size", "unit": "tickets", "until": "8.0", "version_text": "before 8.0", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9929,17 +10020,17 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.used</t>
+          <t>tickets.write.wait</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>8.0 and later</t>
+          <t>7.0 up to 8.0</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.", "bands": "low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)", "doc": "Write tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.", "elevated": 75, "formula": "serverStatus/queues/execution/write/out ÷ serverStatus/queues/execution/write/totalTickets × 100, in %, at each available sample", "levels": [{"down": [25, 50], "name": "low"}, {"band": [25, 40, 65, 80], "name": "moderate"}, {"band": [65, 75, 90, 95], "name": "high"}, {"name": "near_full", "up": [90, 95]}], "min_change": 10, "name": "tickets.write.used", "pack": "admission", "pairs_with": ["tickets.write.scarce", "tickets.write.pool", "tickets.write.wait", "queue.writers"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/queues/execution/write/totalTickets"], "mode": "gauge", "num": ["serverStatus/queues/execution/write/out"], "scale": 100, "unit": "%"}, "since": "8.0", "title": "Write tickets in use", "unit": "%", "version_text": "8.0 and later", "view": "mean"}</t>
+          <t>{"bands": "none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)", "doc": "Milliseconds a second operations spent queued for a write ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it.", "elevated": 100, "formula": "ΔserverStatus/wiredTiger/concurrentTransactions/write/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample", "levels": [{"down": [1, 10], "name": "none"}, {"band": [1, 10, 100, 500], "name": "some"}, {"name": "heavy", "up": [100, 500]}], "min_change": 10, "name": "tickets.write.wait", "pack": "admission", "pairs_with": ["tickets.write.empty", "tickets.write.scarce", "queue.writers"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/wiredTiger/concurrentTransactions/write/totalTimeQueuedMicros"], "scale": 0.001, "unit": "ms/s"}, "since": "7.0", "title": "Time waiting for a write ticket", "unit": "ms/s", "until": "8.0", "version_text": "7.0 up to 8.0", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9949,7 +10040,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.scarce</t>
+          <t>tickets.write.used</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -9959,7 +10050,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which available write tickets were strictly below 10 % of the pool, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/queues/execution/write/available ÷ serverStatus/queues/execution/write/totalTickets × 100, in % available, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.write.scarce", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.write.empty", "tickets.write.used", "tickets.write.pool", "tickets.write.wait"], "reading": "valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/queues/execution/write/totalTickets"], "mode": "gauge", "num": ["serverStatus/queues/execution/write/available"], "scale": 100, "unit": "% available"}, "since": "8.0", "threshold": 10, "title": "Samples with under 10% of write tickets left", "unit": "s/min", "version_text": "8.0 and later", "view": "time_below"}</t>
+          <t>{"applies": "From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.", "bands": "low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)", "doc": "Write tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.", "elevated": 75, "formula": "serverStatus/queues/execution/write/out ÷ serverStatus/queues/execution/write/totalTickets × 100, in %, at each available sample", "levels": [{"down": [25, 50], "name": "low"}, {"band": [25, 40, 65, 80], "name": "moderate"}, {"band": [65, 75, 90, 95], "name": "high"}, {"name": "near_full", "up": [90, 95]}], "min_change": 10, "name": "tickets.write.used", "pack": "admission", "pairs_with": ["tickets.write.scarce", "tickets.write.pool", "tickets.write.wait", "queue.writers"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/queues/execution/write/totalTickets"], "mode": "gauge", "num": ["serverStatus/queues/execution/write/out"], "scale": 100, "unit": "%"}, "since": "8.0", "title": "Write tickets in use", "unit": "%", "version_text": "8.0 and later", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9969,7 +10060,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.empty</t>
+          <t>tickets.write.scarce</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -9979,7 +10070,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which fewer than 0.5 write tickets were available, that is none, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/queues/execution/write/available, in tickets left, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.write.empty", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.write.used", "tickets.write.scarce", "tickets.write.pool", "tickets.write.wait", "queue.writers"], "reading": "valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/queues/execution/write/available"], "scale": 1, "unit": "tickets left"}, "since": "8.0", "threshold": 0.5, "title": "Samples with no write ticket left", "unit": "s/min", "version_text": "8.0 and later", "view": "time_below"}</t>
+          <t>{"applies": "From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which available write tickets were strictly below 10 % of the pool, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/queues/execution/write/available ÷ serverStatus/queues/execution/write/totalTickets × 100, in % available, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.write.scarce", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.write.empty", "tickets.write.used", "tickets.write.pool", "tickets.write.wait"], "reading": "valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/queues/execution/write/totalTickets"], "mode": "gauge", "num": ["serverStatus/queues/execution/write/available"], "scale": 100, "unit": "% available"}, "since": "8.0", "threshold": 10, "title": "Samples with under 10% of write tickets left", "unit": "s/min", "version_text": "8.0 and later", "view": "time_below"}</t>
         </is>
       </c>
     </row>
@@ -9989,7 +10080,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.pool</t>
+          <t>tickets.write.empty</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -9999,7 +10090,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "doc": "How many write tickets the pool held, averaged over the minute.", "formula": "serverStatus/queues/execution/write/totalTickets, in tickets, at each available sample", "min_change": 4, "name": "tickets.write.pool", "pack": "admission", "pairs_with": ["tickets.write.used", "tickets.write.scarce"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/queues/execution/write/totalTickets"], "scale": 1, "unit": "tickets"}, "since": "8.0", "title": "Write ticket pool size", "unit": "tickets", "version_text": "8.0 and later", "view": "mean"}</t>
+          <t>{"applies": "From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which fewer than 0.5 write tickets were available, that is none, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/queues/execution/write/available, in tickets left, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.write.empty", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.write.used", "tickets.write.scarce", "tickets.write.pool", "tickets.write.wait", "queue.writers"], "reading": "valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/queues/execution/write/available"], "scale": 1, "unit": "tickets left"}, "since": "8.0", "threshold": 0.5, "title": "Samples with no write ticket left", "unit": "s/min", "version_text": "8.0 and later", "view": "time_below"}</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10100,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.wait</t>
+          <t>tickets.write.pool</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -10019,7 +10110,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)", "doc": "Milliseconds a second operations spent queued for a write ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. The counter covers normal-priority operations, not exempt operations.", "elevated": 100, "formula": "ΔserverStatus/queues/execution/write/normalPriority/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample", "levels": [{"down": [1, 10], "name": "none"}, {"band": [1, 10, 100, 500], "name": "some"}, {"name": "heavy", "up": [100, 500]}], "min_change": 10, "name": "tickets.write.wait", "pack": "admission", "pairs_with": ["tickets.write.empty", "tickets.write.scarce", "queue.writers"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/queues/execution/write/normalPriority/totalTimeQueuedMicros"], "scale": 0.001, "unit": "ms/s"}, "since": "8.0", "title": "Time waiting for a write ticket", "unit": "ms/s", "version_text": "8.0 and later", "view": "mean"}</t>
+          <t>{"bands": "none — read for its shape only", "doc": "How many write tickets the pool held, averaged over the minute.", "formula": "serverStatus/queues/execution/write/totalTickets, in tickets, at each available sample", "min_change": 4, "name": "tickets.write.pool", "pack": "admission", "pairs_with": ["tickets.write.used", "tickets.write.scarce"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/queues/execution/write/totalTickets"], "scale": 1, "unit": "tickets"}, "since": "8.0", "title": "Write ticket pool size", "unit": "tickets", "version_text": "8.0 and later", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10029,17 +10120,17 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>queue.readers</t>
+          <t>tickets.write.wait</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>8.0 and later</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which globalLock.currentQueue.readers was above 0, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/globalLock/currentQueue/readers, in operations, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "queue.readers", "pack": "admission", "pairs_with": ["tickets.read.empty", "tickets.read.wait"], "reading": "valid-sample share strictly above 0 operations, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/globalLock/currentQueue/readers"], "scale": 1, "unit": "operations"}, "threshold": 0, "title": "Samples with reads queued", "unit": "s/min", "version_text": "all versions", "view": "time_above"}</t>
+          <t>{"bands": "none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)", "doc": "Milliseconds a second operations spent queued for a write ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. The counter covers normal-priority operations, not exempt operations.", "elevated": 100, "formula": "ΔserverStatus/queues/execution/write/normalPriority/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample", "levels": [{"down": [1, 10], "name": "none"}, {"band": [1, 10, 100, 500], "name": "some"}, {"name": "heavy", "up": [100, 500]}], "min_change": 10, "name": "tickets.write.wait", "pack": "admission", "pairs_with": ["tickets.write.empty", "tickets.write.scarce", "queue.writers"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/queues/execution/write/normalPriority/totalTimeQueuedMicros"], "scale": 0.001, "unit": "ms/s"}, "since": "8.0", "title": "Time waiting for a write ticket", "unit": "ms/s", "version_text": "8.0 and later", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10049,7 +10140,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>queue.writers</t>
+          <t>queue.readers</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -10059,7 +10150,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which globalLock.currentQueue.writers was above 0, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/globalLock/currentQueue/writers, in operations, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "queue.writers", "pack": "admission", "pairs_with": ["tickets.write.empty", "tickets.write.wait"], "reading": "valid-sample share strictly above 0 operations, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/globalLock/currentQueue/writers"], "scale": 1, "unit": "operations"}, "threshold": 0, "title": "Samples with writes queued", "unit": "s/min", "version_text": "all versions", "view": "time_above"}</t>
+          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which globalLock.currentQueue.readers was above 0, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/globalLock/currentQueue/readers, in operations, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "queue.readers", "pack": "admission", "pairs_with": ["tickets.read.empty", "tickets.read.wait"], "reading": "valid-sample share strictly above 0 operations, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/globalLock/currentQueue/readers"], "scale": 1, "unit": "operations"}, "threshold": 0, "title": "Samples with reads queued", "unit": "s/min", "version_text": "all versions", "view": "time_above"}</t>
         </is>
       </c>
     </row>
@@ -10069,7 +10160,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>cache.fill</t>
+          <t>queue.writers</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -10079,7 +10170,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "low ≤50 (fading to 70) · normal 70–80 (edges 50, 86) · high 86–93 (edges 80, 95) · above_reference ≥96 (from 94)", "doc": "Bytes in the WiredTiger cache as a share of its configured size, averaged over the minute.", "elevated": 95, "formula": "serverStatus/wiredTiger/cache/bytes currently in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample", "levels": [{"down": [50, 70], "name": "low"}, {"band": [50, 70, 80, 86], "name": "normal"}, {"band": [80, 86, 93, 95], "name": "high"}, {"name": "above_reference", "up": [94, 96]}], "min_change": 5, "name": "cache.fill", "pack": "storage-engine", "pairs_with": ["cache.fill_above_95", "cache.app_eviction", "cache.read_in"], "reading": "each minute's ratio of sums", "reference": {"configured": "not read", "source": "WiredTiger default eviction_trigger; eviction_target defaults to 80", "unit": "%", "value": 95}, "signal": {"den": ["serverStatus/wiredTiger/cache/maximum bytes configured"], "mode": "gauge", "num": ["serverStatus/wiredTiger/cache/bytes currently in the cache"], "scale": 100, "unit": "%"}, "title": "WiredTiger cache fill", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which globalLock.currentQueue.writers was above 0, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/globalLock/currentQueue/writers, in operations, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "queue.writers", "pack": "admission", "pairs_with": ["tickets.write.empty", "tickets.write.wait"], "reading": "valid-sample share strictly above 0 operations, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/globalLock/currentQueue/writers"], "scale": 1, "unit": "operations"}, "threshold": 0, "title": "Samples with writes queued", "unit": "s/min", "version_text": "all versions", "view": "time_above"}</t>
         </is>
       </c>
     </row>
@@ -10089,7 +10180,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>cache.fill_above_95</t>
+          <t>cache.fill</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -10099,7 +10190,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which WiredTiger cache bytes were strictly above 95 % of the configured cache size, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/wiredTiger/cache/bytes currently in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "cache.fill_above_95", "pack": "storage-engine", "pairs_with": ["cache.fill", "cache.app_eviction", "tickets.read.scarce"], "reading": "valid-sample share strictly above 95 %, normalized to 60 s/min; not continuous elapsed time", "reference": {"configured": "not read", "source": "WiredTiger default eviction_trigger", "unit": "%", "value": 95}, "signal": {"den": ["serverStatus/wiredTiger/cache/maximum bytes configured"], "mode": "gauge", "num": ["serverStatus/wiredTiger/cache/bytes currently in the cache"], "scale": 100, "unit": "%"}, "threshold": 95, "title": "Cache-fill samples above 95%", "unit": "s/min", "version_text": "all versions", "view": "time_above"}</t>
+          <t>{"bands": "low ≤50 (fading to 70) · normal 70–80 (edges 50, 86) · high 86–93 (edges 80, 95) · above_reference ≥96 (from 94)", "doc": "Bytes in the WiredTiger cache as a share of its configured size, averaged over the minute.", "elevated": 95, "formula": "serverStatus/wiredTiger/cache/bytes currently in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample", "levels": [{"down": [50, 70], "name": "low"}, {"band": [50, 70, 80, 86], "name": "normal"}, {"band": [80, 86, 93, 95], "name": "high"}, {"name": "above_reference", "up": [94, 96]}], "min_change": 5, "name": "cache.fill", "pack": "storage-engine", "pairs_with": ["cache.fill_above_95", "cache.app_eviction", "cache.read_in"], "reading": "each minute's ratio of sums", "reference": {"configured": "not read", "source": "WiredTiger default eviction_trigger; eviction_target defaults to 80", "unit": "%", "value": 95}, "signal": {"den": ["serverStatus/wiredTiger/cache/maximum bytes configured"], "mode": "gauge", "num": ["serverStatus/wiredTiger/cache/bytes currently in the cache"], "scale": 100, "unit": "%"}, "title": "WiredTiger cache fill", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10109,7 +10200,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>cache.dirty</t>
+          <t>cache.fill_above_95</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -10119,7 +10210,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "low ≤3 (fading to 6) · normal 6–8 (edges 3, 12) · high 12–18 (edges 8, 20) · above_reference ≥21 (from 19)", "doc": "Modified bytes not yet written, as a share of the configured cache, averaged over the minute.", "elevated": 20, "formula": "serverStatus/wiredTiger/cache/tracked dirty bytes in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample", "levels": [{"down": [3, 6], "name": "low"}, {"band": [3, 6, 8, 12], "name": "normal"}, {"band": [8, 12, 18, 20], "name": "high"}, {"name": "above_reference", "up": [19, 21]}], "min_change": 3, "name": "cache.dirty", "pack": "storage-engine", "pairs_with": ["cache.dirty_above_20", "checkpoint.duration", "disk.write_await", "ops.writes"], "reading": "each minute's ratio of sums", "reference": {"configured": "not read", "source": "WiredTiger default eviction_dirty_trigger; eviction_dirty_target defaults to 5", "unit": "%", "value": 20}, "signal": {"den": ["serverStatus/wiredTiger/cache/maximum bytes configured"], "mode": "gauge", "num": ["serverStatus/wiredTiger/cache/tracked dirty bytes in the cache"], "scale": 100, "unit": "%"}, "title": "WiredTiger dirty cache", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which WiredTiger cache bytes were strictly above 95 % of the configured cache size, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/wiredTiger/cache/bytes currently in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "cache.fill_above_95", "pack": "storage-engine", "pairs_with": ["cache.fill", "cache.app_eviction", "tickets.read.scarce"], "reading": "valid-sample share strictly above 95 %, normalized to 60 s/min; not continuous elapsed time", "reference": {"configured": "not read", "source": "WiredTiger default eviction_trigger", "unit": "%", "value": 95}, "signal": {"den": ["serverStatus/wiredTiger/cache/maximum bytes configured"], "mode": "gauge", "num": ["serverStatus/wiredTiger/cache/bytes currently in the cache"], "scale": 100, "unit": "%"}, "threshold": 95, "title": "Cache-fill samples above 95%", "unit": "s/min", "version_text": "all versions", "view": "time_above"}</t>
         </is>
       </c>
     </row>
@@ -10129,7 +10220,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>cache.dirty_above_20</t>
+          <t>cache.dirty</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -10139,7 +10230,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which tracked dirty bytes were strictly above 20 % of the configured cache size, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/wiredTiger/cache/tracked dirty bytes in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "cache.dirty_above_20", "pack": "storage-engine", "pairs_with": ["cache.dirty", "checkpoint.running", "tickets.write.scarce"], "reading": "valid-sample share strictly above 20 %, normalized to 60 s/min; not continuous elapsed time", "reference": {"configured": "not read", "source": "WiredTiger default eviction_dirty_trigger", "unit": "%", "value": 20}, "signal": {"den": ["serverStatus/wiredTiger/cache/maximum bytes configured"], "mode": "gauge", "num": ["serverStatus/wiredTiger/cache/tracked dirty bytes in the cache"], "scale": 100, "unit": "%"}, "threshold": 20, "title": "Dirty-cache samples above 20%", "unit": "s/min", "version_text": "all versions", "view": "time_above"}</t>
+          <t>{"bands": "low ≤3 (fading to 6) · normal 6–8 (edges 3, 12) · high 12–18 (edges 8, 20) · above_reference ≥21 (from 19)", "doc": "Modified bytes not yet written, as a share of the configured cache, averaged over the minute.", "elevated": 20, "formula": "serverStatus/wiredTiger/cache/tracked dirty bytes in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample", "levels": [{"down": [3, 6], "name": "low"}, {"band": [3, 6, 8, 12], "name": "normal"}, {"band": [8, 12, 18, 20], "name": "high"}, {"name": "above_reference", "up": [19, 21]}], "min_change": 3, "name": "cache.dirty", "pack": "storage-engine", "pairs_with": ["cache.dirty_above_20", "checkpoint.duration", "disk.write_await", "ops.writes"], "reading": "each minute's ratio of sums", "reference": {"configured": "not read", "source": "WiredTiger default eviction_dirty_trigger; eviction_dirty_target defaults to 5", "unit": "%", "value": 20}, "signal": {"den": ["serverStatus/wiredTiger/cache/maximum bytes configured"], "mode": "gauge", "num": ["serverStatus/wiredTiger/cache/tracked dirty bytes in the cache"], "scale": 100, "unit": "%"}, "title": "WiredTiger dirty cache", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10149,17 +10240,17 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>cache.app_eviction</t>
+          <t>cache.dirty_above_20</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>before 8.0.16</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤0.1 (fading to 1) · some 1–10 (edges 0.1, 50) · heavy ≥50 (from 10)", "doc": "Rate of pages evicted by application threads; where the version uses attempts and failures, the signal subtracts failure counts from attempt counts.", "elevated": 1, "formula": "ΔserverStatus/wiredTiger/cache/pages evicted by application threads per second, in pages/s, at each available sample", "levels": [{"down": [0.1, 1], "name": "none"}, {"band": [0.1, 1, 10, 50], "name": "some"}, {"name": "heavy", "up": [10, 50]}], "min_change": 5, "name": "cache.app_eviction", "pack": "storage-engine", "pairs_with": ["cache.fill_above_95", "cache.dirty_above_20"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/wiredTiger/cache/pages evicted by application threads"], "scale": 1, "unit": "pages/s"}, "title": "Eviction by application threads", "unit": "pages/s", "until": "8.0.16", "version_text": "before 8.0.16", "view": "mean"}</t>
+          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which tracked dirty bytes were strictly above 20 % of the configured cache size, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/wiredTiger/cache/tracked dirty bytes in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "cache.dirty_above_20", "pack": "storage-engine", "pairs_with": ["cache.dirty", "checkpoint.running", "tickets.write.scarce"], "reading": "valid-sample share strictly above 20 %, normalized to 60 s/min; not continuous elapsed time", "reference": {"configured": "not read", "source": "WiredTiger default eviction_dirty_trigger", "unit": "%", "value": 20}, "signal": {"den": ["serverStatus/wiredTiger/cache/maximum bytes configured"], "mode": "gauge", "num": ["serverStatus/wiredTiger/cache/tracked dirty bytes in the cache"], "scale": 100, "unit": "%"}, "threshold": 20, "title": "Dirty-cache samples above 20%", "unit": "s/min", "version_text": "all versions", "view": "time_above"}</t>
         </is>
       </c>
     </row>
@@ -10174,12 +10265,12 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>8.0.16 and later</t>
+          <t>before 8.0.16</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤0.1 (fading to 1) · some 1–10 (edges 0.1, 50) · heavy ≥50 (from 10)", "doc": "Rate of pages evicted by application threads; where the version uses attempts and failures, the signal subtracts failure counts from attempt counts.", "elevated": 1, "formula": "ΔserverStatus/wiredTiger/cache/page evict attempts by application threads − serverStatus/wiredTiger/cache/page evict failures by application threads per second, in pages/s, at each available sample", "levels": [{"down": [0.1, 1], "name": "none"}, {"band": [0.1, 1, 10, 50], "name": "some"}, {"name": "heavy", "up": [10, 50]}], "min_change": 5, "name": "cache.app_eviction", "pack": "storage-engine", "pairs_with": ["cache.fill_above_95", "cache.dirty_above_20", "cache.app_eviction_time"], "reading": "each minute's mean", "signal": {"minus": ["serverStatus/wiredTiger/cache/page evict failures by application threads"], "mode": "rate", "num": ["serverStatus/wiredTiger/cache/page evict attempts by application threads"], "scale": 1, "unit": "pages/s"}, "since": "8.0.16", "title": "Eviction by application threads", "unit": "pages/s", "version_text": "8.0.16 and later", "view": "mean"}</t>
+          <t>{"bands": "none ≤0.1 (fading to 1) · some 1–10 (edges 0.1, 50) · heavy ≥50 (from 10)", "doc": "Rate of pages evicted by application threads; where the version uses attempts and failures, the signal subtracts failure counts from attempt counts.", "elevated": 1, "formula": "ΔserverStatus/wiredTiger/cache/pages evicted by application threads per second, in pages/s, at each available sample", "levels": [{"down": [0.1, 1], "name": "none"}, {"band": [0.1, 1, 10, 50], "name": "some"}, {"name": "heavy", "up": [10, 50]}], "min_change": 5, "name": "cache.app_eviction", "pack": "storage-engine", "pairs_with": ["cache.fill_above_95", "cache.dirty_above_20"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/wiredTiger/cache/pages evicted by application threads"], "scale": 1, "unit": "pages/s"}, "title": "Eviction by application threads", "unit": "pages/s", "until": "8.0.16", "version_text": "before 8.0.16", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10189,17 +10280,17 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>cache.app_eviction_time</t>
+          <t>cache.app_eviction</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>8.0 and later</t>
+          <t>8.0.16 and later</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)", "doc": "Application-thread eviction time counter advance per elapsed second, summed across threads, in milliseconds.", "elevated": 100, "formula": "ΔserverStatus/wiredTiger/cache/application thread time evicting (usecs) per second × 0.001, in ms/s, at each available sample", "levels": [{"down": [1, 10], "name": "none"}, {"band": [1, 10, 100, 500], "name": "some"}, {"name": "heavy", "up": [100, 500]}], "min_change": 10, "name": "cache.app_eviction_time", "pack": "storage-engine", "pairs_with": ["cache.app_eviction", "cache.fill_above_95", "cache.dirty_above_20"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/wiredTiger/cache/application thread time evicting (usecs)"], "scale": 0.001, "unit": "ms/s"}, "since": "8.0", "title": "Time operations spent evicting", "unit": "ms/s", "version_text": "8.0 and later", "view": "mean"}</t>
+          <t>{"bands": "none ≤0.1 (fading to 1) · some 1–10 (edges 0.1, 50) · heavy ≥50 (from 10)", "doc": "Rate of pages evicted by application threads; where the version uses attempts and failures, the signal subtracts failure counts from attempt counts.", "elevated": 1, "formula": "ΔserverStatus/wiredTiger/cache/page evict attempts by application threads − serverStatus/wiredTiger/cache/page evict failures by application threads per second, in pages/s, at each available sample", "levels": [{"down": [0.1, 1], "name": "none"}, {"band": [0.1, 1, 10, 50], "name": "some"}, {"name": "heavy", "up": [10, 50]}], "min_change": 5, "name": "cache.app_eviction", "pack": "storage-engine", "pairs_with": ["cache.fill_above_95", "cache.dirty_above_20", "cache.app_eviction_time"], "reading": "each minute's mean", "signal": {"minus": ["serverStatus/wiredTiger/cache/page evict failures by application threads"], "mode": "rate", "num": ["serverStatus/wiredTiger/cache/page evict attempts by application threads"], "scale": 1, "unit": "pages/s"}, "since": "8.0.16", "title": "Eviction by application threads", "unit": "pages/s", "version_text": "8.0.16 and later", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10209,17 +10300,17 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>cache.read_in</t>
+          <t>cache.app_eviction_time</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>8.0 and later</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "doc": "WiredTiger bytes-read-into-cache counter advance per elapsed second, scaled to MB/s.", "formula": "ΔserverStatus/wiredTiger/cache/bytes read into cache per second × 1e-06, in MB/s, at each available sample", "min_change": 5, "name": "cache.read_in", "pack": "storage-engine", "pairs_with": ["disk.read_await", "query.collscans", "cache.fill"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/wiredTiger/cache/bytes read into cache"], "scale": 1e-06, "unit": "MB/s"}, "title": "Data read into the cache", "unit": "MB/s", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)", "doc": "Application-thread eviction time counter advance per elapsed second, summed across threads, in milliseconds.", "elevated": 100, "formula": "ΔserverStatus/wiredTiger/cache/application thread time evicting (usecs) per second × 0.001, in ms/s, at each available sample", "levels": [{"down": [1, 10], "name": "none"}, {"band": [1, 10, 100, 500], "name": "some"}, {"name": "heavy", "up": [100, 500]}], "min_change": 10, "name": "cache.app_eviction_time", "pack": "storage-engine", "pairs_with": ["cache.app_eviction", "cache.fill_above_95", "cache.dirty_above_20"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/wiredTiger/cache/application thread time evicting (usecs)"], "scale": 0.001, "unit": "ms/s"}, "since": "8.0", "title": "Time operations spent evicting", "unit": "ms/s", "version_text": "8.0 and later", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10229,17 +10320,17 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>checkpoint.duration</t>
+          <t>cache.read_in</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>before 7.1</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "quick ≤5 (fading to 15) · slow 15–40 (edges 5, 60) · back_to_back ≥60 (from 50)", "doc": "Duration recorded for the most recent WiredTiger checkpoint; the same completed-checkpoint value may appear in multiple samples. Minute summaries select the highest valid sample.", "elevated": 60, "formula": "serverStatus/wiredTiger/transaction/transaction checkpoint most recent time (msecs) × 0.001, in s, at each available sample", "levels": [{"down": [5, 15], "name": "quick"}, {"band": [5, 15, 40, 60], "name": "slow"}, {"name": "back_to_back", "up": [50, 60]}], "min_change": 10, "name": "checkpoint.duration", "pack": "storage-engine", "pairs_with": ["checkpoint.running", "cache.dirty", "disk.write_await"], "reading": "the highest valid sample of each minute", "reference": {"configured": "not read", "source": "default checkpoint interval, storage.syncPeriodSecs", "unit": "s", "value": 60}, "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/transaction/transaction checkpoint most recent time (msecs)"], "scale": 0.001, "unit": "s"}, "title": "Checkpoint duration", "unit": "s", "until": "7.1", "version_text": "before 7.1", "view": "max"}</t>
+          <t>{"bands": "none — read for its shape only", "doc": "WiredTiger bytes-read-into-cache counter advance per elapsed second, scaled to MB/s.", "formula": "ΔserverStatus/wiredTiger/cache/bytes read into cache per second × 1e-06, in MB/s, at each available sample", "min_change": 5, "name": "cache.read_in", "pack": "storage-engine", "pairs_with": ["disk.read_await", "query.collscans", "cache.fill"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/wiredTiger/cache/bytes read into cache"], "scale": 1e-06, "unit": "MB/s"}, "title": "Data read into the cache", "unit": "MB/s", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10254,12 +10345,12 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>7.1 and later</t>
+          <t>before 7.1</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "quick ≤5 (fading to 15) · slow 15–40 (edges 5, 60) · back_to_back ≥60 (from 50)", "doc": "Duration recorded for the most recent WiredTiger checkpoint; the same completed-checkpoint value may appear in multiple samples. Minute summaries select the highest valid sample.", "elevated": 60, "formula": "serverStatus/wiredTiger/checkpoint/most recent time (msecs) × 0.001, in s, at each available sample", "levels": [{"down": [5, 15], "name": "quick"}, {"band": [5, 15, 40, 60], "name": "slow"}, {"name": "back_to_back", "up": [50, 60]}], "min_change": 10, "name": "checkpoint.duration", "pack": "storage-engine", "pairs_with": ["checkpoint.running", "cache.dirty", "disk.write_await"], "reading": "the highest valid sample of each minute", "reference": {"configured": "not read", "source": "default checkpoint interval, storage.syncPeriodSecs", "unit": "s", "value": 60}, "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/checkpoint/most recent time (msecs)"], "scale": 0.001, "unit": "s"}, "since": "7.1", "title": "Checkpoint duration", "unit": "s", "version_text": "7.1 and later", "view": "max"}</t>
+          <t>{"bands": "quick ≤5 (fading to 15) · slow 15–40 (edges 5, 60) · back_to_back ≥60 (from 50)", "doc": "Duration recorded for the most recent WiredTiger checkpoint; the same completed-checkpoint value may appear in multiple samples. Minute summaries select the highest valid sample.", "elevated": 60, "formula": "serverStatus/wiredTiger/transaction/transaction checkpoint most recent time (msecs) × 0.001, in s, at each available sample", "levels": [{"down": [5, 15], "name": "quick"}, {"band": [5, 15, 40, 60], "name": "slow"}, {"name": "back_to_back", "up": [50, 60]}], "min_change": 10, "name": "checkpoint.duration", "pack": "storage-engine", "pairs_with": ["checkpoint.running", "cache.dirty", "disk.write_await"], "reading": "the highest valid sample of each minute", "reference": {"configured": "not read", "source": "default checkpoint interval, storage.syncPeriodSecs", "unit": "s", "value": 60}, "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/transaction/transaction checkpoint most recent time (msecs)"], "scale": 0.001, "unit": "s"}, "title": "Checkpoint duration", "unit": "s", "until": "7.1", "version_text": "before 7.1", "view": "max"}</t>
         </is>
       </c>
     </row>
@@ -10269,17 +10360,17 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>checkpoint.running</t>
+          <t>checkpoint.duration</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>before 7.1</t>
+          <t>7.1 and later</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "brief ≤12 (fading to 24) · long 24–42 (edges 12, 54) · continuous ≥57 (from 48)", "doc": "Share of valid samples in which WiredTiger reported a checkpoint as currently running, normalized to a 60-second minute.", "elevated": 48, "formula": "serverStatus/wiredTiger/transaction/transaction checkpoint currently running, in running, at each available sample", "levels": [{"down": [12, 24], "name": "brief"}, {"band": [12, 24, 42, 54], "name": "long"}, {"name": "continuous", "up": [48, 57]}], "min_change": 9, "name": "checkpoint.running", "pack": "storage-engine", "pairs_with": ["checkpoint.duration", "disk.busy_above_95", "cache.dirty"], "reading": "valid-sample share strictly above 0 running, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/transaction/transaction checkpoint currently running"], "scale": 1, "unit": "running"}, "threshold": 0, "title": "Samples with checkpoint activity", "unit": "s/min", "until": "7.1", "version_text": "before 7.1", "view": "time_above"}</t>
+          <t>{"bands": "quick ≤5 (fading to 15) · slow 15–40 (edges 5, 60) · back_to_back ≥60 (from 50)", "doc": "Duration recorded for the most recent WiredTiger checkpoint; the same completed-checkpoint value may appear in multiple samples. Minute summaries select the highest valid sample.", "elevated": 60, "formula": "serverStatus/wiredTiger/checkpoint/most recent time (msecs) × 0.001, in s, at each available sample", "levels": [{"down": [5, 15], "name": "quick"}, {"band": [5, 15, 40, 60], "name": "slow"}, {"name": "back_to_back", "up": [50, 60]}], "min_change": 10, "name": "checkpoint.duration", "pack": "storage-engine", "pairs_with": ["checkpoint.running", "cache.dirty", "disk.write_await"], "reading": "the highest valid sample of each minute", "reference": {"configured": "not read", "source": "default checkpoint interval, storage.syncPeriodSecs", "unit": "s", "value": 60}, "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/checkpoint/most recent time (msecs)"], "scale": 0.001, "unit": "s"}, "since": "7.1", "title": "Checkpoint duration", "unit": "s", "version_text": "7.1 and later", "view": "max"}</t>
         </is>
       </c>
     </row>
@@ -10294,12 +10385,12 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>7.1 and later</t>
+          <t>before 7.1</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "The progress state's values are not decoded; any non-zero value is read as activity.", "bands": "brief ≤12 (fading to 24) · long 24–42 (edges 12, 54) · continuous ≥57 (from 48)", "doc": "Share of valid samples in which WiredTiger's checkpoint progress state was non-zero, normalized to a 60-second minute.", "elevated": 48, "formula": "serverStatus/wiredTiger/checkpoint/progress state, in state, at each available sample", "levels": [{"down": [12, 24], "name": "brief"}, {"band": [12, 24, 42, 54], "name": "long"}, {"name": "continuous", "up": [48, 57]}], "min_change": 9, "name": "checkpoint.running", "pack": "storage-engine", "pairs_with": ["checkpoint.duration", "disk.busy_above_95", "cache.dirty"], "reading": "valid-sample share strictly above 0 state, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/checkpoint/progress state"], "scale": 1, "unit": "state"}, "since": "7.1", "threshold": 0, "title": "Samples with checkpoint activity", "unit": "s/min", "version_text": "7.1 and later", "view": "time_above"}</t>
+          <t>{"bands": "brief ≤12 (fading to 24) · long 24–42 (edges 12, 54) · continuous ≥57 (from 48)", "doc": "Share of valid samples in which WiredTiger reported a checkpoint as currently running, normalized to a 60-second minute.", "elevated": 48, "formula": "serverStatus/wiredTiger/transaction/transaction checkpoint currently running, in running, at each available sample", "levels": [{"down": [12, 24], "name": "brief"}, {"band": [12, 24, 42, 54], "name": "long"}, {"name": "continuous", "up": [48, 57]}], "min_change": 9, "name": "checkpoint.running", "pack": "storage-engine", "pairs_with": ["checkpoint.duration", "disk.busy_above_95", "cache.dirty"], "reading": "valid-sample share strictly above 0 running, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/transaction/transaction checkpoint currently running"], "scale": 1, "unit": "running"}, "threshold": 0, "title": "Samples with checkpoint activity", "unit": "s/min", "until": "7.1", "version_text": "before 7.1", "view": "time_above"}</t>
         </is>
       </c>
     </row>
@@ -10309,17 +10400,17 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>storage.open_handles</t>
+          <t>checkpoint.running</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>7.1 and later</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "doc": "Count reported by WiredTiger for currently open data handles.", "formula": "serverStatus/wiredTiger/data-handle/connection data handles currently active, in handles, at each available sample", "min_change": 500, "name": "storage.open_handles", "pack": "storage-engine", "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/data-handle/connection data handles currently active"], "scale": 1, "unit": "handles"}, "title": "Open data handles", "unit": "handles", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"applies": "The progress state's values are not decoded; any non-zero value is read as activity.", "bands": "brief ≤12 (fading to 24) · long 24–42 (edges 12, 54) · continuous ≥57 (from 48)", "doc": "Share of valid samples in which WiredTiger's checkpoint progress state was non-zero, normalized to a 60-second minute.", "elevated": 48, "formula": "serverStatus/wiredTiger/checkpoint/progress state, in state, at each available sample", "levels": [{"down": [12, 24], "name": "brief"}, {"band": [12, 24, 42, 54], "name": "long"}, {"name": "continuous", "up": [48, 57]}], "min_change": 9, "name": "checkpoint.running", "pack": "storage-engine", "pairs_with": ["checkpoint.duration", "disk.busy_above_95", "cache.dirty"], "reading": "valid-sample share strictly above 0 state, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/checkpoint/progress state"], "scale": 1, "unit": "state"}, "since": "7.1", "threshold": 0, "title": "Samples with checkpoint activity", "unit": "s/min", "version_text": "7.1 and later", "view": "time_above"}</t>
         </is>
       </c>
     </row>
@@ -10329,7 +10420,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>latency.reads</t>
+          <t>storage.open_handles</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -10339,7 +10430,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "fast ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · slow 20–50 (edges 10, 100) · very_slow ≥100 (from 50)", "doc": "Average milliseconds per read operation over each minute, from opLatencies: every microsecond spent on reads in the minute over every read that finished in it.", "elevated": 50, "formula": "ΔserverStatus/opLatencies/reads/latency ÷ ΔserverStatus/opLatencies/reads/ops × 0.001, in ms, at each available sample; minutes where the divisor sums to under 60 are left out", "levels": [{"down": [1, 3], "name": "fast"}, {"band": [1, 3, 10, 20], "name": "normal"}, {"band": [10, 20, 50, 100], "name": "slow"}, {"name": "very_slow", "up": [50, 100]}], "min_change": 5, "name": "latency.reads", "pack": "workload", "pairs_with": ["tickets.read.scarce", "query.targeting", "cache.fill_above_95", "disk.read_await"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/opLatencies/reads/ops"], "min_den": 60, "mode": "rate", "num": ["serverStatus/opLatencies/reads/latency"], "scale": 0.001, "unit": "ms"}, "title": "Read latency", "unit": "ms", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "none — read for its shape only", "doc": "Count reported by WiredTiger for currently open data handles.", "formula": "serverStatus/wiredTiger/data-handle/connection data handles currently active, in handles, at each available sample", "min_change": 500, "name": "storage.open_handles", "pack": "storage-engine", "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/data-handle/connection data handles currently active"], "scale": 1, "unit": "handles"}, "title": "Open data handles", "unit": "handles", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10349,7 +10440,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>latency.writes</t>
+          <t>latency.reads</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -10359,7 +10450,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "fast ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · slow 20–50 (edges 10, 100) · very_slow ≥100 (from 50)", "doc": "Average milliseconds per write operation over each minute, from opLatencies.", "elevated": 50, "formula": "ΔserverStatus/opLatencies/writes/latency ÷ ΔserverStatus/opLatencies/writes/ops × 0.001, in ms, at each available sample; minutes where the divisor sums to under 60 are left out", "levels": [{"down": [1, 3], "name": "fast"}, {"band": [1, 3, 10, 20], "name": "normal"}, {"band": [10, 20, 50, 100], "name": "slow"}, {"name": "very_slow", "up": [50, 100]}], "min_change": 5, "name": "latency.writes", "pack": "workload", "pairs_with": ["tickets.write.scarce", "cache.dirty_above_20", "flow.lagged", "repl.majority_lag"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/opLatencies/writes/ops"], "min_den": 60, "mode": "rate", "num": ["serverStatus/opLatencies/writes/latency"], "scale": 0.001, "unit": "ms"}, "title": "Write latency", "unit": "ms", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "fast ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · slow 20–50 (edges 10, 100) · very_slow ≥100 (from 50)", "doc": "Average milliseconds per read operation over each minute, from opLatencies: every microsecond spent on reads in the minute over every read that finished in it.", "elevated": 50, "formula": "ΔserverStatus/opLatencies/reads/latency ÷ ΔserverStatus/opLatencies/reads/ops × 0.001, in ms, at each available sample; minutes where the divisor sums to under 60 are left out", "levels": [{"down": [1, 3], "name": "fast"}, {"band": [1, 3, 10, 20], "name": "normal"}, {"band": [10, 20, 50, 100], "name": "slow"}, {"name": "very_slow", "up": [50, 100]}], "min_change": 5, "name": "latency.reads", "pack": "workload", "pairs_with": ["tickets.read.scarce", "query.targeting", "cache.fill_above_95", "disk.read_await"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/opLatencies/reads/ops"], "min_den": 60, "mode": "rate", "num": ["serverStatus/opLatencies/reads/latency"], "scale": 0.001, "unit": "ms"}, "title": "Read latency", "unit": "ms", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10369,7 +10460,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>latency.commands</t>
+          <t>latency.writes</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -10379,7 +10470,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "fast ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · slow 20–50 (edges 10, 100) · very_slow ≥100 (from 50)", "doc": "Ratio of command opLatencies counter advance to command operation-count advance, scaled to milliseconds per operation.", "elevated": 50, "formula": "ΔserverStatus/opLatencies/commands/latency ÷ ΔserverStatus/opLatencies/commands/ops × 0.001, in ms, at each available sample; minutes where the divisor sums to under 60 are left out", "levels": [{"down": [1, 3], "name": "fast"}, {"band": [1, 3, 10, 20], "name": "normal"}, {"band": [10, 20, 50, 100], "name": "slow"}, {"name": "very_slow", "up": [50, 100]}], "min_change": 5, "name": "latency.commands", "pack": "workload", "pairs_with": ["tickets.read.scarce", "query.targeting"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/opLatencies/commands/ops"], "min_den": 60, "mode": "rate", "num": ["serverStatus/opLatencies/commands/latency"], "scale": 0.001, "unit": "ms"}, "title": "Command latency", "unit": "ms", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "fast ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · slow 20–50 (edges 10, 100) · very_slow ≥100 (from 50)", "doc": "Average milliseconds per write operation over each minute, from opLatencies.", "elevated": 50, "formula": "ΔserverStatus/opLatencies/writes/latency ÷ ΔserverStatus/opLatencies/writes/ops × 0.001, in ms, at each available sample; minutes where the divisor sums to under 60 are left out", "levels": [{"down": [1, 3], "name": "fast"}, {"band": [1, 3, 10, 20], "name": "normal"}, {"band": [10, 20, 50, 100], "name": "slow"}, {"name": "very_slow", "up": [50, 100]}], "min_change": 5, "name": "latency.writes", "pack": "workload", "pairs_with": ["tickets.write.scarce", "cache.dirty_above_20", "flow.lagged", "repl.majority_lag"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/opLatencies/writes/ops"], "min_den": 60, "mode": "rate", "num": ["serverStatus/opLatencies/writes/latency"], "scale": 0.001, "unit": "ms"}, "title": "Write latency", "unit": "ms", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10389,7 +10480,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>ops.total</t>
+          <t>latency.commands</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -10399,7 +10490,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "doc": "Sum of query, getMore, insert, update, delete and command operation-counter rates.", "formula": "Δ(serverStatus/opcounters/query + serverStatus/opcounters/getmore + serverStatus/opcounters/insert + serverStatus/opcounters/update + serverStatus/opcounters/delete + serverStatus/opcounters/command) per second, in ops/s, at each available sample", "min_change": 50, "name": "ops.total", "pack": "workload", "pairs_with": ["ops.writes", "connections.current"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/opcounters/query", "serverStatus/opcounters/getmore", "serverStatus/opcounters/insert", "serverStatus/opcounters/update", "serverStatus/opcounters/delete", "serverStatus/opcounters/command"], "scale": 1, "unit": "ops/s"}, "title": "Operations a second", "unit": "ops/s", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "fast ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · slow 20–50 (edges 10, 100) · very_slow ≥100 (from 50)", "doc": "Ratio of command opLatencies counter advance to command operation-count advance, scaled to milliseconds per operation.", "elevated": 50, "formula": "ΔserverStatus/opLatencies/commands/latency ÷ ΔserverStatus/opLatencies/commands/ops × 0.001, in ms, at each available sample; minutes where the divisor sums to under 60 are left out", "levels": [{"down": [1, 3], "name": "fast"}, {"band": [1, 3, 10, 20], "name": "normal"}, {"band": [10, 20, 50, 100], "name": "slow"}, {"name": "very_slow", "up": [50, 100]}], "min_change": 5, "name": "latency.commands", "pack": "workload", "pairs_with": ["tickets.read.scarce", "query.targeting"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/opLatencies/commands/ops"], "min_den": 60, "mode": "rate", "num": ["serverStatus/opLatencies/commands/latency"], "scale": 0.001, "unit": "ms"}, "title": "Command latency", "unit": "ms", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10409,7 +10500,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>ops.writes</t>
+          <t>ops.total</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -10419,7 +10510,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "doc": "Sum of insert, update and delete operation-counter rates.", "formula": "Δ(serverStatus/opcounters/insert + serverStatus/opcounters/update + serverStatus/opcounters/delete) per second, in ops/s, at each available sample", "min_change": 50, "name": "ops.writes", "pack": "workload", "pairs_with": ["cache.dirty", "checkpoint.duration"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/opcounters/insert", "serverStatus/opcounters/update", "serverStatus/opcounters/delete"], "scale": 1, "unit": "ops/s"}, "title": "Writes a second", "unit": "ops/s", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "none — read for its shape only", "doc": "Sum of query, getMore, insert, update, delete and command operation-counter rates.", "formula": "Δ(serverStatus/opcounters/query + serverStatus/opcounters/getmore + serverStatus/opcounters/insert + serverStatus/opcounters/update + serverStatus/opcounters/delete + serverStatus/opcounters/command) per second, in ops/s, at each available sample", "min_change": 50, "name": "ops.total", "pack": "workload", "pairs_with": ["ops.writes", "connections.current"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/opcounters/query", "serverStatus/opcounters/getmore", "serverStatus/opcounters/insert", "serverStatus/opcounters/update", "serverStatus/opcounters/delete", "serverStatus/opcounters/command"], "scale": 1, "unit": "ops/s"}, "title": "Operations a second", "unit": "ops/s", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10429,7 +10520,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>query.targeting</t>
+          <t>ops.writes</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -10439,7 +10530,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "low ≤2 (fading to 10) · moderate 10–50 (edges 2, 100) · high 100–500 (edges 50, 1000) · very_high ≥1000 (from 500)", "doc": "Ratio of documents-examined counter advance to documents-returned counter advance; it does not determine index suitability.", "elevated": 100, "formula": "ΔserverStatus/metrics/queryExecutor/scannedObjects ÷ ΔserverStatus/metrics/document/returned, in ratio, at each available sample; minutes where the divisor sums to under 60 are left out", "levels": [{"down": [2, 10], "name": "low"}, {"band": [2, 10, 50, 100], "name": "moderate"}, {"band": [50, 100, 500, 1000], "name": "high"}, {"name": "very_high", "up": [500, 1000]}], "min_change": 10, "name": "query.targeting", "pack": "workload", "pairs_with": ["query.collscans", "cache.read_in", "cpu.busy"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/metrics/document/returned"], "min_den": 60, "mode": "rate", "num": ["serverStatus/metrics/queryExecutor/scannedObjects"], "scale": 1, "unit": "ratio"}, "title": "Documents examined per document returned", "unit": "ratio", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "none — read for its shape only", "doc": "Sum of insert, update and delete operation-counter rates.", "formula": "Δ(serverStatus/opcounters/insert + serverStatus/opcounters/update + serverStatus/opcounters/delete) per second, in ops/s, at each available sample", "min_change": 50, "name": "ops.writes", "pack": "workload", "pairs_with": ["cache.dirty", "checkpoint.duration"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/opcounters/insert", "serverStatus/opcounters/update", "serverStatus/opcounters/delete"], "scale": 1, "unit": "ops/s"}, "title": "Writes a second", "unit": "ops/s", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10449,17 +10540,17 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>query.collscans</t>
+          <t>query.targeting</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>4.4 and later</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤0.01 (fading to 0.1) · some 0.1–1 (edges 0.01, 10) · many ≥10 (from 1)", "doc": "Rate of the server's collection-scan counter.", "elevated": 1, "formula": "ΔserverStatus/metrics/queryExecutor/collectionScans/total per second, in /s, at each available sample", "levels": [{"down": [0.01, 0.1], "name": "none"}, {"band": [0.01, 0.1, 1, 10], "name": "some"}, {"name": "many", "up": [1, 10]}], "min_change": 0.5, "name": "query.collscans", "pack": "workload", "pairs_with": ["query.targeting", "cache.read_in"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/metrics/queryExecutor/collectionScans/total"], "scale": 1, "unit": "/s"}, "since": "4.4", "title": "Collection scans", "unit": "/s", "version_text": "4.4 and later", "view": "mean"}</t>
+          <t>{"bands": "low ≤2 (fading to 10) · moderate 10–50 (edges 2, 100) · high 100–500 (edges 50, 1000) · very_high ≥1000 (from 500)", "doc": "Ratio of documents-examined counter advance to documents-returned counter advance; it does not determine index suitability.", "elevated": 100, "formula": "ΔserverStatus/metrics/queryExecutor/scannedObjects ÷ ΔserverStatus/metrics/document/returned, in ratio, at each available sample; minutes where the divisor sums to under 60 are left out", "levels": [{"down": [2, 10], "name": "low"}, {"band": [2, 10, 50, 100], "name": "moderate"}, {"band": [50, 100, 500, 1000], "name": "high"}, {"name": "very_high", "up": [500, 1000]}], "min_change": 10, "name": "query.targeting", "pack": "workload", "pairs_with": ["query.collscans", "cache.read_in", "cpu.busy"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/metrics/document/returned"], "min_den": 60, "mode": "rate", "num": ["serverStatus/metrics/queryExecutor/scannedObjects"], "scale": 1, "unit": "ratio"}, "title": "Documents examined per document returned", "unit": "ratio", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10469,17 +10560,17 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>query.scan_and_order</t>
+          <t>query.collscans</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>4.4 and later</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "doc": "Rate of the server's scanAndOrder counter.", "formula": "ΔserverStatus/metrics/operation/scanAndOrder per second, in /s, at each available sample", "min_change": 1, "name": "query.scan_and_order", "pack": "workload", "pairs_with": ["query.targeting", "memory.heap_outside_cache"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/metrics/operation/scanAndOrder"], "scale": 1, "unit": "/s"}, "title": "scanAndOrder counter rate", "unit": "/s", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "none ≤0.01 (fading to 0.1) · some 0.1–1 (edges 0.01, 10) · many ≥10 (from 1)", "doc": "Rate of the server's collection-scan counter.", "elevated": 1, "formula": "ΔserverStatus/metrics/queryExecutor/collectionScans/total per second, in /s, at each available sample", "levels": [{"down": [0.01, 0.1], "name": "none"}, {"band": [0.01, 0.1, 1, 10], "name": "some"}, {"name": "many", "up": [1, 10]}], "min_change": 0.5, "name": "query.collscans", "pack": "workload", "pairs_with": ["query.targeting", "cache.read_in"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/metrics/queryExecutor/collectionScans/total"], "scale": 1, "unit": "/s"}, "since": "4.4", "title": "Collection scans", "unit": "/s", "version_text": "4.4 and later", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10489,7 +10580,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>writes.conflicts</t>
+          <t>query.scan_and_order</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -10499,7 +10590,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "rare ≤0.1 (fading to 1) · some 1–10 (edges 0.1, 50) · heavy ≥50 (from 10)", "doc": "Rate of the server's writeConflicts counter; retries, document identity and contention cause are not inferred from this counter.", "elevated": 10, "formula": "ΔserverStatus/metrics/operation/writeConflicts per second, in /s, at each available sample", "levels": [{"down": [0.1, 1], "name": "rare"}, {"band": [0.1, 1, 10, 50], "name": "some"}, {"name": "heavy", "up": [10, 50]}], "min_change": 2, "name": "writes.conflicts", "pack": "workload", "pairs_with": ["ops.writes", "latency.writes"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/metrics/operation/writeConflicts"], "scale": 1, "unit": "/s"}, "title": "Write conflicts", "unit": "/s", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "none — read for its shape only", "doc": "Rate of the server's scanAndOrder counter.", "formula": "ΔserverStatus/metrics/operation/scanAndOrder per second, in /s, at each available sample", "min_change": 1, "name": "query.scan_and_order", "pack": "workload", "pairs_with": ["query.targeting", "memory.heap_outside_cache"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/metrics/operation/scanAndOrder"], "scale": 1, "unit": "/s"}, "title": "scanAndOrder counter rate", "unit": "/s", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10509,7 +10600,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>ttl.deletes</t>
+          <t>writes.conflicts</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -10519,7 +10610,7 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "doc": "Rate of documents reported deleted by the TTL monitor; collection identity, expiry backlog and latency impact are not inferred.", "formula": "ΔserverStatus/metrics/ttl/deletedDocuments per second, in docs/s, at each available sample", "min_change": 50, "name": "ttl.deletes", "pack": "workload", "pairs_with": ["cache.dirty", "disk.write_await", "repl.member_lag"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/metrics/ttl/deletedDocuments"], "scale": 1, "unit": "docs/s"}, "title": "Documents deleted by TTL", "unit": "docs/s", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "rare ≤0.1 (fading to 1) · some 1–10 (edges 0.1, 50) · heavy ≥50 (from 10)", "doc": "Rate of the server's writeConflicts counter; retries, document identity and contention cause are not inferred from this counter.", "elevated": 10, "formula": "ΔserverStatus/metrics/operation/writeConflicts per second, in /s, at each available sample", "levels": [{"down": [0.1, 1], "name": "rare"}, {"band": [0.1, 1, 10, 50], "name": "some"}, {"name": "heavy", "up": [10, 50]}], "min_change": 2, "name": "writes.conflicts", "pack": "workload", "pairs_with": ["ops.writes", "latency.writes"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/metrics/operation/writeConflicts"], "scale": 1, "unit": "/s"}, "title": "Write conflicts", "unit": "/s", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10529,7 +10620,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>cursors.open</t>
+          <t>ttl.deletes</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -10539,7 +10630,7 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "doc": "Count reported for currently open cursors.", "formula": "serverStatus/metrics/cursor/open/total, in cursors, at each available sample", "min_change": 50, "name": "cursors.open", "pack": "workload", "pairs_with": ["memory.heap_outside_cache", "connections.current"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/metrics/cursor/open/total"], "scale": 1, "unit": "cursors"}, "title": "Open cursors", "unit": "cursors", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "none — read for its shape only", "doc": "Rate of documents reported deleted by the TTL monitor; collection identity, expiry backlog and latency impact are not inferred.", "formula": "ΔserverStatus/metrics/ttl/deletedDocuments per second, in docs/s, at each available sample", "min_change": 50, "name": "ttl.deletes", "pack": "workload", "pairs_with": ["cache.dirty", "disk.write_await", "repl.member_lag"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/metrics/ttl/deletedDocuments"], "scale": 1, "unit": "docs/s"}, "title": "Documents deleted by TTL", "unit": "docs/s", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10549,17 +10640,17 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>repl.member_lag</t>
+          <t>cursors.open</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>before 6.0</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "One result per entry of this node's replica-set status, numbered by position in that list; a position can name a different member after a reconfig. Lag is measured against the newest applied time among members, not against the primary, and a member that stopped reporting keeps its last time.", "bands": "current ≤2 (fading to 5) · behind 5–20 (edges 2, 30) · lagging 30–120 (edges 20, 300) · far_behind ≥300 (from 120)", "doc": "Difference between each member's reported applied-write timestamp and the newest such timestamp in this node's replica-set status, scaled to seconds. Members without a timestamp have no result. optimeDate has one-second resolution. Minute summaries select the highest valid sample.", "elevated": 30, "formula": "newest of every replSetGetStatus/members/{i}/optimeDate − this one × 0.001, in s, at each available sample", "levels": [{"down": [2, 5], "name": "current"}, {"band": [2, 5, 20, 30], "name": "behind"}, {"band": [20, 30, 120, 300], "name": "lagging"}, {"name": "far_behind", "up": [120, 300]}], "min_change": 5, "name": "repl.member_lag", "pack": "replication", "pairs_with": ["repl.majority_lag", "flow.lagged", "net.retransmit"], "reading": "the highest valid sample of each minute", "signal": {"behind": true, "mode": "gauge", "num": ["replSetGetStatus/members/{i}/optimeDate"], "scale": 0.001, "unit": "s"}, "title": "Member replication lag", "unit": "s", "until": "6.0", "version_text": "before 6.0", "view": "max"}</t>
+          <t>{"bands": "none — read for its shape only", "doc": "Count reported for currently open cursors.", "formula": "serverStatus/metrics/cursor/open/total, in cursors, at each available sample", "min_change": 50, "name": "cursors.open", "pack": "workload", "pairs_with": ["memory.heap_outside_cache", "connections.current"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/metrics/cursor/open/total"], "scale": 1, "unit": "cursors"}, "title": "Open cursors", "unit": "cursors", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10574,12 +10665,12 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>6.0 and later</t>
+          <t>before 6.0</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "One result per entry of this node's replica-set status, numbered by position in that list; a position can name a different member after a reconfig. Lag is measured against the newest applied time among members, not against the primary, and a member that stopped reporting keeps its last time.", "bands": "current ≤2 (fading to 5) · behind 5–20 (edges 2, 30) · lagging 30–120 (edges 20, 300) · far_behind ≥300 (from 120)", "doc": "Difference between each member's reported applied-write timestamp and the newest such timestamp in this node's replica-set status, scaled to seconds. Members without a timestamp have no result. Minute summaries select the highest valid sample.", "elevated": 30, "formula": "newest of every replSetGetStatus/members/{i}/lastAppliedWallTime − this one × 0.001, in s, at each available sample", "levels": [{"down": [2, 5], "name": "current"}, {"band": [2, 5, 20, 30], "name": "behind"}, {"band": [20, 30, 120, 300], "name": "lagging"}, {"name": "far_behind", "up": [120, 300]}], "min_change": 5, "name": "repl.member_lag", "pack": "replication", "pairs_with": ["repl.majority_lag", "flow.lagged", "net.retransmit"], "reading": "the highest valid sample of each minute", "signal": {"behind": true, "mode": "gauge", "num": ["replSetGetStatus/members/{i}/lastAppliedWallTime"], "scale": 0.001, "unit": "s"}, "since": "6.0", "title": "Member replication lag", "unit": "s", "version_text": "6.0 and later", "view": "max"}</t>
+          <t>{"applies": "One result per entry of this node's replica-set status, numbered by position in that list; a position can name a different member after a reconfig. Lag is measured against the newest applied time among members, not against the primary, and a member that stopped reporting keeps its last time.", "bands": "current ≤2 (fading to 5) · behind 5–20 (edges 2, 30) · lagging 30–120 (edges 20, 300) · far_behind ≥300 (from 120)", "doc": "Difference between each member's reported applied-write timestamp and the newest such timestamp in this node's replica-set status, scaled to seconds. Members without a timestamp have no result. optimeDate has one-second resolution. Minute summaries select the highest valid sample.", "elevated": 30, "formula": "newest of every replSetGetStatus/members/{i}/optimeDate − this one × 0.001, in s, at each available sample", "levels": [{"down": [2, 5], "name": "current"}, {"band": [2, 5, 20, 30], "name": "behind"}, {"band": [20, 30, 120, 300], "name": "lagging"}, {"name": "far_behind", "up": [120, 300]}], "min_change": 5, "name": "repl.member_lag", "pack": "replication", "pairs_with": ["repl.majority_lag", "flow.lagged", "net.retransmit"], "reading": "the highest valid sample of each minute", "signal": {"behind": true, "mode": "gauge", "num": ["replSetGetStatus/members/{i}/optimeDate"], "scale": 0.001, "unit": "s"}, "title": "Member replication lag", "unit": "s", "until": "6.0", "version_text": "before 6.0", "view": "max"}</t>
         </is>
       </c>
     </row>
@@ -10589,17 +10680,17 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>repl.majority_lag</t>
+          <t>repl.member_lag</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>4.2 and later</t>
+          <t>6.0 and later</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "current ≤1 (fading to 3) · behind 3–10 (edges 1, 20) · lagging ≥20 (from 10)", "doc": "Difference between this node's lastAppliedWallTime and lastCommittedWallTime, scaled to seconds. Minute summaries select the highest valid sample.", "elevated": 10, "formula": "replSetGetStatus/optimes/lastAppliedWallTime − replSetGetStatus/optimes/lastCommittedWallTime × 0.001, in s, at each available sample", "levels": [{"down": [1, 3], "name": "current"}, {"band": [1, 3, 10, 20], "name": "behind"}, {"name": "lagging", "up": [10, 20]}], "min_change": 2, "name": "repl.majority_lag", "pack": "replication", "pairs_with": ["repl.member_lag", "flow.lagged", "latency.writes"], "reading": "the highest valid sample of each minute", "signal": {"minus": ["replSetGetStatus/optimes/lastCommittedWallTime"], "mode": "gauge", "num": ["replSetGetStatus/optimes/lastAppliedWallTime"], "scale": 0.001, "unit": "s"}, "since": "4.2", "title": "Majority commit lag", "unit": "s", "version_text": "4.2 and later", "view": "max"}</t>
+          <t>{"applies": "One result per entry of this node's replica-set status, numbered by position in that list; a position can name a different member after a reconfig. Lag is measured against the newest applied time among members, not against the primary, and a member that stopped reporting keeps its last time.", "bands": "current ≤2 (fading to 5) · behind 5–20 (edges 2, 30) · lagging 30–120 (edges 20, 300) · far_behind ≥300 (from 120)", "doc": "Difference between each member's reported applied-write timestamp and the newest such timestamp in this node's replica-set status, scaled to seconds. Members without a timestamp have no result. Minute summaries select the highest valid sample.", "elevated": 30, "formula": "newest of every replSetGetStatus/members/{i}/lastAppliedWallTime − this one × 0.001, in s, at each available sample", "levels": [{"down": [2, 5], "name": "current"}, {"band": [2, 5, 20, 30], "name": "behind"}, {"band": [20, 30, 120, 300], "name": "lagging"}, {"name": "far_behind", "up": [120, 300]}], "min_change": 5, "name": "repl.member_lag", "pack": "replication", "pairs_with": ["repl.majority_lag", "flow.lagged", "net.retransmit"], "reading": "the highest valid sample of each minute", "signal": {"behind": true, "mode": "gauge", "num": ["replSetGetStatus/members/{i}/lastAppliedWallTime"], "scale": 0.001, "unit": "s"}, "since": "6.0", "title": "Member replication lag", "unit": "s", "version_text": "6.0 and later", "view": "max"}</t>
         </is>
       </c>
     </row>
@@ -10609,17 +10700,17 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>flow.lagged</t>
+          <t>repl.majority_lag</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>4.2 and later</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "Set only on a primary with flow control enabled; a secondary, or a primary with flow control disabled, reports it unset. The flag records that the majority commit point lagged; time writers spent waiting for flow control is flow.wait.", "bands": "none ≤0 (fading to 1) · some 1–30 (edges 0, 48) · most ≥48 (from 30)", "doc": "Share of valid samples in which flowControl.isLagged was set, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/flowControl/isLagged, in lagged, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 30, 48], "name": "some"}, {"name": "most", "up": [30, 48]}], "min_change": 3, "name": "flow.lagged", "pack": "replication", "pairs_with": ["flow.wait", "repl.majority_lag", "latency.writes"], "reading": "valid-sample share strictly above 0 lagged, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/flowControl/isLagged"], "scale": 1, "unit": "lagged"}, "threshold": 0, "title": "Samples with flowControl.isLagged set", "unit": "s/min", "version_text": "all versions", "view": "time_above"}</t>
+          <t>{"bands": "current ≤1 (fading to 3) · behind 3–10 (edges 1, 20) · lagging ≥20 (from 10)", "doc": "Difference between this node's lastAppliedWallTime and lastCommittedWallTime, scaled to seconds. Minute summaries select the highest valid sample. A sample with either time unset (zero) is left out.", "elevated": 10, "formula": "replSetGetStatus/optimes/lastAppliedWallTime − replSetGetStatus/optimes/lastCommittedWallTime × 0.001, in s, at each available sample", "levels": [{"down": [1, 3], "name": "current"}, {"band": [1, 3, 10, 20], "name": "behind"}, {"name": "lagging", "up": [10, 20]}], "min_change": 2, "name": "repl.majority_lag", "pack": "replication", "pairs_with": ["repl.member_lag", "flow.lagged", "latency.writes"], "reading": "the highest valid sample of each minute", "signal": {"minus": ["replSetGetStatus/optimes/lastCommittedWallTime"], "mode": "gauge", "num": ["replSetGetStatus/optimes/lastAppliedWallTime"], "scale": 0.001, "timestamps": true, "unit": "s"}, "since": "4.2", "title": "Majority commit lag", "unit": "s", "version_text": "4.2 and later", "view": "max"}</t>
         </is>
       </c>
     </row>
@@ -10629,7 +10720,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>flow.wait</t>
+          <t>flow.lagged</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -10639,7 +10730,7 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)", "doc": "Milliseconds a second writes spent waiting for flow control tickets on this node, added across every write waiting.", "elevated": 100, "formula": "ΔserverStatus/flowControl/timeAcquiringMicros per second × 0.001, in ms/s, at each available sample", "levels": [{"down": [1, 10], "name": "none"}, {"band": [1, 10, 100, 500], "name": "some"}, {"name": "heavy", "up": [100, 500]}], "min_change": 10, "name": "flow.wait", "pack": "replication", "pairs_with": ["flow.lagged", "latency.writes"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/flowControl/timeAcquiringMicros"], "scale": 0.001, "unit": "ms/s"}, "title": "Time writers waited on flow control", "unit": "ms/s", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"applies": "Set only on a primary with flow control enabled; a secondary, or a primary with flow control disabled, reports it unset. The flag records that the majority commit point lagged; time writers spent waiting for flow control is flow.wait.", "bands": "none ≤0 (fading to 1) · some 1–30 (edges 0, 48) · most ≥48 (from 30)", "doc": "Share of valid samples in which flowControl.isLagged was set, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/flowControl/isLagged, in lagged, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 30, 48], "name": "some"}, {"name": "most", "up": [30, 48]}], "min_change": 3, "name": "flow.lagged", "pack": "replication", "pairs_with": ["flow.wait", "repl.majority_lag", "latency.writes"], "reading": "valid-sample share strictly above 0 lagged, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/flowControl/isLagged"], "scale": 1, "unit": "lagged"}, "threshold": 0, "title": "Samples with flowControl.isLagged set", "unit": "s/min", "version_text": "all versions", "view": "time_above"}</t>
         </is>
       </c>
     </row>
@@ -10649,7 +10740,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>repl.apply_rate</t>
+          <t>flow.wait</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -10659,7 +10750,7 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "direction": "down", "doc": "Rate of the node's oplog application operation counter.", "formula": "ΔserverStatus/metrics/repl/apply/ops per second, in ops/s, at each available sample", "min_change": 50, "name": "repl.apply_rate", "pack": "replication", "pairs_with": ["repl.buffer_fill", "repl.member_lag"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/metrics/repl/apply/ops"], "scale": 1, "unit": "ops/s"}, "title": "Oplog entries applied", "unit": "ops/s", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)", "doc": "Milliseconds a second writes spent waiting for flow control tickets on this node, added across every write waiting.", "elevated": 100, "formula": "ΔserverStatus/flowControl/timeAcquiringMicros per second × 0.001, in ms/s, at each available sample", "levels": [{"down": [1, 10], "name": "none"}, {"band": [1, 10, 100, 500], "name": "some"}, {"name": "heavy", "up": [100, 500]}], "min_change": 10, "name": "flow.wait", "pack": "replication", "pairs_with": ["flow.lagged", "latency.writes"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/flowControl/timeAcquiringMicros"], "scale": 0.001, "unit": "ms/s"}, "title": "Time writers waited on flow control", "unit": "ms/s", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10669,17 +10760,17 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>repl.buffer_fill</t>
+          <t>repl.apply_rate</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>before 8.0</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "empty ≤5 (fading to 20) · filling 20–60 (edges 5, 85) · full ≥90 (from 70)", "doc": "Reported replication buffer bytes as a share of its reported maximum.", "elevated": 70, "formula": "serverStatus/metrics/repl/buffer/sizeBytes ÷ serverStatus/metrics/repl/buffer/maxSizeBytes × 100, in %, at each available sample", "levels": [{"down": [5, 20], "name": "empty"}, {"band": [5, 20, 60, 85], "name": "filling"}, {"name": "full", "up": [70, 90]}], "min_change": 10, "name": "repl.buffer_fill", "pack": "replication", "pairs_with": ["repl.buffer_full", "repl.apply_rate", "repl.member_lag"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/metrics/repl/buffer/maxSizeBytes"], "mode": "gauge", "num": ["serverStatus/metrics/repl/buffer/sizeBytes"], "scale": 100, "unit": "%"}, "title": "Apply buffer fill", "unit": "%", "until": "8.0", "version_text": "before 8.0", "view": "mean"}</t>
+          <t>{"bands": "none — read for its shape only", "direction": "down", "doc": "Rate of the node's oplog application operation counter.", "formula": "ΔserverStatus/metrics/repl/apply/ops per second, in ops/s, at each available sample", "min_change": 50, "name": "repl.apply_rate", "pack": "replication", "pairs_with": ["repl.buffer_fill", "repl.member_lag"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/metrics/repl/apply/ops"], "scale": 1, "unit": "ops/s"}, "title": "Oplog entries applied", "unit": "ops/s", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10694,12 +10785,12 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>8.0 and later</t>
+          <t>before 8.0</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "empty ≤5 (fading to 20) · filling 20–60 (edges 5, 85) · full ≥90 (from 70)", "doc": "Reported replication buffer bytes as a share of its reported maximum.", "elevated": 70, "formula": "serverStatus/metrics/repl/buffer/apply/sizeBytes ÷ serverStatus/metrics/repl/buffer/apply/maxSizeBytes × 100, in %, at each available sample", "levels": [{"down": [5, 20], "name": "empty"}, {"band": [5, 20, 60, 85], "name": "filling"}, {"name": "full", "up": [70, 90]}], "min_change": 10, "name": "repl.buffer_fill", "pack": "replication", "pairs_with": ["repl.buffer_full", "repl.apply_rate", "repl.member_lag"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/metrics/repl/buffer/apply/maxSizeBytes"], "mode": "gauge", "num": ["serverStatus/metrics/repl/buffer/apply/sizeBytes"], "scale": 100, "unit": "%"}, "since": "8.0", "title": "Apply buffer fill", "unit": "%", "version_text": "8.0 and later", "view": "mean"}</t>
+          <t>{"bands": "empty ≤5 (fading to 20) · filling 20–60 (edges 5, 85) · full ≥90 (from 70)", "doc": "Reported replication buffer bytes as a share of its reported maximum.", "elevated": 70, "formula": "serverStatus/metrics/repl/buffer/sizeBytes ÷ serverStatus/metrics/repl/buffer/maxSizeBytes × 100, in %, at each available sample", "levels": [{"down": [5, 20], "name": "empty"}, {"band": [5, 20, 60, 85], "name": "filling"}, {"name": "full", "up": [70, 90]}], "min_change": 10, "name": "repl.buffer_fill", "pack": "replication", "pairs_with": ["repl.buffer_full", "repl.apply_rate", "repl.member_lag"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/metrics/repl/buffer/maxSizeBytes"], "mode": "gauge", "num": ["serverStatus/metrics/repl/buffer/sizeBytes"], "scale": 100, "unit": "%"}, "title": "Apply buffer fill", "unit": "%", "until": "8.0", "version_text": "before 8.0", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10709,17 +10800,17 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>repl.buffer_full</t>
+          <t>repl.buffer_fill</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>before 8.0</t>
+          <t>8.0 and later</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which replication buffer bytes were strictly above 90 % of the reported maximum, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/metrics/repl/buffer/sizeBytes ÷ serverStatus/metrics/repl/buffer/maxSizeBytes × 100, in %, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "repl.buffer_full", "pack": "replication", "pairs_with": ["repl.buffer_fill", "repl.apply_rate"], "reading": "valid-sample share strictly above 90 %, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/metrics/repl/buffer/maxSizeBytes"], "mode": "gauge", "num": ["serverStatus/metrics/repl/buffer/sizeBytes"], "scale": 100, "unit": "%"}, "threshold": 90, "title": "Apply-buffer samples above 90%", "unit": "s/min", "until": "8.0", "version_text": "before 8.0", "view": "time_above"}</t>
+          <t>{"bands": "empty ≤5 (fading to 20) · filling 20–60 (edges 5, 85) · full ≥90 (from 70)", "doc": "Reported replication buffer bytes as a share of its reported maximum.", "elevated": 70, "formula": "serverStatus/metrics/repl/buffer/apply/sizeBytes ÷ serverStatus/metrics/repl/buffer/apply/maxSizeBytes × 100, in %, at each available sample", "levels": [{"down": [5, 20], "name": "empty"}, {"band": [5, 20, 60, 85], "name": "filling"}, {"name": "full", "up": [70, 90]}], "min_change": 10, "name": "repl.buffer_fill", "pack": "replication", "pairs_with": ["repl.buffer_full", "repl.apply_rate", "repl.member_lag"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/metrics/repl/buffer/apply/maxSizeBytes"], "mode": "gauge", "num": ["serverStatus/metrics/repl/buffer/apply/sizeBytes"], "scale": 100, "unit": "%"}, "since": "8.0", "title": "Apply buffer fill", "unit": "%", "version_text": "8.0 and later", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10734,12 +10825,12 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>8.0 and later</t>
+          <t>before 8.0</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which replication buffer bytes were strictly above 90 % of the reported maximum, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/metrics/repl/buffer/apply/sizeBytes ÷ serverStatus/metrics/repl/buffer/apply/maxSizeBytes × 100, in %, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "repl.buffer_full", "pack": "replication", "pairs_with": ["repl.buffer_fill", "repl.apply_rate"], "reading": "valid-sample share strictly above 90 %, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/metrics/repl/buffer/apply/maxSizeBytes"], "mode": "gauge", "num": ["serverStatus/metrics/repl/buffer/apply/sizeBytes"], "scale": 100, "unit": "%"}, "since": "8.0", "threshold": 90, "title": "Apply-buffer samples above 90%", "unit": "s/min", "version_text": "8.0 and later", "view": "time_above"}</t>
+          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which replication buffer bytes were strictly above 90 % of the reported maximum, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/metrics/repl/buffer/sizeBytes ÷ serverStatus/metrics/repl/buffer/maxSizeBytes × 100, in %, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "repl.buffer_full", "pack": "replication", "pairs_with": ["repl.buffer_fill", "repl.apply_rate"], "reading": "valid-sample share strictly above 90 %, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/metrics/repl/buffer/maxSizeBytes"], "mode": "gauge", "num": ["serverStatus/metrics/repl/buffer/sizeBytes"], "scale": 100, "unit": "%"}, "threshold": 90, "title": "Apply-buffer samples above 90%", "unit": "s/min", "until": "8.0", "version_text": "before 8.0", "view": "time_above"}</t>
         </is>
       </c>
     </row>
@@ -10749,17 +10840,17 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>connections.used</t>
+          <t>repl.buffer_full</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>8.0 and later</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "low ≤25 (fading to 50) · moderate 50–70 (edges 25, 85) · high 85–90 (edges 70, 95) · near_limit ≥95 (from 90)", "doc": "Reported current connections divided by current plus available connections.", "elevated": 85, "formula": "serverStatus/connections/current ÷ (serverStatus/connections/current + serverStatus/connections/available) × 100, in %, at each available sample", "levels": [{"down": [25, 50], "name": "low"}, {"band": [25, 50, 70, 85], "name": "moderate"}, {"band": [70, 85, 90, 95], "name": "high"}, {"name": "near_limit", "up": [90, 95]}], "min_change": 10, "name": "connections.used", "pack": "connections", "pairs_with": ["connections.scarce", "connections.created", "connections.rejected"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/connections/current", "serverStatus/connections/available"], "mode": "gauge", "num": ["serverStatus/connections/current"], "scale": 100, "unit": "%"}, "title": "Current connections as a share of current plus available", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which replication buffer bytes were strictly above 90 % of the reported maximum, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/metrics/repl/buffer/apply/sizeBytes ÷ serverStatus/metrics/repl/buffer/apply/maxSizeBytes × 100, in %, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "repl.buffer_full", "pack": "replication", "pairs_with": ["repl.buffer_fill", "repl.apply_rate"], "reading": "valid-sample share strictly above 90 %, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/metrics/repl/buffer/apply/maxSizeBytes"], "mode": "gauge", "num": ["serverStatus/metrics/repl/buffer/apply/sizeBytes"], "scale": 100, "unit": "%"}, "since": "8.0", "threshold": 90, "title": "Apply-buffer samples above 90%", "unit": "s/min", "version_text": "8.0 and later", "view": "time_above"}</t>
         </is>
       </c>
     </row>
@@ -10769,7 +10860,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>connections.scarce</t>
+          <t>connections.used</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -10779,7 +10870,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which available connections were strictly below 10 % of current plus available, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/connections/available ÷ (serverStatus/connections/current + serverStatus/connections/available) × 100, in % available, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "connections.scarce", "open_at": "brief", "pack": "connections", "pairs_with": ["connections.used", "connections.created", "connections.rejected"], "reading": "valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/connections/current", "serverStatus/connections/available"], "mode": "gauge", "num": ["serverStatus/connections/available"], "scale": 100, "unit": "% available"}, "threshold": 10, "title": "Samples with under 10% of connections left", "unit": "s/min", "version_text": "all versions", "view": "time_below"}</t>
+          <t>{"bands": "low ≤25 (fading to 50) · moderate 50–70 (edges 25, 85) · high 85–90 (edges 70, 95) · near_limit ≥95 (from 90)", "doc": "Reported current connections divided by current plus available connections.", "elevated": 85, "formula": "serverStatus/connections/current ÷ (serverStatus/connections/current + serverStatus/connections/available) × 100, in %, at each available sample", "levels": [{"down": [25, 50], "name": "low"}, {"band": [25, 50, 70, 85], "name": "moderate"}, {"band": [70, 85, 90, 95], "name": "high"}, {"name": "near_limit", "up": [90, 95]}], "min_change": 10, "name": "connections.used", "pack": "connections", "pairs_with": ["connections.scarce", "connections.created", "connections.rejected"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/connections/current", "serverStatus/connections/available"], "mode": "gauge", "num": ["serverStatus/connections/current"], "scale": 100, "unit": "%"}, "title": "Current connections as a share of current plus available", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10789,7 +10880,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>connections.created</t>
+          <t>connections.scarce</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -10799,7 +10890,7 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "quiet ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · high ≥20 (from 10)", "doc": "Rate of the server's totalCreated connection counter.", "elevated": 20, "formula": "ΔserverStatus/connections/totalCreated per second, in conn/s, at each available sample", "levels": [{"down": [1, 3], "name": "quiet"}, {"band": [1, 3, 10, 20], "name": "normal"}, {"name": "high", "up": [10, 20]}], "min_change": 5, "name": "connections.created", "pack": "connections", "pairs_with": ["connections.current", "cpu.kernel_share", "net.resets"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/connections/totalCreated"], "scale": 1, "unit": "conn/s"}, "title": "New connections", "unit": "conn/s", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which available connections were strictly below 10 % of current plus available, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/connections/available ÷ (serverStatus/connections/current + serverStatus/connections/available) × 100, in % available, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "connections.scarce", "open_at": "brief", "pack": "connections", "pairs_with": ["connections.used", "connections.created", "connections.rejected"], "reading": "valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/connections/current", "serverStatus/connections/available"], "mode": "gauge", "num": ["serverStatus/connections/available"], "scale": 100, "unit": "% available"}, "threshold": 10, "title": "Samples with under 10% of connections left", "unit": "s/min", "version_text": "all versions", "view": "time_below"}</t>
         </is>
       </c>
     </row>
@@ -10809,17 +10900,17 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>connections.non_active</t>
+          <t>connections.created</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>4.4 and later</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "few ≤300 (fading to 800) · many 800–1500 (edges 300, 2500) · very_high ≥3000 (from 1500)", "doc": "Derived connection count: current plus awaitingTopologyChanges minus active; it is not evidence of unused client pools or a connection leak.", "elevated": 2000, "formula": "(serverStatus/connections/current + serverStatus/connections/awaitingTopologyChanges) − serverStatus/connections/active, in conns, at each available sample", "levels": [{"down": [300, 800], "name": "few"}, {"band": [300, 800, 1500, 2500], "name": "many"}, {"name": "very_high", "up": [1500, 3000]}], "min_change": 100, "name": "connections.non_active", "pack": "connections", "pairs_with": ["connections.current", "connections.created", "connections.working_share", "memory.heap_outside_cache"], "reading": "each minute's mean", "signal": {"minus": ["serverStatus/connections/active"], "mode": "gauge", "num": ["serverStatus/connections/current", "serverStatus/connections/awaitingTopologyChanges"], "scale": 1, "unit": "conns"}, "since": "4.4", "title": "Derived non-active connection count", "unit": "conns", "version_text": "4.4 and later", "view": "mean"}</t>
+          <t>{"bands": "quiet ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · high ≥20 (from 10)", "doc": "Rate of the server's totalCreated connection counter.", "elevated": 20, "formula": "ΔserverStatus/connections/totalCreated per second, in conn/s, at each available sample", "levels": [{"down": [1, 3], "name": "quiet"}, {"band": [1, 3, 10, 20], "name": "normal"}, {"name": "high", "up": [10, 20]}], "min_change": 5, "name": "connections.created", "pack": "connections", "pairs_with": ["connections.current", "cpu.kernel_share", "net.resets"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/connections/totalCreated"], "scale": 1, "unit": "conn/s"}, "title": "New connections", "unit": "conn/s", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10829,7 +10920,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>connections.working_share</t>
+          <t>connections.non_active</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -10839,7 +10930,7 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "calm ≤10 (fading to 25) · busy 25–40 (edges 10, 60) · high ≥60 (from 40)", "doc": "Derived active-connection share: active minus awaitingTopologyChanges divided by current connections. Minute summaries select the highest valid sample.", "elevated": 40, "formula": "serverStatus/connections/active − serverStatus/connections/awaitingTopologyChanges ÷ serverStatus/connections/current × 100, in %, at each available sample; minutes where the divisor sums to under 3000 are left out", "levels": [{"down": [10, 25], "name": "calm"}, {"band": [10, 25, 40, 60], "name": "busy"}, {"name": "high", "up": [40, 60]}], "min_change": 10, "name": "connections.working_share", "pack": "connections", "pairs_with": ["tickets.read.empty", "tickets.write.empty", "queue.readers", "queue.writers", "connections.created"], "reading": "the highest valid sample of each minute", "signal": {"den": ["serverStatus/connections/current"], "min_den": 3000, "minus": ["serverStatus/connections/awaitingTopologyChanges"], "mode": "gauge", "num": ["serverStatus/connections/active"], "scale": 100, "unit": "%"}, "since": "4.4", "title": "Derived active-connection share", "unit": "%", "version_text": "4.4 and later", "view": "max"}</t>
+          <t>{"bands": "few ≤300 (fading to 800) · many 800–1500 (edges 300, 2500) · very_high ≥3000 (from 1500)", "doc": "Derived connection count: current plus awaitingTopologyChanges minus active; it is not evidence of unused client pools or a connection leak.", "elevated": 2000, "formula": "(serverStatus/connections/current + serverStatus/connections/awaitingTopologyChanges) − serverStatus/connections/active, in conns, at each available sample", "levels": [{"down": [300, 800], "name": "few"}, {"band": [300, 800, 1500, 2500], "name": "many"}, {"name": "very_high", "up": [1500, 3000]}], "min_change": 100, "name": "connections.non_active", "pack": "connections", "pairs_with": ["connections.current", "connections.created", "connections.working_share", "memory.heap_outside_cache"], "reading": "each minute's mean", "signal": {"minus": ["serverStatus/connections/active"], "mode": "gauge", "num": ["serverStatus/connections/current", "serverStatus/connections/awaitingTopologyChanges"], "scale": 1, "unit": "conns"}, "since": "4.4", "title": "Derived non-active connection count", "unit": "conns", "version_text": "4.4 and later", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10849,17 +10940,17 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>connections.current</t>
+          <t>connections.working_share</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>4.4 and later</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "doc": "Count reported for currently open server connections.", "formula": "serverStatus/connections/current, in conns, at each available sample", "min_change": 50, "name": "connections.current", "pack": "connections", "pairs_with": ["connections.non_active", "connections.created", "memory.heap_outside_cache"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/connections/current"], "scale": 1, "unit": "conns"}, "title": "Open connections", "unit": "conns", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "calm ≤10 (fading to 25) · busy 25–40 (edges 10, 60) · high ≥60 (from 40)", "doc": "Derived active-connection share: active minus awaitingTopologyChanges divided by current connections. Minute summaries select the highest valid sample.", "elevated": 40, "formula": "serverStatus/connections/active − serverStatus/connections/awaitingTopologyChanges ÷ serverStatus/connections/current × 100, in %, at each available sample; minutes where the divisor sums to under 3000 are left out", "levels": [{"down": [10, 25], "name": "calm"}, {"band": [10, 25, 40, 60], "name": "busy"}, {"name": "high", "up": [40, 60]}], "min_change": 10, "name": "connections.working_share", "pack": "connections", "pairs_with": ["tickets.read.empty", "tickets.write.empty", "queue.readers", "queue.writers", "connections.created"], "reading": "the highest valid sample of each minute", "signal": {"den": ["serverStatus/connections/current"], "min_den": 3000, "minus": ["serverStatus/connections/awaitingTopologyChanges"], "mode": "gauge", "num": ["serverStatus/connections/active"], "scale": 100, "unit": "%"}, "since": "4.4", "title": "Derived active-connection share", "unit": "%", "version_text": "4.4 and later", "view": "max"}</t>
         </is>
       </c>
     </row>
@@ -10869,22 +10960,42 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
+          <t>connections.current</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none — read for its shape only", "doc": "Count reported for currently open server connections.", "formula": "serverStatus/connections/current, in conns, at each available sample", "min_change": 50, "name": "connections.current", "pack": "connections", "pairs_with": ["connections.non_active", "connections.created", "memory.heap_outside_cache"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/connections/current"], "scale": 1, "unit": "conns"}, "title": "Open connections", "unit": "conns", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
           <t>connections.rejected</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr">
         <is>
           <t>6.3 and later</t>
         </is>
       </c>
-      <c r="D92" s="4" t="inlineStr">
+      <c r="D93" s="4" t="inlineStr">
         <is>
           <t>{"bands": "none ≤0.001 (fading to 0.01) · some 0.01–1 (edges 0.001, 5) · many ≥5 (from 1)", "doc": "Rate of the server's rejected connection counter; client impact and rejection cause are not inferred.", "elevated": 0.01, "formula": "ΔserverStatus/connections/rejected per second, in /s, at each available sample", "levels": [{"down": [0.001, 0.01], "name": "none"}, {"band": [0.001, 0.01, 1, 5], "name": "some"}, {"name": "many", "up": [1, 5]}], "min_change": 0.01, "name": "connections.rejected", "pack": "connections", "pairs_with": ["connections.scarce", "connections.used"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/connections/rejected"], "scale": 1, "unit": "/s"}, "since": "6.3", "title": "Connections refused", "unit": "/s", "version_text": "6.3 and later", "view": "mean"}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D92"/>
+  <autoFilter ref="A1:D93"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/labels-review.xlsx
+++ b/docs/labels-review.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Raw definitions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Labels'!$A$1:$U$93</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Raw definitions'!$A$1:$D$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Labels'!$A$1:$U$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Raw definitions'!$A$1:$D$95</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -614,7 +614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U93"/>
+  <dimension ref="A1:U95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>memory.used, memory.page_faults</t>
+          <t>memory.used, memory.page_faults, memory.swap_in</t>
         </is>
       </c>
       <c r="T12" s="4" t="inlineStr"/>
@@ -1750,12 +1750,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>memory.page_faults</t>
+          <t>memory.swap_in</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Page faults</t>
+          <t>Pages swapped in</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1765,12 +1765,12 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Rate of the process's logged major-page-fault counter.</t>
+          <t>Rate of pages the whole machine read back from swap (vmstat pswpin). A process waits for every such page it touches, so a burst of it stalls whatever was running, even with swap mostly free.</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/extra_info/page_faults per second, in /s, at each available sample</t>
+          <t>ΔsystemMetrics/vmstat/pswpin per second, in pages/s, at each available sample</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>/s</t>
+          <t>pages/s</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>none ≤1 (fading to 5) · some 5–50 (edges 1, 200) · heavy ≥200 (from 50)</t>
+          <t>none ≤10 (fading to 50) · some 50–500 (edges 10, 1000) · heavy ≥1000 (from 500)</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>3 /s → 50% none, 50% some</t>
+          <t>30 pages/s → 50% none, 50% some</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
@@ -1800,12 +1800,12 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>50 /s or more</t>
+          <t>500 pages/s or more</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>10 /s</t>
+          <t>50 pages/s</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr"/>
@@ -1817,7 +1817,7 @@
       <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>/s</t>
+          <t>pages/s</t>
         </is>
       </c>
       <c r="R13" s="4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>memory.used, memory.swap_used, disk.read_await</t>
+          <t>memory.swap_out, memory.page_faults, memory.swap_used</t>
         </is>
       </c>
       <c r="T13" s="4" t="inlineStr"/>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>memory.mongod_resident</t>
+          <t>memory.swap_out</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>mongod resident memory</t>
+          <t>Pages swapped out</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1856,47 +1856,47 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>mongod's resident memory as a share of the machine's. Host-wide memory or CPU counters do not establish a container's resource limit.</t>
+          <t>Rate of pages the whole machine wrote out to swap (vmstat pswpout).</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/mem/resident ÷ systemMetrics/memory/MemTotal_kb × 102400, in %, at each available sample</t>
+          <t>ΔsystemMetrics/vmstat/pswpout per second, in pages/s, at each available sample</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>each minute's ratio of sums</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>pages/s</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>modest ≤40 (fading to 60) · large 60–75 (edges 40, 85) · dominant ≥85 (from 75)</t>
+          <t>none ≤10 (fading to 50) · some 50–500 (edges 10, 1000) · heavy ≥1000 (from 500)</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>50 % → 50% modest, 50% large</t>
+          <t>30 pages/s → 50% none, 50% some</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>dominant</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>80 % or more</t>
+          <t>500 pages/s or more</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>5 %</t>
+          <t>50 pages/s</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr"/>
@@ -1908,7 +1908,7 @@
       <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>pages/s</t>
         </is>
       </c>
       <c r="R14" s="4" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>memory.used, memory.heap_outside_cache, memory.cache_of_ram</t>
+          <t>memory.swap_in, memory.used, memory.swap_used</t>
         </is>
       </c>
       <c r="T14" s="4" t="inlineStr"/>
@@ -1932,12 +1932,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>memory.heap_outside_cache</t>
+          <t>memory.page_faults</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Allocated bytes minus WiredTiger cache bytes</t>
+          <t>Page faults</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1947,12 +1947,12 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Difference between tcmalloc allocated bytes and bytes currently held in the WiredTiger cache; this is a derived estimate, not a complete inventory of non-cache allocations.</t>
+          <t>Rate of the process's logged major-page-fault counter.</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/tcmalloc/generic/current_allocated_bytes − serverStatus/wiredTiger/cache/bytes currently in the cache × 9.313225746154785e-10, in GiB, at each available sample</t>
+          <t>ΔserverStatus/extra_info/page_faults per second, in /s, at each available sample</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -1962,24 +1962,32 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>GiB</t>
+          <t>/s</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>none — read for its shape only</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr"/>
+          <t>none ≤1 (fading to 5) · some 5–50 (edges 1, 200) · heavy ≥200 (from 50)</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>3 /s → 50% none, 50% some</t>
+        </is>
+      </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>shape only: a step, an episode, a schedule</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr"/>
+          <t>heavy</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>50 /s or more</t>
+        </is>
+      </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>0.5 GiB</t>
+          <t>10 /s</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr"/>
@@ -1991,7 +1999,7 @@
       <c r="P15" s="4" t="n"/>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>GiB</t>
+          <t>/s</t>
         </is>
       </c>
       <c r="R15" s="4" t="inlineStr">
@@ -2001,7 +2009,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>connections.current, memory.allocator_free, cursors.open</t>
+          <t>memory.used, memory.swap_used, disk.read_await</t>
         </is>
       </c>
       <c r="T15" s="4" t="inlineStr"/>
@@ -2015,27 +2023,27 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>memory.allocator_free</t>
+          <t>memory.mongod_resident</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>tcmalloc pageheap-free share</t>
+          <t>mongod resident memory</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>before 8.0</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Ratio of tcmalloc pageheap_free_bytes to heap_size; these counters do not describe every allocator cache.</t>
+          <t>mongod's resident memory as a share of the machine's. Host-wide memory or CPU counters do not establish a container's resource limit.</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/tcmalloc/tcmalloc/pageheap_free_bytes ÷ serverStatus/tcmalloc/generic/heap_size × 100, in %, at each available sample</t>
+          <t>serverStatus/mem/resident ÷ systemMetrics/memory/MemTotal_kb × 102400, in %, at each available sample</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -2050,22 +2058,22 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>small ≤10 (fading to 20) · notable 20–30 (edges 10, 45) · large ≥45 (from 30)</t>
+          <t>modest ≤40 (fading to 60) · large 60–75 (edges 40, 85) · dominant ≥85 (from 75)</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>15 % → 50% small, 50% notable</t>
+          <t>50 % → 50% modest, 50% large</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>dominant</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>30 % or more</t>
+          <t>80 % or more</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
@@ -2092,7 +2100,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>memory.heap_outside_cache, memory.mongod_resident</t>
+          <t>memory.used, memory.heap_outside_cache, memory.cache_of_ram</t>
         </is>
       </c>
       <c r="T16" s="4" t="inlineStr"/>
@@ -2106,12 +2114,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>memory.cache_of_ram</t>
+          <t>memory.heap_outside_cache</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>WiredTiger cache size against RAM</t>
+          <t>Allocated bytes minus WiredTiger cache bytes</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -2121,47 +2129,39 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>The configured cache as a share of the machine's memory. Host-wide memory or CPU counters do not establish a container's resource limit.</t>
+          <t>Difference between tcmalloc allocated bytes and bytes currently held in the WiredTiger cache; this is a derived estimate, not a complete inventory of non-cache allocations.</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/cache/maximum bytes configured ÷ systemMetrics/memory/MemTotal_kb × 0.09765625, in %, at each available sample</t>
+          <t>serverStatus/tcmalloc/generic/current_allocated_bytes − serverStatus/wiredTiger/cache/bytes currently in the cache × 9.313225746154785e-10, in GiB, at each available sample</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>each minute's ratio of sums</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>GiB</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>low ≤30 (fading to 40) · middle 40–55 (edges 30, 62) · high ≥70 (from 58)</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>35 % → 50% low, 50% middle</t>
-        </is>
-      </c>
+          <t>none — read for its shape only</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>60 % or more</t>
-        </is>
-      </c>
+          <t>shape only: a step, an episode, a schedule</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr"/>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>5 %</t>
+          <t>0.5 GiB</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr"/>
@@ -2173,7 +2173,7 @@
       <c r="P17" s="4" t="n"/>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>GiB</t>
         </is>
       </c>
       <c r="R17" s="4" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>memory.used, memory.mongod_resident</t>
+          <t>connections.current, memory.allocator_free, cursors.open</t>
         </is>
       </c>
       <c r="T17" s="4" t="inlineStr"/>
@@ -2192,37 +2192,37 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>disk</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>disk.busy</t>
+          <t>memory.allocator_free</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Disk busy</t>
+          <t>tcmalloc pageheap-free share</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>before 8.0</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Device io_time counter advance divided by elapsed time; a high value does not establish device capacity exhaustion. Device coverage depends on the block-device counters present in FTDC; logical devices may be absent.</t>
+          <t>Ratio of tcmalloc pageheap_free_bytes to heap_size; these counters do not describe every allocator cache.</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>ΔsystemMetrics/disks/{i}/io_time_ms per second × 0.1, in %, at each available sample; real block devices only</t>
+          <t>serverStatus/tcmalloc/tcmalloc/pageheap_free_bytes ÷ serverStatus/tcmalloc/generic/heap_size × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>each minute's ratio of sums</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -2232,34 +2232,30 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>idle ≤5 (fading to 15) · low 15–40 (edges 5, 60) · moderate 60–75 (edges 40, 85) · high 85–92 (edges 75, 97) · very_high ≥97 (from 92)</t>
+          <t>small ≤10 (fading to 20) · notable 20–30 (edges 10, 45) · large ≥45 (from 30)</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>10 % → 50% idle, 50% low</t>
+          <t>15 % → 50% small, 50% notable</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>high or very_high</t>
+          <t>large</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>85 % or more</t>
+          <t>30 % or more</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>15 %</t>
-        </is>
-      </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>disk.await</t>
-        </is>
-      </c>
+          <t>5 %</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr"/>
       <c r="O18" s="4" t="inlineStr">
         <is>
           <t>mean</t>
@@ -2278,30 +2274,26 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>disk.busy_above_95, disk.await, disk.queue, disk.iops, disk.throughput</t>
+          <t>memory.heap_outside_cache, memory.mongod_resident</t>
         </is>
       </c>
       <c r="T18" s="4" t="inlineStr"/>
-      <c r="U18" s="4" t="inlineStr">
-        <is>
-          <t>A device that serves requests in parallel, such as an SSD, NVMe or network volume, can show io_time near 100 % with capacity to spare; disk.await shows whether requests waited. Device-mapper (dm-*) devices are not read by this tool; the disks under them are.</t>
-        </is>
-      </c>
+      <c r="U18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>disk</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>disk.busy_above_95</t>
+          <t>memory.cache_of_ram</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Device-busy samples above 95%</t>
+          <t>WiredTiger cache size against RAM</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -2311,62 +2303,56 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which a device's io_time advanced by more than 95 % of the elapsed time, normalized to a 60-second minute.</t>
+          <t>The configured cache as a share of the machine's memory. Host-wide memory or CPU counters do not establish a container's resource limit.</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>ΔsystemMetrics/disks/{i}/io_time_ms per second × 0.1, in %, at each available sample; real block devices only</t>
+          <t>serverStatus/wiredTiger/cache/maximum bytes configured ÷ systemMetrics/memory/MemTotal_kb × 0.09765625, in %, at each available sample</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly above 95 %, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>each minute's ratio of sums</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>s/min</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
+          <t>low ≤30 (fading to 40) · middle 40–55 (edges 30, 62) · high ≥70 (from 58)</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>0.5 s/min → 50% none, 50% brief</t>
+          <t>35 % → 50% low, 50% middle</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>frequent or constant</t>
+          <t>high</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>1 s/min or more</t>
+          <t>60 % or more</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>3 s/min</t>
-        </is>
-      </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>disk.await</t>
-        </is>
-      </c>
+          <t>5 %</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr"/>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>time_above</t>
-        </is>
-      </c>
-      <c r="P19" s="4" t="n">
-        <v>95</v>
-      </c>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P19" s="4" t="n"/>
       <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>%</t>
@@ -2379,15 +2365,11 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>disk.busy, disk.await, checkpoint.running</t>
+          <t>memory.used, memory.mongod_resident</t>
         </is>
       </c>
       <c r="T19" s="4" t="inlineStr"/>
-      <c r="U19" s="4" t="inlineStr">
-        <is>
-          <t>A device that serves requests in parallel, such as an SSD, NVMe or network volume, can show io_time near 100 % with capacity to spare; disk.await shows whether requests waited. Device-mapper (dm-*) devices are not read by this tool; the disks under them are.</t>
-        </is>
-      </c>
+      <c r="U19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -2397,65 +2379,69 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
+          <t>disk.busy</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Disk busy</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Device io_time counter advance divided by elapsed time; a high value does not establish device capacity exhaustion. Device coverage depends on the block-device counters present in FTDC; logical devices may be absent.</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>ΔsystemMetrics/disks/{i}/io_time_ms per second × 0.1, in %, at each available sample; real block devices only</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>each minute's mean</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>idle ≤5 (fading to 15) · low 15–40 (edges 5, 60) · moderate 60–75 (edges 40, 85) · high 85–92 (edges 75, 97) · very_high ≥97 (from 92)</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>10 % → 50% idle, 50% low</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>high or very_high</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>85 % or more</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>15 %</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
           <t>disk.await</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Disk time per request</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>all versions</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Average milliseconds a read or write took on each device, queueing included — what iostat calls await.</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Δ(systemMetrics/disks/{i}/read_time_ms + systemMetrics/disks/{i}/write_time_ms) ÷ Δ(systemMetrics/disks/{i}/reads + systemMetrics/disks/{i}/writes), in ms, at each available sample; minutes where the divisor sums to under 60 are left out; real block devices only</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>each minute's ratio of sums</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>ms</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>fast ≤2 (fading to 5) · normal 5–10 (edges 2, 15) · slow 15–30 (edges 10, 50) · very_slow ≥50 (from 30)</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>3.5 ms → 50% fast, 50% normal</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>slow or very_slow</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>20 ms or more</t>
-        </is>
-      </c>
-      <c r="M20" s="4" t="inlineStr">
-        <is>
-          <t>5 ms</t>
-        </is>
-      </c>
-      <c r="N20" s="4" t="inlineStr"/>
       <c r="O20" s="4" t="inlineStr">
         <is>
           <t>mean</t>
@@ -2464,7 +2450,7 @@
       <c r="P20" s="4" t="n"/>
       <c r="Q20" s="4" t="inlineStr">
         <is>
-          <t>ms</t>
+          <t>%</t>
         </is>
       </c>
       <c r="R20" s="4" t="inlineStr">
@@ -2474,11 +2460,15 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>disk.busy, disk.queue, cpu.iowait</t>
+          <t>disk.busy_above_95, disk.await, disk.queue, disk.iops, disk.throughput</t>
         </is>
       </c>
       <c r="T20" s="4" t="inlineStr"/>
-      <c r="U20" s="4" t="inlineStr"/>
+      <c r="U20" s="4" t="inlineStr">
+        <is>
+          <t>A device that serves requests in parallel, such as an SSD, NVMe or network volume, can show io_time near 100 % with capacity to spare; disk.await shows whether requests waited. Device-mapper (dm-*) devices are not read by this tool; the disks under them are.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -2488,12 +2478,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>disk.read_await</t>
+          <t>disk.busy_above_95</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Disk time per read</t>
+          <t>Device-busy samples above 95%</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -2503,59 +2493,65 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Average milliseconds a read took on each device.</t>
+          <t>Share of valid samples in which a device's io_time advanced by more than 95 % of the elapsed time, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>ΔsystemMetrics/disks/{i}/read_time_ms ÷ ΔsystemMetrics/disks/{i}/reads, in ms, at each available sample; minutes where the divisor sums to under 60 are left out; real block devices only</t>
+          <t>ΔsystemMetrics/disks/{i}/io_time_ms per second × 0.1, in %, at each available sample; real block devices only</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>each minute's ratio of sums</t>
+          <t>valid-sample share strictly above 95 %, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>ms</t>
+          <t>s/min</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>fast ≤2 (fading to 5) · normal 5–10 (edges 2, 15) · slow 15–30 (edges 10, 50) · very_slow ≥50 (from 30)</t>
+          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>3.5 ms → 50% fast, 50% normal</t>
+          <t>0.5 s/min → 50% none, 50% brief</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>slow or very_slow</t>
+          <t>frequent or constant</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>20 ms or more</t>
+          <t>1 s/min or more</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>5 ms</t>
-        </is>
-      </c>
-      <c r="N21" s="4" t="inlineStr"/>
+          <t>3 s/min</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>disk.await</t>
+        </is>
+      </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="P21" s="4" t="n"/>
+          <t>time_above</t>
+        </is>
+      </c>
+      <c r="P21" s="4" t="n">
+        <v>95</v>
+      </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>ms</t>
+          <t>%</t>
         </is>
       </c>
       <c r="R21" s="4" t="inlineStr">
@@ -2565,11 +2561,15 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>cache.read_in, disk.busy</t>
+          <t>disk.busy, disk.await, checkpoint.running</t>
         </is>
       </c>
       <c r="T21" s="4" t="inlineStr"/>
-      <c r="U21" s="4" t="inlineStr"/>
+      <c r="U21" s="4" t="inlineStr">
+        <is>
+          <t>A device that serves requests in parallel, such as an SSD, NVMe or network volume, can show io_time near 100 % with capacity to spare; disk.await shows whether requests waited. Device-mapper (dm-*) devices are not read by this tool; the disks under them are.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -2579,12 +2579,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>disk.write_await</t>
+          <t>disk.await</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Disk time per write</t>
+          <t>Disk time per request</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Average milliseconds a write took on each device.</t>
+          <t>Average milliseconds a read or write took on each device, queueing included — what iostat calls await.</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>ΔsystemMetrics/disks/{i}/write_time_ms ÷ ΔsystemMetrics/disks/{i}/writes, in ms, at each available sample; minutes where the divisor sums to under 60 are left out; real block devices only</t>
+          <t>Δ(systemMetrics/disks/{i}/read_time_ms + systemMetrics/disks/{i}/write_time_ms) ÷ Δ(systemMetrics/disks/{i}/reads + systemMetrics/disks/{i}/writes), in ms, at each available sample; minutes where the divisor sums to under 60 are left out; real block devices only</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>checkpoint.duration, cache.dirty, tickets.write.scarce</t>
+          <t>disk.busy, disk.queue, cpu.iowait</t>
         </is>
       </c>
       <c r="T22" s="4" t="inlineStr"/>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>disk.queue</t>
+          <t>disk.read_await</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Disk requests in flight</t>
+          <t>Disk time per read</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -2685,54 +2685,50 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Average number of requests outstanding on each device over the minute (io_queued time over wall time).</t>
+          <t>Average milliseconds a read took on each device.</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>ΔsystemMetrics/disks/{i}/io_queued_ms per second × 0.001, in requests, at each available sample; real block devices only</t>
+          <t>ΔsystemMetrics/disks/{i}/read_time_ms ÷ ΔsystemMetrics/disks/{i}/reads, in ms, at each available sample; minutes where the divisor sums to under 60 are left out; real block devices only</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>each minute's ratio of sums</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>requests</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>shallow ≤1 (fading to 2) · moderate 2–8 (edges 1, 16) · deep ≥16 (from 8)</t>
+          <t>fast ≤2 (fading to 5) · normal 5–10 (edges 2, 15) · slow 15–30 (edges 10, 50) · very_slow ≥50 (from 30)</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>1.5 requests → 50% shallow, 50% moderate</t>
+          <t>3.5 ms → 50% fast, 50% normal</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>deep</t>
+          <t>slow or very_slow</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>8 requests or more</t>
+          <t>20 ms or more</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>2 requests</t>
-        </is>
-      </c>
-      <c r="N23" s="4" t="inlineStr">
-        <is>
-          <t>disk.await</t>
-        </is>
-      </c>
+          <t>5 ms</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr"/>
       <c r="O23" s="4" t="inlineStr">
         <is>
           <t>mean</t>
@@ -2741,7 +2737,7 @@
       <c r="P23" s="4" t="n"/>
       <c r="Q23" s="4" t="inlineStr">
         <is>
-          <t>requests</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="R23" s="4" t="inlineStr">
@@ -2751,7 +2747,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>disk.await, disk.busy</t>
+          <t>cache.read_in, disk.busy</t>
         </is>
       </c>
       <c r="T23" s="4" t="inlineStr"/>
@@ -2765,12 +2761,12 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>disk.iops</t>
+          <t>disk.write_await</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Disk requests a second</t>
+          <t>Disk time per write</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -2780,39 +2776,47 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Reads plus writes a second on each device.</t>
+          <t>Average milliseconds a write took on each device.</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Δ(systemMetrics/disks/{i}/reads + systemMetrics/disks/{i}/writes) per second, in /s, at each available sample; real block devices only</t>
+          <t>ΔsystemMetrics/disks/{i}/write_time_ms ÷ ΔsystemMetrics/disks/{i}/writes, in ms, at each available sample; minutes where the divisor sums to under 60 are left out; real block devices only</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>each minute's ratio of sums</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>/s</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>none — read for its shape only</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr"/>
+          <t>fast ≤2 (fading to 5) · normal 5–10 (edges 2, 15) · slow 15–30 (edges 10, 50) · very_slow ≥50 (from 30)</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>3.5 ms → 50% fast, 50% normal</t>
+        </is>
+      </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>shape only: a step, an episode, a schedule</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr"/>
+          <t>slow or very_slow</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>20 ms or more</t>
+        </is>
+      </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>100 /s</t>
+          <t>5 ms</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr"/>
@@ -2824,7 +2828,7 @@
       <c r="P24" s="4" t="n"/>
       <c r="Q24" s="4" t="inlineStr">
         <is>
-          <t>/s</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="R24" s="4" t="inlineStr">
@@ -2834,7 +2838,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>disk.busy, disk.await</t>
+          <t>checkpoint.duration, cache.dirty, tickets.write.scarce</t>
         </is>
       </c>
       <c r="T24" s="4" t="inlineStr"/>
@@ -2848,12 +2852,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>disk.throughput</t>
+          <t>disk.queue</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Disk throughput</t>
+          <t>Disk requests in flight</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -2863,12 +2867,12 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Megabytes a second read plus written on each device (sectors are 512 bytes).</t>
+          <t>Average number of requests outstanding on each device over the minute (io_queued time over wall time).</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Δ(systemMetrics/disks/{i}/read_sectors + systemMetrics/disks/{i}/write_sectors) per second × 0.000512, in MB/s, at each available sample; real block devices only</t>
+          <t>ΔsystemMetrics/disks/{i}/io_queued_ms per second × 0.001, in requests, at each available sample; real block devices only</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
@@ -2878,27 +2882,39 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>MB/s</t>
+          <t>requests</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>none — read for its shape only</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr"/>
+          <t>shallow ≤1 (fading to 2) · moderate 2–8 (edges 1, 16) · deep ≥16 (from 8)</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>1.5 requests → 50% shallow, 50% moderate</t>
+        </is>
+      </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>shape only: a step, an episode, a schedule</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr"/>
+          <t>deep</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>8 requests or more</t>
+        </is>
+      </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>10 MB/s</t>
-        </is>
-      </c>
-      <c r="N25" s="4" t="inlineStr"/>
+          <t>2 requests</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>disk.await</t>
+        </is>
+      </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
           <t>mean</t>
@@ -2907,7 +2923,7 @@
       <c r="P25" s="4" t="n"/>
       <c r="Q25" s="4" t="inlineStr">
         <is>
-          <t>MB/s</t>
+          <t>requests</t>
         </is>
       </c>
       <c r="R25" s="4" t="inlineStr">
@@ -2917,7 +2933,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>disk.busy, disk.iops</t>
+          <t>disk.await, disk.busy</t>
         </is>
       </c>
       <c r="T25" s="4" t="inlineStr"/>
@@ -2926,17 +2942,17 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>disk</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>net.retransmit</t>
+          <t>disk.iops</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>TCP retransmission</t>
+          <t>Disk requests a second</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -2946,47 +2962,39 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Ratio of the host TCP RetransSegs counter advance to the OutSegs counter advance, across host connections.</t>
+          <t>Reads plus writes a second on each device.</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>ΔsystemMetrics/netstat/Tcp:RetransSegs ÷ ΔsystemMetrics/netstat/Tcp:OutSegs × 100, in %, at each available sample; minutes where the divisor sums to under 1000 are left out</t>
+          <t>Δ(systemMetrics/disks/{i}/reads + systemMetrics/disks/{i}/writes) per second, in /s, at each available sample; real block devices only</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>each minute's ratio of sums</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>/s</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>low ≤0.1 (fading to 0.3) · moderate 0.3–0.7 (edges 0.1, 1) · high 1–2 (edges 0.7, 3) · very_high ≥3 (from 2)</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>0.2 % → 50% low, 50% moderate</t>
-        </is>
-      </c>
+          <t>none — read for its shape only</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr"/>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>high or very_high</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>1 % or more</t>
-        </is>
-      </c>
+          <t>shape only: a step, an episode, a schedule</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr"/>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>0.5 %</t>
+          <t>100 /s</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr"/>
@@ -2998,7 +3006,7 @@
       <c r="P26" s="4" t="n"/>
       <c r="Q26" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>/s</t>
         </is>
       </c>
       <c r="R26" s="4" t="inlineStr">
@@ -3008,7 +3016,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>repl.member_lag, net.resets</t>
+          <t>disk.busy, disk.await</t>
         </is>
       </c>
       <c r="T26" s="4" t="inlineStr"/>
@@ -3017,17 +3025,17 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>disk</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>net.listen_overflows</t>
+          <t>disk.throughput</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Listen queue overflows</t>
+          <t>Disk throughput</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -3037,12 +3045,12 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Rate of the host TCP ListenOverflows counter; the counter does not identify a MongoDB connection or client outcome.</t>
+          <t>Megabytes a second read plus written on each device (sectors are 512 bytes).</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>ΔsystemMetrics/netstat/TcpExt:ListenOverflows per second, in /s, at each available sample</t>
+          <t>Δ(systemMetrics/disks/{i}/read_sectors + systemMetrics/disks/{i}/write_sectors) per second × 0.000512, in MB/s, at each available sample; real block devices only</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
@@ -3052,32 +3060,24 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>/s</t>
+          <t>MB/s</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>none ≤0.01 (fading to 0.1) · some 0.1–1 (edges 0.01, 5) · many ≥5 (from 1)</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>0.055 /s → 50% none, 50% some</t>
-        </is>
-      </c>
+          <t>none — read for its shape only</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr"/>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>many</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>0.1 /s or more</t>
-        </is>
-      </c>
+          <t>shape only: a step, an episode, a schedule</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr"/>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>0.1 /s</t>
+          <t>10 MB/s</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr"/>
@@ -3089,7 +3089,7 @@
       <c r="P27" s="4" t="n"/>
       <c r="Q27" s="4" t="inlineStr">
         <is>
-          <t>/s</t>
+          <t>MB/s</t>
         </is>
       </c>
       <c r="R27" s="4" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>connections.created, cpu.busy_above_95</t>
+          <t>disk.busy, disk.iops</t>
         </is>
       </c>
       <c r="T27" s="4" t="inlineStr"/>
@@ -3113,12 +3113,12 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>net.resets</t>
+          <t>net.retransmit</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>TCP connections reset</t>
+          <t>TCP retransmission</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -3128,39 +3128,47 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Established connections reset a second, host-wide.</t>
+          <t>Ratio of the host TCP RetransSegs counter advance to the OutSegs counter advance, across host connections.</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>ΔsystemMetrics/netstat/Tcp:EstabResets per second, in /s, at each available sample</t>
+          <t>ΔsystemMetrics/netstat/Tcp:RetransSegs ÷ ΔsystemMetrics/netstat/Tcp:OutSegs × 100, in %, at each available sample; minutes where the divisor sums to under 1000 are left out</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>each minute's ratio of sums</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>/s</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>none — read for its shape only</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr"/>
+          <t>low ≤0.1 (fading to 0.3) · moderate 0.3–0.7 (edges 0.1, 1) · high 1–2 (edges 0.7, 3) · very_high ≥3 (from 2)</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>0.2 % → 50% low, 50% moderate</t>
+        </is>
+      </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>shape only: a step, an episode, a schedule</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr"/>
+          <t>high or very_high</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>1 % or more</t>
+        </is>
+      </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>5 /s</t>
+          <t>0.5 %</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr"/>
@@ -3172,7 +3180,7 @@
       <c r="P28" s="4" t="n"/>
       <c r="Q28" s="4" t="inlineStr">
         <is>
-          <t>/s</t>
+          <t>%</t>
         </is>
       </c>
       <c r="R28" s="4" t="inlineStr">
@@ -3182,7 +3190,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>connections.created, net.retransmit</t>
+          <t>repl.member_lag, net.resets</t>
         </is>
       </c>
       <c r="T28" s="4" t="inlineStr"/>
@@ -3196,12 +3204,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>net.traffic</t>
+          <t>net.listen_overflows</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>mongod network traffic</t>
+          <t>Listen queue overflows</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -3211,12 +3219,12 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Sum of the server's bytesIn and bytesOut counter rates, scaled to MB/s.</t>
+          <t>Rate of the host TCP ListenOverflows counter; the counter does not identify a MongoDB connection or client outcome.</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Δ(serverStatus/network/bytesIn + serverStatus/network/bytesOut) per second × 1e-06, in MB/s, at each available sample</t>
+          <t>ΔsystemMetrics/netstat/TcpExt:ListenOverflows per second, in /s, at each available sample</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -3226,24 +3234,32 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>MB/s</t>
+          <t>/s</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>none — read for its shape only</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr"/>
+          <t>none ≤0.01 (fading to 0.1) · some 0.1–1 (edges 0.01, 5) · many ≥5 (from 1)</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>0.055 /s → 50% none, 50% some</t>
+        </is>
+      </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>shape only: a step, an episode, a schedule</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="inlineStr"/>
+          <t>many</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>0.1 /s or more</t>
+        </is>
+      </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>5 MB/s</t>
+          <t>0.1 /s</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr"/>
@@ -3255,7 +3271,7 @@
       <c r="P29" s="4" t="n"/>
       <c r="Q29" s="4" t="inlineStr">
         <is>
-          <t>MB/s</t>
+          <t>/s</t>
         </is>
       </c>
       <c r="R29" s="4" t="inlineStr">
@@ -3265,7 +3281,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>ops.total, net.retransmit</t>
+          <t>connections.created, cpu.busy_above_95</t>
         </is>
       </c>
       <c r="T29" s="4" t="inlineStr"/>
@@ -3274,17 +3290,17 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>files</t>
+          <t>network</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>files.handles</t>
+          <t>net.resets</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>File handles in use</t>
+          <t>TCP connections reset</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -3294,12 +3310,12 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>File handles allocated on the whole machine, every process together. FTDC does not record the kernel's limit (fs.file-max), so the bands are fixed reference counts, not a share of this host's limit; when the limit is reached the kernel refuses new files and sockets to every process. A climb that never comes back down is worth reading beside connections.</t>
+          <t>Established connections reset a second, host-wide.</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>systemMetrics/files/sys_file_handles_in_use, in handles, at each available sample</t>
+          <t>ΔsystemMetrics/netstat/Tcp:EstabResets per second, in /s, at each available sample</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -3309,32 +3325,24 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>handles</t>
+          <t>/s</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>normal ≤15000 (fading to 30000) · many 30000–60000 (edges 15000, 90000) · very_high ≥90000 (from 60000)</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>22500 handles → 50% normal, 50% many</t>
-        </is>
-      </c>
+          <t>none — read for its shape only</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr"/>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>very_high</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>60000 handles or more</t>
-        </is>
-      </c>
+          <t>shape only: a step, an episode, a schedule</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr"/>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>2000 handles</t>
+          <t>5 /s</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr"/>
@@ -3346,7 +3354,7 @@
       <c r="P30" s="4" t="n"/>
       <c r="Q30" s="4" t="inlineStr">
         <is>
-          <t>handles</t>
+          <t>/s</t>
         </is>
       </c>
       <c r="R30" s="4" t="inlineStr">
@@ -3356,7 +3364,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>connections.current</t>
+          <t>connections.created, net.retransmit</t>
         </is>
       </c>
       <c r="T30" s="4" t="inlineStr"/>
@@ -3365,67 +3373,59 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>admission</t>
+          <t>network</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.used</t>
+          <t>net.traffic</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Read tickets in use</t>
+          <t>mongod network traffic</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>before 8.0</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Read tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.</t>
+          <t>Sum of the server's bytesIn and bytesOut counter rates, scaled to MB/s.</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/concurrentTransactions/read/out ÷ serverStatus/wiredTiger/concurrentTransactions/read/totalTickets × 100, in %, at each available sample</t>
+          <t>Δ(serverStatus/network/bytesIn + serverStatus/network/bytesOut) per second × 1e-06, in MB/s, at each available sample</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>each minute's ratio of sums</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>MB/s</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>37.5 % → 50% low, 83% moderate</t>
-        </is>
-      </c>
+          <t>none — read for its shape only</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr"/>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>high or near_full</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>75 % or more</t>
-        </is>
-      </c>
+          <t>shape only: a step, an episode, a schedule</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr"/>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>10 %</t>
+          <t>5 MB/s</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr"/>
@@ -3437,7 +3437,7 @@
       <c r="P31" s="4" t="n"/>
       <c r="Q31" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>MB/s</t>
         </is>
       </c>
       <c r="R31" s="4" t="inlineStr">
@@ -3447,94 +3447,88 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.scarce, tickets.read.pool, tickets.read.wait, queue.readers</t>
+          <t>ops.total, net.retransmit</t>
         </is>
       </c>
       <c r="T31" s="4" t="inlineStr"/>
-      <c r="U31" s="4" t="inlineStr">
-        <is>
-          <t>From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.</t>
-        </is>
-      </c>
+      <c r="U31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>admission</t>
+          <t>files</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.scarce</t>
+          <t>files.handles</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Samples with under 10% of read tickets left</t>
+          <t>File handles in use</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>before 8.0</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which available read tickets were strictly below 10 % of the pool, normalized to a 60-second minute.</t>
+          <t>File handles allocated on the whole machine, every process together. FTDC does not record the kernel's limit (fs.file-max), so the bands are fixed reference counts, not a share of this host's limit; when the limit is reached the kernel refuses new files and sockets to every process. A climb that never comes back down is worth reading beside connections.</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/concurrentTransactions/read/available ÷ serverStatus/wiredTiger/concurrentTransactions/read/totalTickets × 100, in % available, at each available sample</t>
+          <t>systemMetrics/files/sys_file_handles_in_use, in handles, at each available sample</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>s/min</t>
+          <t>handles</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
+          <t>normal ≤15000 (fading to 30000) · many 30000–60000 (edges 15000, 90000) · very_high ≥90000 (from 60000)</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>0.5 s/min → 50% none, 50% brief</t>
+          <t>22500 handles → 50% normal, 50% many</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>brief and above (set by the rule)</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>1 s/min or more</t>
+          <t>60000 handles or more</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>3 s/min</t>
+          <t>2000 handles</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr"/>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>time_below</t>
-        </is>
-      </c>
-      <c r="P32" s="4" t="n">
-        <v>10</v>
-      </c>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P32" s="4" t="n"/>
       <c r="Q32" s="4" t="inlineStr">
         <is>
-          <t>% available</t>
+          <t>handles</t>
         </is>
       </c>
       <c r="R32" s="4" t="inlineStr">
@@ -3544,15 +3538,11 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.empty, tickets.read.used, tickets.read.pool, tickets.read.wait</t>
+          <t>connections.current</t>
         </is>
       </c>
       <c r="T32" s="4" t="inlineStr"/>
-      <c r="U32" s="4" t="inlineStr">
-        <is>
-          <t>From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.</t>
-        </is>
-      </c>
+      <c r="U32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -3562,12 +3552,12 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.empty</t>
+          <t>tickets.read.used</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Samples with no read ticket left</t>
+          <t>Read tickets in use</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -3577,61 +3567,59 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which fewer than 0.5 read tickets were available, that is none, normalized to a 60-second minute.</t>
+          <t>Read tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/concurrentTransactions/read/available, in tickets left, at each available sample</t>
+          <t>serverStatus/wiredTiger/concurrentTransactions/read/out ÷ serverStatus/wiredTiger/concurrentTransactions/read/totalTickets × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>each minute's ratio of sums</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>s/min</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
+          <t>low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>0.5 s/min → 50% none, 50% brief</t>
+          <t>37.5 % → 50% low, 83% moderate</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>brief and above (set by the rule)</t>
+          <t>high or near_full</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>1 s/min or more</t>
+          <t>75 % or more</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>3 s/min</t>
+          <t>10 %</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr"/>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>time_below</t>
-        </is>
-      </c>
-      <c r="P33" s="4" t="n">
-        <v>0.5</v>
-      </c>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P33" s="4" t="n"/>
       <c r="Q33" s="4" t="inlineStr">
         <is>
-          <t>tickets left</t>
+          <t>%</t>
         </is>
       </c>
       <c r="R33" s="4" t="inlineStr">
@@ -3641,7 +3629,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.used, tickets.read.scarce, tickets.read.pool, tickets.read.wait, queue.readers</t>
+          <t>tickets.read.scarce, tickets.read.pool, tickets.read.wait, queue.readers</t>
         </is>
       </c>
       <c r="T33" s="4" t="inlineStr"/>
@@ -3659,12 +3647,12 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.pool</t>
+          <t>tickets.read.scarce</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Read ticket pool size</t>
+          <t>Samples with under 10% of read tickets left</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -3674,51 +3662,61 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>How many read tickets the pool held, averaged over the minute.</t>
+          <t>Share of valid samples in which available read tickets were strictly below 10 % of the pool, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/concurrentTransactions/read/totalTickets, in tickets, at each available sample</t>
+          <t>serverStatus/wiredTiger/concurrentTransactions/read/available ÷ serverStatus/wiredTiger/concurrentTransactions/read/totalTickets × 100, in % available, at each available sample</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>tickets</t>
+          <t>s/min</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>none — read for its shape only</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr"/>
+          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>0.5 s/min → 50% none, 50% brief</t>
+        </is>
+      </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>shape only: a step, an episode, a schedule</t>
-        </is>
-      </c>
-      <c r="L34" s="4" t="inlineStr"/>
+          <t>brief and above (set by the rule)</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>1 s/min or more</t>
+        </is>
+      </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>4 tickets</t>
+          <t>3 s/min</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr"/>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="P34" s="4" t="n"/>
+          <t>time_below</t>
+        </is>
+      </c>
+      <c r="P34" s="4" t="n">
+        <v>10</v>
+      </c>
       <c r="Q34" s="4" t="inlineStr">
         <is>
-          <t>tickets</t>
+          <t>% available</t>
         </is>
       </c>
       <c r="R34" s="4" t="inlineStr">
@@ -3728,11 +3726,15 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.used, tickets.read.scarce</t>
+          <t>tickets.read.empty, tickets.read.used, tickets.read.pool, tickets.read.wait</t>
         </is>
       </c>
       <c r="T34" s="4" t="inlineStr"/>
-      <c r="U34" s="4" t="inlineStr"/>
+      <c r="U34" s="4" t="inlineStr">
+        <is>
+          <t>From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -3742,74 +3744,76 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.wait</t>
+          <t>tickets.read.empty</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Time waiting for a read ticket</t>
+          <t>Samples with no read ticket left</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>7.0 up to 8.0</t>
+          <t>before 8.0</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Milliseconds a second operations spent queued for a read ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it.</t>
+          <t>Share of valid samples in which fewer than 0.5 read tickets were available, that is none, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/wiredTiger/concurrentTransactions/read/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample</t>
+          <t>serverStatus/wiredTiger/concurrentTransactions/read/available, in tickets left, at each available sample</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>ms/s</t>
+          <t>s/min</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)</t>
+          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>5.5 ms/s → 50% none, 50% some</t>
+          <t>0.5 s/min → 50% none, 50% brief</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>brief and above (set by the rule)</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>100 ms/s or more</t>
+          <t>1 s/min or more</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>10 ms/s</t>
+          <t>3 s/min</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr"/>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="P35" s="4" t="n"/>
+          <t>time_below</t>
+        </is>
+      </c>
+      <c r="P35" s="4" t="n">
+        <v>0.5</v>
+      </c>
       <c r="Q35" s="4" t="inlineStr">
         <is>
-          <t>ms/s</t>
+          <t>tickets left</t>
         </is>
       </c>
       <c r="R35" s="4" t="inlineStr">
@@ -3819,11 +3823,15 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.empty, tickets.read.scarce, queue.readers</t>
+          <t>tickets.read.used, tickets.read.scarce, tickets.read.pool, tickets.read.wait, queue.readers</t>
         </is>
       </c>
       <c r="T35" s="4" t="inlineStr"/>
-      <c r="U35" s="4" t="inlineStr"/>
+      <c r="U35" s="4" t="inlineStr">
+        <is>
+          <t>From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -3833,62 +3841,54 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.used</t>
+          <t>tickets.read.pool</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Read tickets in use</t>
+          <t>Read ticket pool size</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>8.0 and later</t>
+          <t>before 8.0</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Read tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.</t>
+          <t>How many read tickets the pool held, averaged over the minute.</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/queues/execution/read/out ÷ serverStatus/queues/execution/read/totalTickets × 100, in %, at each available sample</t>
+          <t>serverStatus/wiredTiger/concurrentTransactions/read/totalTickets, in tickets, at each available sample</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>each minute's ratio of sums</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>tickets</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)</t>
-        </is>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>37.5 % → 50% low, 83% moderate</t>
-        </is>
-      </c>
+          <t>none — read for its shape only</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr"/>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>high or near_full</t>
-        </is>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>75 % or more</t>
-        </is>
-      </c>
+          <t>shape only: a step, an episode, a schedule</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr"/>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>10 %</t>
+          <t>4 tickets</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr"/>
@@ -3900,7 +3900,7 @@
       <c r="P36" s="4" t="n"/>
       <c r="Q36" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>tickets</t>
         </is>
       </c>
       <c r="R36" s="4" t="inlineStr">
@@ -3910,15 +3910,11 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.scarce, tickets.read.pool, tickets.read.wait, queue.readers</t>
+          <t>tickets.read.used, tickets.read.scarce</t>
         </is>
       </c>
       <c r="T36" s="4" t="inlineStr"/>
-      <c r="U36" s="4" t="inlineStr">
-        <is>
-          <t>From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.</t>
-        </is>
-      </c>
+      <c r="U36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -3928,76 +3924,74 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.scarce</t>
+          <t>tickets.read.wait</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Samples with under 10% of read tickets left</t>
+          <t>Time waiting for a read ticket</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>8.0 and later</t>
+          <t>7.0 up to 8.0</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which available read tickets were strictly below 10 % of the pool, normalized to a 60-second minute.</t>
+          <t>Milliseconds a second operations spent queued for a read ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it.</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/queues/execution/read/available ÷ serverStatus/queues/execution/read/totalTickets × 100, in % available, at each available sample</t>
+          <t>ΔserverStatus/wiredTiger/concurrentTransactions/read/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>s/min</t>
+          <t>ms/s</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
+          <t>none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>0.5 s/min → 50% none, 50% brief</t>
+          <t>5.5 ms/s → 50% none, 50% some</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>brief and above (set by the rule)</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>1 s/min or more</t>
+          <t>100 ms/s or more</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>3 s/min</t>
+          <t>10 ms/s</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr"/>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>time_below</t>
-        </is>
-      </c>
-      <c r="P37" s="4" t="n">
-        <v>10</v>
-      </c>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P37" s="4" t="n"/>
       <c r="Q37" s="4" t="inlineStr">
         <is>
-          <t>% available</t>
+          <t>ms/s</t>
         </is>
       </c>
       <c r="R37" s="4" t="inlineStr">
@@ -4007,15 +4001,11 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.empty, tickets.read.used, tickets.read.pool, tickets.read.wait</t>
+          <t>tickets.read.empty, tickets.read.scarce, queue.readers</t>
         </is>
       </c>
       <c r="T37" s="4" t="inlineStr"/>
-      <c r="U37" s="4" t="inlineStr">
-        <is>
-          <t>From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.</t>
-        </is>
-      </c>
+      <c r="U37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -4025,12 +4015,12 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.empty</t>
+          <t>tickets.read.used</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Samples with no read ticket left</t>
+          <t>Read tickets in use</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -4040,61 +4030,59 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which fewer than 0.5 read tickets were available, that is none, normalized to a 60-second minute.</t>
+          <t>Read tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/queues/execution/read/available, in tickets left, at each available sample</t>
+          <t>serverStatus/queues/execution/read/out ÷ serverStatus/queues/execution/read/totalTickets × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>each minute's ratio of sums</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>s/min</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
+          <t>low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>0.5 s/min → 50% none, 50% brief</t>
+          <t>37.5 % → 50% low, 83% moderate</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>brief and above (set by the rule)</t>
+          <t>high or near_full</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>1 s/min or more</t>
+          <t>75 % or more</t>
         </is>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>3 s/min</t>
+          <t>10 %</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr"/>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>time_below</t>
-        </is>
-      </c>
-      <c r="P38" s="4" t="n">
-        <v>0.5</v>
-      </c>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P38" s="4" t="n"/>
       <c r="Q38" s="4" t="inlineStr">
         <is>
-          <t>tickets left</t>
+          <t>%</t>
         </is>
       </c>
       <c r="R38" s="4" t="inlineStr">
@@ -4104,7 +4092,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.used, tickets.read.scarce, tickets.read.pool, tickets.read.wait, queue.readers</t>
+          <t>tickets.read.scarce, tickets.read.pool, tickets.read.wait, queue.readers</t>
         </is>
       </c>
       <c r="T38" s="4" t="inlineStr"/>
@@ -4122,12 +4110,12 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.pool</t>
+          <t>tickets.read.scarce</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Read ticket pool size</t>
+          <t>Samples with under 10% of read tickets left</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -4137,51 +4125,61 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>How many read tickets the pool held, averaged over the minute.</t>
+          <t>Share of valid samples in which available read tickets were strictly below 10 % of the pool, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/queues/execution/read/totalTickets, in tickets, at each available sample</t>
+          <t>serverStatus/queues/execution/read/available ÷ serverStatus/queues/execution/read/totalTickets × 100, in % available, at each available sample</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>tickets</t>
+          <t>s/min</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>none — read for its shape only</t>
-        </is>
-      </c>
-      <c r="J39" s="4" t="inlineStr"/>
+          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>0.5 s/min → 50% none, 50% brief</t>
+        </is>
+      </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>shape only: a step, an episode, a schedule</t>
-        </is>
-      </c>
-      <c r="L39" s="4" t="inlineStr"/>
+          <t>brief and above (set by the rule)</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>1 s/min or more</t>
+        </is>
+      </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>4 tickets</t>
+          <t>3 s/min</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr"/>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="P39" s="4" t="n"/>
+          <t>time_below</t>
+        </is>
+      </c>
+      <c r="P39" s="4" t="n">
+        <v>10</v>
+      </c>
       <c r="Q39" s="4" t="inlineStr">
         <is>
-          <t>tickets</t>
+          <t>% available</t>
         </is>
       </c>
       <c r="R39" s="4" t="inlineStr">
@@ -4191,11 +4189,15 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.used, tickets.read.scarce</t>
+          <t>tickets.read.empty, tickets.read.used, tickets.read.pool, tickets.read.wait</t>
         </is>
       </c>
       <c r="T39" s="4" t="inlineStr"/>
-      <c r="U39" s="4" t="inlineStr"/>
+      <c r="U39" s="4" t="inlineStr">
+        <is>
+          <t>From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -4205,12 +4207,12 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.wait</t>
+          <t>tickets.read.empty</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Time waiting for a read ticket</t>
+          <t>Samples with no read ticket left</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -4220,59 +4222,61 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Milliseconds a second operations spent queued for a read ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. The counter covers normal-priority operations, not exempt operations.</t>
+          <t>Share of valid samples in which fewer than 0.5 read tickets were available, that is none, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/queues/execution/read/normalPriority/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample</t>
+          <t>serverStatus/queues/execution/read/available, in tickets left, at each available sample</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>ms/s</t>
+          <t>s/min</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)</t>
+          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>5.5 ms/s → 50% none, 50% some</t>
+          <t>0.5 s/min → 50% none, 50% brief</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>brief and above (set by the rule)</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>100 ms/s or more</t>
+          <t>1 s/min or more</t>
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>10 ms/s</t>
+          <t>3 s/min</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr"/>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="P40" s="4" t="n"/>
+          <t>time_below</t>
+        </is>
+      </c>
+      <c r="P40" s="4" t="n">
+        <v>0.5</v>
+      </c>
       <c r="Q40" s="4" t="inlineStr">
         <is>
-          <t>ms/s</t>
+          <t>tickets left</t>
         </is>
       </c>
       <c r="R40" s="4" t="inlineStr">
@@ -4282,11 +4286,15 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.empty, tickets.read.scarce, queue.readers</t>
+          <t>tickets.read.used, tickets.read.scarce, tickets.read.pool, tickets.read.wait, queue.readers</t>
         </is>
       </c>
       <c r="T40" s="4" t="inlineStr"/>
-      <c r="U40" s="4" t="inlineStr"/>
+      <c r="U40" s="4" t="inlineStr">
+        <is>
+          <t>From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -4296,62 +4304,54 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.used</t>
+          <t>tickets.read.pool</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Write tickets in use</t>
+          <t>Read ticket pool size</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>before 8.0</t>
+          <t>8.0 and later</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Write tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.</t>
+          <t>How many read tickets the pool held, averaged over the minute.</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/concurrentTransactions/write/out ÷ serverStatus/wiredTiger/concurrentTransactions/write/totalTickets × 100, in %, at each available sample</t>
+          <t>serverStatus/queues/execution/read/totalTickets, in tickets, at each available sample</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>each minute's ratio of sums</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>tickets</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>37.5 % → 50% low, 83% moderate</t>
-        </is>
-      </c>
+          <t>none — read for its shape only</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr"/>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>high or near_full</t>
-        </is>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>75 % or more</t>
-        </is>
-      </c>
+          <t>shape only: a step, an episode, a schedule</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr"/>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>10 %</t>
+          <t>4 tickets</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr"/>
@@ -4363,7 +4363,7 @@
       <c r="P41" s="4" t="n"/>
       <c r="Q41" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>tickets</t>
         </is>
       </c>
       <c r="R41" s="4" t="inlineStr">
@@ -4373,15 +4373,11 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.scarce, tickets.write.pool, tickets.write.wait, queue.writers</t>
+          <t>tickets.read.used, tickets.read.scarce</t>
         </is>
       </c>
       <c r="T41" s="4" t="inlineStr"/>
-      <c r="U41" s="4" t="inlineStr">
-        <is>
-          <t>From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.</t>
-        </is>
-      </c>
+      <c r="U41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -4391,76 +4387,74 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.scarce</t>
+          <t>tickets.read.wait</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Samples with under 10% of write tickets left</t>
+          <t>Time waiting for a read ticket</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>before 8.0</t>
+          <t>8.0 and later</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which available write tickets were strictly below 10 % of the pool, normalized to a 60-second minute.</t>
+          <t>Milliseconds a second operations spent queued for a read ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. The counter covers normal-priority operations, not exempt operations.</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/concurrentTransactions/write/available ÷ serverStatus/wiredTiger/concurrentTransactions/write/totalTickets × 100, in % available, at each available sample</t>
+          <t>ΔserverStatus/queues/execution/read/normalPriority/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>s/min</t>
+          <t>ms/s</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
+          <t>none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>0.5 s/min → 50% none, 50% brief</t>
+          <t>5.5 ms/s → 50% none, 50% some</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>brief and above (set by the rule)</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>1 s/min or more</t>
+          <t>100 ms/s or more</t>
         </is>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>3 s/min</t>
+          <t>10 ms/s</t>
         </is>
       </c>
       <c r="N42" s="4" t="inlineStr"/>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>time_below</t>
-        </is>
-      </c>
-      <c r="P42" s="4" t="n">
-        <v>10</v>
-      </c>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P42" s="4" t="n"/>
       <c r="Q42" s="4" t="inlineStr">
         <is>
-          <t>% available</t>
+          <t>ms/s</t>
         </is>
       </c>
       <c r="R42" s="4" t="inlineStr">
@@ -4470,15 +4464,11 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.empty, tickets.write.used, tickets.write.pool, tickets.write.wait</t>
+          <t>tickets.read.empty, tickets.read.scarce, queue.readers</t>
         </is>
       </c>
       <c r="T42" s="4" t="inlineStr"/>
-      <c r="U42" s="4" t="inlineStr">
-        <is>
-          <t>From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.</t>
-        </is>
-      </c>
+      <c r="U42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -4488,12 +4478,12 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.empty</t>
+          <t>tickets.write.used</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Samples with no write ticket left</t>
+          <t>Write tickets in use</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -4503,61 +4493,59 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which fewer than 0.5 write tickets were available, that is none, normalized to a 60-second minute.</t>
+          <t>Write tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/concurrentTransactions/write/available, in tickets left, at each available sample</t>
+          <t>serverStatus/wiredTiger/concurrentTransactions/write/out ÷ serverStatus/wiredTiger/concurrentTransactions/write/totalTickets × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>each minute's ratio of sums</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>s/min</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
+          <t>low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>0.5 s/min → 50% none, 50% brief</t>
+          <t>37.5 % → 50% low, 83% moderate</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>brief and above (set by the rule)</t>
+          <t>high or near_full</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>1 s/min or more</t>
+          <t>75 % or more</t>
         </is>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>3 s/min</t>
+          <t>10 %</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr"/>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>time_below</t>
-        </is>
-      </c>
-      <c r="P43" s="4" t="n">
-        <v>0.5</v>
-      </c>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P43" s="4" t="n"/>
       <c r="Q43" s="4" t="inlineStr">
         <is>
-          <t>tickets left</t>
+          <t>%</t>
         </is>
       </c>
       <c r="R43" s="4" t="inlineStr">
@@ -4567,7 +4555,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.used, tickets.write.scarce, tickets.write.pool, tickets.write.wait, queue.writers</t>
+          <t>tickets.write.scarce, tickets.write.pool, tickets.write.wait, queue.writers</t>
         </is>
       </c>
       <c r="T43" s="4" t="inlineStr"/>
@@ -4585,12 +4573,12 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.pool</t>
+          <t>tickets.write.scarce</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Write ticket pool size</t>
+          <t>Samples with under 10% of write tickets left</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -4600,51 +4588,61 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>How many write tickets the pool held, averaged over the minute.</t>
+          <t>Share of valid samples in which available write tickets were strictly below 10 % of the pool, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/concurrentTransactions/write/totalTickets, in tickets, at each available sample</t>
+          <t>serverStatus/wiredTiger/concurrentTransactions/write/available ÷ serverStatus/wiredTiger/concurrentTransactions/write/totalTickets × 100, in % available, at each available sample</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>tickets</t>
+          <t>s/min</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>none — read for its shape only</t>
-        </is>
-      </c>
-      <c r="J44" s="4" t="inlineStr"/>
+          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>0.5 s/min → 50% none, 50% brief</t>
+        </is>
+      </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>shape only: a step, an episode, a schedule</t>
-        </is>
-      </c>
-      <c r="L44" s="4" t="inlineStr"/>
+          <t>brief and above (set by the rule)</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>1 s/min or more</t>
+        </is>
+      </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>4 tickets</t>
+          <t>3 s/min</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr"/>
       <c r="O44" s="4" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="P44" s="4" t="n"/>
+          <t>time_below</t>
+        </is>
+      </c>
+      <c r="P44" s="4" t="n">
+        <v>10</v>
+      </c>
       <c r="Q44" s="4" t="inlineStr">
         <is>
-          <t>tickets</t>
+          <t>% available</t>
         </is>
       </c>
       <c r="R44" s="4" t="inlineStr">
@@ -4654,11 +4652,15 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.used, tickets.write.scarce</t>
+          <t>tickets.write.empty, tickets.write.used, tickets.write.pool, tickets.write.wait</t>
         </is>
       </c>
       <c r="T44" s="4" t="inlineStr"/>
-      <c r="U44" s="4" t="inlineStr"/>
+      <c r="U44" s="4" t="inlineStr">
+        <is>
+          <t>From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -4668,74 +4670,76 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.wait</t>
+          <t>tickets.write.empty</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Time waiting for a write ticket</t>
+          <t>Samples with no write ticket left</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>7.0 up to 8.0</t>
+          <t>before 8.0</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Milliseconds a second operations spent queued for a write ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it.</t>
+          <t>Share of valid samples in which fewer than 0.5 write tickets were available, that is none, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/wiredTiger/concurrentTransactions/write/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample</t>
+          <t>serverStatus/wiredTiger/concurrentTransactions/write/available, in tickets left, at each available sample</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>ms/s</t>
+          <t>s/min</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)</t>
+          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>5.5 ms/s → 50% none, 50% some</t>
+          <t>0.5 s/min → 50% none, 50% brief</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>brief and above (set by the rule)</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>100 ms/s or more</t>
+          <t>1 s/min or more</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>10 ms/s</t>
+          <t>3 s/min</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr"/>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="P45" s="4" t="n"/>
+          <t>time_below</t>
+        </is>
+      </c>
+      <c r="P45" s="4" t="n">
+        <v>0.5</v>
+      </c>
       <c r="Q45" s="4" t="inlineStr">
         <is>
-          <t>ms/s</t>
+          <t>tickets left</t>
         </is>
       </c>
       <c r="R45" s="4" t="inlineStr">
@@ -4745,11 +4749,15 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.empty, tickets.write.scarce, queue.writers</t>
+          <t>tickets.write.used, tickets.write.scarce, tickets.write.pool, tickets.write.wait, queue.writers</t>
         </is>
       </c>
       <c r="T45" s="4" t="inlineStr"/>
-      <c r="U45" s="4" t="inlineStr"/>
+      <c r="U45" s="4" t="inlineStr">
+        <is>
+          <t>From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -4759,62 +4767,54 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.used</t>
+          <t>tickets.write.pool</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Write tickets in use</t>
+          <t>Write ticket pool size</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>8.0 and later</t>
+          <t>before 8.0</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Write tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.</t>
+          <t>How many write tickets the pool held, averaged over the minute.</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/queues/execution/write/out ÷ serverStatus/queues/execution/write/totalTickets × 100, in %, at each available sample</t>
+          <t>serverStatus/wiredTiger/concurrentTransactions/write/totalTickets, in tickets, at each available sample</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>each minute's ratio of sums</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>tickets</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)</t>
-        </is>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>37.5 % → 50% low, 83% moderate</t>
-        </is>
-      </c>
+          <t>none — read for its shape only</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr"/>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>high or near_full</t>
-        </is>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>75 % or more</t>
-        </is>
-      </c>
+          <t>shape only: a step, an episode, a schedule</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="inlineStr"/>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>10 %</t>
+          <t>4 tickets</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr"/>
@@ -4826,7 +4826,7 @@
       <c r="P46" s="4" t="n"/>
       <c r="Q46" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>tickets</t>
         </is>
       </c>
       <c r="R46" s="4" t="inlineStr">
@@ -4836,15 +4836,11 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.scarce, tickets.write.pool, tickets.write.wait, queue.writers</t>
+          <t>tickets.write.used, tickets.write.scarce</t>
         </is>
       </c>
       <c r="T46" s="4" t="inlineStr"/>
-      <c r="U46" s="4" t="inlineStr">
-        <is>
-          <t>From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.</t>
-        </is>
-      </c>
+      <c r="U46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -4854,76 +4850,74 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.scarce</t>
+          <t>tickets.write.wait</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Samples with under 10% of write tickets left</t>
+          <t>Time waiting for a write ticket</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>8.0 and later</t>
+          <t>7.0 up to 8.0</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which available write tickets were strictly below 10 % of the pool, normalized to a 60-second minute.</t>
+          <t>Milliseconds a second operations spent queued for a write ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it.</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/queues/execution/write/available ÷ serverStatus/queues/execution/write/totalTickets × 100, in % available, at each available sample</t>
+          <t>ΔserverStatus/wiredTiger/concurrentTransactions/write/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>s/min</t>
+          <t>ms/s</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
+          <t>none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>0.5 s/min → 50% none, 50% brief</t>
+          <t>5.5 ms/s → 50% none, 50% some</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>brief and above (set by the rule)</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>1 s/min or more</t>
+          <t>100 ms/s or more</t>
         </is>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>3 s/min</t>
+          <t>10 ms/s</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr"/>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>time_below</t>
-        </is>
-      </c>
-      <c r="P47" s="4" t="n">
-        <v>10</v>
-      </c>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P47" s="4" t="n"/>
       <c r="Q47" s="4" t="inlineStr">
         <is>
-          <t>% available</t>
+          <t>ms/s</t>
         </is>
       </c>
       <c r="R47" s="4" t="inlineStr">
@@ -4933,15 +4927,11 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.empty, tickets.write.used, tickets.write.pool, tickets.write.wait</t>
+          <t>tickets.write.empty, tickets.write.scarce, queue.writers</t>
         </is>
       </c>
       <c r="T47" s="4" t="inlineStr"/>
-      <c r="U47" s="4" t="inlineStr">
-        <is>
-          <t>From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.</t>
-        </is>
-      </c>
+      <c r="U47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -4951,12 +4941,12 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.empty</t>
+          <t>tickets.write.used</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Samples with no write ticket left</t>
+          <t>Write tickets in use</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -4966,61 +4956,59 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which fewer than 0.5 write tickets were available, that is none, normalized to a 60-second minute.</t>
+          <t>Write tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/queues/execution/write/available, in tickets left, at each available sample</t>
+          <t>serverStatus/queues/execution/write/out ÷ serverStatus/queues/execution/write/totalTickets × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>each minute's ratio of sums</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>s/min</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
+          <t>low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>0.5 s/min → 50% none, 50% brief</t>
+          <t>37.5 % → 50% low, 83% moderate</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>brief and above (set by the rule)</t>
+          <t>high or near_full</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>1 s/min or more</t>
+          <t>75 % or more</t>
         </is>
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>3 s/min</t>
+          <t>10 %</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr"/>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t>time_below</t>
-        </is>
-      </c>
-      <c r="P48" s="4" t="n">
-        <v>0.5</v>
-      </c>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P48" s="4" t="n"/>
       <c r="Q48" s="4" t="inlineStr">
         <is>
-          <t>tickets left</t>
+          <t>%</t>
         </is>
       </c>
       <c r="R48" s="4" t="inlineStr">
@@ -5030,7 +5018,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.used, tickets.write.scarce, tickets.write.pool, tickets.write.wait, queue.writers</t>
+          <t>tickets.write.scarce, tickets.write.pool, tickets.write.wait, queue.writers</t>
         </is>
       </c>
       <c r="T48" s="4" t="inlineStr"/>
@@ -5048,12 +5036,12 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.pool</t>
+          <t>tickets.write.scarce</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Write ticket pool size</t>
+          <t>Samples with under 10% of write tickets left</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -5063,51 +5051,61 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>How many write tickets the pool held, averaged over the minute.</t>
+          <t>Share of valid samples in which available write tickets were strictly below 10 % of the pool, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/queues/execution/write/totalTickets, in tickets, at each available sample</t>
+          <t>serverStatus/queues/execution/write/available ÷ serverStatus/queues/execution/write/totalTickets × 100, in % available, at each available sample</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>tickets</t>
+          <t>s/min</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>none — read for its shape only</t>
-        </is>
-      </c>
-      <c r="J49" s="4" t="inlineStr"/>
+          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>0.5 s/min → 50% none, 50% brief</t>
+        </is>
+      </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>shape only: a step, an episode, a schedule</t>
-        </is>
-      </c>
-      <c r="L49" s="4" t="inlineStr"/>
+          <t>brief and above (set by the rule)</t>
+        </is>
+      </c>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>1 s/min or more</t>
+        </is>
+      </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>4 tickets</t>
+          <t>3 s/min</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr"/>
       <c r="O49" s="4" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="P49" s="4" t="n"/>
+          <t>time_below</t>
+        </is>
+      </c>
+      <c r="P49" s="4" t="n">
+        <v>10</v>
+      </c>
       <c r="Q49" s="4" t="inlineStr">
         <is>
-          <t>tickets</t>
+          <t>% available</t>
         </is>
       </c>
       <c r="R49" s="4" t="inlineStr">
@@ -5117,11 +5115,15 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.used, tickets.write.scarce</t>
+          <t>tickets.write.empty, tickets.write.used, tickets.write.pool, tickets.write.wait</t>
         </is>
       </c>
       <c r="T49" s="4" t="inlineStr"/>
-      <c r="U49" s="4" t="inlineStr"/>
+      <c r="U49" s="4" t="inlineStr">
+        <is>
+          <t>From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -5131,12 +5133,12 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.wait</t>
+          <t>tickets.write.empty</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Time waiting for a write ticket</t>
+          <t>Samples with no write ticket left</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -5146,59 +5148,61 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Milliseconds a second operations spent queued for a write ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. The counter covers normal-priority operations, not exempt operations.</t>
+          <t>Share of valid samples in which fewer than 0.5 write tickets were available, that is none, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/queues/execution/write/normalPriority/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample</t>
+          <t>serverStatus/queues/execution/write/available, in tickets left, at each available sample</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>ms/s</t>
+          <t>s/min</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)</t>
+          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>5.5 ms/s → 50% none, 50% some</t>
+          <t>0.5 s/min → 50% none, 50% brief</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>brief and above (set by the rule)</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>100 ms/s or more</t>
+          <t>1 s/min or more</t>
         </is>
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>10 ms/s</t>
+          <t>3 s/min</t>
         </is>
       </c>
       <c r="N50" s="4" t="inlineStr"/>
       <c r="O50" s="4" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="P50" s="4" t="n"/>
+          <t>time_below</t>
+        </is>
+      </c>
+      <c r="P50" s="4" t="n">
+        <v>0.5</v>
+      </c>
       <c r="Q50" s="4" t="inlineStr">
         <is>
-          <t>ms/s</t>
+          <t>tickets left</t>
         </is>
       </c>
       <c r="R50" s="4" t="inlineStr">
@@ -5208,11 +5212,15 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.empty, tickets.write.scarce, queue.writers</t>
+          <t>tickets.write.used, tickets.write.scarce, tickets.write.pool, tickets.write.wait, queue.writers</t>
         </is>
       </c>
       <c r="T50" s="4" t="inlineStr"/>
-      <c r="U50" s="4" t="inlineStr"/>
+      <c r="U50" s="4" t="inlineStr">
+        <is>
+          <t>From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -5222,76 +5230,66 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>queue.readers</t>
+          <t>tickets.write.pool</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Samples with reads queued</t>
+          <t>Write ticket pool size</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>8.0 and later</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which globalLock.currentQueue.readers was above 0, normalized to a 60-second minute.</t>
+          <t>How many write tickets the pool held, averaged over the minute.</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/globalLock/currentQueue/readers, in operations, at each available sample</t>
+          <t>serverStatus/queues/execution/write/totalTickets, in tickets, at each available sample</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly above 0 operations, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>s/min</t>
+          <t>tickets</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
-        </is>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>0.5 s/min → 50% none, 50% brief</t>
-        </is>
-      </c>
+          <t>none — read for its shape only</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr"/>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>frequent or constant</t>
-        </is>
-      </c>
-      <c r="L51" s="4" t="inlineStr">
-        <is>
-          <t>1 s/min or more</t>
-        </is>
-      </c>
+          <t>shape only: a step, an episode, a schedule</t>
+        </is>
+      </c>
+      <c r="L51" s="4" t="inlineStr"/>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>3 s/min</t>
+          <t>4 tickets</t>
         </is>
       </c>
       <c r="N51" s="4" t="inlineStr"/>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>time_above</t>
-        </is>
-      </c>
-      <c r="P51" s="4" t="n">
-        <v>0</v>
-      </c>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P51" s="4" t="n"/>
       <c r="Q51" s="4" t="inlineStr">
         <is>
-          <t>operations</t>
+          <t>tickets</t>
         </is>
       </c>
       <c r="R51" s="4" t="inlineStr">
@@ -5301,7 +5299,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.empty, tickets.read.wait</t>
+          <t>tickets.write.used, tickets.write.scarce</t>
         </is>
       </c>
       <c r="T51" s="4" t="inlineStr"/>
@@ -5315,76 +5313,74 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>queue.writers</t>
+          <t>tickets.write.wait</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Samples with writes queued</t>
+          <t>Time waiting for a write ticket</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>8.0 and later</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which globalLock.currentQueue.writers was above 0, normalized to a 60-second minute.</t>
+          <t>Milliseconds a second operations spent queued for a write ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. The counter covers normal-priority operations, not exempt operations.</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/globalLock/currentQueue/writers, in operations, at each available sample</t>
+          <t>ΔserverStatus/queues/execution/write/normalPriority/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly above 0 operations, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>s/min</t>
+          <t>ms/s</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
+          <t>none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>0.5 s/min → 50% none, 50% brief</t>
+          <t>5.5 ms/s → 50% none, 50% some</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>frequent or constant</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>1 s/min or more</t>
+          <t>100 ms/s or more</t>
         </is>
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>3 s/min</t>
+          <t>10 ms/s</t>
         </is>
       </c>
       <c r="N52" s="4" t="inlineStr"/>
       <c r="O52" s="4" t="inlineStr">
         <is>
-          <t>time_above</t>
-        </is>
-      </c>
-      <c r="P52" s="4" t="n">
-        <v>0</v>
-      </c>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P52" s="4" t="n"/>
       <c r="Q52" s="4" t="inlineStr">
         <is>
-          <t>operations</t>
+          <t>ms/s</t>
         </is>
       </c>
       <c r="R52" s="4" t="inlineStr">
@@ -5394,7 +5390,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.empty, tickets.write.wait</t>
+          <t>tickets.write.empty, tickets.write.scarce, queue.writers</t>
         </is>
       </c>
       <c r="T52" s="4" t="inlineStr"/>
@@ -5403,17 +5399,17 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>storage-engine</t>
+          <t>admission</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>cache.fill</t>
+          <t>queue.readers</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>WiredTiger cache fill</t>
+          <t>Samples with reads queued</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -5423,59 +5419,61 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Bytes in the WiredTiger cache as a share of its configured size, averaged over the minute.</t>
+          <t>Share of valid samples in which globalLock.currentQueue.readers was above 0, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/cache/bytes currently in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample</t>
+          <t>serverStatus/globalLock/currentQueue/readers, in operations, at each available sample</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>each minute's ratio of sums</t>
+          <t>valid-sample share strictly above 0 operations, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>s/min</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>low ≤50 (fading to 70) · normal 70–80 (edges 50, 86) · high 86–93 (edges 80, 95) · above_reference ≥96 (from 94)</t>
+          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>60 % → 50% low, 50% normal</t>
+          <t>0.5 s/min → 50% none, 50% brief</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>high or above_reference</t>
+          <t>frequent or constant</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>95 % or more</t>
+          <t>1 s/min or more</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>5 %</t>
+          <t>3 s/min</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr"/>
       <c r="O53" s="4" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="P53" s="4" t="n"/>
+          <t>time_above</t>
+        </is>
+      </c>
+      <c r="P53" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Q53" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="R53" s="4" t="inlineStr">
@@ -5485,30 +5483,26 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>cache.fill_above_95, cache.app_eviction, cache.read_in</t>
-        </is>
-      </c>
-      <c r="T53" s="4" t="inlineStr">
-        <is>
-          <t>95 %: WiredTiger default eviction_trigger; eviction_target defaults to 80 (configured value not read)</t>
-        </is>
-      </c>
+          <t>tickets.read.empty, tickets.read.wait</t>
+        </is>
+      </c>
+      <c r="T53" s="4" t="inlineStr"/>
       <c r="U53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>storage-engine</t>
+          <t>admission</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>cache.fill_above_95</t>
+          <t>queue.writers</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Cache-fill samples above 95%</t>
+          <t>Samples with writes queued</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -5518,17 +5512,17 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which WiredTiger cache bytes were strictly above 95 % of the configured cache size, normalized to a 60-second minute.</t>
+          <t>Share of valid samples in which globalLock.currentQueue.writers was above 0, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/cache/bytes currently in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample</t>
+          <t>serverStatus/globalLock/currentQueue/writers, in operations, at each available sample</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly above 95 %, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>valid-sample share strictly above 0 operations, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -5568,11 +5562,11 @@
         </is>
       </c>
       <c r="P54" s="4" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="Q54" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="R54" s="4" t="inlineStr">
@@ -5582,14 +5576,10 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>cache.fill, cache.app_eviction, tickets.read.scarce</t>
-        </is>
-      </c>
-      <c r="T54" s="4" t="inlineStr">
-        <is>
-          <t>95 %: WiredTiger default eviction_trigger (configured value not read)</t>
-        </is>
-      </c>
+          <t>tickets.write.empty, tickets.write.wait</t>
+        </is>
+      </c>
+      <c r="T54" s="4" t="inlineStr"/>
       <c r="U54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
@@ -5600,12 +5590,12 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>cache.dirty</t>
+          <t>cache.fill</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>WiredTiger dirty cache</t>
+          <t>WiredTiger cache fill</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -5615,12 +5605,12 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Modified bytes not yet written, as a share of the configured cache, averaged over the minute.</t>
+          <t>Bytes in the WiredTiger cache as a share of its configured size, averaged over the minute.</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/cache/tracked dirty bytes in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample</t>
+          <t>serverStatus/wiredTiger/cache/bytes currently in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
@@ -5635,12 +5625,12 @@
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>low ≤3 (fading to 6) · normal 6–8 (edges 3, 12) · high 12–18 (edges 8, 20) · above_reference ≥21 (from 19)</t>
+          <t>low ≤50 (fading to 70) · normal 70–80 (edges 50, 86) · high 86–93 (edges 80, 95) · above_reference ≥96 (from 94)</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>4.5 % → 50% low, 50% normal</t>
+          <t>60 % → 50% low, 50% normal</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
@@ -5650,12 +5640,12 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>20 % or more</t>
+          <t>95 % or more</t>
         </is>
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>3 %</t>
+          <t>5 %</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr"/>
@@ -5677,12 +5667,12 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>cache.dirty_above_20, checkpoint.duration, disk.write_await, ops.writes</t>
+          <t>cache.fill_above_95, cache.app_eviction, cache.read_in</t>
         </is>
       </c>
       <c r="T55" s="4" t="inlineStr">
         <is>
-          <t>20 %: WiredTiger default eviction_dirty_trigger; eviction_dirty_target defaults to 5 (configured value not read)</t>
+          <t>95 %: WiredTiger default eviction_trigger; eviction_target defaults to 80 (configured value not read)</t>
         </is>
       </c>
       <c r="U55" s="4" t="inlineStr"/>
@@ -5695,12 +5685,12 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>cache.dirty_above_20</t>
+          <t>cache.fill_above_95</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Dirty-cache samples above 20%</t>
+          <t>Cache-fill samples above 95%</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -5710,17 +5700,17 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which tracked dirty bytes were strictly above 20 % of the configured cache size, normalized to a 60-second minute.</t>
+          <t>Share of valid samples in which WiredTiger cache bytes were strictly above 95 % of the configured cache size, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/cache/tracked dirty bytes in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample</t>
+          <t>serverStatus/wiredTiger/cache/bytes currently in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly above 20 %, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>valid-sample share strictly above 95 %, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -5760,7 +5750,7 @@
         </is>
       </c>
       <c r="P56" s="4" t="n">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="Q56" s="4" t="inlineStr">
         <is>
@@ -5774,12 +5764,12 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>cache.dirty, checkpoint.running, tickets.write.scarce</t>
+          <t>cache.fill, cache.app_eviction, tickets.read.scarce</t>
         </is>
       </c>
       <c r="T56" s="4" t="inlineStr">
         <is>
-          <t>20 %: WiredTiger default eviction_dirty_trigger (configured value not read)</t>
+          <t>95 %: WiredTiger default eviction_trigger (configured value not read)</t>
         </is>
       </c>
       <c r="U56" s="4" t="inlineStr"/>
@@ -5792,62 +5782,62 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>cache.app_eviction</t>
+          <t>cache.dirty</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Eviction by application threads</t>
+          <t>WiredTiger dirty cache</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>before 8.0.16</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Rate of pages evicted by application threads; where the version uses attempts and failures, the signal subtracts failure counts from attempt counts.</t>
+          <t>Modified bytes not yet written, as a share of the configured cache, averaged over the minute.</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/wiredTiger/cache/pages evicted by application threads per second, in pages/s, at each available sample</t>
+          <t>serverStatus/wiredTiger/cache/tracked dirty bytes in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>each minute's ratio of sums</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>pages/s</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>none ≤0.1 (fading to 1) · some 1–10 (edges 0.1, 50) · heavy ≥50 (from 10)</t>
+          <t>low ≤3 (fading to 6) · normal 6–8 (edges 3, 12) · high 12–18 (edges 8, 20) · above_reference ≥21 (from 19)</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>0.55 pages/s → 50% none, 50% some</t>
+          <t>4.5 % → 50% low, 50% normal</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>high or above_reference</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>1 pages/s or more</t>
+          <t>20 % or more</t>
         </is>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>5 pages/s</t>
+          <t>3 %</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr"/>
@@ -5859,7 +5849,7 @@
       <c r="P57" s="4" t="n"/>
       <c r="Q57" s="4" t="inlineStr">
         <is>
-          <t>pages/s</t>
+          <t>%</t>
         </is>
       </c>
       <c r="R57" s="4" t="inlineStr">
@@ -5869,10 +5859,14 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>cache.fill_above_95, cache.dirty_above_20</t>
-        </is>
-      </c>
-      <c r="T57" s="4" t="inlineStr"/>
+          <t>cache.dirty_above_20, checkpoint.duration, disk.write_await, ops.writes</t>
+        </is>
+      </c>
+      <c r="T57" s="4" t="inlineStr">
+        <is>
+          <t>20 %: WiredTiger default eviction_dirty_trigger; eviction_dirty_target defaults to 5 (configured value not read)</t>
+        </is>
+      </c>
       <c r="U57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
@@ -5883,74 +5877,76 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>cache.app_eviction</t>
+          <t>cache.dirty_above_20</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Eviction by application threads</t>
+          <t>Dirty-cache samples above 20%</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>8.0.16 and later</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Rate of pages evicted by application threads; where the version uses attempts and failures, the signal subtracts failure counts from attempt counts.</t>
+          <t>Share of valid samples in which tracked dirty bytes were strictly above 20 % of the configured cache size, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/wiredTiger/cache/page evict attempts by application threads − serverStatus/wiredTiger/cache/page evict failures by application threads per second, in pages/s, at each available sample</t>
+          <t>serverStatus/wiredTiger/cache/tracked dirty bytes in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>valid-sample share strictly above 20 %, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>pages/s</t>
+          <t>s/min</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>none ≤0.1 (fading to 1) · some 1–10 (edges 0.1, 50) · heavy ≥50 (from 10)</t>
+          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>0.55 pages/s → 50% none, 50% some</t>
+          <t>0.5 s/min → 50% none, 50% brief</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>frequent or constant</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>1 pages/s or more</t>
+          <t>1 s/min or more</t>
         </is>
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>5 pages/s</t>
+          <t>3 s/min</t>
         </is>
       </c>
       <c r="N58" s="4" t="inlineStr"/>
       <c r="O58" s="4" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="P58" s="4" t="n"/>
+          <t>time_above</t>
+        </is>
+      </c>
+      <c r="P58" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="Q58" s="4" t="inlineStr">
         <is>
-          <t>pages/s</t>
+          <t>%</t>
         </is>
       </c>
       <c r="R58" s="4" t="inlineStr">
@@ -5960,10 +5956,14 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>cache.fill_above_95, cache.dirty_above_20, cache.app_eviction_time</t>
-        </is>
-      </c>
-      <c r="T58" s="4" t="inlineStr"/>
+          <t>cache.dirty, checkpoint.running, tickets.write.scarce</t>
+        </is>
+      </c>
+      <c r="T58" s="4" t="inlineStr">
+        <is>
+          <t>20 %: WiredTiger default eviction_dirty_trigger (configured value not read)</t>
+        </is>
+      </c>
       <c r="U58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
@@ -5974,27 +5974,27 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>cache.app_eviction_time</t>
+          <t>cache.app_eviction</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Time operations spent evicting</t>
+          <t>Eviction by application threads</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>8.0 and later</t>
+          <t>before 8.0.16</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Application-thread eviction time counter advance per elapsed second, summed across threads, in milliseconds.</t>
+          <t>Rate of pages evicted by application threads; where the version uses attempts and failures, the signal subtracts failure counts from attempt counts.</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/wiredTiger/cache/application thread time evicting (usecs) per second × 0.001, in ms/s, at each available sample</t>
+          <t>ΔserverStatus/wiredTiger/cache/pages evicted by application threads per second, in pages/s, at each available sample</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
@@ -6004,17 +6004,17 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>ms/s</t>
+          <t>pages/s</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)</t>
+          <t>none ≤0.1 (fading to 1) · some 1–10 (edges 0.1, 50) · heavy ≥50 (from 10)</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>5.5 ms/s → 50% none, 50% some</t>
+          <t>0.55 pages/s → 50% none, 50% some</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
@@ -6024,12 +6024,12 @@
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>100 ms/s or more</t>
+          <t>1 pages/s or more</t>
         </is>
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>10 ms/s</t>
+          <t>5 pages/s</t>
         </is>
       </c>
       <c r="N59" s="4" t="inlineStr"/>
@@ -6041,7 +6041,7 @@
       <c r="P59" s="4" t="n"/>
       <c r="Q59" s="4" t="inlineStr">
         <is>
-          <t>ms/s</t>
+          <t>pages/s</t>
         </is>
       </c>
       <c r="R59" s="4" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>cache.app_eviction, cache.fill_above_95, cache.dirty_above_20</t>
+          <t>cache.fill_above_95, cache.dirty_above_20</t>
         </is>
       </c>
       <c r="T59" s="4" t="inlineStr"/>
@@ -6065,27 +6065,27 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>cache.read_in</t>
+          <t>cache.app_eviction</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Data read into the cache</t>
+          <t>Eviction by application threads</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>8.0.16 and later</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>WiredTiger bytes-read-into-cache counter advance per elapsed second, scaled to MB/s.</t>
+          <t>Rate of pages evicted by application threads; where the version uses attempts and failures, the signal subtracts failure counts from attempt counts.</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/wiredTiger/cache/bytes read into cache per second × 1e-06, in MB/s, at each available sample</t>
+          <t>ΔserverStatus/wiredTiger/cache/page evict attempts by application threads − serverStatus/wiredTiger/cache/page evict failures by application threads per second, in pages/s, at each available sample</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
@@ -6095,24 +6095,32 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>MB/s</t>
+          <t>pages/s</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>none — read for its shape only</t>
-        </is>
-      </c>
-      <c r="J60" s="4" t="inlineStr"/>
+          <t>none ≤0.1 (fading to 1) · some 1–10 (edges 0.1, 50) · heavy ≥50 (from 10)</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>0.55 pages/s → 50% none, 50% some</t>
+        </is>
+      </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>shape only: a step, an episode, a schedule</t>
-        </is>
-      </c>
-      <c r="L60" s="4" t="inlineStr"/>
+          <t>heavy</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>1 pages/s or more</t>
+        </is>
+      </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>5 MB/s</t>
+          <t>5 pages/s</t>
         </is>
       </c>
       <c r="N60" s="4" t="inlineStr"/>
@@ -6124,7 +6132,7 @@
       <c r="P60" s="4" t="n"/>
       <c r="Q60" s="4" t="inlineStr">
         <is>
-          <t>MB/s</t>
+          <t>pages/s</t>
         </is>
       </c>
       <c r="R60" s="4" t="inlineStr">
@@ -6134,7 +6142,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>disk.read_await, query.collscans, cache.fill</t>
+          <t>cache.fill_above_95, cache.dirty_above_20, cache.app_eviction_time</t>
         </is>
       </c>
       <c r="T60" s="4" t="inlineStr"/>
@@ -6148,74 +6156,74 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>checkpoint.duration</t>
+          <t>cache.app_eviction_time</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Checkpoint duration</t>
+          <t>Time operations spent evicting</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>before 7.1</t>
+          <t>8.0 and later</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Duration recorded for the most recent WiredTiger checkpoint; the same completed-checkpoint value may appear in multiple samples. Minute summaries select the highest valid sample.</t>
+          <t>Application-thread eviction time counter advance per elapsed second, summed across threads, in milliseconds.</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/transaction/transaction checkpoint most recent time (msecs) × 0.001, in s, at each available sample</t>
+          <t>ΔserverStatus/wiredTiger/cache/application thread time evicting (usecs) per second × 0.001, in ms/s, at each available sample</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>the highest valid sample of each minute</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>ms/s</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>quick ≤5 (fading to 15) · slow 15–40 (edges 5, 60) · back_to_back ≥60 (from 50)</t>
+          <t>none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>10 s → 50% quick, 50% slow</t>
+          <t>5.5 ms/s → 50% none, 50% some</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>back_to_back</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>60 s or more</t>
+          <t>100 ms/s or more</t>
         </is>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>10 s</t>
+          <t>10 ms/s</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr"/>
       <c r="O61" s="4" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="P61" s="4" t="n"/>
       <c r="Q61" s="4" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>ms/s</t>
         </is>
       </c>
       <c r="R61" s="4" t="inlineStr">
@@ -6225,14 +6233,10 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>checkpoint.running, cache.dirty, disk.write_await</t>
-        </is>
-      </c>
-      <c r="T61" s="4" t="inlineStr">
-        <is>
-          <t>60 s: default checkpoint interval, storage.syncPeriodSecs (configured value not read)</t>
-        </is>
-      </c>
+          <t>cache.app_eviction, cache.fill_above_95, cache.dirty_above_20</t>
+        </is>
+      </c>
+      <c r="T61" s="4" t="inlineStr"/>
       <c r="U61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
@@ -6243,74 +6247,66 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>checkpoint.duration</t>
+          <t>cache.read_in</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Checkpoint duration</t>
+          <t>Data read into the cache</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>7.1 and later</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Duration recorded for the most recent WiredTiger checkpoint; the same completed-checkpoint value may appear in multiple samples. Minute summaries select the highest valid sample.</t>
+          <t>WiredTiger bytes-read-into-cache counter advance per elapsed second, scaled to MB/s.</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/checkpoint/most recent time (msecs) × 0.001, in s, at each available sample</t>
+          <t>ΔserverStatus/wiredTiger/cache/bytes read into cache per second × 1e-06, in MB/s, at each available sample</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>the highest valid sample of each minute</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>MB/s</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>quick ≤5 (fading to 15) · slow 15–40 (edges 5, 60) · back_to_back ≥60 (from 50)</t>
-        </is>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>10 s → 50% quick, 50% slow</t>
-        </is>
-      </c>
+          <t>none — read for its shape only</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr"/>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>back_to_back</t>
-        </is>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>60 s or more</t>
-        </is>
-      </c>
+          <t>shape only: a step, an episode, a schedule</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="inlineStr"/>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>10 s</t>
+          <t>5 MB/s</t>
         </is>
       </c>
       <c r="N62" s="4" t="inlineStr"/>
       <c r="O62" s="4" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="P62" s="4" t="n"/>
       <c r="Q62" s="4" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>MB/s</t>
         </is>
       </c>
       <c r="R62" s="4" t="inlineStr">
@@ -6320,14 +6316,10 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>checkpoint.running, cache.dirty, disk.write_await</t>
-        </is>
-      </c>
-      <c r="T62" s="4" t="inlineStr">
-        <is>
-          <t>60 s: default checkpoint interval, storage.syncPeriodSecs (configured value not read)</t>
-        </is>
-      </c>
+          <t>disk.read_await, query.collscans, cache.fill</t>
+        </is>
+      </c>
+      <c r="T62" s="4" t="inlineStr"/>
       <c r="U62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
@@ -6338,12 +6330,12 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>checkpoint.running</t>
+          <t>checkpoint.duration</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Samples with checkpoint activity</t>
+          <t>Checkpoint duration</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -6353,61 +6345,59 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which WiredTiger reported a checkpoint as currently running, normalized to a 60-second minute.</t>
+          <t>Duration recorded for the most recent WiredTiger checkpoint; the same completed-checkpoint value may appear in multiple samples. Minute summaries select the highest valid sample.</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/transaction/transaction checkpoint currently running, in running, at each available sample</t>
+          <t>serverStatus/wiredTiger/transaction/transaction checkpoint most recent time (msecs) × 0.001, in s, at each available sample</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly above 0 running, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>the highest valid sample of each minute</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>s/min</t>
+          <t>s</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>brief ≤12 (fading to 24) · long 24–42 (edges 12, 54) · continuous ≥57 (from 48)</t>
+          <t>quick ≤5 (fading to 15) · slow 15–40 (edges 5, 60) · back_to_back ≥60 (from 50)</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>18 s/min → 50% brief, 50% long</t>
+          <t>10 s → 50% quick, 50% slow</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>continuous</t>
+          <t>back_to_back</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>48 s/min or more</t>
+          <t>60 s or more</t>
         </is>
       </c>
       <c r="M63" s="4" t="inlineStr">
         <is>
-          <t>9 s/min</t>
+          <t>10 s</t>
         </is>
       </c>
       <c r="N63" s="4" t="inlineStr"/>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>time_above</t>
-        </is>
-      </c>
-      <c r="P63" s="4" t="n">
-        <v>0</v>
-      </c>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="P63" s="4" t="n"/>
       <c r="Q63" s="4" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>s</t>
         </is>
       </c>
       <c r="R63" s="4" t="inlineStr">
@@ -6417,10 +6407,14 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>checkpoint.duration, disk.busy_above_95, cache.dirty</t>
-        </is>
-      </c>
-      <c r="T63" s="4" t="inlineStr"/>
+          <t>checkpoint.running, cache.dirty, disk.write_await</t>
+        </is>
+      </c>
+      <c r="T63" s="4" t="inlineStr">
+        <is>
+          <t>60 s: default checkpoint interval, storage.syncPeriodSecs (configured value not read)</t>
+        </is>
+      </c>
       <c r="U63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
@@ -6431,12 +6425,12 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>checkpoint.running</t>
+          <t>checkpoint.duration</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Samples with checkpoint activity</t>
+          <t>Checkpoint duration</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -6446,61 +6440,59 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which WiredTiger's checkpoint progress state was non-zero, normalized to a 60-second minute.</t>
+          <t>Duration recorded for the most recent WiredTiger checkpoint; the same completed-checkpoint value may appear in multiple samples. Minute summaries select the highest valid sample.</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/checkpoint/progress state, in state, at each available sample</t>
+          <t>serverStatus/wiredTiger/checkpoint/most recent time (msecs) × 0.001, in s, at each available sample</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly above 0 state, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>the highest valid sample of each minute</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>s/min</t>
+          <t>s</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>brief ≤12 (fading to 24) · long 24–42 (edges 12, 54) · continuous ≥57 (from 48)</t>
+          <t>quick ≤5 (fading to 15) · slow 15–40 (edges 5, 60) · back_to_back ≥60 (from 50)</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>18 s/min → 50% brief, 50% long</t>
+          <t>10 s → 50% quick, 50% slow</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>continuous</t>
+          <t>back_to_back</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>48 s/min or more</t>
+          <t>60 s or more</t>
         </is>
       </c>
       <c r="M64" s="4" t="inlineStr">
         <is>
-          <t>9 s/min</t>
+          <t>10 s</t>
         </is>
       </c>
       <c r="N64" s="4" t="inlineStr"/>
       <c r="O64" s="4" t="inlineStr">
         <is>
-          <t>time_above</t>
-        </is>
-      </c>
-      <c r="P64" s="4" t="n">
-        <v>0</v>
-      </c>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="P64" s="4" t="n"/>
       <c r="Q64" s="4" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>s</t>
         </is>
       </c>
       <c r="R64" s="4" t="inlineStr">
@@ -6510,15 +6502,15 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>checkpoint.duration, disk.busy_above_95, cache.dirty</t>
-        </is>
-      </c>
-      <c r="T64" s="4" t="inlineStr"/>
-      <c r="U64" s="4" t="inlineStr">
-        <is>
-          <t>The progress state's values are not decoded; any non-zero value is read as activity.</t>
-        </is>
-      </c>
+          <t>checkpoint.running, cache.dirty, disk.write_await</t>
+        </is>
+      </c>
+      <c r="T64" s="4" t="inlineStr">
+        <is>
+          <t>60 s: default checkpoint interval, storage.syncPeriodSecs (configured value not read)</t>
+        </is>
+      </c>
+      <c r="U64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -6528,66 +6520,76 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>storage.open_handles</t>
+          <t>checkpoint.running</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Open data handles</t>
+          <t>Samples with checkpoint activity</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>before 7.1</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Count reported by WiredTiger for currently open data handles.</t>
+          <t>Share of valid samples in which WiredTiger reported a checkpoint as currently running, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/wiredTiger/data-handle/connection data handles currently active, in handles, at each available sample</t>
+          <t>serverStatus/wiredTiger/transaction/transaction checkpoint currently running, in running, at each available sample</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>valid-sample share strictly above 0 running, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>handles</t>
+          <t>s/min</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>none — read for its shape only</t>
-        </is>
-      </c>
-      <c r="J65" s="4" t="inlineStr"/>
+          <t>brief ≤12 (fading to 24) · long 24–42 (edges 12, 54) · continuous ≥57 (from 48)</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>18 s/min → 50% brief, 50% long</t>
+        </is>
+      </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>shape only: a step, an episode, a schedule</t>
-        </is>
-      </c>
-      <c r="L65" s="4" t="inlineStr"/>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>48 s/min or more</t>
+        </is>
+      </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>500 handles</t>
+          <t>9 s/min</t>
         </is>
       </c>
       <c r="N65" s="4" t="inlineStr"/>
       <c r="O65" s="4" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="P65" s="4" t="n"/>
+          <t>time_above</t>
+        </is>
+      </c>
+      <c r="P65" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Q65" s="4" t="inlineStr">
         <is>
-          <t>handles</t>
+          <t>running</t>
         </is>
       </c>
       <c r="R65" s="4" t="inlineStr">
@@ -6595,86 +6597,92 @@
           <t>up</t>
         </is>
       </c>
-      <c r="S65" s="4" t="inlineStr"/>
+      <c r="S65" s="4" t="inlineStr">
+        <is>
+          <t>checkpoint.duration, disk.busy_above_95, cache.dirty</t>
+        </is>
+      </c>
       <c r="T65" s="4" t="inlineStr"/>
       <c r="U65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>workload</t>
+          <t>storage-engine</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>latency.reads</t>
+          <t>checkpoint.running</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Read latency</t>
+          <t>Samples with checkpoint activity</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>7.1 and later</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Average milliseconds per read operation over each minute, from opLatencies: every microsecond spent on reads in the minute over every read that finished in it.</t>
+          <t>Share of valid samples in which WiredTiger's checkpoint progress state was non-zero, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/opLatencies/reads/latency ÷ ΔserverStatus/opLatencies/reads/ops × 0.001, in ms, at each available sample; minutes where the divisor sums to under 60 are left out</t>
+          <t>serverStatus/wiredTiger/checkpoint/progress state, in state, at each available sample</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>each minute's ratio of sums</t>
+          <t>valid-sample share strictly above 0 state, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>ms</t>
+          <t>s/min</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>fast ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · slow 20–50 (edges 10, 100) · very_slow ≥100 (from 50)</t>
+          <t>brief ≤12 (fading to 24) · long 24–42 (edges 12, 54) · continuous ≥57 (from 48)</t>
         </is>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>2 ms → 50% fast, 50% normal</t>
+          <t>18 s/min → 50% brief, 50% long</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>slow or very_slow</t>
+          <t>continuous</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>50 ms or more</t>
+          <t>48 s/min or more</t>
         </is>
       </c>
       <c r="M66" s="4" t="inlineStr">
         <is>
-          <t>5 ms</t>
+          <t>9 s/min</t>
         </is>
       </c>
       <c r="N66" s="4" t="inlineStr"/>
       <c r="O66" s="4" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="P66" s="4" t="n"/>
+          <t>time_above</t>
+        </is>
+      </c>
+      <c r="P66" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Q66" s="4" t="inlineStr">
         <is>
-          <t>ms</t>
+          <t>state</t>
         </is>
       </c>
       <c r="R66" s="4" t="inlineStr">
@@ -6684,26 +6692,30 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.scarce, query.targeting, cache.fill_above_95, disk.read_await</t>
+          <t>checkpoint.duration, disk.busy_above_95, cache.dirty</t>
         </is>
       </c>
       <c r="T66" s="4" t="inlineStr"/>
-      <c r="U66" s="4" t="inlineStr"/>
+      <c r="U66" s="4" t="inlineStr">
+        <is>
+          <t>The progress state's values are not decoded; any non-zero value is read as activity.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>workload</t>
+          <t>storage-engine</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>latency.writes</t>
+          <t>storage.open_handles</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Write latency</t>
+          <t>Open data handles</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -6713,47 +6725,39 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Average milliseconds per write operation over each minute, from opLatencies.</t>
+          <t>Count reported by WiredTiger for currently open data handles.</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/opLatencies/writes/latency ÷ ΔserverStatus/opLatencies/writes/ops × 0.001, in ms, at each available sample; minutes where the divisor sums to under 60 are left out</t>
+          <t>serverStatus/wiredTiger/data-handle/connection data handles currently active, in handles, at each available sample</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>each minute's ratio of sums</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>ms</t>
+          <t>handles</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>fast ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · slow 20–50 (edges 10, 100) · very_slow ≥100 (from 50)</t>
-        </is>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>2 ms → 50% fast, 50% normal</t>
-        </is>
-      </c>
+          <t>none — read for its shape only</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr"/>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>slow or very_slow</t>
-        </is>
-      </c>
-      <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t>50 ms or more</t>
-        </is>
-      </c>
+          <t>shape only: a step, an episode, a schedule</t>
+        </is>
+      </c>
+      <c r="L67" s="4" t="inlineStr"/>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>5 ms</t>
+          <t>500 handles</t>
         </is>
       </c>
       <c r="N67" s="4" t="inlineStr"/>
@@ -6765,7 +6769,7 @@
       <c r="P67" s="4" t="n"/>
       <c r="Q67" s="4" t="inlineStr">
         <is>
-          <t>ms</t>
+          <t>handles</t>
         </is>
       </c>
       <c r="R67" s="4" t="inlineStr">
@@ -6773,11 +6777,7 @@
           <t>up</t>
         </is>
       </c>
-      <c r="S67" s="4" t="inlineStr">
-        <is>
-          <t>tickets.write.scarce, cache.dirty_above_20, flow.lagged, repl.majority_lag</t>
-        </is>
-      </c>
+      <c r="S67" s="4" t="inlineStr"/>
       <c r="T67" s="4" t="inlineStr"/>
       <c r="U67" s="4" t="inlineStr"/>
     </row>
@@ -6789,12 +6789,12 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>latency.commands</t>
+          <t>latency.reads</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Command latency</t>
+          <t>Read latency</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Ratio of command opLatencies counter advance to command operation-count advance, scaled to milliseconds per operation.</t>
+          <t>Average milliseconds per read operation over each minute, from opLatencies: every microsecond spent on reads in the minute over every read that finished in it.</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/opLatencies/commands/latency ÷ ΔserverStatus/opLatencies/commands/ops × 0.001, in ms, at each available sample; minutes where the divisor sums to under 60 are left out</t>
+          <t>ΔserverStatus/opLatencies/reads/latency ÷ ΔserverStatus/opLatencies/reads/ops × 0.001, in ms, at each available sample; minutes where the divisor sums to under 60 are left out</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.scarce, query.targeting</t>
+          <t>tickets.read.scarce, query.targeting, cache.fill_above_95, disk.read_await</t>
         </is>
       </c>
       <c r="T68" s="4" t="inlineStr"/>
@@ -6880,12 +6880,12 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>ops.total</t>
+          <t>latency.writes</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Operations a second</t>
+          <t>Write latency</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -6895,39 +6895,47 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Sum of query, getMore, insert, update, delete and command operation-counter rates.</t>
+          <t>Average milliseconds per write operation over each minute, from opLatencies.</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Δ(serverStatus/opcounters/query + serverStatus/opcounters/getmore + serverStatus/opcounters/insert + serverStatus/opcounters/update + serverStatus/opcounters/delete + serverStatus/opcounters/command) per second, in ops/s, at each available sample</t>
+          <t>ΔserverStatus/opLatencies/writes/latency ÷ ΔserverStatus/opLatencies/writes/ops × 0.001, in ms, at each available sample; minutes where the divisor sums to under 60 are left out</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>each minute's ratio of sums</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>ops/s</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>none — read for its shape only</t>
-        </is>
-      </c>
-      <c r="J69" s="4" t="inlineStr"/>
+          <t>fast ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · slow 20–50 (edges 10, 100) · very_slow ≥100 (from 50)</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>2 ms → 50% fast, 50% normal</t>
+        </is>
+      </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>shape only: a step, an episode, a schedule</t>
-        </is>
-      </c>
-      <c r="L69" s="4" t="inlineStr"/>
+          <t>slow or very_slow</t>
+        </is>
+      </c>
+      <c r="L69" s="4" t="inlineStr">
+        <is>
+          <t>50 ms or more</t>
+        </is>
+      </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>50 ops/s</t>
+          <t>5 ms</t>
         </is>
       </c>
       <c r="N69" s="4" t="inlineStr"/>
@@ -6939,7 +6947,7 @@
       <c r="P69" s="4" t="n"/>
       <c r="Q69" s="4" t="inlineStr">
         <is>
-          <t>ops/s</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="R69" s="4" t="inlineStr">
@@ -6949,7 +6957,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>ops.writes, connections.current</t>
+          <t>tickets.write.scarce, cache.dirty_above_20, flow.lagged, repl.majority_lag</t>
         </is>
       </c>
       <c r="T69" s="4" t="inlineStr"/>
@@ -6963,12 +6971,12 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>ops.writes</t>
+          <t>latency.commands</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Writes a second</t>
+          <t>Command latency</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -6978,39 +6986,47 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Sum of insert, update and delete operation-counter rates.</t>
+          <t>Ratio of command opLatencies counter advance to command operation-count advance, scaled to milliseconds per operation.</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>Δ(serverStatus/opcounters/insert + serverStatus/opcounters/update + serverStatus/opcounters/delete) per second, in ops/s, at each available sample</t>
+          <t>ΔserverStatus/opLatencies/commands/latency ÷ ΔserverStatus/opLatencies/commands/ops × 0.001, in ms, at each available sample; minutes where the divisor sums to under 60 are left out</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>each minute's ratio of sums</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>ops/s</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>none — read for its shape only</t>
-        </is>
-      </c>
-      <c r="J70" s="4" t="inlineStr"/>
+          <t>fast ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · slow 20–50 (edges 10, 100) · very_slow ≥100 (from 50)</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>2 ms → 50% fast, 50% normal</t>
+        </is>
+      </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>shape only: a step, an episode, a schedule</t>
-        </is>
-      </c>
-      <c r="L70" s="4" t="inlineStr"/>
+          <t>slow or very_slow</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>50 ms or more</t>
+        </is>
+      </c>
       <c r="M70" s="4" t="inlineStr">
         <is>
-          <t>50 ops/s</t>
+          <t>5 ms</t>
         </is>
       </c>
       <c r="N70" s="4" t="inlineStr"/>
@@ -7022,7 +7038,7 @@
       <c r="P70" s="4" t="n"/>
       <c r="Q70" s="4" t="inlineStr">
         <is>
-          <t>ops/s</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="R70" s="4" t="inlineStr">
@@ -7032,7 +7048,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>cache.dirty, checkpoint.duration</t>
+          <t>tickets.read.scarce, query.targeting</t>
         </is>
       </c>
       <c r="T70" s="4" t="inlineStr"/>
@@ -7046,12 +7062,12 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>query.targeting</t>
+          <t>ops.total</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Documents examined per document returned</t>
+          <t>Operations a second</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -7061,47 +7077,39 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Ratio of documents-examined counter advance to documents-returned counter advance; it does not determine index suitability.</t>
+          <t>Sum of query, getMore, insert, update, delete and command operation-counter rates.</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/metrics/queryExecutor/scannedObjects ÷ ΔserverStatus/metrics/document/returned, in ratio, at each available sample; minutes where the divisor sums to under 60 are left out</t>
+          <t>Δ(serverStatus/opcounters/query + serverStatus/opcounters/getmore + serverStatus/opcounters/insert + serverStatus/opcounters/update + serverStatus/opcounters/delete + serverStatus/opcounters/command) per second, in ops/s, at each available sample</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>each minute's ratio of sums</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>ops/s</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>low ≤2 (fading to 10) · moderate 10–50 (edges 2, 100) · high 100–500 (edges 50, 1000) · very_high ≥1000 (from 500)</t>
-        </is>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>6 ratio → 50% low, 50% moderate</t>
-        </is>
-      </c>
+          <t>none — read for its shape only</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr"/>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>high or very_high</t>
-        </is>
-      </c>
-      <c r="L71" s="4" t="inlineStr">
-        <is>
-          <t>100 ratio or more</t>
-        </is>
-      </c>
+          <t>shape only: a step, an episode, a schedule</t>
+        </is>
+      </c>
+      <c r="L71" s="4" t="inlineStr"/>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>10 ratio</t>
+          <t>50 ops/s</t>
         </is>
       </c>
       <c r="N71" s="4" t="inlineStr"/>
@@ -7113,7 +7121,7 @@
       <c r="P71" s="4" t="n"/>
       <c r="Q71" s="4" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>ops/s</t>
         </is>
       </c>
       <c r="R71" s="4" t="inlineStr">
@@ -7123,7 +7131,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>query.collscans, cache.read_in, cpu.busy</t>
+          <t>ops.writes, connections.current</t>
         </is>
       </c>
       <c r="T71" s="4" t="inlineStr"/>
@@ -7137,27 +7145,27 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>query.collscans</t>
+          <t>ops.writes</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Collection scans</t>
+          <t>Writes a second</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>4.4 and later</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Rate of the server's collection-scan counter.</t>
+          <t>Sum of insert, update and delete operation-counter rates.</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/metrics/queryExecutor/collectionScans/total per second, in /s, at each available sample</t>
+          <t>Δ(serverStatus/opcounters/insert + serverStatus/opcounters/update + serverStatus/opcounters/delete) per second, in ops/s, at each available sample</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
@@ -7167,32 +7175,24 @@
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>/s</t>
+          <t>ops/s</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>none ≤0.01 (fading to 0.1) · some 0.1–1 (edges 0.01, 10) · many ≥10 (from 1)</t>
-        </is>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>0.055 /s → 50% none, 50% some</t>
-        </is>
-      </c>
+          <t>none — read for its shape only</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr"/>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>many</t>
-        </is>
-      </c>
-      <c r="L72" s="4" t="inlineStr">
-        <is>
-          <t>1 /s or more</t>
-        </is>
-      </c>
+          <t>shape only: a step, an episode, a schedule</t>
+        </is>
+      </c>
+      <c r="L72" s="4" t="inlineStr"/>
       <c r="M72" s="4" t="inlineStr">
         <is>
-          <t>0.5 /s</t>
+          <t>50 ops/s</t>
         </is>
       </c>
       <c r="N72" s="4" t="inlineStr"/>
@@ -7204,7 +7204,7 @@
       <c r="P72" s="4" t="n"/>
       <c r="Q72" s="4" t="inlineStr">
         <is>
-          <t>/s</t>
+          <t>ops/s</t>
         </is>
       </c>
       <c r="R72" s="4" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>query.targeting, cache.read_in</t>
+          <t>cache.dirty, checkpoint.duration</t>
         </is>
       </c>
       <c r="T72" s="4" t="inlineStr"/>
@@ -7228,12 +7228,12 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>query.scan_and_order</t>
+          <t>query.targeting</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>scanAndOrder counter rate</t>
+          <t>Documents examined per document returned</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -7243,39 +7243,47 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Rate of the server's scanAndOrder counter.</t>
+          <t>Ratio of documents-examined counter advance to documents-returned counter advance; it does not determine index suitability.</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/metrics/operation/scanAndOrder per second, in /s, at each available sample</t>
+          <t>ΔserverStatus/metrics/queryExecutor/scannedObjects ÷ ΔserverStatus/metrics/document/returned, in ratio, at each available sample; minutes where the divisor sums to under 60 are left out</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>each minute's ratio of sums</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>/s</t>
+          <t>ratio</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>none — read for its shape only</t>
-        </is>
-      </c>
-      <c r="J73" s="4" t="inlineStr"/>
+          <t>low ≤2 (fading to 10) · moderate 10–50 (edges 2, 100) · high 100–500 (edges 50, 1000) · very_high ≥1000 (from 500)</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>6 ratio → 50% low, 50% moderate</t>
+        </is>
+      </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>shape only: a step, an episode, a schedule</t>
-        </is>
-      </c>
-      <c r="L73" s="4" t="inlineStr"/>
+          <t>high or very_high</t>
+        </is>
+      </c>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>100 ratio or more</t>
+        </is>
+      </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>1 /s</t>
+          <t>10 ratio</t>
         </is>
       </c>
       <c r="N73" s="4" t="inlineStr"/>
@@ -7287,7 +7295,7 @@
       <c r="P73" s="4" t="n"/>
       <c r="Q73" s="4" t="inlineStr">
         <is>
-          <t>/s</t>
+          <t>ratio</t>
         </is>
       </c>
       <c r="R73" s="4" t="inlineStr">
@@ -7297,7 +7305,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>query.targeting, memory.heap_outside_cache</t>
+          <t>query.collscans, cache.read_in, cpu.busy</t>
         </is>
       </c>
       <c r="T73" s="4" t="inlineStr"/>
@@ -7311,27 +7319,27 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>writes.conflicts</t>
+          <t>query.collscans</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Write conflicts</t>
+          <t>Collection scans</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>4.4 and later</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Rate of the server's writeConflicts counter; retries, document identity and contention cause are not inferred from this counter.</t>
+          <t>Rate of the server's collection-scan counter.</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/metrics/operation/writeConflicts per second, in /s, at each available sample</t>
+          <t>ΔserverStatus/metrics/queryExecutor/collectionScans/total per second, in /s, at each available sample</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -7346,27 +7354,27 @@
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>rare ≤0.1 (fading to 1) · some 1–10 (edges 0.1, 50) · heavy ≥50 (from 10)</t>
+          <t>none ≤0.01 (fading to 0.1) · some 0.1–1 (edges 0.01, 10) · many ≥10 (from 1)</t>
         </is>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>0.55 /s → 50% rare, 50% some</t>
+          <t>0.055 /s → 50% none, 50% some</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>many</t>
         </is>
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>10 /s or more</t>
+          <t>1 /s or more</t>
         </is>
       </c>
       <c r="M74" s="4" t="inlineStr">
         <is>
-          <t>2 /s</t>
+          <t>0.5 /s</t>
         </is>
       </c>
       <c r="N74" s="4" t="inlineStr"/>
@@ -7388,7 +7396,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>ops.writes, latency.writes</t>
+          <t>query.targeting, cache.read_in</t>
         </is>
       </c>
       <c r="T74" s="4" t="inlineStr"/>
@@ -7402,12 +7410,12 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>ttl.deletes</t>
+          <t>query.scan_and_order</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Documents deleted by TTL</t>
+          <t>scanAndOrder counter rate</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -7417,12 +7425,12 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Rate of documents reported deleted by the TTL monitor; collection identity, expiry backlog and latency impact are not inferred.</t>
+          <t>Rate of the server's scanAndOrder counter.</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/metrics/ttl/deletedDocuments per second, in docs/s, at each available sample</t>
+          <t>ΔserverStatus/metrics/operation/scanAndOrder per second, in /s, at each available sample</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
@@ -7432,7 +7440,7 @@
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>docs/s</t>
+          <t>/s</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -7449,7 +7457,7 @@
       <c r="L75" s="4" t="inlineStr"/>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>50 docs/s</t>
+          <t>1 /s</t>
         </is>
       </c>
       <c r="N75" s="4" t="inlineStr"/>
@@ -7461,7 +7469,7 @@
       <c r="P75" s="4" t="n"/>
       <c r="Q75" s="4" t="inlineStr">
         <is>
-          <t>docs/s</t>
+          <t>/s</t>
         </is>
       </c>
       <c r="R75" s="4" t="inlineStr">
@@ -7471,7 +7479,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>cache.dirty, disk.write_await, repl.member_lag</t>
+          <t>query.targeting, memory.heap_outside_cache</t>
         </is>
       </c>
       <c r="T75" s="4" t="inlineStr"/>
@@ -7485,12 +7493,12 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>cursors.open</t>
+          <t>writes.conflicts</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Open cursors</t>
+          <t>Write conflicts</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -7500,12 +7508,12 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Count reported for currently open cursors.</t>
+          <t>Rate of the server's writeConflicts counter; retries, document identity and contention cause are not inferred from this counter.</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/metrics/cursor/open/total, in cursors, at each available sample</t>
+          <t>ΔserverStatus/metrics/operation/writeConflicts per second, in /s, at each available sample</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
@@ -7515,24 +7523,32 @@
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>cursors</t>
+          <t>/s</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>none — read for its shape only</t>
-        </is>
-      </c>
-      <c r="J76" s="4" t="inlineStr"/>
+          <t>rare ≤0.1 (fading to 1) · some 1–10 (edges 0.1, 50) · heavy ≥50 (from 10)</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>0.55 /s → 50% rare, 50% some</t>
+        </is>
+      </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>shape only: a step, an episode, a schedule</t>
-        </is>
-      </c>
-      <c r="L76" s="4" t="inlineStr"/>
+          <t>heavy</t>
+        </is>
+      </c>
+      <c r="L76" s="4" t="inlineStr">
+        <is>
+          <t>10 /s or more</t>
+        </is>
+      </c>
       <c r="M76" s="4" t="inlineStr">
         <is>
-          <t>50 cursors</t>
+          <t>2 /s</t>
         </is>
       </c>
       <c r="N76" s="4" t="inlineStr"/>
@@ -7544,7 +7560,7 @@
       <c r="P76" s="4" t="n"/>
       <c r="Q76" s="4" t="inlineStr">
         <is>
-          <t>cursors</t>
+          <t>/s</t>
         </is>
       </c>
       <c r="R76" s="4" t="inlineStr">
@@ -7554,7 +7570,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>memory.heap_outside_cache, connections.current</t>
+          <t>ops.writes, latency.writes</t>
         </is>
       </c>
       <c r="T76" s="4" t="inlineStr"/>
@@ -7563,79 +7579,71 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>replication</t>
+          <t>workload</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>repl.member_lag</t>
+          <t>ttl.deletes</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Member replication lag</t>
+          <t>Documents deleted by TTL</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>before 6.0</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Difference between each member's reported applied-write timestamp and the newest such timestamp in this node's replica-set status, scaled to seconds. Members without a timestamp have no result. optimeDate has one-second resolution. Minute summaries select the highest valid sample.</t>
+          <t>Rate of documents reported deleted by the TTL monitor; collection identity, expiry backlog and latency impact are not inferred.</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>newest of every replSetGetStatus/members/{i}/optimeDate − this one × 0.001, in s, at each available sample</t>
+          <t>ΔserverStatus/metrics/ttl/deletedDocuments per second, in docs/s, at each available sample</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>the highest valid sample of each minute</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>docs/s</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>current ≤2 (fading to 5) · behind 5–20 (edges 2, 30) · lagging 30–120 (edges 20, 300) · far_behind ≥300 (from 120)</t>
-        </is>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>3.5 s → 50% current, 50% behind</t>
-        </is>
-      </c>
+          <t>none — read for its shape only</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr"/>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>lagging or far_behind</t>
-        </is>
-      </c>
-      <c r="L77" s="4" t="inlineStr">
-        <is>
-          <t>30 s or more</t>
-        </is>
-      </c>
+          <t>shape only: a step, an episode, a schedule</t>
+        </is>
+      </c>
+      <c r="L77" s="4" t="inlineStr"/>
       <c r="M77" s="4" t="inlineStr">
         <is>
-          <t>5 s</t>
+          <t>50 docs/s</t>
         </is>
       </c>
       <c r="N77" s="4" t="inlineStr"/>
       <c r="O77" s="4" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="P77" s="4" t="n"/>
       <c r="Q77" s="4" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>docs/s</t>
         </is>
       </c>
       <c r="R77" s="4" t="inlineStr">
@@ -7645,92 +7653,80 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>repl.majority_lag, flow.lagged, net.retransmit</t>
+          <t>cache.dirty, disk.write_await, repl.member_lag</t>
         </is>
       </c>
       <c r="T77" s="4" t="inlineStr"/>
-      <c r="U77" s="4" t="inlineStr">
-        <is>
-          <t>One result per entry of this node's replica-set status, numbered by position in that list; a position can name a different member after a reconfig. Lag is measured against the newest applied time among members, not against the primary, and a member that stopped reporting keeps its last time.</t>
-        </is>
-      </c>
+      <c r="U77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>replication</t>
+          <t>workload</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>repl.member_lag</t>
+          <t>cursors.open</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Member replication lag</t>
+          <t>Open cursors</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>6.0 and later</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Difference between each member's reported applied-write timestamp and the newest such timestamp in this node's replica-set status, scaled to seconds. Members without a timestamp have no result. Minute summaries select the highest valid sample.</t>
+          <t>Count reported for currently open cursors.</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>newest of every replSetGetStatus/members/{i}/lastAppliedWallTime − this one × 0.001, in s, at each available sample</t>
+          <t>serverStatus/metrics/cursor/open/total, in cursors, at each available sample</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>the highest valid sample of each minute</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>cursors</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>current ≤2 (fading to 5) · behind 5–20 (edges 2, 30) · lagging 30–120 (edges 20, 300) · far_behind ≥300 (from 120)</t>
-        </is>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>3.5 s → 50% current, 50% behind</t>
-        </is>
-      </c>
+          <t>none — read for its shape only</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr"/>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>lagging or far_behind</t>
-        </is>
-      </c>
-      <c r="L78" s="4" t="inlineStr">
-        <is>
-          <t>30 s or more</t>
-        </is>
-      </c>
+          <t>shape only: a step, an episode, a schedule</t>
+        </is>
+      </c>
+      <c r="L78" s="4" t="inlineStr"/>
       <c r="M78" s="4" t="inlineStr">
         <is>
-          <t>5 s</t>
+          <t>50 cursors</t>
         </is>
       </c>
       <c r="N78" s="4" t="inlineStr"/>
       <c r="O78" s="4" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="P78" s="4" t="n"/>
       <c r="Q78" s="4" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>cursors</t>
         </is>
       </c>
       <c r="R78" s="4" t="inlineStr">
@@ -7740,15 +7736,11 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>repl.majority_lag, flow.lagged, net.retransmit</t>
+          <t>memory.heap_outside_cache, connections.current</t>
         </is>
       </c>
       <c r="T78" s="4" t="inlineStr"/>
-      <c r="U78" s="4" t="inlineStr">
-        <is>
-          <t>One result per entry of this node's replica-set status, numbered by position in that list; a position can name a different member after a reconfig. Lag is measured against the newest applied time among members, not against the primary, and a member that stopped reporting keeps its last time.</t>
-        </is>
-      </c>
+      <c r="U78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -7758,27 +7750,27 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>repl.majority_lag</t>
+          <t>repl.member_lag</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Majority commit lag</t>
+          <t>Member replication lag</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>4.2 and later</t>
+          <t>before 6.0</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Difference between this node's lastAppliedWallTime and lastCommittedWallTime, scaled to seconds. Minute summaries select the highest valid sample. A sample with either time unset (zero) is left out.</t>
+          <t>Difference between each member's reported applied-write timestamp and the newest such timestamp in this node's replica-set status, scaled to seconds. Members without a timestamp have no result. optimeDate has one-second resolution. Minute summaries select the highest valid sample.</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>replSetGetStatus/optimes/lastAppliedWallTime − replSetGetStatus/optimes/lastCommittedWallTime × 0.001, in s, at each available sample</t>
+          <t>newest of every replSetGetStatus/members/{i}/optimeDate − this one × 0.001, in s, at each available sample</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
@@ -7793,27 +7785,27 @@
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>current ≤1 (fading to 3) · behind 3–10 (edges 1, 20) · lagging ≥20 (from 10)</t>
+          <t>current ≤2 (fading to 5) · behind 5–20 (edges 2, 30) · lagging 30–120 (edges 20, 300) · far_behind ≥300 (from 120)</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>2 s → 50% current, 50% behind</t>
+          <t>3.5 s → 50% current, 50% behind</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>lagging</t>
+          <t>lagging or far_behind</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>10 s or more</t>
+          <t>30 s or more</t>
         </is>
       </c>
       <c r="M79" s="4" t="inlineStr">
         <is>
-          <t>2 s</t>
+          <t>5 s</t>
         </is>
       </c>
       <c r="N79" s="4" t="inlineStr"/>
@@ -7835,11 +7827,15 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>repl.member_lag, flow.lagged, latency.writes</t>
+          <t>repl.majority_lag, flow.lagged, net.retransmit</t>
         </is>
       </c>
       <c r="T79" s="4" t="inlineStr"/>
-      <c r="U79" s="4" t="inlineStr"/>
+      <c r="U79" s="4" t="inlineStr">
+        <is>
+          <t>One result per entry of this node's replica-set status, numbered by position in that list; a position can name a different member after a reconfig. Lag is measured against the newest applied time among members, not against the primary, and a member that stopped reporting keeps its last time.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -7849,76 +7845,74 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>flow.lagged</t>
+          <t>repl.member_lag</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Samples with flowControl.isLagged set</t>
+          <t>Member replication lag</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>6.0 and later</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which flowControl.isLagged was set, normalized to a 60-second minute.</t>
+          <t>Difference between each member's reported applied-write timestamp and the newest such timestamp in this node's replica-set status, scaled to seconds. Members without a timestamp have no result. Minute summaries select the highest valid sample.</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/flowControl/isLagged, in lagged, at each available sample</t>
+          <t>newest of every replSetGetStatus/members/{i}/lastAppliedWallTime − this one × 0.001, in s, at each available sample</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly above 0 lagged, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>the highest valid sample of each minute</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>s/min</t>
+          <t>s</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>none ≤0 (fading to 1) · some 1–30 (edges 0, 48) · most ≥48 (from 30)</t>
+          <t>current ≤2 (fading to 5) · behind 5–20 (edges 2, 30) · lagging 30–120 (edges 20, 300) · far_behind ≥300 (from 120)</t>
         </is>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>0.5 s/min → 50% none, 50% some</t>
+          <t>3.5 s → 50% current, 50% behind</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>most</t>
+          <t>lagging or far_behind</t>
         </is>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
-          <t>1 s/min or more</t>
+          <t>30 s or more</t>
         </is>
       </c>
       <c r="M80" s="4" t="inlineStr">
         <is>
-          <t>3 s/min</t>
+          <t>5 s</t>
         </is>
       </c>
       <c r="N80" s="4" t="inlineStr"/>
       <c r="O80" s="4" t="inlineStr">
         <is>
-          <t>time_above</t>
-        </is>
-      </c>
-      <c r="P80" s="4" t="n">
-        <v>0</v>
-      </c>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="P80" s="4" t="n"/>
       <c r="Q80" s="4" t="inlineStr">
         <is>
-          <t>lagged</t>
+          <t>s</t>
         </is>
       </c>
       <c r="R80" s="4" t="inlineStr">
@@ -7928,13 +7922,13 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>flow.wait, repl.majority_lag, latency.writes</t>
+          <t>repl.majority_lag, flow.lagged, net.retransmit</t>
         </is>
       </c>
       <c r="T80" s="4" t="inlineStr"/>
       <c r="U80" s="4" t="inlineStr">
         <is>
-          <t>Set only on a primary with flow control enabled; a secondary, or a primary with flow control disabled, reports it unset. The flag records that the majority commit point lagged; time writers spent waiting for flow control is flow.wait.</t>
+          <t>One result per entry of this node's replica-set status, numbered by position in that list; a position can name a different member after a reconfig. Lag is measured against the newest applied time among members, not against the primary, and a member that stopped reporting keeps its last time.</t>
         </is>
       </c>
     </row>
@@ -7946,74 +7940,74 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>flow.wait</t>
+          <t>repl.majority_lag</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Time writers waited on flow control</t>
+          <t>Majority commit lag</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>4.2 and later</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Milliseconds a second writes spent waiting for flow control tickets on this node, added across every write waiting.</t>
+          <t>Difference between this node's lastAppliedWallTime and lastCommittedWallTime, scaled to seconds. Minute summaries select the highest valid sample. A sample with either time unset (zero) is left out.</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/flowControl/timeAcquiringMicros per second × 0.001, in ms/s, at each available sample</t>
+          <t>replSetGetStatus/optimes/lastAppliedWallTime − replSetGetStatus/optimes/lastCommittedWallTime × 0.001, in s, at each available sample</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>the highest valid sample of each minute</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>ms/s</t>
+          <t>s</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)</t>
+          <t>current ≤1 (fading to 3) · behind 3–10 (edges 1, 20) · lagging ≥20 (from 10)</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>5.5 ms/s → 50% none, 50% some</t>
+          <t>2 s → 50% current, 50% behind</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>heavy</t>
+          <t>lagging</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t>100 ms/s or more</t>
+          <t>10 s or more</t>
         </is>
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>10 ms/s</t>
+          <t>2 s</t>
         </is>
       </c>
       <c r="N81" s="4" t="inlineStr"/>
       <c r="O81" s="4" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>max</t>
         </is>
       </c>
       <c r="P81" s="4" t="n"/>
       <c r="Q81" s="4" t="inlineStr">
         <is>
-          <t>ms/s</t>
+          <t>s</t>
         </is>
       </c>
       <c r="R81" s="4" t="inlineStr">
@@ -8023,7 +8017,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>flow.lagged, latency.writes</t>
+          <t>repl.member_lag, flow.lagged, latency.writes</t>
         </is>
       </c>
       <c r="T81" s="4" t="inlineStr"/>
@@ -8037,12 +8031,12 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>repl.apply_rate</t>
+          <t>flow.lagged</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Oplog entries applied</t>
+          <t>Samples with flowControl.isLagged set</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -8052,65 +8046,79 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Rate of the node's oplog application operation counter.</t>
+          <t>Share of valid samples in which flowControl.isLagged was set, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/metrics/repl/apply/ops per second, in ops/s, at each available sample</t>
+          <t>serverStatus/flowControl/isLagged, in lagged, at each available sample</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>valid-sample share strictly above 0 lagged, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>ops/s</t>
+          <t>s/min</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>none — read for its shape only</t>
-        </is>
-      </c>
-      <c r="J82" s="4" t="inlineStr"/>
+          <t>none ≤0 (fading to 1) · some 1–30 (edges 0, 48) · most ≥48 (from 30)</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>0.5 s/min → 50% none, 50% some</t>
+        </is>
+      </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>shape only: a step, an episode, a schedule</t>
-        </is>
-      </c>
-      <c r="L82" s="4" t="inlineStr"/>
+          <t>most</t>
+        </is>
+      </c>
+      <c r="L82" s="4" t="inlineStr">
+        <is>
+          <t>1 s/min or more</t>
+        </is>
+      </c>
       <c r="M82" s="4" t="inlineStr">
         <is>
-          <t>50 ops/s</t>
+          <t>3 s/min</t>
         </is>
       </c>
       <c r="N82" s="4" t="inlineStr"/>
       <c r="O82" s="4" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="P82" s="4" t="n"/>
+          <t>time_above</t>
+        </is>
+      </c>
+      <c r="P82" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Q82" s="4" t="inlineStr">
         <is>
-          <t>ops/s</t>
+          <t>lagged</t>
         </is>
       </c>
       <c r="R82" s="4" t="inlineStr">
         <is>
-          <t>down</t>
+          <t>up</t>
         </is>
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>repl.buffer_fill, repl.member_lag</t>
+          <t>flow.wait, repl.majority_lag, latency.writes</t>
         </is>
       </c>
       <c r="T82" s="4" t="inlineStr"/>
-      <c r="U82" s="4" t="inlineStr"/>
+      <c r="U82" s="4" t="inlineStr">
+        <is>
+          <t>Set only on a primary with flow control enabled; a secondary, or a primary with flow control disabled, reports it unset. The flag records that the majority commit point lagged; time writers spent waiting for flow control is flow.wait.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -8120,62 +8128,62 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>repl.buffer_fill</t>
+          <t>flow.wait</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Apply buffer fill</t>
+          <t>Time writers waited on flow control</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>before 8.0</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Reported replication buffer bytes as a share of its reported maximum.</t>
+          <t>Milliseconds a second writes spent waiting for flow control tickets on this node, added across every write waiting.</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/metrics/repl/buffer/sizeBytes ÷ serverStatus/metrics/repl/buffer/maxSizeBytes × 100, in %, at each available sample</t>
+          <t>ΔserverStatus/flowControl/timeAcquiringMicros per second × 0.001, in ms/s, at each available sample</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>each minute's ratio of sums</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>ms/s</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>empty ≤5 (fading to 20) · filling 20–60 (edges 5, 85) · full ≥90 (from 70)</t>
+          <t>none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>12.5 % → 50% empty, 50% filling</t>
+          <t>5.5 ms/s → 50% none, 50% some</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
-          <t>70 % or more</t>
+          <t>100 ms/s or more</t>
         </is>
       </c>
       <c r="M83" s="4" t="inlineStr">
         <is>
-          <t>10 %</t>
+          <t>10 ms/s</t>
         </is>
       </c>
       <c r="N83" s="4" t="inlineStr"/>
@@ -8187,7 +8195,7 @@
       <c r="P83" s="4" t="n"/>
       <c r="Q83" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>ms/s</t>
         </is>
       </c>
       <c r="R83" s="4" t="inlineStr">
@@ -8197,7 +8205,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>repl.buffer_full, repl.apply_rate, repl.member_lag</t>
+          <t>flow.lagged, latency.writes</t>
         </is>
       </c>
       <c r="T83" s="4" t="inlineStr"/>
@@ -8211,62 +8219,54 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>repl.buffer_fill</t>
+          <t>repl.apply_rate</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Apply buffer fill</t>
+          <t>Oplog entries applied</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>8.0 and later</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Reported replication buffer bytes as a share of its reported maximum.</t>
+          <t>Rate of the node's oplog application operation counter.</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/metrics/repl/buffer/apply/sizeBytes ÷ serverStatus/metrics/repl/buffer/apply/maxSizeBytes × 100, in %, at each available sample</t>
+          <t>ΔserverStatus/metrics/repl/apply/ops per second, in ops/s, at each available sample</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>each minute's ratio of sums</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>ops/s</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
         <is>
-          <t>empty ≤5 (fading to 20) · filling 20–60 (edges 5, 85) · full ≥90 (from 70)</t>
-        </is>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>12.5 % → 50% empty, 50% filling</t>
-        </is>
-      </c>
+          <t>none — read for its shape only</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr"/>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="L84" s="4" t="inlineStr">
-        <is>
-          <t>70 % or more</t>
-        </is>
-      </c>
+          <t>shape only: a step, an episode, a schedule</t>
+        </is>
+      </c>
+      <c r="L84" s="4" t="inlineStr"/>
       <c r="M84" s="4" t="inlineStr">
         <is>
-          <t>10 %</t>
+          <t>50 ops/s</t>
         </is>
       </c>
       <c r="N84" s="4" t="inlineStr"/>
@@ -8278,17 +8278,17 @@
       <c r="P84" s="4" t="n"/>
       <c r="Q84" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>ops/s</t>
         </is>
       </c>
       <c r="R84" s="4" t="inlineStr">
         <is>
-          <t>up</t>
+          <t>down</t>
         </is>
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>repl.buffer_full, repl.apply_rate, repl.member_lag</t>
+          <t>repl.buffer_fill, repl.member_lag</t>
         </is>
       </c>
       <c r="T84" s="4" t="inlineStr"/>
@@ -8302,12 +8302,12 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>repl.buffer_full</t>
+          <t>repl.buffer_fill</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Apply-buffer samples above 90%</t>
+          <t>Apply buffer fill</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which replication buffer bytes were strictly above 90 % of the reported maximum, normalized to a 60-second minute.</t>
+          <t>Reported replication buffer bytes as a share of its reported maximum.</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -8327,48 +8327,46 @@
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly above 90 %, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>each minute's ratio of sums</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>s/min</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
+          <t>empty ≤5 (fading to 20) · filling 20–60 (edges 5, 85) · full ≥90 (from 70)</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>0.5 s/min → 50% none, 50% brief</t>
+          <t>12.5 % → 50% empty, 50% filling</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>frequent or constant</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t>1 s/min or more</t>
+          <t>70 % or more</t>
         </is>
       </c>
       <c r="M85" s="4" t="inlineStr">
         <is>
-          <t>3 s/min</t>
+          <t>10 %</t>
         </is>
       </c>
       <c r="N85" s="4" t="inlineStr"/>
       <c r="O85" s="4" t="inlineStr">
         <is>
-          <t>time_above</t>
-        </is>
-      </c>
-      <c r="P85" s="4" t="n">
-        <v>90</v>
-      </c>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P85" s="4" t="n"/>
       <c r="Q85" s="4" t="inlineStr">
         <is>
           <t>%</t>
@@ -8381,7 +8379,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>repl.buffer_fill, repl.apply_rate</t>
+          <t>repl.buffer_full, repl.apply_rate, repl.member_lag</t>
         </is>
       </c>
       <c r="T85" s="4" t="inlineStr"/>
@@ -8395,12 +8393,12 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>repl.buffer_full</t>
+          <t>repl.buffer_fill</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Apply-buffer samples above 90%</t>
+          <t>Apply buffer fill</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -8410,7 +8408,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which replication buffer bytes were strictly above 90 % of the reported maximum, normalized to a 60-second minute.</t>
+          <t>Reported replication buffer bytes as a share of its reported maximum.</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -8420,48 +8418,46 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly above 90 %, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>each minute's ratio of sums</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>s/min</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I86" s="4" t="inlineStr">
         <is>
-          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
+          <t>empty ≤5 (fading to 20) · filling 20–60 (edges 5, 85) · full ≥90 (from 70)</t>
         </is>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>0.5 s/min → 50% none, 50% brief</t>
+          <t>12.5 % → 50% empty, 50% filling</t>
         </is>
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>frequent or constant</t>
+          <t>full</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>1 s/min or more</t>
+          <t>70 % or more</t>
         </is>
       </c>
       <c r="M86" s="4" t="inlineStr">
         <is>
-          <t>3 s/min</t>
+          <t>10 %</t>
         </is>
       </c>
       <c r="N86" s="4" t="inlineStr"/>
       <c r="O86" s="4" t="inlineStr">
         <is>
-          <t>time_above</t>
-        </is>
-      </c>
-      <c r="P86" s="4" t="n">
-        <v>90</v>
-      </c>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P86" s="4" t="n"/>
       <c r="Q86" s="4" t="inlineStr">
         <is>
           <t>%</t>
@@ -8474,7 +8470,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>repl.buffer_fill, repl.apply_rate</t>
+          <t>repl.buffer_full, repl.apply_rate, repl.member_lag</t>
         </is>
       </c>
       <c r="T86" s="4" t="inlineStr"/>
@@ -8483,76 +8479,78 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>connections</t>
+          <t>replication</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>connections.used</t>
+          <t>repl.buffer_full</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Current connections as a share of current plus available</t>
+          <t>Apply-buffer samples above 90%</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>before 8.0</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Reported current connections divided by current plus available connections.</t>
+          <t>Share of valid samples in which replication buffer bytes were strictly above 90 % of the reported maximum, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/connections/current ÷ (serverStatus/connections/current + serverStatus/connections/available) × 100, in %, at each available sample</t>
+          <t>serverStatus/metrics/repl/buffer/sizeBytes ÷ serverStatus/metrics/repl/buffer/maxSizeBytes × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>each minute's ratio of sums</t>
+          <t>valid-sample share strictly above 90 %, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>s/min</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>low ≤25 (fading to 50) · moderate 50–70 (edges 25, 85) · high 85–90 (edges 70, 95) · near_limit ≥95 (from 90)</t>
+          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>37.5 % → 50% low, 50% moderate</t>
+          <t>0.5 s/min → 50% none, 50% brief</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>high or near_limit</t>
+          <t>frequent or constant</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>85 % or more</t>
+          <t>1 s/min or more</t>
         </is>
       </c>
       <c r="M87" s="4" t="inlineStr">
         <is>
-          <t>10 %</t>
+          <t>3 s/min</t>
         </is>
       </c>
       <c r="N87" s="4" t="inlineStr"/>
       <c r="O87" s="4" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="P87" s="4" t="n"/>
+          <t>time_above</t>
+        </is>
+      </c>
+      <c r="P87" s="4" t="n">
+        <v>90</v>
+      </c>
       <c r="Q87" s="4" t="inlineStr">
         <is>
           <t>%</t>
@@ -8565,7 +8563,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>connections.scarce, connections.created, connections.rejected</t>
+          <t>repl.buffer_fill, repl.apply_rate</t>
         </is>
       </c>
       <c r="T87" s="4" t="inlineStr"/>
@@ -8574,37 +8572,37 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>connections</t>
+          <t>replication</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>connections.scarce</t>
+          <t>repl.buffer_full</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Samples with under 10% of connections left</t>
+          <t>Apply-buffer samples above 90%</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>8.0 and later</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Share of valid samples in which available connections were strictly below 10 % of current plus available, normalized to a 60-second minute.</t>
+          <t>Share of valid samples in which replication buffer bytes were strictly above 90 % of the reported maximum, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/connections/available ÷ (serverStatus/connections/current + serverStatus/connections/available) × 100, in % available, at each available sample</t>
+          <t>serverStatus/metrics/repl/buffer/apply/sizeBytes ÷ serverStatus/metrics/repl/buffer/apply/maxSizeBytes × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time</t>
+          <t>valid-sample share strictly above 90 %, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -8624,7 +8622,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>brief and above (set by the rule)</t>
+          <t>frequent or constant</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
@@ -8640,15 +8638,15 @@
       <c r="N88" s="4" t="inlineStr"/>
       <c r="O88" s="4" t="inlineStr">
         <is>
-          <t>time_below</t>
+          <t>time_above</t>
         </is>
       </c>
       <c r="P88" s="4" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="Q88" s="4" t="inlineStr">
         <is>
-          <t>% available</t>
+          <t>%</t>
         </is>
       </c>
       <c r="R88" s="4" t="inlineStr">
@@ -8658,7 +8656,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>connections.used, connections.created, connections.rejected</t>
+          <t>repl.buffer_fill, repl.apply_rate</t>
         </is>
       </c>
       <c r="T88" s="4" t="inlineStr"/>
@@ -8672,12 +8670,12 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>connections.created</t>
+          <t>connections.used</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>New connections</t>
+          <t>Current connections as a share of current plus available</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -8687,47 +8685,47 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Rate of the server's totalCreated connection counter.</t>
+          <t>Reported current connections divided by current plus available connections.</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/connections/totalCreated per second, in conn/s, at each available sample</t>
+          <t>serverStatus/connections/current ÷ (serverStatus/connections/current + serverStatus/connections/available) × 100, in %, at each available sample</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>each minute's ratio of sums</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>conn/s</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>quiet ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · high ≥20 (from 10)</t>
+          <t>low ≤25 (fading to 50) · moderate 50–70 (edges 25, 85) · high 85–90 (edges 70, 95) · near_limit ≥95 (from 90)</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>2 conn/s → 50% quiet, 50% normal</t>
+          <t>37.5 % → 50% low, 50% moderate</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>high or near_limit</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>20 conn/s or more</t>
+          <t>85 % or more</t>
         </is>
       </c>
       <c r="M89" s="4" t="inlineStr">
         <is>
-          <t>5 conn/s</t>
+          <t>10 %</t>
         </is>
       </c>
       <c r="N89" s="4" t="inlineStr"/>
@@ -8739,7 +8737,7 @@
       <c r="P89" s="4" t="n"/>
       <c r="Q89" s="4" t="inlineStr">
         <is>
-          <t>conn/s</t>
+          <t>%</t>
         </is>
       </c>
       <c r="R89" s="4" t="inlineStr">
@@ -8749,7 +8747,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>connections.current, cpu.kernel_share, net.resets</t>
+          <t>connections.scarce, connections.created, connections.rejected</t>
         </is>
       </c>
       <c r="T89" s="4" t="inlineStr"/>
@@ -8763,74 +8761,76 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>connections.non_active</t>
+          <t>connections.scarce</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Derived non-active connection count</t>
+          <t>Samples with under 10% of connections left</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>4.4 and later</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Derived connection count: current plus awaitingTopologyChanges minus active; it is not evidence of unused client pools or a connection leak.</t>
+          <t>Share of valid samples in which available connections were strictly below 10 % of current plus available, normalized to a 60-second minute.</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>(serverStatus/connections/current + serverStatus/connections/awaitingTopologyChanges) − serverStatus/connections/active, in conns, at each available sample</t>
+          <t>serverStatus/connections/available ÷ (serverStatus/connections/current + serverStatus/connections/available) × 100, in % available, at each available sample</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>conns</t>
+          <t>s/min</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>few ≤300 (fading to 800) · many 800–1500 (edges 300, 2500) · very_high ≥3000 (from 1500)</t>
+          <t>none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)</t>
         </is>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>550 conns → 50% few, 50% many</t>
+          <t>0.5 s/min → 50% none, 50% brief</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>brief and above (set by the rule)</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>2000 conns or more</t>
+          <t>1 s/min or more</t>
         </is>
       </c>
       <c r="M90" s="4" t="inlineStr">
         <is>
-          <t>100 conns</t>
+          <t>3 s/min</t>
         </is>
       </c>
       <c r="N90" s="4" t="inlineStr"/>
       <c r="O90" s="4" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="P90" s="4" t="n"/>
+          <t>time_below</t>
+        </is>
+      </c>
+      <c r="P90" s="4" t="n">
+        <v>10</v>
+      </c>
       <c r="Q90" s="4" t="inlineStr">
         <is>
-          <t>conns</t>
+          <t>% available</t>
         </is>
       </c>
       <c r="R90" s="4" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>connections.current, connections.created, connections.working_share, memory.heap_outside_cache</t>
+          <t>connections.used, connections.created, connections.rejected</t>
         </is>
       </c>
       <c r="T90" s="4" t="inlineStr"/>
@@ -8854,47 +8854,47 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>connections.working_share</t>
+          <t>connections.created</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Derived active-connection share</t>
+          <t>New connections</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>4.4 and later</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Derived active-connection share: active minus awaitingTopologyChanges divided by current connections. Minute summaries select the highest valid sample.</t>
+          <t>Rate of the server's totalCreated connection counter.</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/connections/active − serverStatus/connections/awaitingTopologyChanges ÷ serverStatus/connections/current × 100, in %, at each available sample; minutes where the divisor sums to under 3000 are left out</t>
+          <t>ΔserverStatus/connections/totalCreated per second, in conn/s, at each available sample</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>the highest valid sample of each minute</t>
+          <t>each minute's mean</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>conn/s</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>calm ≤10 (fading to 25) · busy 25–40 (edges 10, 60) · high ≥60 (from 40)</t>
+          <t>quiet ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · high ≥20 (from 10)</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>17.5 % → 50% calm, 50% busy</t>
+          <t>2 conn/s → 50% quiet, 50% normal</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
@@ -8904,24 +8904,24 @@
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>40 % or more</t>
+          <t>20 conn/s or more</t>
         </is>
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>10 %</t>
+          <t>5 conn/s</t>
         </is>
       </c>
       <c r="N91" s="4" t="inlineStr"/>
       <c r="O91" s="4" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="P91" s="4" t="n"/>
       <c r="Q91" s="4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>conn/s</t>
         </is>
       </c>
       <c r="R91" s="4" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.empty, tickets.write.empty, queue.readers, queue.writers, connections.created</t>
+          <t>connections.current, cpu.kernel_share, net.resets</t>
         </is>
       </c>
       <c r="T91" s="4" t="inlineStr"/>
@@ -8945,27 +8945,27 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>connections.current</t>
+          <t>connections.non_active</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Open connections</t>
+          <t>Derived non-active connection count</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>4.4 and later</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Count reported for currently open server connections.</t>
+          <t>Derived connection count: current plus awaitingTopologyChanges minus active; it is not evidence of unused client pools or a connection leak.</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>serverStatus/connections/current, in conns, at each available sample</t>
+          <t>(serverStatus/connections/current + serverStatus/connections/awaitingTopologyChanges) − serverStatus/connections/active, in conns, at each available sample</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
@@ -8980,19 +8980,27 @@
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>none — read for its shape only</t>
-        </is>
-      </c>
-      <c r="J92" s="4" t="inlineStr"/>
+          <t>few ≤300 (fading to 800) · many 800–1500 (edges 300, 2500) · very_high ≥3000 (from 1500)</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>550 conns → 50% few, 50% many</t>
+        </is>
+      </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>shape only: a step, an episode, a schedule</t>
-        </is>
-      </c>
-      <c r="L92" s="4" t="inlineStr"/>
+          <t>very_high</t>
+        </is>
+      </c>
+      <c r="L92" s="4" t="inlineStr">
+        <is>
+          <t>2000 conns or more</t>
+        </is>
+      </c>
       <c r="M92" s="4" t="inlineStr">
         <is>
-          <t>50 conns</t>
+          <t>100 conns</t>
         </is>
       </c>
       <c r="N92" s="4" t="inlineStr"/>
@@ -9014,7 +9022,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>connections.non_active, connections.created, memory.heap_outside_cache</t>
+          <t>connections.current, connections.created, connections.working_share, memory.heap_outside_cache</t>
         </is>
       </c>
       <c r="T92" s="4" t="inlineStr"/>
@@ -9028,74 +9036,74 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>connections.rejected</t>
+          <t>connections.working_share</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Connections refused</t>
+          <t>Derived active-connection share</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>6.3 and later</t>
+          <t>4.4 and later</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Rate of the server's rejected connection counter; client impact and rejection cause are not inferred.</t>
+          <t>Derived active-connection share: active minus awaitingTopologyChanges divided by current connections. Minute summaries select the highest valid sample.</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>ΔserverStatus/connections/rejected per second, in /s, at each available sample</t>
+          <t>serverStatus/connections/active − serverStatus/connections/awaitingTopologyChanges ÷ serverStatus/connections/current × 100, in %, at each available sample; minutes where the divisor sums to under 3000 are left out</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>each minute's mean</t>
+          <t>the highest valid sample of each minute</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>/s</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>none ≤0.001 (fading to 0.01) · some 0.01–1 (edges 0.001, 5) · many ≥5 (from 1)</t>
+          <t>calm ≤10 (fading to 25) · busy 25–40 (edges 10, 60) · high ≥60 (from 40)</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>0.005 /s → 56% none, 44% some</t>
+          <t>17.5 % → 50% calm, 50% busy</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>many</t>
+          <t>high</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>0.01 /s or more</t>
+          <t>40 % or more</t>
         </is>
       </c>
       <c r="M93" s="4" t="inlineStr">
         <is>
-          <t>0.01 /s</t>
+          <t>10 %</t>
         </is>
       </c>
       <c r="N93" s="4" t="inlineStr"/>
       <c r="O93" s="4" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>max</t>
         </is>
       </c>
       <c r="P93" s="4" t="n"/>
       <c r="Q93" s="4" t="inlineStr">
         <is>
-          <t>/s</t>
+          <t>%</t>
         </is>
       </c>
       <c r="R93" s="4" t="inlineStr">
@@ -9105,14 +9113,188 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>connections.scarce, connections.used</t>
+          <t>tickets.read.empty, tickets.write.empty, queue.readers, queue.writers, connections.created</t>
         </is>
       </c>
       <c r="T93" s="4" t="inlineStr"/>
       <c r="U93" s="4" t="inlineStr"/>
     </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>connections</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>connections.current</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>Open connections</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>Count reported for currently open server connections.</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>serverStatus/connections/current, in conns, at each available sample</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>each minute's mean</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>conns</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>none — read for its shape only</t>
+        </is>
+      </c>
+      <c r="J94" s="4" t="inlineStr"/>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>shape only: a step, an episode, a schedule</t>
+        </is>
+      </c>
+      <c r="L94" s="4" t="inlineStr"/>
+      <c r="M94" s="4" t="inlineStr">
+        <is>
+          <t>50 conns</t>
+        </is>
+      </c>
+      <c r="N94" s="4" t="inlineStr"/>
+      <c r="O94" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P94" s="4" t="n"/>
+      <c r="Q94" s="4" t="inlineStr">
+        <is>
+          <t>conns</t>
+        </is>
+      </c>
+      <c r="R94" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S94" s="4" t="inlineStr">
+        <is>
+          <t>connections.non_active, connections.created, memory.heap_outside_cache</t>
+        </is>
+      </c>
+      <c r="T94" s="4" t="inlineStr"/>
+      <c r="U94" s="4" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>connections</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>connections.rejected</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>Connections refused</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>6.3 and later</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>Rate of the server's rejected connection counter; client impact and rejection cause are not inferred.</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>ΔserverStatus/connections/rejected per second, in /s, at each available sample</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>each minute's mean</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>/s</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>none ≤0.001 (fading to 0.01) · some 0.01–1 (edges 0.001, 5) · many ≥5 (from 1)</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>0.005 /s → 56% none, 44% some</t>
+        </is>
+      </c>
+      <c r="K95" s="4" t="inlineStr">
+        <is>
+          <t>many</t>
+        </is>
+      </c>
+      <c r="L95" s="4" t="inlineStr">
+        <is>
+          <t>0.01 /s or more</t>
+        </is>
+      </c>
+      <c r="M95" s="4" t="inlineStr">
+        <is>
+          <t>0.01 /s</t>
+        </is>
+      </c>
+      <c r="N95" s="4" t="inlineStr"/>
+      <c r="O95" s="4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="P95" s="4" t="n"/>
+      <c r="Q95" s="4" t="inlineStr">
+        <is>
+          <t>/s</t>
+        </is>
+      </c>
+      <c r="R95" s="4" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="S95" s="4" t="inlineStr">
+        <is>
+          <t>connections.scarce, connections.used</t>
+        </is>
+      </c>
+      <c r="T95" s="4" t="inlineStr"/>
+      <c r="U95" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U93"/>
+  <autoFilter ref="A1:U95"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9123,7 +9305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9370,7 +9552,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤1 (fading to 3) · some 3–20 (edges 1, 40) · heavy ≥40 (from 20)", "doc": "Share of swap holding pages. Host-wide memory or CPU counters do not establish a container's resource limit.", "elevated": 10, "formula": "100 − (systemMetrics/memory/SwapFree_kb ÷ systemMetrics/memory/SwapTotal_kb × 100), in %, at each available sample", "levels": [{"down": [1, 3], "name": "none"}, {"band": [1, 3, 20, 40], "name": "some"}, {"name": "heavy", "up": [20, 40]}], "min_change": 5, "name": "memory.swap_used", "pack": "memory", "pairs_with": ["memory.used", "memory.page_faults"], "reading": "each minute's ratio of sums", "signal": {"complement": true, "den": ["systemMetrics/memory/SwapTotal_kb"], "mode": "gauge", "num": ["systemMetrics/memory/SwapFree_kb"], "scale": 100, "unit": "%"}, "title": "Swap in use", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "none ≤1 (fading to 3) · some 3–20 (edges 1, 40) · heavy ≥40 (from 20)", "doc": "Share of swap holding pages. Host-wide memory or CPU counters do not establish a container's resource limit.", "elevated": 10, "formula": "100 − (systemMetrics/memory/SwapFree_kb ÷ systemMetrics/memory/SwapTotal_kb × 100), in %, at each available sample", "levels": [{"down": [1, 3], "name": "none"}, {"band": [1, 3, 20, 40], "name": "some"}, {"name": "heavy", "up": [20, 40]}], "min_change": 5, "name": "memory.swap_used", "pack": "memory", "pairs_with": ["memory.used", "memory.page_faults", "memory.swap_in"], "reading": "each minute's ratio of sums", "signal": {"complement": true, "den": ["systemMetrics/memory/SwapTotal_kb"], "mode": "gauge", "num": ["systemMetrics/memory/SwapFree_kb"], "scale": 100, "unit": "%"}, "title": "Swap in use", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9380,7 +9562,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>memory.page_faults</t>
+          <t>memory.swap_in</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -9390,7 +9572,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤1 (fading to 5) · some 5–50 (edges 1, 200) · heavy ≥200 (from 50)", "doc": "Rate of the process's logged major-page-fault counter.", "elevated": 50, "formula": "ΔserverStatus/extra_info/page_faults per second, in /s, at each available sample", "levels": [{"down": [1, 5], "name": "none"}, {"band": [1, 5, 50, 200], "name": "some"}, {"name": "heavy", "up": [50, 200]}], "min_change": 10, "name": "memory.page_faults", "pack": "memory", "pairs_with": ["memory.used", "memory.swap_used", "disk.read_await"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/extra_info/page_faults"], "scale": 1, "unit": "/s"}, "title": "Page faults", "unit": "/s", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "none ≤10 (fading to 50) · some 50–500 (edges 10, 1000) · heavy ≥1000 (from 500)", "doc": "Rate of pages the whole machine read back from swap (vmstat pswpin). A process waits for every such page it touches, so a burst of it stalls whatever was running, even with swap mostly free.", "elevated": 500, "formula": "ΔsystemMetrics/vmstat/pswpin per second, in pages/s, at each available sample", "levels": [{"down": [10, 50], "name": "none"}, {"band": [10, 50, 500, 1000], "name": "some"}, {"name": "heavy", "up": [500, 1000]}], "min_change": 50, "name": "memory.swap_in", "pack": "memory", "pairs_with": ["memory.swap_out", "memory.page_faults", "memory.swap_used"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["systemMetrics/vmstat/pswpin"], "scale": 1, "unit": "pages/s"}, "title": "Pages swapped in", "unit": "pages/s", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9582,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>memory.mongod_resident</t>
+          <t>memory.swap_out</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -9410,7 +9592,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "modest ≤40 (fading to 60) · large 60–75 (edges 40, 85) · dominant ≥85 (from 75)", "doc": "mongod's resident memory as a share of the machine's. Host-wide memory or CPU counters do not establish a container's resource limit.", "elevated": 80, "formula": "serverStatus/mem/resident ÷ systemMetrics/memory/MemTotal_kb × 102400, in %, at each available sample", "levels": [{"down": [40, 60], "name": "modest"}, {"band": [40, 60, 75, 85], "name": "large"}, {"name": "dominant", "up": [75, 85]}], "min_change": 5, "name": "memory.mongod_resident", "pack": "memory", "pairs_with": ["memory.used", "memory.heap_outside_cache", "memory.cache_of_ram"], "reading": "each minute's ratio of sums", "signal": {"den": ["systemMetrics/memory/MemTotal_kb"], "mode": "gauge", "num": ["serverStatus/mem/resident"], "scale": 102400, "unit": "%"}, "title": "mongod resident memory", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "none ≤10 (fading to 50) · some 50–500 (edges 10, 1000) · heavy ≥1000 (from 500)", "doc": "Rate of pages the whole machine wrote out to swap (vmstat pswpout).", "elevated": 500, "formula": "ΔsystemMetrics/vmstat/pswpout per second, in pages/s, at each available sample", "levels": [{"down": [10, 50], "name": "none"}, {"band": [10, 50, 500, 1000], "name": "some"}, {"name": "heavy", "up": [500, 1000]}], "min_change": 50, "name": "memory.swap_out", "pack": "memory", "pairs_with": ["memory.swap_in", "memory.used", "memory.swap_used"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["systemMetrics/vmstat/pswpout"], "scale": 1, "unit": "pages/s"}, "title": "Pages swapped out", "unit": "pages/s", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9420,7 +9602,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>memory.heap_outside_cache</t>
+          <t>memory.page_faults</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -9430,7 +9612,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "doc": "Difference between tcmalloc allocated bytes and bytes currently held in the WiredTiger cache; this is a derived estimate, not a complete inventory of non-cache allocations.", "formula": "serverStatus/tcmalloc/generic/current_allocated_bytes − serverStatus/wiredTiger/cache/bytes currently in the cache × 9.313225746154785e-10, in GiB, at each available sample", "min_change": 0.5, "name": "memory.heap_outside_cache", "pack": "memory", "pairs_with": ["connections.current", "memory.allocator_free", "cursors.open"], "reading": "each minute's mean", "signal": {"minus": ["serverStatus/wiredTiger/cache/bytes currently in the cache"], "mode": "gauge", "num": ["serverStatus/tcmalloc/generic/current_allocated_bytes"], "scale": 9.313225746154785e-10, "unit": "GiB"}, "title": "Allocated bytes minus WiredTiger cache bytes", "unit": "GiB", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "none ≤1 (fading to 5) · some 5–50 (edges 1, 200) · heavy ≥200 (from 50)", "doc": "Rate of the process's logged major-page-fault counter.", "elevated": 50, "formula": "ΔserverStatus/extra_info/page_faults per second, in /s, at each available sample", "levels": [{"down": [1, 5], "name": "none"}, {"band": [1, 5, 50, 200], "name": "some"}, {"name": "heavy", "up": [50, 200]}], "min_change": 10, "name": "memory.page_faults", "pack": "memory", "pairs_with": ["memory.used", "memory.swap_used", "disk.read_await"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/extra_info/page_faults"], "scale": 1, "unit": "/s"}, "title": "Page faults", "unit": "/s", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9440,17 +9622,17 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>memory.allocator_free</t>
+          <t>memory.mongod_resident</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>before 8.0</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "small ≤10 (fading to 20) · notable 20–30 (edges 10, 45) · large ≥45 (from 30)", "doc": "Ratio of tcmalloc pageheap_free_bytes to heap_size; these counters do not describe every allocator cache.", "elevated": 30, "formula": "serverStatus/tcmalloc/tcmalloc/pageheap_free_bytes ÷ serverStatus/tcmalloc/generic/heap_size × 100, in %, at each available sample", "levels": [{"down": [10, 20], "name": "small"}, {"band": [10, 20, 30, 45], "name": "notable"}, {"name": "large", "up": [30, 45]}], "min_change": 5, "name": "memory.allocator_free", "pack": "memory", "pairs_with": ["memory.heap_outside_cache", "memory.mongod_resident"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/tcmalloc/generic/heap_size"], "mode": "gauge", "num": ["serverStatus/tcmalloc/tcmalloc/pageheap_free_bytes"], "scale": 100, "unit": "%"}, "title": "tcmalloc pageheap-free share", "unit": "%", "until": "8.0", "version_text": "before 8.0", "view": "mean"}</t>
+          <t>{"bands": "modest ≤40 (fading to 60) · large 60–75 (edges 40, 85) · dominant ≥85 (from 75)", "doc": "mongod's resident memory as a share of the machine's. Host-wide memory or CPU counters do not establish a container's resource limit.", "elevated": 80, "formula": "serverStatus/mem/resident ÷ systemMetrics/memory/MemTotal_kb × 102400, in %, at each available sample", "levels": [{"down": [40, 60], "name": "modest"}, {"band": [40, 60, 75, 85], "name": "large"}, {"name": "dominant", "up": [75, 85]}], "min_change": 5, "name": "memory.mongod_resident", "pack": "memory", "pairs_with": ["memory.used", "memory.heap_outside_cache", "memory.cache_of_ram"], "reading": "each minute's ratio of sums", "signal": {"den": ["systemMetrics/memory/MemTotal_kb"], "mode": "gauge", "num": ["serverStatus/mem/resident"], "scale": 102400, "unit": "%"}, "title": "mongod resident memory", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9460,7 +9642,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>memory.cache_of_ram</t>
+          <t>memory.heap_outside_cache</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -9470,7 +9652,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "low ≤30 (fading to 40) · middle 40–55 (edges 30, 62) · high ≥70 (from 58)", "doc": "The configured cache as a share of the machine's memory. Host-wide memory or CPU counters do not establish a container's resource limit.", "elevated": 60, "formula": "serverStatus/wiredTiger/cache/maximum bytes configured ÷ systemMetrics/memory/MemTotal_kb × 0.09765625, in %, at each available sample", "levels": [{"down": [30, 40], "name": "low"}, {"band": [30, 40, 55, 62], "name": "middle"}, {"name": "high", "up": [58, 70]}], "min_change": 5, "name": "memory.cache_of_ram", "pack": "memory", "pairs_with": ["memory.used", "memory.mongod_resident"], "reading": "each minute's ratio of sums", "signal": {"den": ["systemMetrics/memory/MemTotal_kb"], "mode": "gauge", "num": ["serverStatus/wiredTiger/cache/maximum bytes configured"], "scale": 0.09765625, "unit": "%"}, "title": "WiredTiger cache size against RAM", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "none — read for its shape only", "doc": "Difference between tcmalloc allocated bytes and bytes currently held in the WiredTiger cache; this is a derived estimate, not a complete inventory of non-cache allocations.", "formula": "serverStatus/tcmalloc/generic/current_allocated_bytes − serverStatus/wiredTiger/cache/bytes currently in the cache × 9.313225746154785e-10, in GiB, at each available sample", "min_change": 0.5, "name": "memory.heap_outside_cache", "pack": "memory", "pairs_with": ["connections.current", "memory.allocator_free", "cursors.open"], "reading": "each minute's mean", "signal": {"minus": ["serverStatus/wiredTiger/cache/bytes currently in the cache"], "mode": "gauge", "num": ["serverStatus/tcmalloc/generic/current_allocated_bytes"], "scale": 9.313225746154785e-10, "unit": "GiB"}, "title": "Allocated bytes minus WiredTiger cache bytes", "unit": "GiB", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9480,17 +9662,17 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>disk.busy</t>
+          <t>memory.allocator_free</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>before 8.0</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "A device that serves requests in parallel, such as an SSD, NVMe or network volume, can show io_time near 100 % with capacity to spare; disk.await shows whether requests waited. Device-mapper (dm-*) devices are not read by this tool; the disks under them are.", "bands": "idle ≤5 (fading to 15) · low 15–40 (edges 5, 60) · moderate 60–75 (edges 40, 85) · high 85–92 (edges 75, 97) · very_high ≥97 (from 92)", "doc": "Device io_time counter advance divided by elapsed time; a high value does not establish device capacity exhaustion. Device coverage depends on the block-device counters present in FTDC; logical devices may be absent.", "elevated": 85, "formula": "ΔsystemMetrics/disks/{i}/io_time_ms per second × 0.1, in %, at each available sample; real block devices only", "levels": [{"down": [5, 15], "name": "idle"}, {"band": [5, 15, 40, 60], "name": "low"}, {"band": [40, 60, 75, 85], "name": "moderate"}, {"band": [75, 85, 92, 97], "name": "high"}, {"name": "very_high", "up": [92, 97]}], "min_change": 15, "name": "disk.busy", "open_with": ["disk.await"], "pack": "disk", "pairs_with": ["disk.busy_above_95", "disk.await", "disk.queue", "disk.iops", "disk.throughput"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["systemMetrics/disks/{i}/io_time_ms"], "real_device": true, "scale": 0.1, "unit": "%"}, "title": "Disk busy", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "small ≤10 (fading to 20) · notable 20–30 (edges 10, 45) · large ≥45 (from 30)", "doc": "Ratio of tcmalloc pageheap_free_bytes to heap_size; these counters do not describe every allocator cache.", "elevated": 30, "formula": "serverStatus/tcmalloc/tcmalloc/pageheap_free_bytes ÷ serverStatus/tcmalloc/generic/heap_size × 100, in %, at each available sample", "levels": [{"down": [10, 20], "name": "small"}, {"band": [10, 20, 30, 45], "name": "notable"}, {"name": "large", "up": [30, 45]}], "min_change": 5, "name": "memory.allocator_free", "pack": "memory", "pairs_with": ["memory.heap_outside_cache", "memory.mongod_resident"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/tcmalloc/generic/heap_size"], "mode": "gauge", "num": ["serverStatus/tcmalloc/tcmalloc/pageheap_free_bytes"], "scale": 100, "unit": "%"}, "title": "tcmalloc pageheap-free share", "unit": "%", "until": "8.0", "version_text": "before 8.0", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9500,7 +9682,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>disk.busy_above_95</t>
+          <t>memory.cache_of_ram</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -9510,7 +9692,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "A device that serves requests in parallel, such as an SSD, NVMe or network volume, can show io_time near 100 % with capacity to spare; disk.await shows whether requests waited. Device-mapper (dm-*) devices are not read by this tool; the disks under them are.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which a device's io_time advanced by more than 95 % of the elapsed time, normalized to a 60-second minute.", "elevated": 1, "formula": "ΔsystemMetrics/disks/{i}/io_time_ms per second × 0.1, in %, at each available sample; real block devices only", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "disk.busy_above_95", "open_with": ["disk.await"], "pack": "disk", "pairs_with": ["disk.busy", "disk.await", "checkpoint.running"], "reading": "valid-sample share strictly above 95 %, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "rate", "num": ["systemMetrics/disks/{i}/io_time_ms"], "real_device": true, "scale": 0.1, "unit": "%"}, "threshold": 95, "title": "Device-busy samples above 95%", "unit": "s/min", "version_text": "all versions", "view": "time_above"}</t>
+          <t>{"bands": "low ≤30 (fading to 40) · middle 40–55 (edges 30, 62) · high ≥70 (from 58)", "doc": "The configured cache as a share of the machine's memory. Host-wide memory or CPU counters do not establish a container's resource limit.", "elevated": 60, "formula": "serverStatus/wiredTiger/cache/maximum bytes configured ÷ systemMetrics/memory/MemTotal_kb × 0.09765625, in %, at each available sample", "levels": [{"down": [30, 40], "name": "low"}, {"band": [30, 40, 55, 62], "name": "middle"}, {"name": "high", "up": [58, 70]}], "min_change": 5, "name": "memory.cache_of_ram", "pack": "memory", "pairs_with": ["memory.used", "memory.mongod_resident"], "reading": "each minute's ratio of sums", "signal": {"den": ["systemMetrics/memory/MemTotal_kb"], "mode": "gauge", "num": ["serverStatus/wiredTiger/cache/maximum bytes configured"], "scale": 0.09765625, "unit": "%"}, "title": "WiredTiger cache size against RAM", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9520,7 +9702,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>disk.await</t>
+          <t>disk.busy</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -9530,7 +9712,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "fast ≤2 (fading to 5) · normal 5–10 (edges 2, 15) · slow 15–30 (edges 10, 50) · very_slow ≥50 (from 30)", "doc": "Average milliseconds a read or write took on each device, queueing included — what iostat calls await.", "elevated": 20, "formula": "Δ(systemMetrics/disks/{i}/read_time_ms + systemMetrics/disks/{i}/write_time_ms) ÷ Δ(systemMetrics/disks/{i}/reads + systemMetrics/disks/{i}/writes), in ms, at each available sample; minutes where the divisor sums to under 60 are left out; real block devices only", "levels": [{"down": [2, 5], "name": "fast"}, {"band": [2, 5, 10, 15], "name": "normal"}, {"band": [10, 15, 30, 50], "name": "slow"}, {"name": "very_slow", "up": [30, 50]}], "min_change": 5, "name": "disk.await", "pack": "disk", "pairs_with": ["disk.busy", "disk.queue", "cpu.iowait"], "reading": "each minute's ratio of sums", "signal": {"den": ["systemMetrics/disks/{i}/reads", "systemMetrics/disks/{i}/writes"], "min_den": 60, "mode": "rate", "num": ["systemMetrics/disks/{i}/read_time_ms", "systemMetrics/disks/{i}/write_time_ms"], "real_device": true, "scale": 1, "unit": "ms"}, "title": "Disk time per request", "unit": "ms", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"applies": "A device that serves requests in parallel, such as an SSD, NVMe or network volume, can show io_time near 100 % with capacity to spare; disk.await shows whether requests waited. Device-mapper (dm-*) devices are not read by this tool; the disks under them are.", "bands": "idle ≤5 (fading to 15) · low 15–40 (edges 5, 60) · moderate 60–75 (edges 40, 85) · high 85–92 (edges 75, 97) · very_high ≥97 (from 92)", "doc": "Device io_time counter advance divided by elapsed time; a high value does not establish device capacity exhaustion. Device coverage depends on the block-device counters present in FTDC; logical devices may be absent.", "elevated": 85, "formula": "ΔsystemMetrics/disks/{i}/io_time_ms per second × 0.1, in %, at each available sample; real block devices only", "levels": [{"down": [5, 15], "name": "idle"}, {"band": [5, 15, 40, 60], "name": "low"}, {"band": [40, 60, 75, 85], "name": "moderate"}, {"band": [75, 85, 92, 97], "name": "high"}, {"name": "very_high", "up": [92, 97]}], "min_change": 15, "name": "disk.busy", "open_with": ["disk.await"], "pack": "disk", "pairs_with": ["disk.busy_above_95", "disk.await", "disk.queue", "disk.iops", "disk.throughput"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["systemMetrics/disks/{i}/io_time_ms"], "real_device": true, "scale": 0.1, "unit": "%"}, "title": "Disk busy", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9540,7 +9722,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>disk.read_await</t>
+          <t>disk.busy_above_95</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -9550,7 +9732,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "fast ≤2 (fading to 5) · normal 5–10 (edges 2, 15) · slow 15–30 (edges 10, 50) · very_slow ≥50 (from 30)", "doc": "Average milliseconds a read took on each device.", "elevated": 20, "formula": "ΔsystemMetrics/disks/{i}/read_time_ms ÷ ΔsystemMetrics/disks/{i}/reads, in ms, at each available sample; minutes where the divisor sums to under 60 are left out; real block devices only", "levels": [{"down": [2, 5], "name": "fast"}, {"band": [2, 5, 10, 15], "name": "normal"}, {"band": [10, 15, 30, 50], "name": "slow"}, {"name": "very_slow", "up": [30, 50]}], "min_change": 5, "name": "disk.read_await", "pack": "disk", "pairs_with": ["cache.read_in", "disk.busy"], "reading": "each minute's ratio of sums", "signal": {"den": ["systemMetrics/disks/{i}/reads"], "min_den": 60, "mode": "rate", "num": ["systemMetrics/disks/{i}/read_time_ms"], "real_device": true, "scale": 1, "unit": "ms"}, "title": "Disk time per read", "unit": "ms", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"applies": "A device that serves requests in parallel, such as an SSD, NVMe or network volume, can show io_time near 100 % with capacity to spare; disk.await shows whether requests waited. Device-mapper (dm-*) devices are not read by this tool; the disks under them are.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which a device's io_time advanced by more than 95 % of the elapsed time, normalized to a 60-second minute.", "elevated": 1, "formula": "ΔsystemMetrics/disks/{i}/io_time_ms per second × 0.1, in %, at each available sample; real block devices only", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "disk.busy_above_95", "open_with": ["disk.await"], "pack": "disk", "pairs_with": ["disk.busy", "disk.await", "checkpoint.running"], "reading": "valid-sample share strictly above 95 %, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "rate", "num": ["systemMetrics/disks/{i}/io_time_ms"], "real_device": true, "scale": 0.1, "unit": "%"}, "threshold": 95, "title": "Device-busy samples above 95%", "unit": "s/min", "version_text": "all versions", "view": "time_above"}</t>
         </is>
       </c>
     </row>
@@ -9560,7 +9742,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>disk.write_await</t>
+          <t>disk.await</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -9570,7 +9752,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "fast ≤2 (fading to 5) · normal 5–10 (edges 2, 15) · slow 15–30 (edges 10, 50) · very_slow ≥50 (from 30)", "doc": "Average milliseconds a write took on each device.", "elevated": 20, "formula": "ΔsystemMetrics/disks/{i}/write_time_ms ÷ ΔsystemMetrics/disks/{i}/writes, in ms, at each available sample; minutes where the divisor sums to under 60 are left out; real block devices only", "levels": [{"down": [2, 5], "name": "fast"}, {"band": [2, 5, 10, 15], "name": "normal"}, {"band": [10, 15, 30, 50], "name": "slow"}, {"name": "very_slow", "up": [30, 50]}], "min_change": 5, "name": "disk.write_await", "pack": "disk", "pairs_with": ["checkpoint.duration", "cache.dirty", "tickets.write.scarce"], "reading": "each minute's ratio of sums", "signal": {"den": ["systemMetrics/disks/{i}/writes"], "min_den": 60, "mode": "rate", "num": ["systemMetrics/disks/{i}/write_time_ms"], "real_device": true, "scale": 1, "unit": "ms"}, "title": "Disk time per write", "unit": "ms", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "fast ≤2 (fading to 5) · normal 5–10 (edges 2, 15) · slow 15–30 (edges 10, 50) · very_slow ≥50 (from 30)", "doc": "Average milliseconds a read or write took on each device, queueing included — what iostat calls await.", "elevated": 20, "formula": "Δ(systemMetrics/disks/{i}/read_time_ms + systemMetrics/disks/{i}/write_time_ms) ÷ Δ(systemMetrics/disks/{i}/reads + systemMetrics/disks/{i}/writes), in ms, at each available sample; minutes where the divisor sums to under 60 are left out; real block devices only", "levels": [{"down": [2, 5], "name": "fast"}, {"band": [2, 5, 10, 15], "name": "normal"}, {"band": [10, 15, 30, 50], "name": "slow"}, {"name": "very_slow", "up": [30, 50]}], "min_change": 5, "name": "disk.await", "pack": "disk", "pairs_with": ["disk.busy", "disk.queue", "cpu.iowait"], "reading": "each minute's ratio of sums", "signal": {"den": ["systemMetrics/disks/{i}/reads", "systemMetrics/disks/{i}/writes"], "min_den": 60, "mode": "rate", "num": ["systemMetrics/disks/{i}/read_time_ms", "systemMetrics/disks/{i}/write_time_ms"], "real_device": true, "scale": 1, "unit": "ms"}, "title": "Disk time per request", "unit": "ms", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9580,7 +9762,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>disk.queue</t>
+          <t>disk.read_await</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -9590,7 +9772,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "shallow ≤1 (fading to 2) · moderate 2–8 (edges 1, 16) · deep ≥16 (from 8)", "doc": "Average number of requests outstanding on each device over the minute (io_queued time over wall time).", "elevated": 8, "formula": "ΔsystemMetrics/disks/{i}/io_queued_ms per second × 0.001, in requests, at each available sample; real block devices only", "levels": [{"down": [1, 2], "name": "shallow"}, {"band": [1, 2, 8, 16], "name": "moderate"}, {"name": "deep", "up": [8, 16]}], "min_change": 2, "name": "disk.queue", "open_with": ["disk.await"], "pack": "disk", "pairs_with": ["disk.await", "disk.busy"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["systemMetrics/disks/{i}/io_queued_ms"], "real_device": true, "scale": 0.001, "unit": "requests"}, "title": "Disk requests in flight", "unit": "requests", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "fast ≤2 (fading to 5) · normal 5–10 (edges 2, 15) · slow 15–30 (edges 10, 50) · very_slow ≥50 (from 30)", "doc": "Average milliseconds a read took on each device.", "elevated": 20, "formula": "ΔsystemMetrics/disks/{i}/read_time_ms ÷ ΔsystemMetrics/disks/{i}/reads, in ms, at each available sample; minutes where the divisor sums to under 60 are left out; real block devices only", "levels": [{"down": [2, 5], "name": "fast"}, {"band": [2, 5, 10, 15], "name": "normal"}, {"band": [10, 15, 30, 50], "name": "slow"}, {"name": "very_slow", "up": [30, 50]}], "min_change": 5, "name": "disk.read_await", "pack": "disk", "pairs_with": ["cache.read_in", "disk.busy"], "reading": "each minute's ratio of sums", "signal": {"den": ["systemMetrics/disks/{i}/reads"], "min_den": 60, "mode": "rate", "num": ["systemMetrics/disks/{i}/read_time_ms"], "real_device": true, "scale": 1, "unit": "ms"}, "title": "Disk time per read", "unit": "ms", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9600,7 +9782,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>disk.iops</t>
+          <t>disk.write_await</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -9610,7 +9792,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "doc": "Reads plus writes a second on each device.", "formula": "Δ(systemMetrics/disks/{i}/reads + systemMetrics/disks/{i}/writes) per second, in /s, at each available sample; real block devices only", "min_change": 100, "name": "disk.iops", "pack": "disk", "pairs_with": ["disk.busy", "disk.await"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["systemMetrics/disks/{i}/reads", "systemMetrics/disks/{i}/writes"], "real_device": true, "scale": 1, "unit": "/s"}, "title": "Disk requests a second", "unit": "/s", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "fast ≤2 (fading to 5) · normal 5–10 (edges 2, 15) · slow 15–30 (edges 10, 50) · very_slow ≥50 (from 30)", "doc": "Average milliseconds a write took on each device.", "elevated": 20, "formula": "ΔsystemMetrics/disks/{i}/write_time_ms ÷ ΔsystemMetrics/disks/{i}/writes, in ms, at each available sample; minutes where the divisor sums to under 60 are left out; real block devices only", "levels": [{"down": [2, 5], "name": "fast"}, {"band": [2, 5, 10, 15], "name": "normal"}, {"band": [10, 15, 30, 50], "name": "slow"}, {"name": "very_slow", "up": [30, 50]}], "min_change": 5, "name": "disk.write_await", "pack": "disk", "pairs_with": ["checkpoint.duration", "cache.dirty", "tickets.write.scarce"], "reading": "each minute's ratio of sums", "signal": {"den": ["systemMetrics/disks/{i}/writes"], "min_den": 60, "mode": "rate", "num": ["systemMetrics/disks/{i}/write_time_ms"], "real_device": true, "scale": 1, "unit": "ms"}, "title": "Disk time per write", "unit": "ms", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9802,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>disk.throughput</t>
+          <t>disk.queue</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -9630,7 +9812,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "doc": "Megabytes a second read plus written on each device (sectors are 512 bytes).", "formula": "Δ(systemMetrics/disks/{i}/read_sectors + systemMetrics/disks/{i}/write_sectors) per second × 0.000512, in MB/s, at each available sample; real block devices only", "min_change": 10, "name": "disk.throughput", "pack": "disk", "pairs_with": ["disk.busy", "disk.iops"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["systemMetrics/disks/{i}/read_sectors", "systemMetrics/disks/{i}/write_sectors"], "real_device": true, "scale": 0.000512, "unit": "MB/s"}, "title": "Disk throughput", "unit": "MB/s", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "shallow ≤1 (fading to 2) · moderate 2–8 (edges 1, 16) · deep ≥16 (from 8)", "doc": "Average number of requests outstanding on each device over the minute (io_queued time over wall time).", "elevated": 8, "formula": "ΔsystemMetrics/disks/{i}/io_queued_ms per second × 0.001, in requests, at each available sample; real block devices only", "levels": [{"down": [1, 2], "name": "shallow"}, {"band": [1, 2, 8, 16], "name": "moderate"}, {"name": "deep", "up": [8, 16]}], "min_change": 2, "name": "disk.queue", "open_with": ["disk.await"], "pack": "disk", "pairs_with": ["disk.await", "disk.busy"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["systemMetrics/disks/{i}/io_queued_ms"], "real_device": true, "scale": 0.001, "unit": "requests"}, "title": "Disk requests in flight", "unit": "requests", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9640,7 +9822,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>net.retransmit</t>
+          <t>disk.iops</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -9650,7 +9832,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "low ≤0.1 (fading to 0.3) · moderate 0.3–0.7 (edges 0.1, 1) · high 1–2 (edges 0.7, 3) · very_high ≥3 (from 2)", "doc": "Ratio of the host TCP RetransSegs counter advance to the OutSegs counter advance, across host connections.", "elevated": 1, "formula": "ΔsystemMetrics/netstat/Tcp:RetransSegs ÷ ΔsystemMetrics/netstat/Tcp:OutSegs × 100, in %, at each available sample; minutes where the divisor sums to under 1000 are left out", "levels": [{"down": [0.1, 0.3], "name": "low"}, {"band": [0.1, 0.3, 0.7, 1], "name": "moderate"}, {"band": [0.7, 1, 2, 3], "name": "high"}, {"name": "very_high", "up": [2, 3]}], "min_change": 0.5, "name": "net.retransmit", "pack": "network", "pairs_with": ["repl.member_lag", "net.resets"], "reading": "each minute's ratio of sums", "signal": {"den": ["systemMetrics/netstat/Tcp:OutSegs"], "min_den": 1000, "mode": "rate", "num": ["systemMetrics/netstat/Tcp:RetransSegs"], "scale": 100, "unit": "%"}, "title": "TCP retransmission", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "none — read for its shape only", "doc": "Reads plus writes a second on each device.", "formula": "Δ(systemMetrics/disks/{i}/reads + systemMetrics/disks/{i}/writes) per second, in /s, at each available sample; real block devices only", "min_change": 100, "name": "disk.iops", "pack": "disk", "pairs_with": ["disk.busy", "disk.await"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["systemMetrics/disks/{i}/reads", "systemMetrics/disks/{i}/writes"], "real_device": true, "scale": 1, "unit": "/s"}, "title": "Disk requests a second", "unit": "/s", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9842,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>net.listen_overflows</t>
+          <t>disk.throughput</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -9670,7 +9852,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤0.01 (fading to 0.1) · some 0.1–1 (edges 0.01, 5) · many ≥5 (from 1)", "doc": "Rate of the host TCP ListenOverflows counter; the counter does not identify a MongoDB connection or client outcome.", "elevated": 0.1, "formula": "ΔsystemMetrics/netstat/TcpExt:ListenOverflows per second, in /s, at each available sample", "levels": [{"down": [0.01, 0.1], "name": "none"}, {"band": [0.01, 0.1, 1, 5], "name": "some"}, {"name": "many", "up": [1, 5]}], "min_change": 0.1, "name": "net.listen_overflows", "pack": "network", "pairs_with": ["connections.created", "cpu.busy_above_95"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["systemMetrics/netstat/TcpExt:ListenOverflows"], "scale": 1, "unit": "/s"}, "title": "Listen queue overflows", "unit": "/s", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "none — read for its shape only", "doc": "Megabytes a second read plus written on each device (sectors are 512 bytes).", "formula": "Δ(systemMetrics/disks/{i}/read_sectors + systemMetrics/disks/{i}/write_sectors) per second × 0.000512, in MB/s, at each available sample; real block devices only", "min_change": 10, "name": "disk.throughput", "pack": "disk", "pairs_with": ["disk.busy", "disk.iops"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["systemMetrics/disks/{i}/read_sectors", "systemMetrics/disks/{i}/write_sectors"], "real_device": true, "scale": 0.000512, "unit": "MB/s"}, "title": "Disk throughput", "unit": "MB/s", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9680,7 +9862,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>net.resets</t>
+          <t>net.retransmit</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -9690,7 +9872,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "doc": "Established connections reset a second, host-wide.", "formula": "ΔsystemMetrics/netstat/Tcp:EstabResets per second, in /s, at each available sample", "min_change": 5, "name": "net.resets", "pack": "network", "pairs_with": ["connections.created", "net.retransmit"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["systemMetrics/netstat/Tcp:EstabResets"], "scale": 1, "unit": "/s"}, "title": "TCP connections reset", "unit": "/s", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "low ≤0.1 (fading to 0.3) · moderate 0.3–0.7 (edges 0.1, 1) · high 1–2 (edges 0.7, 3) · very_high ≥3 (from 2)", "doc": "Ratio of the host TCP RetransSegs counter advance to the OutSegs counter advance, across host connections.", "elevated": 1, "formula": "ΔsystemMetrics/netstat/Tcp:RetransSegs ÷ ΔsystemMetrics/netstat/Tcp:OutSegs × 100, in %, at each available sample; minutes where the divisor sums to under 1000 are left out", "levels": [{"down": [0.1, 0.3], "name": "low"}, {"band": [0.1, 0.3, 0.7, 1], "name": "moderate"}, {"band": [0.7, 1, 2, 3], "name": "high"}, {"name": "very_high", "up": [2, 3]}], "min_change": 0.5, "name": "net.retransmit", "pack": "network", "pairs_with": ["repl.member_lag", "net.resets"], "reading": "each minute's ratio of sums", "signal": {"den": ["systemMetrics/netstat/Tcp:OutSegs"], "min_den": 1000, "mode": "rate", "num": ["systemMetrics/netstat/Tcp:RetransSegs"], "scale": 100, "unit": "%"}, "title": "TCP retransmission", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9700,7 +9882,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>net.traffic</t>
+          <t>net.listen_overflows</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -9710,7 +9892,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "doc": "Sum of the server's bytesIn and bytesOut counter rates, scaled to MB/s.", "formula": "Δ(serverStatus/network/bytesIn + serverStatus/network/bytesOut) per second × 1e-06, in MB/s, at each available sample", "min_change": 5, "name": "net.traffic", "pack": "network", "pairs_with": ["ops.total", "net.retransmit"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/network/bytesIn", "serverStatus/network/bytesOut"], "scale": 1e-06, "unit": "MB/s"}, "title": "mongod network traffic", "unit": "MB/s", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "none ≤0.01 (fading to 0.1) · some 0.1–1 (edges 0.01, 5) · many ≥5 (from 1)", "doc": "Rate of the host TCP ListenOverflows counter; the counter does not identify a MongoDB connection or client outcome.", "elevated": 0.1, "formula": "ΔsystemMetrics/netstat/TcpExt:ListenOverflows per second, in /s, at each available sample", "levels": [{"down": [0.01, 0.1], "name": "none"}, {"band": [0.01, 0.1, 1, 5], "name": "some"}, {"name": "many", "up": [1, 5]}], "min_change": 0.1, "name": "net.listen_overflows", "pack": "network", "pairs_with": ["connections.created", "cpu.busy_above_95"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["systemMetrics/netstat/TcpExt:ListenOverflows"], "scale": 1, "unit": "/s"}, "title": "Listen queue overflows", "unit": "/s", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9720,7 +9902,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>files.handles</t>
+          <t>net.resets</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -9730,7 +9912,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "normal ≤15000 (fading to 30000) · many 30000–60000 (edges 15000, 90000) · very_high ≥90000 (from 60000)", "doc": "File handles allocated on the whole machine, every process together. FTDC does not record the kernel's limit (fs.file-max), so the bands are fixed reference counts, not a share of this host's limit; when the limit is reached the kernel refuses new files and sockets to every process. A climb that never comes back down is worth reading beside connections.", "elevated": 60000, "formula": "systemMetrics/files/sys_file_handles_in_use, in handles, at each available sample", "levels": [{"down": [15000, 30000], "name": "normal"}, {"band": [15000, 30000, 60000, 90000], "name": "many"}, {"name": "very_high", "up": [60000, 90000]}], "min_change": 2000, "name": "files.handles", "pack": "files", "pairs_with": ["connections.current"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["systemMetrics/files/sys_file_handles_in_use"], "scale": 1, "unit": "handles"}, "title": "File handles in use", "unit": "handles", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "none — read for its shape only", "doc": "Established connections reset a second, host-wide.", "formula": "ΔsystemMetrics/netstat/Tcp:EstabResets per second, in /s, at each available sample", "min_change": 5, "name": "net.resets", "pack": "network", "pairs_with": ["connections.created", "net.retransmit"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["systemMetrics/netstat/Tcp:EstabResets"], "scale": 1, "unit": "/s"}, "title": "TCP connections reset", "unit": "/s", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9740,17 +9922,17 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.used</t>
+          <t>net.traffic</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>before 8.0</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.", "bands": "low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)", "doc": "Read tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.", "elevated": 75, "formula": "serverStatus/wiredTiger/concurrentTransactions/read/out ÷ serverStatus/wiredTiger/concurrentTransactions/read/totalTickets × 100, in %, at each available sample", "levels": [{"down": [25, 50], "name": "low"}, {"band": [25, 40, 65, 80], "name": "moderate"}, {"band": [65, 75, 90, 95], "name": "high"}, {"name": "near_full", "up": [90, 95]}], "min_change": 10, "name": "tickets.read.used", "pack": "admission", "pairs_with": ["tickets.read.scarce", "tickets.read.pool", "tickets.read.wait", "queue.readers"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/wiredTiger/concurrentTransactions/read/totalTickets"], "mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/read/out"], "scale": 100, "unit": "%"}, "title": "Read tickets in use", "unit": "%", "until": "8.0", "version_text": "before 8.0", "view": "mean"}</t>
+          <t>{"bands": "none — read for its shape only", "doc": "Sum of the server's bytesIn and bytesOut counter rates, scaled to MB/s.", "formula": "Δ(serverStatus/network/bytesIn + serverStatus/network/bytesOut) per second × 1e-06, in MB/s, at each available sample", "min_change": 5, "name": "net.traffic", "pack": "network", "pairs_with": ["ops.total", "net.retransmit"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/network/bytesIn", "serverStatus/network/bytesOut"], "scale": 1e-06, "unit": "MB/s"}, "title": "mongod network traffic", "unit": "MB/s", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9760,17 +9942,17 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.scarce</t>
+          <t>files.handles</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>before 8.0</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which available read tickets were strictly below 10 % of the pool, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/wiredTiger/concurrentTransactions/read/available ÷ serverStatus/wiredTiger/concurrentTransactions/read/totalTickets × 100, in % available, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.read.scarce", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.read.empty", "tickets.read.used", "tickets.read.pool", "tickets.read.wait"], "reading": "valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/wiredTiger/concurrentTransactions/read/totalTickets"], "mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/read/available"], "scale": 100, "unit": "% available"}, "threshold": 10, "title": "Samples with under 10% of read tickets left", "unit": "s/min", "until": "8.0", "version_text": "before 8.0", "view": "time_below"}</t>
+          <t>{"bands": "normal ≤15000 (fading to 30000) · many 30000–60000 (edges 15000, 90000) · very_high ≥90000 (from 60000)", "doc": "File handles allocated on the whole machine, every process together. FTDC does not record the kernel's limit (fs.file-max), so the bands are fixed reference counts, not a share of this host's limit; when the limit is reached the kernel refuses new files and sockets to every process. A climb that never comes back down is worth reading beside connections.", "elevated": 60000, "formula": "systemMetrics/files/sys_file_handles_in_use, in handles, at each available sample", "levels": [{"down": [15000, 30000], "name": "normal"}, {"band": [15000, 30000, 60000, 90000], "name": "many"}, {"name": "very_high", "up": [60000, 90000]}], "min_change": 2000, "name": "files.handles", "pack": "files", "pairs_with": ["connections.current"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["systemMetrics/files/sys_file_handles_in_use"], "scale": 1, "unit": "handles"}, "title": "File handles in use", "unit": "handles", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9780,7 +9962,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.empty</t>
+          <t>tickets.read.used</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -9790,7 +9972,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which fewer than 0.5 read tickets were available, that is none, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/wiredTiger/concurrentTransactions/read/available, in tickets left, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.read.empty", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.read.used", "tickets.read.scarce", "tickets.read.pool", "tickets.read.wait", "queue.readers"], "reading": "valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/read/available"], "scale": 1, "unit": "tickets left"}, "threshold": 0.5, "title": "Samples with no read ticket left", "unit": "s/min", "until": "8.0", "version_text": "before 8.0", "view": "time_below"}</t>
+          <t>{"applies": "From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.", "bands": "low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)", "doc": "Read tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.", "elevated": 75, "formula": "serverStatus/wiredTiger/concurrentTransactions/read/out ÷ serverStatus/wiredTiger/concurrentTransactions/read/totalTickets × 100, in %, at each available sample", "levels": [{"down": [25, 50], "name": "low"}, {"band": [25, 40, 65, 80], "name": "moderate"}, {"band": [65, 75, 90, 95], "name": "high"}, {"name": "near_full", "up": [90, 95]}], "min_change": 10, "name": "tickets.read.used", "pack": "admission", "pairs_with": ["tickets.read.scarce", "tickets.read.pool", "tickets.read.wait", "queue.readers"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/wiredTiger/concurrentTransactions/read/totalTickets"], "mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/read/out"], "scale": 100, "unit": "%"}, "title": "Read tickets in use", "unit": "%", "until": "8.0", "version_text": "before 8.0", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9800,7 +9982,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.pool</t>
+          <t>tickets.read.scarce</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -9810,7 +9992,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "doc": "How many read tickets the pool held, averaged over the minute.", "formula": "serverStatus/wiredTiger/concurrentTransactions/read/totalTickets, in tickets, at each available sample", "min_change": 4, "name": "tickets.read.pool", "pack": "admission", "pairs_with": ["tickets.read.used", "tickets.read.scarce"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/read/totalTickets"], "scale": 1, "unit": "tickets"}, "title": "Read ticket pool size", "unit": "tickets", "until": "8.0", "version_text": "before 8.0", "view": "mean"}</t>
+          <t>{"applies": "From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which available read tickets were strictly below 10 % of the pool, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/wiredTiger/concurrentTransactions/read/available ÷ serverStatus/wiredTiger/concurrentTransactions/read/totalTickets × 100, in % available, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.read.scarce", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.read.empty", "tickets.read.used", "tickets.read.pool", "tickets.read.wait"], "reading": "valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/wiredTiger/concurrentTransactions/read/totalTickets"], "mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/read/available"], "scale": 100, "unit": "% available"}, "threshold": 10, "title": "Samples with under 10% of read tickets left", "unit": "s/min", "until": "8.0", "version_text": "before 8.0", "view": "time_below"}</t>
         </is>
       </c>
     </row>
@@ -9820,17 +10002,17 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.wait</t>
+          <t>tickets.read.empty</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>7.0 up to 8.0</t>
+          <t>before 8.0</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)", "doc": "Milliseconds a second operations spent queued for a read ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it.", "elevated": 100, "formula": "ΔserverStatus/wiredTiger/concurrentTransactions/read/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample", "levels": [{"down": [1, 10], "name": "none"}, {"band": [1, 10, 100, 500], "name": "some"}, {"name": "heavy", "up": [100, 500]}], "min_change": 10, "name": "tickets.read.wait", "pack": "admission", "pairs_with": ["tickets.read.empty", "tickets.read.scarce", "queue.readers"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/wiredTiger/concurrentTransactions/read/totalTimeQueuedMicros"], "scale": 0.001, "unit": "ms/s"}, "since": "7.0", "title": "Time waiting for a read ticket", "unit": "ms/s", "until": "8.0", "version_text": "7.0 up to 8.0", "view": "mean"}</t>
+          <t>{"applies": "From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which fewer than 0.5 read tickets were available, that is none, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/wiredTiger/concurrentTransactions/read/available, in tickets left, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.read.empty", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.read.used", "tickets.read.scarce", "tickets.read.pool", "tickets.read.wait", "queue.readers"], "reading": "valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/read/available"], "scale": 1, "unit": "tickets left"}, "threshold": 0.5, "title": "Samples with no read ticket left", "unit": "s/min", "until": "8.0", "version_text": "before 8.0", "view": "time_below"}</t>
         </is>
       </c>
     </row>
@@ -9840,17 +10022,17 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.used</t>
+          <t>tickets.read.pool</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>8.0 and later</t>
+          <t>before 8.0</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.", "bands": "low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)", "doc": "Read tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.", "elevated": 75, "formula": "serverStatus/queues/execution/read/out ÷ serverStatus/queues/execution/read/totalTickets × 100, in %, at each available sample", "levels": [{"down": [25, 50], "name": "low"}, {"band": [25, 40, 65, 80], "name": "moderate"}, {"band": [65, 75, 90, 95], "name": "high"}, {"name": "near_full", "up": [90, 95]}], "min_change": 10, "name": "tickets.read.used", "pack": "admission", "pairs_with": ["tickets.read.scarce", "tickets.read.pool", "tickets.read.wait", "queue.readers"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/queues/execution/read/totalTickets"], "mode": "gauge", "num": ["serverStatus/queues/execution/read/out"], "scale": 100, "unit": "%"}, "since": "8.0", "title": "Read tickets in use", "unit": "%", "version_text": "8.0 and later", "view": "mean"}</t>
+          <t>{"bands": "none — read for its shape only", "doc": "How many read tickets the pool held, averaged over the minute.", "formula": "serverStatus/wiredTiger/concurrentTransactions/read/totalTickets, in tickets, at each available sample", "min_change": 4, "name": "tickets.read.pool", "pack": "admission", "pairs_with": ["tickets.read.used", "tickets.read.scarce"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/read/totalTickets"], "scale": 1, "unit": "tickets"}, "title": "Read ticket pool size", "unit": "tickets", "until": "8.0", "version_text": "before 8.0", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9860,17 +10042,17 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.scarce</t>
+          <t>tickets.read.wait</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>8.0 and later</t>
+          <t>7.0 up to 8.0</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which available read tickets were strictly below 10 % of the pool, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/queues/execution/read/available ÷ serverStatus/queues/execution/read/totalTickets × 100, in % available, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.read.scarce", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.read.empty", "tickets.read.used", "tickets.read.pool", "tickets.read.wait"], "reading": "valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/queues/execution/read/totalTickets"], "mode": "gauge", "num": ["serverStatus/queues/execution/read/available"], "scale": 100, "unit": "% available"}, "since": "8.0", "threshold": 10, "title": "Samples with under 10% of read tickets left", "unit": "s/min", "version_text": "8.0 and later", "view": "time_below"}</t>
+          <t>{"bands": "none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)", "doc": "Milliseconds a second operations spent queued for a read ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it.", "elevated": 100, "formula": "ΔserverStatus/wiredTiger/concurrentTransactions/read/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample", "levels": [{"down": [1, 10], "name": "none"}, {"band": [1, 10, 100, 500], "name": "some"}, {"name": "heavy", "up": [100, 500]}], "min_change": 10, "name": "tickets.read.wait", "pack": "admission", "pairs_with": ["tickets.read.empty", "tickets.read.scarce", "queue.readers"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/wiredTiger/concurrentTransactions/read/totalTimeQueuedMicros"], "scale": 0.001, "unit": "ms/s"}, "since": "7.0", "title": "Time waiting for a read ticket", "unit": "ms/s", "until": "8.0", "version_text": "7.0 up to 8.0", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9880,7 +10062,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.empty</t>
+          <t>tickets.read.used</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -9890,7 +10072,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which fewer than 0.5 read tickets were available, that is none, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/queues/execution/read/available, in tickets left, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.read.empty", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.read.used", "tickets.read.scarce", "tickets.read.pool", "tickets.read.wait", "queue.readers"], "reading": "valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/queues/execution/read/available"], "scale": 1, "unit": "tickets left"}, "since": "8.0", "threshold": 0.5, "title": "Samples with no read ticket left", "unit": "s/min", "version_text": "8.0 and later", "view": "time_below"}</t>
+          <t>{"applies": "From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.", "bands": "low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)", "doc": "Read tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.", "elevated": 75, "formula": "serverStatus/queues/execution/read/out ÷ serverStatus/queues/execution/read/totalTickets × 100, in %, at each available sample", "levels": [{"down": [25, 50], "name": "low"}, {"band": [25, 40, 65, 80], "name": "moderate"}, {"band": [65, 75, 90, 95], "name": "high"}, {"name": "near_full", "up": [90, 95]}], "min_change": 10, "name": "tickets.read.used", "pack": "admission", "pairs_with": ["tickets.read.scarce", "tickets.read.pool", "tickets.read.wait", "queue.readers"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/queues/execution/read/totalTickets"], "mode": "gauge", "num": ["serverStatus/queues/execution/read/out"], "scale": 100, "unit": "%"}, "since": "8.0", "title": "Read tickets in use", "unit": "%", "version_text": "8.0 and later", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9900,7 +10082,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.pool</t>
+          <t>tickets.read.scarce</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -9910,7 +10092,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "doc": "How many read tickets the pool held, averaged over the minute.", "formula": "serverStatus/queues/execution/read/totalTickets, in tickets, at each available sample", "min_change": 4, "name": "tickets.read.pool", "pack": "admission", "pairs_with": ["tickets.read.used", "tickets.read.scarce"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/queues/execution/read/totalTickets"], "scale": 1, "unit": "tickets"}, "since": "8.0", "title": "Read ticket pool size", "unit": "tickets", "version_text": "8.0 and later", "view": "mean"}</t>
+          <t>{"applies": "From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which available read tickets were strictly below 10 % of the pool, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/queues/execution/read/available ÷ serverStatus/queues/execution/read/totalTickets × 100, in % available, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.read.scarce", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.read.empty", "tickets.read.used", "tickets.read.pool", "tickets.read.wait"], "reading": "valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/queues/execution/read/totalTickets"], "mode": "gauge", "num": ["serverStatus/queues/execution/read/available"], "scale": 100, "unit": "% available"}, "since": "8.0", "threshold": 10, "title": "Samples with under 10% of read tickets left", "unit": "s/min", "version_text": "8.0 and later", "view": "time_below"}</t>
         </is>
       </c>
     </row>
@@ -9920,7 +10102,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>tickets.read.wait</t>
+          <t>tickets.read.empty</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -9930,7 +10112,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)", "doc": "Milliseconds a second operations spent queued for a read ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. The counter covers normal-priority operations, not exempt operations.", "elevated": 100, "formula": "ΔserverStatus/queues/execution/read/normalPriority/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample", "levels": [{"down": [1, 10], "name": "none"}, {"band": [1, 10, 100, 500], "name": "some"}, {"name": "heavy", "up": [100, 500]}], "min_change": 10, "name": "tickets.read.wait", "pack": "admission", "pairs_with": ["tickets.read.empty", "tickets.read.scarce", "queue.readers"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/queues/execution/read/normalPriority/totalTimeQueuedMicros"], "scale": 0.001, "unit": "ms/s"}, "since": "8.0", "title": "Time waiting for a read ticket", "unit": "ms/s", "version_text": "8.0 and later", "view": "mean"}</t>
+          <t>{"applies": "From 7.0 the server may resize the read ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.read.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which fewer than 0.5 read tickets were available, that is none, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/queues/execution/read/available, in tickets left, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.read.empty", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.read.used", "tickets.read.scarce", "tickets.read.pool", "tickets.read.wait", "queue.readers"], "reading": "valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/queues/execution/read/available"], "scale": 1, "unit": "tickets left"}, "since": "8.0", "threshold": 0.5, "title": "Samples with no read ticket left", "unit": "s/min", "version_text": "8.0 and later", "view": "time_below"}</t>
         </is>
       </c>
     </row>
@@ -9940,17 +10122,17 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.used</t>
+          <t>tickets.read.pool</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>before 8.0</t>
+          <t>8.0 and later</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.", "bands": "low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)", "doc": "Write tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.", "elevated": 75, "formula": "serverStatus/wiredTiger/concurrentTransactions/write/out ÷ serverStatus/wiredTiger/concurrentTransactions/write/totalTickets × 100, in %, at each available sample", "levels": [{"down": [25, 50], "name": "low"}, {"band": [25, 40, 65, 80], "name": "moderate"}, {"band": [65, 75, 90, 95], "name": "high"}, {"name": "near_full", "up": [90, 95]}], "min_change": 10, "name": "tickets.write.used", "pack": "admission", "pairs_with": ["tickets.write.scarce", "tickets.write.pool", "tickets.write.wait", "queue.writers"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/wiredTiger/concurrentTransactions/write/totalTickets"], "mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/write/out"], "scale": 100, "unit": "%"}, "title": "Write tickets in use", "unit": "%", "until": "8.0", "version_text": "before 8.0", "view": "mean"}</t>
+          <t>{"bands": "none — read for its shape only", "doc": "How many read tickets the pool held, averaged over the minute.", "formula": "serverStatus/queues/execution/read/totalTickets, in tickets, at each available sample", "min_change": 4, "name": "tickets.read.pool", "pack": "admission", "pairs_with": ["tickets.read.used", "tickets.read.scarce"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/queues/execution/read/totalTickets"], "scale": 1, "unit": "tickets"}, "since": "8.0", "title": "Read ticket pool size", "unit": "tickets", "version_text": "8.0 and later", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9960,17 +10142,17 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.scarce</t>
+          <t>tickets.read.wait</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>before 8.0</t>
+          <t>8.0 and later</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which available write tickets were strictly below 10 % of the pool, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/wiredTiger/concurrentTransactions/write/available ÷ serverStatus/wiredTiger/concurrentTransactions/write/totalTickets × 100, in % available, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.write.scarce", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.write.empty", "tickets.write.used", "tickets.write.pool", "tickets.write.wait"], "reading": "valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/wiredTiger/concurrentTransactions/write/totalTickets"], "mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/write/available"], "scale": 100, "unit": "% available"}, "threshold": 10, "title": "Samples with under 10% of write tickets left", "unit": "s/min", "until": "8.0", "version_text": "before 8.0", "view": "time_below"}</t>
+          <t>{"bands": "none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)", "doc": "Milliseconds a second operations spent queued for a read ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. The counter covers normal-priority operations, not exempt operations.", "elevated": 100, "formula": "ΔserverStatus/queues/execution/read/normalPriority/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample", "levels": [{"down": [1, 10], "name": "none"}, {"band": [1, 10, 100, 500], "name": "some"}, {"name": "heavy", "up": [100, 500]}], "min_change": 10, "name": "tickets.read.wait", "pack": "admission", "pairs_with": ["tickets.read.empty", "tickets.read.scarce", "queue.readers"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/queues/execution/read/normalPriority/totalTimeQueuedMicros"], "scale": 0.001, "unit": "ms/s"}, "since": "8.0", "title": "Time waiting for a read ticket", "unit": "ms/s", "version_text": "8.0 and later", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -9980,7 +10162,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.empty</t>
+          <t>tickets.write.used</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -9990,7 +10172,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which fewer than 0.5 write tickets were available, that is none, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/wiredTiger/concurrentTransactions/write/available, in tickets left, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.write.empty", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.write.used", "tickets.write.scarce", "tickets.write.pool", "tickets.write.wait", "queue.writers"], "reading": "valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/write/available"], "scale": 1, "unit": "tickets left"}, "threshold": 0.5, "title": "Samples with no write ticket left", "unit": "s/min", "until": "8.0", "version_text": "before 8.0", "view": "time_below"}</t>
+          <t>{"applies": "From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.", "bands": "low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)", "doc": "Write tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.", "elevated": 75, "formula": "serverStatus/wiredTiger/concurrentTransactions/write/out ÷ serverStatus/wiredTiger/concurrentTransactions/write/totalTickets × 100, in %, at each available sample", "levels": [{"down": [25, 50], "name": "low"}, {"band": [25, 40, 65, 80], "name": "moderate"}, {"band": [65, 75, 90, 95], "name": "high"}, {"name": "near_full", "up": [90, 95]}], "min_change": 10, "name": "tickets.write.used", "pack": "admission", "pairs_with": ["tickets.write.scarce", "tickets.write.pool", "tickets.write.wait", "queue.writers"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/wiredTiger/concurrentTransactions/write/totalTickets"], "mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/write/out"], "scale": 100, "unit": "%"}, "title": "Write tickets in use", "unit": "%", "until": "8.0", "version_text": "before 8.0", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10000,7 +10182,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.pool</t>
+          <t>tickets.write.scarce</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -10010,7 +10192,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "doc": "How many write tickets the pool held, averaged over the minute.", "formula": "serverStatus/wiredTiger/concurrentTransactions/write/totalTickets, in tickets, at each available sample", "min_change": 4, "name": "tickets.write.pool", "pack": "admission", "pairs_with": ["tickets.write.used", "tickets.write.scarce"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/write/totalTickets"], "scale": 1, "unit": "tickets"}, "title": "Write ticket pool size", "unit": "tickets", "until": "8.0", "version_text": "before 8.0", "view": "mean"}</t>
+          <t>{"applies": "From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which available write tickets were strictly below 10 % of the pool, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/wiredTiger/concurrentTransactions/write/available ÷ serverStatus/wiredTiger/concurrentTransactions/write/totalTickets × 100, in % available, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.write.scarce", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.write.empty", "tickets.write.used", "tickets.write.pool", "tickets.write.wait"], "reading": "valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/wiredTiger/concurrentTransactions/write/totalTickets"], "mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/write/available"], "scale": 100, "unit": "% available"}, "threshold": 10, "title": "Samples with under 10% of write tickets left", "unit": "s/min", "until": "8.0", "version_text": "before 8.0", "view": "time_below"}</t>
         </is>
       </c>
     </row>
@@ -10020,17 +10202,17 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.wait</t>
+          <t>tickets.write.empty</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>7.0 up to 8.0</t>
+          <t>before 8.0</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)", "doc": "Milliseconds a second operations spent queued for a write ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it.", "elevated": 100, "formula": "ΔserverStatus/wiredTiger/concurrentTransactions/write/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample", "levels": [{"down": [1, 10], "name": "none"}, {"band": [1, 10, 100, 500], "name": "some"}, {"name": "heavy", "up": [100, 500]}], "min_change": 10, "name": "tickets.write.wait", "pack": "admission", "pairs_with": ["tickets.write.empty", "tickets.write.scarce", "queue.writers"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/wiredTiger/concurrentTransactions/write/totalTimeQueuedMicros"], "scale": 0.001, "unit": "ms/s"}, "since": "7.0", "title": "Time waiting for a write ticket", "unit": "ms/s", "until": "8.0", "version_text": "7.0 up to 8.0", "view": "mean"}</t>
+          <t>{"applies": "From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which fewer than 0.5 write tickets were available, that is none, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/wiredTiger/concurrentTransactions/write/available, in tickets left, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.write.empty", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.write.used", "tickets.write.scarce", "tickets.write.pool", "tickets.write.wait", "queue.writers"], "reading": "valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/write/available"], "scale": 1, "unit": "tickets left"}, "threshold": 0.5, "title": "Samples with no write ticket left", "unit": "s/min", "until": "8.0", "version_text": "before 8.0", "view": "time_below"}</t>
         </is>
       </c>
     </row>
@@ -10040,17 +10222,17 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.used</t>
+          <t>tickets.write.pool</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>8.0 and later</t>
+          <t>before 8.0</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.", "bands": "low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)", "doc": "Write tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.", "elevated": 75, "formula": "serverStatus/queues/execution/write/out ÷ serverStatus/queues/execution/write/totalTickets × 100, in %, at each available sample", "levels": [{"down": [25, 50], "name": "low"}, {"band": [25, 40, 65, 80], "name": "moderate"}, {"band": [65, 75, 90, 95], "name": "high"}, {"name": "near_full", "up": [90, 95]}], "min_change": 10, "name": "tickets.write.used", "pack": "admission", "pairs_with": ["tickets.write.scarce", "tickets.write.pool", "tickets.write.wait", "queue.writers"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/queues/execution/write/totalTickets"], "mode": "gauge", "num": ["serverStatus/queues/execution/write/out"], "scale": 100, "unit": "%"}, "since": "8.0", "title": "Write tickets in use", "unit": "%", "version_text": "8.0 and later", "view": "mean"}</t>
+          <t>{"bands": "none — read for its shape only", "doc": "How many write tickets the pool held, averaged over the minute.", "formula": "serverStatus/wiredTiger/concurrentTransactions/write/totalTickets, in tickets, at each available sample", "min_change": 4, "name": "tickets.write.pool", "pack": "admission", "pairs_with": ["tickets.write.used", "tickets.write.scarce"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/concurrentTransactions/write/totalTickets"], "scale": 1, "unit": "tickets"}, "title": "Write ticket pool size", "unit": "tickets", "until": "8.0", "version_text": "before 8.0", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10060,17 +10242,17 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.scarce</t>
+          <t>tickets.write.wait</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>8.0 and later</t>
+          <t>7.0 up to 8.0</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which available write tickets were strictly below 10 % of the pool, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/queues/execution/write/available ÷ serverStatus/queues/execution/write/totalTickets × 100, in % available, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.write.scarce", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.write.empty", "tickets.write.used", "tickets.write.pool", "tickets.write.wait"], "reading": "valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/queues/execution/write/totalTickets"], "mode": "gauge", "num": ["serverStatus/queues/execution/write/available"], "scale": 100, "unit": "% available"}, "since": "8.0", "threshold": 10, "title": "Samples with under 10% of write tickets left", "unit": "s/min", "version_text": "8.0 and later", "view": "time_below"}</t>
+          <t>{"bands": "none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)", "doc": "Milliseconds a second operations spent queued for a write ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it.", "elevated": 100, "formula": "ΔserverStatus/wiredTiger/concurrentTransactions/write/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample", "levels": [{"down": [1, 10], "name": "none"}, {"band": [1, 10, 100, 500], "name": "some"}, {"name": "heavy", "up": [100, 500]}], "min_change": 10, "name": "tickets.write.wait", "pack": "admission", "pairs_with": ["tickets.write.empty", "tickets.write.scarce", "queue.writers"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/wiredTiger/concurrentTransactions/write/totalTimeQueuedMicros"], "scale": 0.001, "unit": "ms/s"}, "since": "7.0", "title": "Time waiting for a write ticket", "unit": "ms/s", "until": "8.0", "version_text": "7.0 up to 8.0", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10080,7 +10262,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.empty</t>
+          <t>tickets.write.used</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -10090,7 +10272,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which fewer than 0.5 write tickets were available, that is none, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/queues/execution/write/available, in tickets left, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.write.empty", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.write.used", "tickets.write.scarce", "tickets.write.pool", "tickets.write.wait", "queue.writers"], "reading": "valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/queues/execution/write/available"], "scale": 1, "unit": "tickets left"}, "since": "8.0", "threshold": 0.5, "title": "Samples with no write ticket left", "unit": "s/min", "version_text": "8.0 and later", "view": "time_below"}</t>
+          <t>{"applies": "From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.", "bands": "low ≤25 (fading to 50) · moderate 40–65 (edges 25, 80) · high 75–90 (edges 65, 95) · near_full ≥95 (from 90)", "doc": "Write tickets in use as a share of the pool as it was that second (out over totalTickets), averaged over the minute.", "elevated": 75, "formula": "serverStatus/queues/execution/write/out ÷ serverStatus/queues/execution/write/totalTickets × 100, in %, at each available sample", "levels": [{"down": [25, 50], "name": "low"}, {"band": [25, 40, 65, 80], "name": "moderate"}, {"band": [65, 75, 90, 95], "name": "high"}, {"name": "near_full", "up": [90, 95]}], "min_change": 10, "name": "tickets.write.used", "pack": "admission", "pairs_with": ["tickets.write.scarce", "tickets.write.pool", "tickets.write.wait", "queue.writers"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/queues/execution/write/totalTickets"], "mode": "gauge", "num": ["serverStatus/queues/execution/write/out"], "scale": 100, "unit": "%"}, "since": "8.0", "title": "Write tickets in use", "unit": "%", "version_text": "8.0 and later", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10100,7 +10282,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.pool</t>
+          <t>tickets.write.scarce</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -10110,7 +10292,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "doc": "How many write tickets the pool held, averaged over the minute.", "formula": "serverStatus/queues/execution/write/totalTickets, in tickets, at each available sample", "min_change": 4, "name": "tickets.write.pool", "pack": "admission", "pairs_with": ["tickets.write.used", "tickets.write.scarce"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/queues/execution/write/totalTickets"], "scale": 1, "unit": "tickets"}, "since": "8.0", "title": "Write ticket pool size", "unit": "tickets", "version_text": "8.0 and later", "view": "mean"}</t>
+          <t>{"applies": "From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which available write tickets were strictly below 10 % of the pool, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/queues/execution/write/available ÷ serverStatus/queues/execution/write/totalTickets × 100, in % available, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.write.scarce", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.write.empty", "tickets.write.used", "tickets.write.pool", "tickets.write.wait"], "reading": "valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/queues/execution/write/totalTickets"], "mode": "gauge", "num": ["serverStatus/queues/execution/write/available"], "scale": 100, "unit": "% available"}, "since": "8.0", "threshold": 10, "title": "Samples with under 10% of write tickets left", "unit": "s/min", "version_text": "8.0 and later", "view": "time_below"}</t>
         </is>
       </c>
     </row>
@@ -10120,7 +10302,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>tickets.write.wait</t>
+          <t>tickets.write.empty</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -10130,7 +10312,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)", "doc": "Milliseconds a second operations spent queued for a write ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. The counter covers normal-priority operations, not exempt operations.", "elevated": 100, "formula": "ΔserverStatus/queues/execution/write/normalPriority/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample", "levels": [{"down": [1, 10], "name": "none"}, {"band": [1, 10, 100, 500], "name": "some"}, {"name": "heavy", "up": [100, 500]}], "min_change": 10, "name": "tickets.write.wait", "pack": "admission", "pairs_with": ["tickets.write.empty", "tickets.write.scarce", "queue.writers"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/queues/execution/write/normalPriority/totalTimeQueuedMicros"], "scale": 0.001, "unit": "ms/s"}, "since": "8.0", "title": "Time waiting for a write ticket", "unit": "ms/s", "version_text": "8.0 and later", "view": "mean"}</t>
+          <t>{"applies": "From 7.0 the server may resize the write ticket pool itself; a share of a small pool and of a large one are not alike, so read it beside tickets.write.pool.", "bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which fewer than 0.5 write tickets were available, that is none, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/queues/execution/write/available, in tickets left, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "tickets.write.empty", "open_at": "brief", "pack": "admission", "pairs_with": ["tickets.write.used", "tickets.write.scarce", "tickets.write.pool", "tickets.write.wait", "queue.writers"], "reading": "valid-sample share strictly below 0.5 tickets left, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/queues/execution/write/available"], "scale": 1, "unit": "tickets left"}, "since": "8.0", "threshold": 0.5, "title": "Samples with no write ticket left", "unit": "s/min", "version_text": "8.0 and later", "view": "time_below"}</t>
         </is>
       </c>
     </row>
@@ -10140,17 +10322,17 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>queue.readers</t>
+          <t>tickets.write.pool</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>8.0 and later</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which globalLock.currentQueue.readers was above 0, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/globalLock/currentQueue/readers, in operations, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "queue.readers", "pack": "admission", "pairs_with": ["tickets.read.empty", "tickets.read.wait"], "reading": "valid-sample share strictly above 0 operations, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/globalLock/currentQueue/readers"], "scale": 1, "unit": "operations"}, "threshold": 0, "title": "Samples with reads queued", "unit": "s/min", "version_text": "all versions", "view": "time_above"}</t>
+          <t>{"bands": "none — read for its shape only", "doc": "How many write tickets the pool held, averaged over the minute.", "formula": "serverStatus/queues/execution/write/totalTickets, in tickets, at each available sample", "min_change": 4, "name": "tickets.write.pool", "pack": "admission", "pairs_with": ["tickets.write.used", "tickets.write.scarce"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/queues/execution/write/totalTickets"], "scale": 1, "unit": "tickets"}, "since": "8.0", "title": "Write ticket pool size", "unit": "tickets", "version_text": "8.0 and later", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10160,17 +10342,17 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>queue.writers</t>
+          <t>tickets.write.wait</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>8.0 and later</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which globalLock.currentQueue.writers was above 0, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/globalLock/currentQueue/writers, in operations, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "queue.writers", "pack": "admission", "pairs_with": ["tickets.write.empty", "tickets.write.wait"], "reading": "valid-sample share strictly above 0 operations, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/globalLock/currentQueue/writers"], "scale": 1, "unit": "operations"}, "threshold": 0, "title": "Samples with writes queued", "unit": "s/min", "version_text": "all versions", "view": "time_above"}</t>
+          <t>{"bands": "none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)", "doc": "Milliseconds a second operations spent queued for a write ticket, added across every operation waiting: 1000 is one operation waiting the whole second, or ten waiting a tenth of it. The counter covers normal-priority operations, not exempt operations.", "elevated": 100, "formula": "ΔserverStatus/queues/execution/write/normalPriority/totalTimeQueuedMicros per second × 0.001, in ms/s, at each available sample", "levels": [{"down": [1, 10], "name": "none"}, {"band": [1, 10, 100, 500], "name": "some"}, {"name": "heavy", "up": [100, 500]}], "min_change": 10, "name": "tickets.write.wait", "pack": "admission", "pairs_with": ["tickets.write.empty", "tickets.write.scarce", "queue.writers"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/queues/execution/write/normalPriority/totalTimeQueuedMicros"], "scale": 0.001, "unit": "ms/s"}, "since": "8.0", "title": "Time waiting for a write ticket", "unit": "ms/s", "version_text": "8.0 and later", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10180,7 +10362,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>cache.fill</t>
+          <t>queue.readers</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -10190,7 +10372,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "low ≤50 (fading to 70) · normal 70–80 (edges 50, 86) · high 86–93 (edges 80, 95) · above_reference ≥96 (from 94)", "doc": "Bytes in the WiredTiger cache as a share of its configured size, averaged over the minute.", "elevated": 95, "formula": "serverStatus/wiredTiger/cache/bytes currently in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample", "levels": [{"down": [50, 70], "name": "low"}, {"band": [50, 70, 80, 86], "name": "normal"}, {"band": [80, 86, 93, 95], "name": "high"}, {"name": "above_reference", "up": [94, 96]}], "min_change": 5, "name": "cache.fill", "pack": "storage-engine", "pairs_with": ["cache.fill_above_95", "cache.app_eviction", "cache.read_in"], "reading": "each minute's ratio of sums", "reference": {"configured": "not read", "source": "WiredTiger default eviction_trigger; eviction_target defaults to 80", "unit": "%", "value": 95}, "signal": {"den": ["serverStatus/wiredTiger/cache/maximum bytes configured"], "mode": "gauge", "num": ["serverStatus/wiredTiger/cache/bytes currently in the cache"], "scale": 100, "unit": "%"}, "title": "WiredTiger cache fill", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which globalLock.currentQueue.readers was above 0, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/globalLock/currentQueue/readers, in operations, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "queue.readers", "pack": "admission", "pairs_with": ["tickets.read.empty", "tickets.read.wait"], "reading": "valid-sample share strictly above 0 operations, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/globalLock/currentQueue/readers"], "scale": 1, "unit": "operations"}, "threshold": 0, "title": "Samples with reads queued", "unit": "s/min", "version_text": "all versions", "view": "time_above"}</t>
         </is>
       </c>
     </row>
@@ -10200,7 +10382,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>cache.fill_above_95</t>
+          <t>queue.writers</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -10210,7 +10392,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which WiredTiger cache bytes were strictly above 95 % of the configured cache size, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/wiredTiger/cache/bytes currently in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "cache.fill_above_95", "pack": "storage-engine", "pairs_with": ["cache.fill", "cache.app_eviction", "tickets.read.scarce"], "reading": "valid-sample share strictly above 95 %, normalized to 60 s/min; not continuous elapsed time", "reference": {"configured": "not read", "source": "WiredTiger default eviction_trigger", "unit": "%", "value": 95}, "signal": {"den": ["serverStatus/wiredTiger/cache/maximum bytes configured"], "mode": "gauge", "num": ["serverStatus/wiredTiger/cache/bytes currently in the cache"], "scale": 100, "unit": "%"}, "threshold": 95, "title": "Cache-fill samples above 95%", "unit": "s/min", "version_text": "all versions", "view": "time_above"}</t>
+          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which globalLock.currentQueue.writers was above 0, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/globalLock/currentQueue/writers, in operations, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "queue.writers", "pack": "admission", "pairs_with": ["tickets.write.empty", "tickets.write.wait"], "reading": "valid-sample share strictly above 0 operations, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/globalLock/currentQueue/writers"], "scale": 1, "unit": "operations"}, "threshold": 0, "title": "Samples with writes queued", "unit": "s/min", "version_text": "all versions", "view": "time_above"}</t>
         </is>
       </c>
     </row>
@@ -10220,7 +10402,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>cache.dirty</t>
+          <t>cache.fill</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -10230,7 +10412,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "low ≤3 (fading to 6) · normal 6–8 (edges 3, 12) · high 12–18 (edges 8, 20) · above_reference ≥21 (from 19)", "doc": "Modified bytes not yet written, as a share of the configured cache, averaged over the minute.", "elevated": 20, "formula": "serverStatus/wiredTiger/cache/tracked dirty bytes in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample", "levels": [{"down": [3, 6], "name": "low"}, {"band": [3, 6, 8, 12], "name": "normal"}, {"band": [8, 12, 18, 20], "name": "high"}, {"name": "above_reference", "up": [19, 21]}], "min_change": 3, "name": "cache.dirty", "pack": "storage-engine", "pairs_with": ["cache.dirty_above_20", "checkpoint.duration", "disk.write_await", "ops.writes"], "reading": "each minute's ratio of sums", "reference": {"configured": "not read", "source": "WiredTiger default eviction_dirty_trigger; eviction_dirty_target defaults to 5", "unit": "%", "value": 20}, "signal": {"den": ["serverStatus/wiredTiger/cache/maximum bytes configured"], "mode": "gauge", "num": ["serverStatus/wiredTiger/cache/tracked dirty bytes in the cache"], "scale": 100, "unit": "%"}, "title": "WiredTiger dirty cache", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "low ≤50 (fading to 70) · normal 70–80 (edges 50, 86) · high 86–93 (edges 80, 95) · above_reference ≥96 (from 94)", "doc": "Bytes in the WiredTiger cache as a share of its configured size, averaged over the minute.", "elevated": 95, "formula": "serverStatus/wiredTiger/cache/bytes currently in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample", "levels": [{"down": [50, 70], "name": "low"}, {"band": [50, 70, 80, 86], "name": "normal"}, {"band": [80, 86, 93, 95], "name": "high"}, {"name": "above_reference", "up": [94, 96]}], "min_change": 5, "name": "cache.fill", "pack": "storage-engine", "pairs_with": ["cache.fill_above_95", "cache.app_eviction", "cache.read_in"], "reading": "each minute's ratio of sums", "reference": {"configured": "not read", "source": "WiredTiger default eviction_trigger; eviction_target defaults to 80", "unit": "%", "value": 95}, "signal": {"den": ["serverStatus/wiredTiger/cache/maximum bytes configured"], "mode": "gauge", "num": ["serverStatus/wiredTiger/cache/bytes currently in the cache"], "scale": 100, "unit": "%"}, "title": "WiredTiger cache fill", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10240,7 +10422,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>cache.dirty_above_20</t>
+          <t>cache.fill_above_95</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -10250,7 +10432,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which tracked dirty bytes were strictly above 20 % of the configured cache size, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/wiredTiger/cache/tracked dirty bytes in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "cache.dirty_above_20", "pack": "storage-engine", "pairs_with": ["cache.dirty", "checkpoint.running", "tickets.write.scarce"], "reading": "valid-sample share strictly above 20 %, normalized to 60 s/min; not continuous elapsed time", "reference": {"configured": "not read", "source": "WiredTiger default eviction_dirty_trigger", "unit": "%", "value": 20}, "signal": {"den": ["serverStatus/wiredTiger/cache/maximum bytes configured"], "mode": "gauge", "num": ["serverStatus/wiredTiger/cache/tracked dirty bytes in the cache"], "scale": 100, "unit": "%"}, "threshold": 20, "title": "Dirty-cache samples above 20%", "unit": "s/min", "version_text": "all versions", "view": "time_above"}</t>
+          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which WiredTiger cache bytes were strictly above 95 % of the configured cache size, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/wiredTiger/cache/bytes currently in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "cache.fill_above_95", "pack": "storage-engine", "pairs_with": ["cache.fill", "cache.app_eviction", "tickets.read.scarce"], "reading": "valid-sample share strictly above 95 %, normalized to 60 s/min; not continuous elapsed time", "reference": {"configured": "not read", "source": "WiredTiger default eviction_trigger", "unit": "%", "value": 95}, "signal": {"den": ["serverStatus/wiredTiger/cache/maximum bytes configured"], "mode": "gauge", "num": ["serverStatus/wiredTiger/cache/bytes currently in the cache"], "scale": 100, "unit": "%"}, "threshold": 95, "title": "Cache-fill samples above 95%", "unit": "s/min", "version_text": "all versions", "view": "time_above"}</t>
         </is>
       </c>
     </row>
@@ -10260,17 +10442,17 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>cache.app_eviction</t>
+          <t>cache.dirty</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>before 8.0.16</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤0.1 (fading to 1) · some 1–10 (edges 0.1, 50) · heavy ≥50 (from 10)", "doc": "Rate of pages evicted by application threads; where the version uses attempts and failures, the signal subtracts failure counts from attempt counts.", "elevated": 1, "formula": "ΔserverStatus/wiredTiger/cache/pages evicted by application threads per second, in pages/s, at each available sample", "levels": [{"down": [0.1, 1], "name": "none"}, {"band": [0.1, 1, 10, 50], "name": "some"}, {"name": "heavy", "up": [10, 50]}], "min_change": 5, "name": "cache.app_eviction", "pack": "storage-engine", "pairs_with": ["cache.fill_above_95", "cache.dirty_above_20"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/wiredTiger/cache/pages evicted by application threads"], "scale": 1, "unit": "pages/s"}, "title": "Eviction by application threads", "unit": "pages/s", "until": "8.0.16", "version_text": "before 8.0.16", "view": "mean"}</t>
+          <t>{"bands": "low ≤3 (fading to 6) · normal 6–8 (edges 3, 12) · high 12–18 (edges 8, 20) · above_reference ≥21 (from 19)", "doc": "Modified bytes not yet written, as a share of the configured cache, averaged over the minute.", "elevated": 20, "formula": "serverStatus/wiredTiger/cache/tracked dirty bytes in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample", "levels": [{"down": [3, 6], "name": "low"}, {"band": [3, 6, 8, 12], "name": "normal"}, {"band": [8, 12, 18, 20], "name": "high"}, {"name": "above_reference", "up": [19, 21]}], "min_change": 3, "name": "cache.dirty", "pack": "storage-engine", "pairs_with": ["cache.dirty_above_20", "checkpoint.duration", "disk.write_await", "ops.writes"], "reading": "each minute's ratio of sums", "reference": {"configured": "not read", "source": "WiredTiger default eviction_dirty_trigger; eviction_dirty_target defaults to 5", "unit": "%", "value": 20}, "signal": {"den": ["serverStatus/wiredTiger/cache/maximum bytes configured"], "mode": "gauge", "num": ["serverStatus/wiredTiger/cache/tracked dirty bytes in the cache"], "scale": 100, "unit": "%"}, "title": "WiredTiger dirty cache", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10280,17 +10462,17 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>cache.app_eviction</t>
+          <t>cache.dirty_above_20</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>8.0.16 and later</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤0.1 (fading to 1) · some 1–10 (edges 0.1, 50) · heavy ≥50 (from 10)", "doc": "Rate of pages evicted by application threads; where the version uses attempts and failures, the signal subtracts failure counts from attempt counts.", "elevated": 1, "formula": "ΔserverStatus/wiredTiger/cache/page evict attempts by application threads − serverStatus/wiredTiger/cache/page evict failures by application threads per second, in pages/s, at each available sample", "levels": [{"down": [0.1, 1], "name": "none"}, {"band": [0.1, 1, 10, 50], "name": "some"}, {"name": "heavy", "up": [10, 50]}], "min_change": 5, "name": "cache.app_eviction", "pack": "storage-engine", "pairs_with": ["cache.fill_above_95", "cache.dirty_above_20", "cache.app_eviction_time"], "reading": "each minute's mean", "signal": {"minus": ["serverStatus/wiredTiger/cache/page evict failures by application threads"], "mode": "rate", "num": ["serverStatus/wiredTiger/cache/page evict attempts by application threads"], "scale": 1, "unit": "pages/s"}, "since": "8.0.16", "title": "Eviction by application threads", "unit": "pages/s", "version_text": "8.0.16 and later", "view": "mean"}</t>
+          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which tracked dirty bytes were strictly above 20 % of the configured cache size, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/wiredTiger/cache/tracked dirty bytes in the cache ÷ serverStatus/wiredTiger/cache/maximum bytes configured × 100, in %, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "cache.dirty_above_20", "pack": "storage-engine", "pairs_with": ["cache.dirty", "checkpoint.running", "tickets.write.scarce"], "reading": "valid-sample share strictly above 20 %, normalized to 60 s/min; not continuous elapsed time", "reference": {"configured": "not read", "source": "WiredTiger default eviction_dirty_trigger", "unit": "%", "value": 20}, "signal": {"den": ["serverStatus/wiredTiger/cache/maximum bytes configured"], "mode": "gauge", "num": ["serverStatus/wiredTiger/cache/tracked dirty bytes in the cache"], "scale": 100, "unit": "%"}, "threshold": 20, "title": "Dirty-cache samples above 20%", "unit": "s/min", "version_text": "all versions", "view": "time_above"}</t>
         </is>
       </c>
     </row>
@@ -10300,17 +10482,17 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>cache.app_eviction_time</t>
+          <t>cache.app_eviction</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>8.0 and later</t>
+          <t>before 8.0.16</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)", "doc": "Application-thread eviction time counter advance per elapsed second, summed across threads, in milliseconds.", "elevated": 100, "formula": "ΔserverStatus/wiredTiger/cache/application thread time evicting (usecs) per second × 0.001, in ms/s, at each available sample", "levels": [{"down": [1, 10], "name": "none"}, {"band": [1, 10, 100, 500], "name": "some"}, {"name": "heavy", "up": [100, 500]}], "min_change": 10, "name": "cache.app_eviction_time", "pack": "storage-engine", "pairs_with": ["cache.app_eviction", "cache.fill_above_95", "cache.dirty_above_20"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/wiredTiger/cache/application thread time evicting (usecs)"], "scale": 0.001, "unit": "ms/s"}, "since": "8.0", "title": "Time operations spent evicting", "unit": "ms/s", "version_text": "8.0 and later", "view": "mean"}</t>
+          <t>{"bands": "none ≤0.1 (fading to 1) · some 1–10 (edges 0.1, 50) · heavy ≥50 (from 10)", "doc": "Rate of pages evicted by application threads; where the version uses attempts and failures, the signal subtracts failure counts from attempt counts.", "elevated": 1, "formula": "ΔserverStatus/wiredTiger/cache/pages evicted by application threads per second, in pages/s, at each available sample", "levels": [{"down": [0.1, 1], "name": "none"}, {"band": [0.1, 1, 10, 50], "name": "some"}, {"name": "heavy", "up": [10, 50]}], "min_change": 5, "name": "cache.app_eviction", "pack": "storage-engine", "pairs_with": ["cache.fill_above_95", "cache.dirty_above_20"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/wiredTiger/cache/pages evicted by application threads"], "scale": 1, "unit": "pages/s"}, "title": "Eviction by application threads", "unit": "pages/s", "until": "8.0.16", "version_text": "before 8.0.16", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10320,17 +10502,17 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>cache.read_in</t>
+          <t>cache.app_eviction</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>8.0.16 and later</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "doc": "WiredTiger bytes-read-into-cache counter advance per elapsed second, scaled to MB/s.", "formula": "ΔserverStatus/wiredTiger/cache/bytes read into cache per second × 1e-06, in MB/s, at each available sample", "min_change": 5, "name": "cache.read_in", "pack": "storage-engine", "pairs_with": ["disk.read_await", "query.collscans", "cache.fill"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/wiredTiger/cache/bytes read into cache"], "scale": 1e-06, "unit": "MB/s"}, "title": "Data read into the cache", "unit": "MB/s", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "none ≤0.1 (fading to 1) · some 1–10 (edges 0.1, 50) · heavy ≥50 (from 10)", "doc": "Rate of pages evicted by application threads; where the version uses attempts and failures, the signal subtracts failure counts from attempt counts.", "elevated": 1, "formula": "ΔserverStatus/wiredTiger/cache/page evict attempts by application threads − serverStatus/wiredTiger/cache/page evict failures by application threads per second, in pages/s, at each available sample", "levels": [{"down": [0.1, 1], "name": "none"}, {"band": [0.1, 1, 10, 50], "name": "some"}, {"name": "heavy", "up": [10, 50]}], "min_change": 5, "name": "cache.app_eviction", "pack": "storage-engine", "pairs_with": ["cache.fill_above_95", "cache.dirty_above_20", "cache.app_eviction_time"], "reading": "each minute's mean", "signal": {"minus": ["serverStatus/wiredTiger/cache/page evict failures by application threads"], "mode": "rate", "num": ["serverStatus/wiredTiger/cache/page evict attempts by application threads"], "scale": 1, "unit": "pages/s"}, "since": "8.0.16", "title": "Eviction by application threads", "unit": "pages/s", "version_text": "8.0.16 and later", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10340,17 +10522,17 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>checkpoint.duration</t>
+          <t>cache.app_eviction_time</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>before 7.1</t>
+          <t>8.0 and later</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "quick ≤5 (fading to 15) · slow 15–40 (edges 5, 60) · back_to_back ≥60 (from 50)", "doc": "Duration recorded for the most recent WiredTiger checkpoint; the same completed-checkpoint value may appear in multiple samples. Minute summaries select the highest valid sample.", "elevated": 60, "formula": "serverStatus/wiredTiger/transaction/transaction checkpoint most recent time (msecs) × 0.001, in s, at each available sample", "levels": [{"down": [5, 15], "name": "quick"}, {"band": [5, 15, 40, 60], "name": "slow"}, {"name": "back_to_back", "up": [50, 60]}], "min_change": 10, "name": "checkpoint.duration", "pack": "storage-engine", "pairs_with": ["checkpoint.running", "cache.dirty", "disk.write_await"], "reading": "the highest valid sample of each minute", "reference": {"configured": "not read", "source": "default checkpoint interval, storage.syncPeriodSecs", "unit": "s", "value": 60}, "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/transaction/transaction checkpoint most recent time (msecs)"], "scale": 0.001, "unit": "s"}, "title": "Checkpoint duration", "unit": "s", "until": "7.1", "version_text": "before 7.1", "view": "max"}</t>
+          <t>{"bands": "none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)", "doc": "Application-thread eviction time counter advance per elapsed second, summed across threads, in milliseconds.", "elevated": 100, "formula": "ΔserverStatus/wiredTiger/cache/application thread time evicting (usecs) per second × 0.001, in ms/s, at each available sample", "levels": [{"down": [1, 10], "name": "none"}, {"band": [1, 10, 100, 500], "name": "some"}, {"name": "heavy", "up": [100, 500]}], "min_change": 10, "name": "cache.app_eviction_time", "pack": "storage-engine", "pairs_with": ["cache.app_eviction", "cache.fill_above_95", "cache.dirty_above_20"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/wiredTiger/cache/application thread time evicting (usecs)"], "scale": 0.001, "unit": "ms/s"}, "since": "8.0", "title": "Time operations spent evicting", "unit": "ms/s", "version_text": "8.0 and later", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10360,17 +10542,17 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>checkpoint.duration</t>
+          <t>cache.read_in</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>7.1 and later</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "quick ≤5 (fading to 15) · slow 15–40 (edges 5, 60) · back_to_back ≥60 (from 50)", "doc": "Duration recorded for the most recent WiredTiger checkpoint; the same completed-checkpoint value may appear in multiple samples. Minute summaries select the highest valid sample.", "elevated": 60, "formula": "serverStatus/wiredTiger/checkpoint/most recent time (msecs) × 0.001, in s, at each available sample", "levels": [{"down": [5, 15], "name": "quick"}, {"band": [5, 15, 40, 60], "name": "slow"}, {"name": "back_to_back", "up": [50, 60]}], "min_change": 10, "name": "checkpoint.duration", "pack": "storage-engine", "pairs_with": ["checkpoint.running", "cache.dirty", "disk.write_await"], "reading": "the highest valid sample of each minute", "reference": {"configured": "not read", "source": "default checkpoint interval, storage.syncPeriodSecs", "unit": "s", "value": 60}, "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/checkpoint/most recent time (msecs)"], "scale": 0.001, "unit": "s"}, "since": "7.1", "title": "Checkpoint duration", "unit": "s", "version_text": "7.1 and later", "view": "max"}</t>
+          <t>{"bands": "none — read for its shape only", "doc": "WiredTiger bytes-read-into-cache counter advance per elapsed second, scaled to MB/s.", "formula": "ΔserverStatus/wiredTiger/cache/bytes read into cache per second × 1e-06, in MB/s, at each available sample", "min_change": 5, "name": "cache.read_in", "pack": "storage-engine", "pairs_with": ["disk.read_await", "query.collscans", "cache.fill"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/wiredTiger/cache/bytes read into cache"], "scale": 1e-06, "unit": "MB/s"}, "title": "Data read into the cache", "unit": "MB/s", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10380,7 +10562,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>checkpoint.running</t>
+          <t>checkpoint.duration</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -10390,7 +10572,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "brief ≤12 (fading to 24) · long 24–42 (edges 12, 54) · continuous ≥57 (from 48)", "doc": "Share of valid samples in which WiredTiger reported a checkpoint as currently running, normalized to a 60-second minute.", "elevated": 48, "formula": "serverStatus/wiredTiger/transaction/transaction checkpoint currently running, in running, at each available sample", "levels": [{"down": [12, 24], "name": "brief"}, {"band": [12, 24, 42, 54], "name": "long"}, {"name": "continuous", "up": [48, 57]}], "min_change": 9, "name": "checkpoint.running", "pack": "storage-engine", "pairs_with": ["checkpoint.duration", "disk.busy_above_95", "cache.dirty"], "reading": "valid-sample share strictly above 0 running, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/transaction/transaction checkpoint currently running"], "scale": 1, "unit": "running"}, "threshold": 0, "title": "Samples with checkpoint activity", "unit": "s/min", "until": "7.1", "version_text": "before 7.1", "view": "time_above"}</t>
+          <t>{"bands": "quick ≤5 (fading to 15) · slow 15–40 (edges 5, 60) · back_to_back ≥60 (from 50)", "doc": "Duration recorded for the most recent WiredTiger checkpoint; the same completed-checkpoint value may appear in multiple samples. Minute summaries select the highest valid sample.", "elevated": 60, "formula": "serverStatus/wiredTiger/transaction/transaction checkpoint most recent time (msecs) × 0.001, in s, at each available sample", "levels": [{"down": [5, 15], "name": "quick"}, {"band": [5, 15, 40, 60], "name": "slow"}, {"name": "back_to_back", "up": [50, 60]}], "min_change": 10, "name": "checkpoint.duration", "pack": "storage-engine", "pairs_with": ["checkpoint.running", "cache.dirty", "disk.write_await"], "reading": "the highest valid sample of each minute", "reference": {"configured": "not read", "source": "default checkpoint interval, storage.syncPeriodSecs", "unit": "s", "value": 60}, "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/transaction/transaction checkpoint most recent time (msecs)"], "scale": 0.001, "unit": "s"}, "title": "Checkpoint duration", "unit": "s", "until": "7.1", "version_text": "before 7.1", "view": "max"}</t>
         </is>
       </c>
     </row>
@@ -10400,7 +10582,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>checkpoint.running</t>
+          <t>checkpoint.duration</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -10410,7 +10592,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "The progress state's values are not decoded; any non-zero value is read as activity.", "bands": "brief ≤12 (fading to 24) · long 24–42 (edges 12, 54) · continuous ≥57 (from 48)", "doc": "Share of valid samples in which WiredTiger's checkpoint progress state was non-zero, normalized to a 60-second minute.", "elevated": 48, "formula": "serverStatus/wiredTiger/checkpoint/progress state, in state, at each available sample", "levels": [{"down": [12, 24], "name": "brief"}, {"band": [12, 24, 42, 54], "name": "long"}, {"name": "continuous", "up": [48, 57]}], "min_change": 9, "name": "checkpoint.running", "pack": "storage-engine", "pairs_with": ["checkpoint.duration", "disk.busy_above_95", "cache.dirty"], "reading": "valid-sample share strictly above 0 state, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/checkpoint/progress state"], "scale": 1, "unit": "state"}, "since": "7.1", "threshold": 0, "title": "Samples with checkpoint activity", "unit": "s/min", "version_text": "7.1 and later", "view": "time_above"}</t>
+          <t>{"bands": "quick ≤5 (fading to 15) · slow 15–40 (edges 5, 60) · back_to_back ≥60 (from 50)", "doc": "Duration recorded for the most recent WiredTiger checkpoint; the same completed-checkpoint value may appear in multiple samples. Minute summaries select the highest valid sample.", "elevated": 60, "formula": "serverStatus/wiredTiger/checkpoint/most recent time (msecs) × 0.001, in s, at each available sample", "levels": [{"down": [5, 15], "name": "quick"}, {"band": [5, 15, 40, 60], "name": "slow"}, {"name": "back_to_back", "up": [50, 60]}], "min_change": 10, "name": "checkpoint.duration", "pack": "storage-engine", "pairs_with": ["checkpoint.running", "cache.dirty", "disk.write_await"], "reading": "the highest valid sample of each minute", "reference": {"configured": "not read", "source": "default checkpoint interval, storage.syncPeriodSecs", "unit": "s", "value": 60}, "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/checkpoint/most recent time (msecs)"], "scale": 0.001, "unit": "s"}, "since": "7.1", "title": "Checkpoint duration", "unit": "s", "version_text": "7.1 and later", "view": "max"}</t>
         </is>
       </c>
     </row>
@@ -10420,17 +10602,17 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>storage.open_handles</t>
+          <t>checkpoint.running</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>before 7.1</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "doc": "Count reported by WiredTiger for currently open data handles.", "formula": "serverStatus/wiredTiger/data-handle/connection data handles currently active, in handles, at each available sample", "min_change": 500, "name": "storage.open_handles", "pack": "storage-engine", "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/data-handle/connection data handles currently active"], "scale": 1, "unit": "handles"}, "title": "Open data handles", "unit": "handles", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "brief ≤12 (fading to 24) · long 24–42 (edges 12, 54) · continuous ≥57 (from 48)", "doc": "Share of valid samples in which WiredTiger reported a checkpoint as currently running, normalized to a 60-second minute.", "elevated": 48, "formula": "serverStatus/wiredTiger/transaction/transaction checkpoint currently running, in running, at each available sample", "levels": [{"down": [12, 24], "name": "brief"}, {"band": [12, 24, 42, 54], "name": "long"}, {"name": "continuous", "up": [48, 57]}], "min_change": 9, "name": "checkpoint.running", "pack": "storage-engine", "pairs_with": ["checkpoint.duration", "disk.busy_above_95", "cache.dirty"], "reading": "valid-sample share strictly above 0 running, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/transaction/transaction checkpoint currently running"], "scale": 1, "unit": "running"}, "threshold": 0, "title": "Samples with checkpoint activity", "unit": "s/min", "until": "7.1", "version_text": "before 7.1", "view": "time_above"}</t>
         </is>
       </c>
     </row>
@@ -10440,17 +10622,17 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>latency.reads</t>
+          <t>checkpoint.running</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>7.1 and later</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "fast ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · slow 20–50 (edges 10, 100) · very_slow ≥100 (from 50)", "doc": "Average milliseconds per read operation over each minute, from opLatencies: every microsecond spent on reads in the minute over every read that finished in it.", "elevated": 50, "formula": "ΔserverStatus/opLatencies/reads/latency ÷ ΔserverStatus/opLatencies/reads/ops × 0.001, in ms, at each available sample; minutes where the divisor sums to under 60 are left out", "levels": [{"down": [1, 3], "name": "fast"}, {"band": [1, 3, 10, 20], "name": "normal"}, {"band": [10, 20, 50, 100], "name": "slow"}, {"name": "very_slow", "up": [50, 100]}], "min_change": 5, "name": "latency.reads", "pack": "workload", "pairs_with": ["tickets.read.scarce", "query.targeting", "cache.fill_above_95", "disk.read_await"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/opLatencies/reads/ops"], "min_den": 60, "mode": "rate", "num": ["serverStatus/opLatencies/reads/latency"], "scale": 0.001, "unit": "ms"}, "title": "Read latency", "unit": "ms", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"applies": "The progress state's values are not decoded; any non-zero value is read as activity.", "bands": "brief ≤12 (fading to 24) · long 24–42 (edges 12, 54) · continuous ≥57 (from 48)", "doc": "Share of valid samples in which WiredTiger's checkpoint progress state was non-zero, normalized to a 60-second minute.", "elevated": 48, "formula": "serverStatus/wiredTiger/checkpoint/progress state, in state, at each available sample", "levels": [{"down": [12, 24], "name": "brief"}, {"band": [12, 24, 42, 54], "name": "long"}, {"name": "continuous", "up": [48, 57]}], "min_change": 9, "name": "checkpoint.running", "pack": "storage-engine", "pairs_with": ["checkpoint.duration", "disk.busy_above_95", "cache.dirty"], "reading": "valid-sample share strictly above 0 state, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/checkpoint/progress state"], "scale": 1, "unit": "state"}, "since": "7.1", "threshold": 0, "title": "Samples with checkpoint activity", "unit": "s/min", "version_text": "7.1 and later", "view": "time_above"}</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10642,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>latency.writes</t>
+          <t>storage.open_handles</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -10470,7 +10652,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "fast ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · slow 20–50 (edges 10, 100) · very_slow ≥100 (from 50)", "doc": "Average milliseconds per write operation over each minute, from opLatencies.", "elevated": 50, "formula": "ΔserverStatus/opLatencies/writes/latency ÷ ΔserverStatus/opLatencies/writes/ops × 0.001, in ms, at each available sample; minutes where the divisor sums to under 60 are left out", "levels": [{"down": [1, 3], "name": "fast"}, {"band": [1, 3, 10, 20], "name": "normal"}, {"band": [10, 20, 50, 100], "name": "slow"}, {"name": "very_slow", "up": [50, 100]}], "min_change": 5, "name": "latency.writes", "pack": "workload", "pairs_with": ["tickets.write.scarce", "cache.dirty_above_20", "flow.lagged", "repl.majority_lag"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/opLatencies/writes/ops"], "min_den": 60, "mode": "rate", "num": ["serverStatus/opLatencies/writes/latency"], "scale": 0.001, "unit": "ms"}, "title": "Write latency", "unit": "ms", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "none — read for its shape only", "doc": "Count reported by WiredTiger for currently open data handles.", "formula": "serverStatus/wiredTiger/data-handle/connection data handles currently active, in handles, at each available sample", "min_change": 500, "name": "storage.open_handles", "pack": "storage-engine", "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/wiredTiger/data-handle/connection data handles currently active"], "scale": 1, "unit": "handles"}, "title": "Open data handles", "unit": "handles", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10480,7 +10662,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>latency.commands</t>
+          <t>latency.reads</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -10490,7 +10672,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "fast ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · slow 20–50 (edges 10, 100) · very_slow ≥100 (from 50)", "doc": "Ratio of command opLatencies counter advance to command operation-count advance, scaled to milliseconds per operation.", "elevated": 50, "formula": "ΔserverStatus/opLatencies/commands/latency ÷ ΔserverStatus/opLatencies/commands/ops × 0.001, in ms, at each available sample; minutes where the divisor sums to under 60 are left out", "levels": [{"down": [1, 3], "name": "fast"}, {"band": [1, 3, 10, 20], "name": "normal"}, {"band": [10, 20, 50, 100], "name": "slow"}, {"name": "very_slow", "up": [50, 100]}], "min_change": 5, "name": "latency.commands", "pack": "workload", "pairs_with": ["tickets.read.scarce", "query.targeting"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/opLatencies/commands/ops"], "min_den": 60, "mode": "rate", "num": ["serverStatus/opLatencies/commands/latency"], "scale": 0.001, "unit": "ms"}, "title": "Command latency", "unit": "ms", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "fast ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · slow 20–50 (edges 10, 100) · very_slow ≥100 (from 50)", "doc": "Average milliseconds per read operation over each minute, from opLatencies: every microsecond spent on reads in the minute over every read that finished in it.", "elevated": 50, "formula": "ΔserverStatus/opLatencies/reads/latency ÷ ΔserverStatus/opLatencies/reads/ops × 0.001, in ms, at each available sample; minutes where the divisor sums to under 60 are left out", "levels": [{"down": [1, 3], "name": "fast"}, {"band": [1, 3, 10, 20], "name": "normal"}, {"band": [10, 20, 50, 100], "name": "slow"}, {"name": "very_slow", "up": [50, 100]}], "min_change": 5, "name": "latency.reads", "pack": "workload", "pairs_with": ["tickets.read.scarce", "query.targeting", "cache.fill_above_95", "disk.read_await"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/opLatencies/reads/ops"], "min_den": 60, "mode": "rate", "num": ["serverStatus/opLatencies/reads/latency"], "scale": 0.001, "unit": "ms"}, "title": "Read latency", "unit": "ms", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10500,7 +10682,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>ops.total</t>
+          <t>latency.writes</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -10510,7 +10692,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "doc": "Sum of query, getMore, insert, update, delete and command operation-counter rates.", "formula": "Δ(serverStatus/opcounters/query + serverStatus/opcounters/getmore + serverStatus/opcounters/insert + serverStatus/opcounters/update + serverStatus/opcounters/delete + serverStatus/opcounters/command) per second, in ops/s, at each available sample", "min_change": 50, "name": "ops.total", "pack": "workload", "pairs_with": ["ops.writes", "connections.current"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/opcounters/query", "serverStatus/opcounters/getmore", "serverStatus/opcounters/insert", "serverStatus/opcounters/update", "serverStatus/opcounters/delete", "serverStatus/opcounters/command"], "scale": 1, "unit": "ops/s"}, "title": "Operations a second", "unit": "ops/s", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "fast ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · slow 20–50 (edges 10, 100) · very_slow ≥100 (from 50)", "doc": "Average milliseconds per write operation over each minute, from opLatencies.", "elevated": 50, "formula": "ΔserverStatus/opLatencies/writes/latency ÷ ΔserverStatus/opLatencies/writes/ops × 0.001, in ms, at each available sample; minutes where the divisor sums to under 60 are left out", "levels": [{"down": [1, 3], "name": "fast"}, {"band": [1, 3, 10, 20], "name": "normal"}, {"band": [10, 20, 50, 100], "name": "slow"}, {"name": "very_slow", "up": [50, 100]}], "min_change": 5, "name": "latency.writes", "pack": "workload", "pairs_with": ["tickets.write.scarce", "cache.dirty_above_20", "flow.lagged", "repl.majority_lag"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/opLatencies/writes/ops"], "min_den": 60, "mode": "rate", "num": ["serverStatus/opLatencies/writes/latency"], "scale": 0.001, "unit": "ms"}, "title": "Write latency", "unit": "ms", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10520,7 +10702,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>ops.writes</t>
+          <t>latency.commands</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -10530,7 +10712,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "doc": "Sum of insert, update and delete operation-counter rates.", "formula": "Δ(serverStatus/opcounters/insert + serverStatus/opcounters/update + serverStatus/opcounters/delete) per second, in ops/s, at each available sample", "min_change": 50, "name": "ops.writes", "pack": "workload", "pairs_with": ["cache.dirty", "checkpoint.duration"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/opcounters/insert", "serverStatus/opcounters/update", "serverStatus/opcounters/delete"], "scale": 1, "unit": "ops/s"}, "title": "Writes a second", "unit": "ops/s", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "fast ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · slow 20–50 (edges 10, 100) · very_slow ≥100 (from 50)", "doc": "Ratio of command opLatencies counter advance to command operation-count advance, scaled to milliseconds per operation.", "elevated": 50, "formula": "ΔserverStatus/opLatencies/commands/latency ÷ ΔserverStatus/opLatencies/commands/ops × 0.001, in ms, at each available sample; minutes where the divisor sums to under 60 are left out", "levels": [{"down": [1, 3], "name": "fast"}, {"band": [1, 3, 10, 20], "name": "normal"}, {"band": [10, 20, 50, 100], "name": "slow"}, {"name": "very_slow", "up": [50, 100]}], "min_change": 5, "name": "latency.commands", "pack": "workload", "pairs_with": ["tickets.read.scarce", "query.targeting"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/opLatencies/commands/ops"], "min_den": 60, "mode": "rate", "num": ["serverStatus/opLatencies/commands/latency"], "scale": 0.001, "unit": "ms"}, "title": "Command latency", "unit": "ms", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10540,7 +10722,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>query.targeting</t>
+          <t>ops.total</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -10550,7 +10732,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "low ≤2 (fading to 10) · moderate 10–50 (edges 2, 100) · high 100–500 (edges 50, 1000) · very_high ≥1000 (from 500)", "doc": "Ratio of documents-examined counter advance to documents-returned counter advance; it does not determine index suitability.", "elevated": 100, "formula": "ΔserverStatus/metrics/queryExecutor/scannedObjects ÷ ΔserverStatus/metrics/document/returned, in ratio, at each available sample; minutes where the divisor sums to under 60 are left out", "levels": [{"down": [2, 10], "name": "low"}, {"band": [2, 10, 50, 100], "name": "moderate"}, {"band": [50, 100, 500, 1000], "name": "high"}, {"name": "very_high", "up": [500, 1000]}], "min_change": 10, "name": "query.targeting", "pack": "workload", "pairs_with": ["query.collscans", "cache.read_in", "cpu.busy"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/metrics/document/returned"], "min_den": 60, "mode": "rate", "num": ["serverStatus/metrics/queryExecutor/scannedObjects"], "scale": 1, "unit": "ratio"}, "title": "Documents examined per document returned", "unit": "ratio", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "none — read for its shape only", "doc": "Sum of query, getMore, insert, update, delete and command operation-counter rates.", "formula": "Δ(serverStatus/opcounters/query + serverStatus/opcounters/getmore + serverStatus/opcounters/insert + serverStatus/opcounters/update + serverStatus/opcounters/delete + serverStatus/opcounters/command) per second, in ops/s, at each available sample", "min_change": 50, "name": "ops.total", "pack": "workload", "pairs_with": ["ops.writes", "connections.current"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/opcounters/query", "serverStatus/opcounters/getmore", "serverStatus/opcounters/insert", "serverStatus/opcounters/update", "serverStatus/opcounters/delete", "serverStatus/opcounters/command"], "scale": 1, "unit": "ops/s"}, "title": "Operations a second", "unit": "ops/s", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10560,17 +10742,17 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>query.collscans</t>
+          <t>ops.writes</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>4.4 and later</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤0.01 (fading to 0.1) · some 0.1–1 (edges 0.01, 10) · many ≥10 (from 1)", "doc": "Rate of the server's collection-scan counter.", "elevated": 1, "formula": "ΔserverStatus/metrics/queryExecutor/collectionScans/total per second, in /s, at each available sample", "levels": [{"down": [0.01, 0.1], "name": "none"}, {"band": [0.01, 0.1, 1, 10], "name": "some"}, {"name": "many", "up": [1, 10]}], "min_change": 0.5, "name": "query.collscans", "pack": "workload", "pairs_with": ["query.targeting", "cache.read_in"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/metrics/queryExecutor/collectionScans/total"], "scale": 1, "unit": "/s"}, "since": "4.4", "title": "Collection scans", "unit": "/s", "version_text": "4.4 and later", "view": "mean"}</t>
+          <t>{"bands": "none — read for its shape only", "doc": "Sum of insert, update and delete operation-counter rates.", "formula": "Δ(serverStatus/opcounters/insert + serverStatus/opcounters/update + serverStatus/opcounters/delete) per second, in ops/s, at each available sample", "min_change": 50, "name": "ops.writes", "pack": "workload", "pairs_with": ["cache.dirty", "checkpoint.duration"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/opcounters/insert", "serverStatus/opcounters/update", "serverStatus/opcounters/delete"], "scale": 1, "unit": "ops/s"}, "title": "Writes a second", "unit": "ops/s", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10762,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>query.scan_and_order</t>
+          <t>query.targeting</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -10590,7 +10772,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "doc": "Rate of the server's scanAndOrder counter.", "formula": "ΔserverStatus/metrics/operation/scanAndOrder per second, in /s, at each available sample", "min_change": 1, "name": "query.scan_and_order", "pack": "workload", "pairs_with": ["query.targeting", "memory.heap_outside_cache"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/metrics/operation/scanAndOrder"], "scale": 1, "unit": "/s"}, "title": "scanAndOrder counter rate", "unit": "/s", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "low ≤2 (fading to 10) · moderate 10–50 (edges 2, 100) · high 100–500 (edges 50, 1000) · very_high ≥1000 (from 500)", "doc": "Ratio of documents-examined counter advance to documents-returned counter advance; it does not determine index suitability.", "elevated": 100, "formula": "ΔserverStatus/metrics/queryExecutor/scannedObjects ÷ ΔserverStatus/metrics/document/returned, in ratio, at each available sample; minutes where the divisor sums to under 60 are left out", "levels": [{"down": [2, 10], "name": "low"}, {"band": [2, 10, 50, 100], "name": "moderate"}, {"band": [50, 100, 500, 1000], "name": "high"}, {"name": "very_high", "up": [500, 1000]}], "min_change": 10, "name": "query.targeting", "pack": "workload", "pairs_with": ["query.collscans", "cache.read_in", "cpu.busy"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/metrics/document/returned"], "min_den": 60, "mode": "rate", "num": ["serverStatus/metrics/queryExecutor/scannedObjects"], "scale": 1, "unit": "ratio"}, "title": "Documents examined per document returned", "unit": "ratio", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10600,17 +10782,17 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>writes.conflicts</t>
+          <t>query.collscans</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>4.4 and later</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "rare ≤0.1 (fading to 1) · some 1–10 (edges 0.1, 50) · heavy ≥50 (from 10)", "doc": "Rate of the server's writeConflicts counter; retries, document identity and contention cause are not inferred from this counter.", "elevated": 10, "formula": "ΔserverStatus/metrics/operation/writeConflicts per second, in /s, at each available sample", "levels": [{"down": [0.1, 1], "name": "rare"}, {"band": [0.1, 1, 10, 50], "name": "some"}, {"name": "heavy", "up": [10, 50]}], "min_change": 2, "name": "writes.conflicts", "pack": "workload", "pairs_with": ["ops.writes", "latency.writes"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/metrics/operation/writeConflicts"], "scale": 1, "unit": "/s"}, "title": "Write conflicts", "unit": "/s", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "none ≤0.01 (fading to 0.1) · some 0.1–1 (edges 0.01, 10) · many ≥10 (from 1)", "doc": "Rate of the server's collection-scan counter.", "elevated": 1, "formula": "ΔserverStatus/metrics/queryExecutor/collectionScans/total per second, in /s, at each available sample", "levels": [{"down": [0.01, 0.1], "name": "none"}, {"band": [0.01, 0.1, 1, 10], "name": "some"}, {"name": "many", "up": [1, 10]}], "min_change": 0.5, "name": "query.collscans", "pack": "workload", "pairs_with": ["query.targeting", "cache.read_in"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/metrics/queryExecutor/collectionScans/total"], "scale": 1, "unit": "/s"}, "since": "4.4", "title": "Collection scans", "unit": "/s", "version_text": "4.4 and later", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10620,7 +10802,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>ttl.deletes</t>
+          <t>query.scan_and_order</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -10630,7 +10812,7 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "doc": "Rate of documents reported deleted by the TTL monitor; collection identity, expiry backlog and latency impact are not inferred.", "formula": "ΔserverStatus/metrics/ttl/deletedDocuments per second, in docs/s, at each available sample", "min_change": 50, "name": "ttl.deletes", "pack": "workload", "pairs_with": ["cache.dirty", "disk.write_await", "repl.member_lag"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/metrics/ttl/deletedDocuments"], "scale": 1, "unit": "docs/s"}, "title": "Documents deleted by TTL", "unit": "docs/s", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "none — read for its shape only", "doc": "Rate of the server's scanAndOrder counter.", "formula": "ΔserverStatus/metrics/operation/scanAndOrder per second, in /s, at each available sample", "min_change": 1, "name": "query.scan_and_order", "pack": "workload", "pairs_with": ["query.targeting", "memory.heap_outside_cache"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/metrics/operation/scanAndOrder"], "scale": 1, "unit": "/s"}, "title": "scanAndOrder counter rate", "unit": "/s", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10640,7 +10822,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>cursors.open</t>
+          <t>writes.conflicts</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -10650,7 +10832,7 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "doc": "Count reported for currently open cursors.", "formula": "serverStatus/metrics/cursor/open/total, in cursors, at each available sample", "min_change": 50, "name": "cursors.open", "pack": "workload", "pairs_with": ["memory.heap_outside_cache", "connections.current"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/metrics/cursor/open/total"], "scale": 1, "unit": "cursors"}, "title": "Open cursors", "unit": "cursors", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "rare ≤0.1 (fading to 1) · some 1–10 (edges 0.1, 50) · heavy ≥50 (from 10)", "doc": "Rate of the server's writeConflicts counter; retries, document identity and contention cause are not inferred from this counter.", "elevated": 10, "formula": "ΔserverStatus/metrics/operation/writeConflicts per second, in /s, at each available sample", "levels": [{"down": [0.1, 1], "name": "rare"}, {"band": [0.1, 1, 10, 50], "name": "some"}, {"name": "heavy", "up": [10, 50]}], "min_change": 2, "name": "writes.conflicts", "pack": "workload", "pairs_with": ["ops.writes", "latency.writes"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/metrics/operation/writeConflicts"], "scale": 1, "unit": "/s"}, "title": "Write conflicts", "unit": "/s", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10660,17 +10842,17 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>repl.member_lag</t>
+          <t>ttl.deletes</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>before 6.0</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "One result per entry of this node's replica-set status, numbered by position in that list; a position can name a different member after a reconfig. Lag is measured against the newest applied time among members, not against the primary, and a member that stopped reporting keeps its last time.", "bands": "current ≤2 (fading to 5) · behind 5–20 (edges 2, 30) · lagging 30–120 (edges 20, 300) · far_behind ≥300 (from 120)", "doc": "Difference between each member's reported applied-write timestamp and the newest such timestamp in this node's replica-set status, scaled to seconds. Members without a timestamp have no result. optimeDate has one-second resolution. Minute summaries select the highest valid sample.", "elevated": 30, "formula": "newest of every replSetGetStatus/members/{i}/optimeDate − this one × 0.001, in s, at each available sample", "levels": [{"down": [2, 5], "name": "current"}, {"band": [2, 5, 20, 30], "name": "behind"}, {"band": [20, 30, 120, 300], "name": "lagging"}, {"name": "far_behind", "up": [120, 300]}], "min_change": 5, "name": "repl.member_lag", "pack": "replication", "pairs_with": ["repl.majority_lag", "flow.lagged", "net.retransmit"], "reading": "the highest valid sample of each minute", "signal": {"behind": true, "mode": "gauge", "num": ["replSetGetStatus/members/{i}/optimeDate"], "scale": 0.001, "unit": "s"}, "title": "Member replication lag", "unit": "s", "until": "6.0", "version_text": "before 6.0", "view": "max"}</t>
+          <t>{"bands": "none — read for its shape only", "doc": "Rate of documents reported deleted by the TTL monitor; collection identity, expiry backlog and latency impact are not inferred.", "formula": "ΔserverStatus/metrics/ttl/deletedDocuments per second, in docs/s, at each available sample", "min_change": 50, "name": "ttl.deletes", "pack": "workload", "pairs_with": ["cache.dirty", "disk.write_await", "repl.member_lag"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/metrics/ttl/deletedDocuments"], "scale": 1, "unit": "docs/s"}, "title": "Documents deleted by TTL", "unit": "docs/s", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10680,17 +10862,17 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>repl.member_lag</t>
+          <t>cursors.open</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>6.0 and later</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "One result per entry of this node's replica-set status, numbered by position in that list; a position can name a different member after a reconfig. Lag is measured against the newest applied time among members, not against the primary, and a member that stopped reporting keeps its last time.", "bands": "current ≤2 (fading to 5) · behind 5–20 (edges 2, 30) · lagging 30–120 (edges 20, 300) · far_behind ≥300 (from 120)", "doc": "Difference between each member's reported applied-write timestamp and the newest such timestamp in this node's replica-set status, scaled to seconds. Members without a timestamp have no result. Minute summaries select the highest valid sample.", "elevated": 30, "formula": "newest of every replSetGetStatus/members/{i}/lastAppliedWallTime − this one × 0.001, in s, at each available sample", "levels": [{"down": [2, 5], "name": "current"}, {"band": [2, 5, 20, 30], "name": "behind"}, {"band": [20, 30, 120, 300], "name": "lagging"}, {"name": "far_behind", "up": [120, 300]}], "min_change": 5, "name": "repl.member_lag", "pack": "replication", "pairs_with": ["repl.majority_lag", "flow.lagged", "net.retransmit"], "reading": "the highest valid sample of each minute", "signal": {"behind": true, "mode": "gauge", "num": ["replSetGetStatus/members/{i}/lastAppliedWallTime"], "scale": 0.001, "unit": "s"}, "since": "6.0", "title": "Member replication lag", "unit": "s", "version_text": "6.0 and later", "view": "max"}</t>
+          <t>{"bands": "none — read for its shape only", "doc": "Count reported for currently open cursors.", "formula": "serverStatus/metrics/cursor/open/total, in cursors, at each available sample", "min_change": 50, "name": "cursors.open", "pack": "workload", "pairs_with": ["memory.heap_outside_cache", "connections.current"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/metrics/cursor/open/total"], "scale": 1, "unit": "cursors"}, "title": "Open cursors", "unit": "cursors", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10700,17 +10882,17 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>repl.majority_lag</t>
+          <t>repl.member_lag</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>4.2 and later</t>
+          <t>before 6.0</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "current ≤1 (fading to 3) · behind 3–10 (edges 1, 20) · lagging ≥20 (from 10)", "doc": "Difference between this node's lastAppliedWallTime and lastCommittedWallTime, scaled to seconds. Minute summaries select the highest valid sample. A sample with either time unset (zero) is left out.", "elevated": 10, "formula": "replSetGetStatus/optimes/lastAppliedWallTime − replSetGetStatus/optimes/lastCommittedWallTime × 0.001, in s, at each available sample", "levels": [{"down": [1, 3], "name": "current"}, {"band": [1, 3, 10, 20], "name": "behind"}, {"name": "lagging", "up": [10, 20]}], "min_change": 2, "name": "repl.majority_lag", "pack": "replication", "pairs_with": ["repl.member_lag", "flow.lagged", "latency.writes"], "reading": "the highest valid sample of each minute", "signal": {"minus": ["replSetGetStatus/optimes/lastCommittedWallTime"], "mode": "gauge", "num": ["replSetGetStatus/optimes/lastAppliedWallTime"], "scale": 0.001, "timestamps": true, "unit": "s"}, "since": "4.2", "title": "Majority commit lag", "unit": "s", "version_text": "4.2 and later", "view": "max"}</t>
+          <t>{"applies": "One result per entry of this node's replica-set status, numbered by position in that list; a position can name a different member after a reconfig. Lag is measured against the newest applied time among members, not against the primary, and a member that stopped reporting keeps its last time.", "bands": "current ≤2 (fading to 5) · behind 5–20 (edges 2, 30) · lagging 30–120 (edges 20, 300) · far_behind ≥300 (from 120)", "doc": "Difference between each member's reported applied-write timestamp and the newest such timestamp in this node's replica-set status, scaled to seconds. Members without a timestamp have no result. optimeDate has one-second resolution. Minute summaries select the highest valid sample.", "elevated": 30, "formula": "newest of every replSetGetStatus/members/{i}/optimeDate − this one × 0.001, in s, at each available sample", "levels": [{"down": [2, 5], "name": "current"}, {"band": [2, 5, 20, 30], "name": "behind"}, {"band": [20, 30, 120, 300], "name": "lagging"}, {"name": "far_behind", "up": [120, 300]}], "min_change": 5, "name": "repl.member_lag", "pack": "replication", "pairs_with": ["repl.majority_lag", "flow.lagged", "net.retransmit"], "reading": "the highest valid sample of each minute", "signal": {"behind": true, "mode": "gauge", "num": ["replSetGetStatus/members/{i}/optimeDate"], "scale": 0.001, "unit": "s"}, "title": "Member replication lag", "unit": "s", "until": "6.0", "version_text": "before 6.0", "view": "max"}</t>
         </is>
       </c>
     </row>
@@ -10720,17 +10902,17 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>flow.lagged</t>
+          <t>repl.member_lag</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>6.0 and later</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>{"applies": "Set only on a primary with flow control enabled; a secondary, or a primary with flow control disabled, reports it unset. The flag records that the majority commit point lagged; time writers spent waiting for flow control is flow.wait.", "bands": "none ≤0 (fading to 1) · some 1–30 (edges 0, 48) · most ≥48 (from 30)", "doc": "Share of valid samples in which flowControl.isLagged was set, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/flowControl/isLagged, in lagged, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 30, 48], "name": "some"}, {"name": "most", "up": [30, 48]}], "min_change": 3, "name": "flow.lagged", "pack": "replication", "pairs_with": ["flow.wait", "repl.majority_lag", "latency.writes"], "reading": "valid-sample share strictly above 0 lagged, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/flowControl/isLagged"], "scale": 1, "unit": "lagged"}, "threshold": 0, "title": "Samples with flowControl.isLagged set", "unit": "s/min", "version_text": "all versions", "view": "time_above"}</t>
+          <t>{"applies": "One result per entry of this node's replica-set status, numbered by position in that list; a position can name a different member after a reconfig. Lag is measured against the newest applied time among members, not against the primary, and a member that stopped reporting keeps its last time.", "bands": "current ≤2 (fading to 5) · behind 5–20 (edges 2, 30) · lagging 30–120 (edges 20, 300) · far_behind ≥300 (from 120)", "doc": "Difference between each member's reported applied-write timestamp and the newest such timestamp in this node's replica-set status, scaled to seconds. Members without a timestamp have no result. Minute summaries select the highest valid sample.", "elevated": 30, "formula": "newest of every replSetGetStatus/members/{i}/lastAppliedWallTime − this one × 0.001, in s, at each available sample", "levels": [{"down": [2, 5], "name": "current"}, {"band": [2, 5, 20, 30], "name": "behind"}, {"band": [20, 30, 120, 300], "name": "lagging"}, {"name": "far_behind", "up": [120, 300]}], "min_change": 5, "name": "repl.member_lag", "pack": "replication", "pairs_with": ["repl.majority_lag", "flow.lagged", "net.retransmit"], "reading": "the highest valid sample of each minute", "signal": {"behind": true, "mode": "gauge", "num": ["replSetGetStatus/members/{i}/lastAppliedWallTime"], "scale": 0.001, "unit": "s"}, "since": "6.0", "title": "Member replication lag", "unit": "s", "version_text": "6.0 and later", "view": "max"}</t>
         </is>
       </c>
     </row>
@@ -10740,17 +10922,17 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>flow.wait</t>
+          <t>repl.majority_lag</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>4.2 and later</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)", "doc": "Milliseconds a second writes spent waiting for flow control tickets on this node, added across every write waiting.", "elevated": 100, "formula": "ΔserverStatus/flowControl/timeAcquiringMicros per second × 0.001, in ms/s, at each available sample", "levels": [{"down": [1, 10], "name": "none"}, {"band": [1, 10, 100, 500], "name": "some"}, {"name": "heavy", "up": [100, 500]}], "min_change": 10, "name": "flow.wait", "pack": "replication", "pairs_with": ["flow.lagged", "latency.writes"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/flowControl/timeAcquiringMicros"], "scale": 0.001, "unit": "ms/s"}, "title": "Time writers waited on flow control", "unit": "ms/s", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "current ≤1 (fading to 3) · behind 3–10 (edges 1, 20) · lagging ≥20 (from 10)", "doc": "Difference between this node's lastAppliedWallTime and lastCommittedWallTime, scaled to seconds. Minute summaries select the highest valid sample. A sample with either time unset (zero) is left out.", "elevated": 10, "formula": "replSetGetStatus/optimes/lastAppliedWallTime − replSetGetStatus/optimes/lastCommittedWallTime × 0.001, in s, at each available sample", "levels": [{"down": [1, 3], "name": "current"}, {"band": [1, 3, 10, 20], "name": "behind"}, {"name": "lagging", "up": [10, 20]}], "min_change": 2, "name": "repl.majority_lag", "pack": "replication", "pairs_with": ["repl.member_lag", "flow.lagged", "latency.writes"], "reading": "the highest valid sample of each minute", "signal": {"minus": ["replSetGetStatus/optimes/lastCommittedWallTime"], "mode": "gauge", "num": ["replSetGetStatus/optimes/lastAppliedWallTime"], "scale": 0.001, "timestamps": true, "unit": "s"}, "since": "4.2", "title": "Majority commit lag", "unit": "s", "version_text": "4.2 and later", "view": "max"}</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10942,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>repl.apply_rate</t>
+          <t>flow.lagged</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -10770,7 +10952,7 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "direction": "down", "doc": "Rate of the node's oplog application operation counter.", "formula": "ΔserverStatus/metrics/repl/apply/ops per second, in ops/s, at each available sample", "min_change": 50, "name": "repl.apply_rate", "pack": "replication", "pairs_with": ["repl.buffer_fill", "repl.member_lag"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/metrics/repl/apply/ops"], "scale": 1, "unit": "ops/s"}, "title": "Oplog entries applied", "unit": "ops/s", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"applies": "Set only on a primary with flow control enabled; a secondary, or a primary with flow control disabled, reports it unset. The flag records that the majority commit point lagged; time writers spent waiting for flow control is flow.wait.", "bands": "none ≤0 (fading to 1) · some 1–30 (edges 0, 48) · most ≥48 (from 30)", "doc": "Share of valid samples in which flowControl.isLagged was set, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/flowControl/isLagged, in lagged, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 30, 48], "name": "some"}, {"name": "most", "up": [30, 48]}], "min_change": 3, "name": "flow.lagged", "pack": "replication", "pairs_with": ["flow.wait", "repl.majority_lag", "latency.writes"], "reading": "valid-sample share strictly above 0 lagged, normalized to 60 s/min; not continuous elapsed time", "signal": {"mode": "gauge", "num": ["serverStatus/flowControl/isLagged"], "scale": 1, "unit": "lagged"}, "threshold": 0, "title": "Samples with flowControl.isLagged set", "unit": "s/min", "version_text": "all versions", "view": "time_above"}</t>
         </is>
       </c>
     </row>
@@ -10780,17 +10962,17 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>repl.buffer_fill</t>
+          <t>flow.wait</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>before 8.0</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "empty ≤5 (fading to 20) · filling 20–60 (edges 5, 85) · full ≥90 (from 70)", "doc": "Reported replication buffer bytes as a share of its reported maximum.", "elevated": 70, "formula": "serverStatus/metrics/repl/buffer/sizeBytes ÷ serverStatus/metrics/repl/buffer/maxSizeBytes × 100, in %, at each available sample", "levels": [{"down": [5, 20], "name": "empty"}, {"band": [5, 20, 60, 85], "name": "filling"}, {"name": "full", "up": [70, 90]}], "min_change": 10, "name": "repl.buffer_fill", "pack": "replication", "pairs_with": ["repl.buffer_full", "repl.apply_rate", "repl.member_lag"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/metrics/repl/buffer/maxSizeBytes"], "mode": "gauge", "num": ["serverStatus/metrics/repl/buffer/sizeBytes"], "scale": 100, "unit": "%"}, "title": "Apply buffer fill", "unit": "%", "until": "8.0", "version_text": "before 8.0", "view": "mean"}</t>
+          <t>{"bands": "none ≤1 (fading to 10) · some 10–100 (edges 1, 500) · heavy ≥500 (from 100)", "doc": "Milliseconds a second writes spent waiting for flow control tickets on this node, added across every write waiting.", "elevated": 100, "formula": "ΔserverStatus/flowControl/timeAcquiringMicros per second × 0.001, in ms/s, at each available sample", "levels": [{"down": [1, 10], "name": "none"}, {"band": [1, 10, 100, 500], "name": "some"}, {"name": "heavy", "up": [100, 500]}], "min_change": 10, "name": "flow.wait", "pack": "replication", "pairs_with": ["flow.lagged", "latency.writes"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/flowControl/timeAcquiringMicros"], "scale": 0.001, "unit": "ms/s"}, "title": "Time writers waited on flow control", "unit": "ms/s", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10800,17 +10982,17 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>repl.buffer_fill</t>
+          <t>repl.apply_rate</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>8.0 and later</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "empty ≤5 (fading to 20) · filling 20–60 (edges 5, 85) · full ≥90 (from 70)", "doc": "Reported replication buffer bytes as a share of its reported maximum.", "elevated": 70, "formula": "serverStatus/metrics/repl/buffer/apply/sizeBytes ÷ serverStatus/metrics/repl/buffer/apply/maxSizeBytes × 100, in %, at each available sample", "levels": [{"down": [5, 20], "name": "empty"}, {"band": [5, 20, 60, 85], "name": "filling"}, {"name": "full", "up": [70, 90]}], "min_change": 10, "name": "repl.buffer_fill", "pack": "replication", "pairs_with": ["repl.buffer_full", "repl.apply_rate", "repl.member_lag"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/metrics/repl/buffer/apply/maxSizeBytes"], "mode": "gauge", "num": ["serverStatus/metrics/repl/buffer/apply/sizeBytes"], "scale": 100, "unit": "%"}, "since": "8.0", "title": "Apply buffer fill", "unit": "%", "version_text": "8.0 and later", "view": "mean"}</t>
+          <t>{"bands": "none — read for its shape only", "direction": "down", "doc": "Rate of the node's oplog application operation counter.", "formula": "ΔserverStatus/metrics/repl/apply/ops per second, in ops/s, at each available sample", "min_change": 50, "name": "repl.apply_rate", "pack": "replication", "pairs_with": ["repl.buffer_fill", "repl.member_lag"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/metrics/repl/apply/ops"], "scale": 1, "unit": "ops/s"}, "title": "Oplog entries applied", "unit": "ops/s", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10820,7 +11002,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>repl.buffer_full</t>
+          <t>repl.buffer_fill</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -10830,7 +11012,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which replication buffer bytes were strictly above 90 % of the reported maximum, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/metrics/repl/buffer/sizeBytes ÷ serverStatus/metrics/repl/buffer/maxSizeBytes × 100, in %, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "repl.buffer_full", "pack": "replication", "pairs_with": ["repl.buffer_fill", "repl.apply_rate"], "reading": "valid-sample share strictly above 90 %, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/metrics/repl/buffer/maxSizeBytes"], "mode": "gauge", "num": ["serverStatus/metrics/repl/buffer/sizeBytes"], "scale": 100, "unit": "%"}, "threshold": 90, "title": "Apply-buffer samples above 90%", "unit": "s/min", "until": "8.0", "version_text": "before 8.0", "view": "time_above"}</t>
+          <t>{"bands": "empty ≤5 (fading to 20) · filling 20–60 (edges 5, 85) · full ≥90 (from 70)", "doc": "Reported replication buffer bytes as a share of its reported maximum.", "elevated": 70, "formula": "serverStatus/metrics/repl/buffer/sizeBytes ÷ serverStatus/metrics/repl/buffer/maxSizeBytes × 100, in %, at each available sample", "levels": [{"down": [5, 20], "name": "empty"}, {"band": [5, 20, 60, 85], "name": "filling"}, {"name": "full", "up": [70, 90]}], "min_change": 10, "name": "repl.buffer_fill", "pack": "replication", "pairs_with": ["repl.buffer_full", "repl.apply_rate", "repl.member_lag"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/metrics/repl/buffer/maxSizeBytes"], "mode": "gauge", "num": ["serverStatus/metrics/repl/buffer/sizeBytes"], "scale": 100, "unit": "%"}, "title": "Apply buffer fill", "unit": "%", "until": "8.0", "version_text": "before 8.0", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10840,7 +11022,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>repl.buffer_full</t>
+          <t>repl.buffer_fill</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -10850,7 +11032,7 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which replication buffer bytes were strictly above 90 % of the reported maximum, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/metrics/repl/buffer/apply/sizeBytes ÷ serverStatus/metrics/repl/buffer/apply/maxSizeBytes × 100, in %, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "repl.buffer_full", "pack": "replication", "pairs_with": ["repl.buffer_fill", "repl.apply_rate"], "reading": "valid-sample share strictly above 90 %, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/metrics/repl/buffer/apply/maxSizeBytes"], "mode": "gauge", "num": ["serverStatus/metrics/repl/buffer/apply/sizeBytes"], "scale": 100, "unit": "%"}, "since": "8.0", "threshold": 90, "title": "Apply-buffer samples above 90%", "unit": "s/min", "version_text": "8.0 and later", "view": "time_above"}</t>
+          <t>{"bands": "empty ≤5 (fading to 20) · filling 20–60 (edges 5, 85) · full ≥90 (from 70)", "doc": "Reported replication buffer bytes as a share of its reported maximum.", "elevated": 70, "formula": "serverStatus/metrics/repl/buffer/apply/sizeBytes ÷ serverStatus/metrics/repl/buffer/apply/maxSizeBytes × 100, in %, at each available sample", "levels": [{"down": [5, 20], "name": "empty"}, {"band": [5, 20, 60, 85], "name": "filling"}, {"name": "full", "up": [70, 90]}], "min_change": 10, "name": "repl.buffer_fill", "pack": "replication", "pairs_with": ["repl.buffer_full", "repl.apply_rate", "repl.member_lag"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/metrics/repl/buffer/apply/maxSizeBytes"], "mode": "gauge", "num": ["serverStatus/metrics/repl/buffer/apply/sizeBytes"], "scale": 100, "unit": "%"}, "since": "8.0", "title": "Apply buffer fill", "unit": "%", "version_text": "8.0 and later", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10860,17 +11042,17 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>connections.used</t>
+          <t>repl.buffer_full</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>before 8.0</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "low ≤25 (fading to 50) · moderate 50–70 (edges 25, 85) · high 85–90 (edges 70, 95) · near_limit ≥95 (from 90)", "doc": "Reported current connections divided by current plus available connections.", "elevated": 85, "formula": "serverStatus/connections/current ÷ (serverStatus/connections/current + serverStatus/connections/available) × 100, in %, at each available sample", "levels": [{"down": [25, 50], "name": "low"}, {"band": [25, 50, 70, 85], "name": "moderate"}, {"band": [70, 85, 90, 95], "name": "high"}, {"name": "near_limit", "up": [90, 95]}], "min_change": 10, "name": "connections.used", "pack": "connections", "pairs_with": ["connections.scarce", "connections.created", "connections.rejected"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/connections/current", "serverStatus/connections/available"], "mode": "gauge", "num": ["serverStatus/connections/current"], "scale": 100, "unit": "%"}, "title": "Current connections as a share of current plus available", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which replication buffer bytes were strictly above 90 % of the reported maximum, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/metrics/repl/buffer/sizeBytes ÷ serverStatus/metrics/repl/buffer/maxSizeBytes × 100, in %, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "repl.buffer_full", "pack": "replication", "pairs_with": ["repl.buffer_fill", "repl.apply_rate"], "reading": "valid-sample share strictly above 90 %, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/metrics/repl/buffer/maxSizeBytes"], "mode": "gauge", "num": ["serverStatus/metrics/repl/buffer/sizeBytes"], "scale": 100, "unit": "%"}, "threshold": 90, "title": "Apply-buffer samples above 90%", "unit": "s/min", "until": "8.0", "version_text": "before 8.0", "view": "time_above"}</t>
         </is>
       </c>
     </row>
@@ -10880,17 +11062,17 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>connections.scarce</t>
+          <t>repl.buffer_full</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>8.0 and later</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which available connections were strictly below 10 % of current plus available, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/connections/available ÷ (serverStatus/connections/current + serverStatus/connections/available) × 100, in % available, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "connections.scarce", "open_at": "brief", "pack": "connections", "pairs_with": ["connections.used", "connections.created", "connections.rejected"], "reading": "valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/connections/current", "serverStatus/connections/available"], "mode": "gauge", "num": ["serverStatus/connections/available"], "scale": 100, "unit": "% available"}, "threshold": 10, "title": "Samples with under 10% of connections left", "unit": "s/min", "version_text": "all versions", "view": "time_below"}</t>
+          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which replication buffer bytes were strictly above 90 % of the reported maximum, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/metrics/repl/buffer/apply/sizeBytes ÷ serverStatus/metrics/repl/buffer/apply/maxSizeBytes × 100, in %, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "repl.buffer_full", "pack": "replication", "pairs_with": ["repl.buffer_fill", "repl.apply_rate"], "reading": "valid-sample share strictly above 90 %, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/metrics/repl/buffer/apply/maxSizeBytes"], "mode": "gauge", "num": ["serverStatus/metrics/repl/buffer/apply/sizeBytes"], "scale": 100, "unit": "%"}, "since": "8.0", "threshold": 90, "title": "Apply-buffer samples above 90%", "unit": "s/min", "version_text": "8.0 and later", "view": "time_above"}</t>
         </is>
       </c>
     </row>
@@ -10900,7 +11082,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>connections.created</t>
+          <t>connections.used</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -10910,7 +11092,7 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "quiet ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · high ≥20 (from 10)", "doc": "Rate of the server's totalCreated connection counter.", "elevated": 20, "formula": "ΔserverStatus/connections/totalCreated per second, in conn/s, at each available sample", "levels": [{"down": [1, 3], "name": "quiet"}, {"band": [1, 3, 10, 20], "name": "normal"}, {"name": "high", "up": [10, 20]}], "min_change": 5, "name": "connections.created", "pack": "connections", "pairs_with": ["connections.current", "cpu.kernel_share", "net.resets"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/connections/totalCreated"], "scale": 1, "unit": "conn/s"}, "title": "New connections", "unit": "conn/s", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "low ≤25 (fading to 50) · moderate 50–70 (edges 25, 85) · high 85–90 (edges 70, 95) · near_limit ≥95 (from 90)", "doc": "Reported current connections divided by current plus available connections.", "elevated": 85, "formula": "serverStatus/connections/current ÷ (serverStatus/connections/current + serverStatus/connections/available) × 100, in %, at each available sample", "levels": [{"down": [25, 50], "name": "low"}, {"band": [25, 50, 70, 85], "name": "moderate"}, {"band": [70, 85, 90, 95], "name": "high"}, {"name": "near_limit", "up": [90, 95]}], "min_change": 10, "name": "connections.used", "pack": "connections", "pairs_with": ["connections.scarce", "connections.created", "connections.rejected"], "reading": "each minute's ratio of sums", "signal": {"den": ["serverStatus/connections/current", "serverStatus/connections/available"], "mode": "gauge", "num": ["serverStatus/connections/current"], "scale": 100, "unit": "%"}, "title": "Current connections as a share of current plus available", "unit": "%", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10920,17 +11102,17 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>connections.non_active</t>
+          <t>connections.scarce</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>4.4 and later</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "few ≤300 (fading to 800) · many 800–1500 (edges 300, 2500) · very_high ≥3000 (from 1500)", "doc": "Derived connection count: current plus awaitingTopologyChanges minus active; it is not evidence of unused client pools or a connection leak.", "elevated": 2000, "formula": "(serverStatus/connections/current + serverStatus/connections/awaitingTopologyChanges) − serverStatus/connections/active, in conns, at each available sample", "levels": [{"down": [300, 800], "name": "few"}, {"band": [300, 800, 1500, 2500], "name": "many"}, {"name": "very_high", "up": [1500, 3000]}], "min_change": 100, "name": "connections.non_active", "pack": "connections", "pairs_with": ["connections.current", "connections.created", "connections.working_share", "memory.heap_outside_cache"], "reading": "each minute's mean", "signal": {"minus": ["serverStatus/connections/active"], "mode": "gauge", "num": ["serverStatus/connections/current", "serverStatus/connections/awaitingTopologyChanges"], "scale": 1, "unit": "conns"}, "since": "4.4", "title": "Derived non-active connection count", "unit": "conns", "version_text": "4.4 and later", "view": "mean"}</t>
+          <t>{"bands": "none ≤0 (fading to 1) · brief 1–10 (edges 0, 20) · frequent 20–40 (edges 10, 50) · constant ≥55 (from 40)", "doc": "Share of valid samples in which available connections were strictly below 10 % of current plus available, normalized to a 60-second minute.", "elevated": 1, "formula": "serverStatus/connections/available ÷ (serverStatus/connections/current + serverStatus/connections/available) × 100, in % available, at each available sample", "levels": [{"down": [0, 1], "name": "none"}, {"band": [0, 1, 10, 20], "name": "brief"}, {"band": [10, 20, 40, 50], "name": "frequent"}, {"name": "constant", "up": [40, 55]}], "min_change": 3, "name": "connections.scarce", "open_at": "brief", "pack": "connections", "pairs_with": ["connections.used", "connections.created", "connections.rejected"], "reading": "valid-sample share strictly below 10 % available, normalized to 60 s/min; not continuous elapsed time", "signal": {"den": ["serverStatus/connections/current", "serverStatus/connections/available"], "mode": "gauge", "num": ["serverStatus/connections/available"], "scale": 100, "unit": "% available"}, "threshold": 10, "title": "Samples with under 10% of connections left", "unit": "s/min", "version_text": "all versions", "view": "time_below"}</t>
         </is>
       </c>
     </row>
@@ -10940,17 +11122,17 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>connections.working_share</t>
+          <t>connections.created</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>4.4 and later</t>
+          <t>all versions</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "calm ≤10 (fading to 25) · busy 25–40 (edges 10, 60) · high ≥60 (from 40)", "doc": "Derived active-connection share: active minus awaitingTopologyChanges divided by current connections. Minute summaries select the highest valid sample.", "elevated": 40, "formula": "serverStatus/connections/active − serverStatus/connections/awaitingTopologyChanges ÷ serverStatus/connections/current × 100, in %, at each available sample; minutes where the divisor sums to under 3000 are left out", "levels": [{"down": [10, 25], "name": "calm"}, {"band": [10, 25, 40, 60], "name": "busy"}, {"name": "high", "up": [40, 60]}], "min_change": 10, "name": "connections.working_share", "pack": "connections", "pairs_with": ["tickets.read.empty", "tickets.write.empty", "queue.readers", "queue.writers", "connections.created"], "reading": "the highest valid sample of each minute", "signal": {"den": ["serverStatus/connections/current"], "min_den": 3000, "minus": ["serverStatus/connections/awaitingTopologyChanges"], "mode": "gauge", "num": ["serverStatus/connections/active"], "scale": 100, "unit": "%"}, "since": "4.4", "title": "Derived active-connection share", "unit": "%", "version_text": "4.4 and later", "view": "max"}</t>
+          <t>{"bands": "quiet ≤1 (fading to 3) · normal 3–10 (edges 1, 20) · high ≥20 (from 10)", "doc": "Rate of the server's totalCreated connection counter.", "elevated": 20, "formula": "ΔserverStatus/connections/totalCreated per second, in conn/s, at each available sample", "levels": [{"down": [1, 3], "name": "quiet"}, {"band": [1, 3, 10, 20], "name": "normal"}, {"name": "high", "up": [10, 20]}], "min_change": 5, "name": "connections.created", "pack": "connections", "pairs_with": ["connections.current", "cpu.kernel_share", "net.resets"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/connections/totalCreated"], "scale": 1, "unit": "conn/s"}, "title": "New connections", "unit": "conn/s", "version_text": "all versions", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10960,17 +11142,17 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>connections.current</t>
+          <t>connections.non_active</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>all versions</t>
+          <t>4.4 and later</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>{"bands": "none — read for its shape only", "doc": "Count reported for currently open server connections.", "formula": "serverStatus/connections/current, in conns, at each available sample", "min_change": 50, "name": "connections.current", "pack": "connections", "pairs_with": ["connections.non_active", "connections.created", "memory.heap_outside_cache"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/connections/current"], "scale": 1, "unit": "conns"}, "title": "Open connections", "unit": "conns", "version_text": "all versions", "view": "mean"}</t>
+          <t>{"bands": "few ≤300 (fading to 800) · many 800–1500 (edges 300, 2500) · very_high ≥3000 (from 1500)", "doc": "Derived connection count: current plus awaitingTopologyChanges minus active; it is not evidence of unused client pools or a connection leak.", "elevated": 2000, "formula": "(serverStatus/connections/current + serverStatus/connections/awaitingTopologyChanges) − serverStatus/connections/active, in conns, at each available sample", "levels": [{"down": [300, 800], "name": "few"}, {"band": [300, 800, 1500, 2500], "name": "many"}, {"name": "very_high", "up": [1500, 3000]}], "min_change": 100, "name": "connections.non_active", "pack": "connections", "pairs_with": ["connections.current", "connections.created", "connections.working_share", "memory.heap_outside_cache"], "reading": "each minute's mean", "signal": {"minus": ["serverStatus/connections/active"], "mode": "gauge", "num": ["serverStatus/connections/current", "serverStatus/connections/awaitingTopologyChanges"], "scale": 1, "unit": "conns"}, "since": "4.4", "title": "Derived non-active connection count", "unit": "conns", "version_text": "4.4 and later", "view": "mean"}</t>
         </is>
       </c>
     </row>
@@ -10980,22 +11162,62 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
+          <t>connections.working_share</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>4.4 and later</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "calm ≤10 (fading to 25) · busy 25–40 (edges 10, 60) · high ≥60 (from 40)", "doc": "Derived active-connection share: active minus awaitingTopologyChanges divided by current connections. Minute summaries select the highest valid sample.", "elevated": 40, "formula": "serverStatus/connections/active − serverStatus/connections/awaitingTopologyChanges ÷ serverStatus/connections/current × 100, in %, at each available sample; minutes where the divisor sums to under 3000 are left out", "levels": [{"down": [10, 25], "name": "calm"}, {"band": [10, 25, 40, 60], "name": "busy"}, {"name": "high", "up": [40, 60]}], "min_change": 10, "name": "connections.working_share", "pack": "connections", "pairs_with": ["tickets.read.empty", "tickets.write.empty", "queue.readers", "queue.writers", "connections.created"], "reading": "the highest valid sample of each minute", "signal": {"den": ["serverStatus/connections/current"], "min_den": 3000, "minus": ["serverStatus/connections/awaitingTopologyChanges"], "mode": "gauge", "num": ["serverStatus/connections/active"], "scale": 100, "unit": "%"}, "since": "4.4", "title": "Derived active-connection share", "unit": "%", "version_text": "4.4 and later", "view": "max"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>connections.current</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>all versions</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>{"bands": "none — read for its shape only", "doc": "Count reported for currently open server connections.", "formula": "serverStatus/connections/current, in conns, at each available sample", "min_change": 50, "name": "connections.current", "pack": "connections", "pairs_with": ["connections.non_active", "connections.created", "memory.heap_outside_cache"], "reading": "each minute's mean", "signal": {"mode": "gauge", "num": ["serverStatus/connections/current"], "scale": 1, "unit": "conns"}, "title": "Open connections", "unit": "conns", "version_text": "all versions", "view": "mean"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
           <t>connections.rejected</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>6.3 and later</t>
         </is>
       </c>
-      <c r="D93" s="4" t="inlineStr">
+      <c r="D95" s="4" t="inlineStr">
         <is>
           <t>{"bands": "none ≤0.001 (fading to 0.01) · some 0.01–1 (edges 0.001, 5) · many ≥5 (from 1)", "doc": "Rate of the server's rejected connection counter; client impact and rejection cause are not inferred.", "elevated": 0.01, "formula": "ΔserverStatus/connections/rejected per second, in /s, at each available sample", "levels": [{"down": [0.001, 0.01], "name": "none"}, {"band": [0.001, 0.01, 1, 5], "name": "some"}, {"name": "many", "up": [1, 5]}], "min_change": 0.01, "name": "connections.rejected", "pack": "connections", "pairs_with": ["connections.scarce", "connections.used"], "reading": "each minute's mean", "signal": {"mode": "rate", "num": ["serverStatus/connections/rejected"], "scale": 1, "unit": "/s"}, "since": "6.3", "title": "Connections refused", "unit": "/s", "version_text": "6.3 and later", "view": "mean"}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D93"/>
+  <autoFilter ref="A1:D95"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>